--- a/docs/Vinland_Game_Development_Plan.xlsx
+++ b/docs/Vinland_Game_Development_Plan.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1856" uniqueCount="1135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="1166">
   <si>
     <t xml:space="preserve">VINLAND</t>
   </si>
@@ -841,6 +841,99 @@
     <t xml:space="preserve">Sickness: chance multiplier on days with no drink</t>
   </si>
   <si>
+    <t xml:space="preserve">Hooks carried</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hand line: a snapped or cut line costs a hook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMP TUNING (FEEDS THE GAME BUILD THROUGH data/knobs.json)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work to raise a booth (builder-days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build: a turf-and-timber booth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">People sheltered per booth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shelter: the unsheltered sicken faster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your seated joint counts as (builder-days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build: the joint mini-game is the skilled work that holds the frame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shore fishing per worker-day (person-days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fish: crew working without you</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forage per worker-day (person-days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forage: placeholder until the forage mini-game (F13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timber felled per worker-day (units)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felled, trimmed and hauled to the slip; 4 units open the return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hay cut per worker-day (units)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hay, from 1 August</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First hay day (day of year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hay: 1 August</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milk per fed cow per day (person-days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Livestock: summer grazing feeds them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsheltered sickness multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shelter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tending shortens sickness by (days per tender-day)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tend the sick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slice ends (day of year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vertical slice runs to 1 September</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Booth plots at the camp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build queue: booths first, then the longhouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work to raise the longhouse (builder-days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build queue: the hall that gets the camp through winter (F17)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pillars, fantasy, clocks, and the win</t>
   </si>
   <si>
@@ -1954,7 +2047,7 @@
     <t xml:space="preserve">Hand-line fishing</t>
   </si>
   <si>
-    <t xml:space="preserve">A bite reads through the trigger; a cut line keeps the hook.</t>
+    <t xml:space="preserve">A bite reads through the trigger; a cut line keeps the hook.  [Playable: depth by stick, nibbles, two-beat bite, set on the ease, haul under line strain, snap, cut; hooks are a stock. Bots: skilled watch ~19.5 person-days.]</t>
   </si>
   <si>
     <t xml:space="preserve">F06</t>
@@ -1963,13 +2056,13 @@
     <t xml:space="preserve">One camp day loop</t>
   </si>
   <si>
-    <t xml:space="preserve">Morning job queue, one verb, evening tally that changes the hold.</t>
+    <t xml:space="preserve">Morning job queue, one verb, evening tally that changes the hold.  [Playable: morning job board, you play the joint or the hand line, evening tally, a week at a time, G1 checklist at autumn.]</t>
   </si>
   <si>
     <t xml:space="preserve">Joint construction</t>
   </si>
   <si>
-    <t xml:space="preserve">Grain reported on RT; a split log costs the day.</t>
+    <t xml:space="preserve">Grain reported on RT; a split log costs the day.  [Playable: brace, set the peg, drive by trigger depth; rain lowers the grain cap. Bots: steady 100%, full force 0%, timid 0%, no brace 22%.]</t>
   </si>
   <si>
     <t xml:space="preserve">F08</t>
@@ -2089,7 +2182,7 @@
     <t xml:space="preserve">Livestock, milk, hay</t>
   </si>
   <si>
-    <t xml:space="preserve">Hay cut in late summer or the byre is a tomb.</t>
+    <t xml:space="preserve">Hay cut in late summer or the byre is a tomb.  [Milk from fed cows; hay job opens 1 August. Byre and winter feeding still to come.]</t>
   </si>
   <si>
     <t xml:space="preserve">F17</t>
@@ -2098,7 +2191,7 @@
     <t xml:space="preserve">Byre, longhouse, booths</t>
   </si>
   <si>
-    <t xml:space="preserve">Three buildings raised with the joint and lift verbs; no tech tree.</t>
+    <t xml:space="preserve">Three buildings raised with the joint and lift verbs; no tech tree.  [Booth plots and the longhouse as a build queue with visible stages (placeholder drawings).]</t>
   </si>
   <si>
     <t xml:space="preserve">Lift and slipway</t>
@@ -4695,11 +4788,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="11242108"/>
-        <c:axId val="77860988"/>
+        <c:axId val="73134574"/>
+        <c:axId val="63984756"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="11242108"/>
+        <c:axId val="73134574"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4731,7 +4824,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77860988"/>
+        <c:crossAx val="63984756"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4739,7 +4832,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="77860988"/>
+        <c:axId val="63984756"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4815,7 +4908,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11242108"/>
+        <c:crossAx val="73134574"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4854,9 +4947,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>744840</xdr:colOff>
+      <xdr:colOff>744120</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>61200</xdr:rowOff>
+      <xdr:rowOff>60480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4865,7 +4958,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="6562800"/>
-        <a:ext cx="5396760" cy="2156760"/>
+        <a:ext cx="5396040" cy="2156040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5947,7 +6040,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>839</v>
+        <v>870</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5959,10 +6052,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>840</v>
+        <v>871</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>841</v>
+        <v>872</v>
       </c>
       <c r="C4" s="57" t="s">
         <v>96</v>
@@ -5983,7 +6076,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="57" t="s">
-        <v>842</v>
+        <v>873</v>
       </c>
       <c r="J4" s="57" t="s">
         <v>7</v>
@@ -5991,7 +6084,7 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="B5" s="89" t="n">
         <f aca="false">Assumptions!B26</f>
@@ -6026,7 +6119,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="B6" s="89" t="n">
         <f aca="false">Assumptions!B27</f>
@@ -6061,7 +6154,7 @@
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="B7" s="89" t="n">
         <f aca="false">Assumptions!B28</f>
@@ -6096,7 +6189,7 @@
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>700</v>
+        <v>731</v>
       </c>
       <c r="B8" s="89" t="n">
         <f aca="false">Assumptions!B29</f>
@@ -6131,7 +6224,7 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>755</v>
+        <v>786</v>
       </c>
       <c r="B9" s="89" t="n">
         <f aca="false">Assumptions!B30</f>
@@ -6201,10 +6294,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="71" t="s">
-        <v>843</v>
+        <v>874</v>
       </c>
       <c r="B11" s="71" t="s">
-        <v>844</v>
+        <v>875</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -6241,10 +6334,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="71" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>846</v>
+        <v>877</v>
       </c>
       <c r="C12" s="62" t="n">
         <f aca="false">IF(Assumptions!B16=0,0,C11/Assumptions!B16)</f>
@@ -6277,7 +6370,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>847</v>
+        <v>878</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -6292,28 +6385,28 @@
         <v>5</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>848</v>
+        <v>879</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>700</v>
+        <v>731</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>755</v>
+        <v>786</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>100</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>842</v>
+        <v>873</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>7</v>
@@ -6573,7 +6666,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>849</v>
+        <v>880</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -6590,7 +6683,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="50" t="s">
-        <v>850</v>
+        <v>881</v>
       </c>
       <c r="B22" s="50"/>
       <c r="C22" s="50"/>
@@ -6610,7 +6703,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="50" t="s">
-        <v>851</v>
+        <v>882</v>
       </c>
       <c r="B23" s="50"/>
       <c r="C23" s="50"/>
@@ -6627,7 +6720,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="50" t="s">
-        <v>852</v>
+        <v>883</v>
       </c>
       <c r="B24" s="50"/>
       <c r="C24" s="50"/>
@@ -6695,7 +6788,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="50" t="s">
-        <v>853</v>
+        <v>884</v>
       </c>
       <c r="B28" s="50"/>
       <c r="C28" s="50"/>
@@ -6712,7 +6805,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>854</v>
+        <v>885</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
@@ -6749,7 +6842,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="66" t="s">
-        <v>855</v>
+        <v>886</v>
       </c>
       <c r="B31" s="66"/>
       <c r="C31" s="66"/>
@@ -6767,12 +6860,12 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="71" t="s">
-        <v>856</v>
+        <v>887</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="95" t="s">
-        <v>857</v>
+        <v>888</v>
       </c>
       <c r="B34" s="95"/>
       <c r="C34" s="95"/>
@@ -6786,7 +6879,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>849</v>
+        <v>880</v>
       </c>
       <c r="B35" s="90" t="n">
         <f aca="false">J21</f>
@@ -6795,7 +6888,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>858</v>
+        <v>889</v>
       </c>
       <c r="B36" s="90" t="n">
         <f aca="false">J31</f>
@@ -6804,7 +6897,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>859</v>
+        <v>890</v>
       </c>
       <c r="B37" s="90" t="n">
         <f aca="false">SUM(J22:J28)*(1+I30)</f>
@@ -6856,7 +6949,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>860</v>
+        <v>891</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -6865,7 +6958,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>861</v>
+        <v>892</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -6880,7 +6973,7 @@
         <v>42</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>432</v>
+        <v>463</v>
       </c>
       <c r="D5" s="29"/>
       <c r="E5" s="29"/>
@@ -6894,28 +6987,28 @@
         <v>19.99</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>862</v>
+        <v>893</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>863</v>
+        <v>894</v>
       </c>
       <c r="B7" s="97" t="n">
         <f aca="false">B6*Assumptions!B70</f>
         <v>15.992</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>864</v>
+        <v>895</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>865</v>
+        <v>896</v>
       </c>
       <c r="B8" s="97" t="n">
         <f aca="false">B7*(1-Assumptions!B71)</f>
@@ -6927,35 +7020,35 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>866</v>
+        <v>897</v>
       </c>
       <c r="B9" s="74" t="n">
         <f aca="false">Assumptions!B72*(1-Assumptions!B74)+Assumptions!B73*Assumptions!B74</f>
         <v>0.29</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>867</v>
+        <v>898</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>868</v>
+        <v>899</v>
       </c>
       <c r="B10" s="98" t="n">
         <f aca="false">B8*(1-B9)</f>
         <v>10.4459744</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>869</v>
+        <v>900</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>870</v>
+        <v>901</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -6970,7 +7063,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>432</v>
+        <v>463</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="29"/>
@@ -6984,70 +7077,70 @@
         <v>460504.8</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>871</v>
+        <v>902</v>
       </c>
       <c r="D14" s="33"/>
       <c r="E14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="66" t="s">
-        <v>872</v>
+        <v>903</v>
       </c>
       <c r="B15" s="99" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B14/B10,0))</f>
         <v>44085</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>873</v>
+        <v>904</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>874</v>
+        <v>905</v>
       </c>
       <c r="B16" s="89" t="n">
         <f aca="false">TeamBudget!B37</f>
         <v>98632.8</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>875</v>
+        <v>906</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="66" t="s">
-        <v>876</v>
+        <v>907</v>
       </c>
       <c r="B17" s="99" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B16/B10,0))</f>
         <v>9443</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>877</v>
+        <v>908</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>878</v>
+        <v>909</v>
       </c>
       <c r="B18" s="90" t="n">
         <f aca="false">B15*B6</f>
         <v>881259.15</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>879</v>
+        <v>910</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>880</v>
+        <v>911</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -7056,19 +7149,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>881</v>
+        <v>912</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>882</v>
+        <v>913</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>883</v>
+        <v>914</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>884</v>
+        <v>915</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>794</v>
+        <v>825</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7183,7 +7276,7 @@
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="54" t="s">
-        <v>885</v>
+        <v>916</v>
       </c>
       <c r="B28" s="54"/>
       <c r="C28" s="54"/>
@@ -7265,7 +7358,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>886</v>
+        <v>917</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7277,195 +7370,195 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>804</v>
+        <v>835</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>887</v>
+        <v>918</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>888</v>
+        <v>919</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>889</v>
+        <v>920</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>588</v>
+        <v>619</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>890</v>
+        <v>921</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>891</v>
+        <v>922</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>808</v>
+        <v>839</v>
       </c>
       <c r="B5" s="86" t="n">
         <f aca="false">Schedule!D5</f>
         <v>46383</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>892</v>
+        <v>923</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>893</v>
+        <v>924</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="F5" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>894</v>
+        <v>925</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>895</v>
+        <v>926</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>812</v>
+        <v>843</v>
       </c>
       <c r="B6" s="86" t="n">
         <f aca="false">Schedule!D6</f>
         <v>46453</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>896</v>
+        <v>927</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>897</v>
+        <v>928</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>898</v>
+        <v>929</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>899</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>816</v>
+        <v>847</v>
       </c>
       <c r="B7" s="86" t="n">
         <f aca="false">Schedule!D7</f>
         <v>46579</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>900</v>
+        <v>931</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>901</v>
+        <v>932</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="F7" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>902</v>
+        <v>933</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>903</v>
+        <v>934</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>820</v>
+        <v>851</v>
       </c>
       <c r="B8" s="86" t="n">
         <f aca="false">Schedule!D8</f>
         <v>46621</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>904</v>
+        <v>935</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>905</v>
+        <v>936</v>
       </c>
       <c r="E8" s="58" t="s">
         <v>100</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>906</v>
+        <v>937</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>907</v>
+        <v>938</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>824</v>
+        <v>855</v>
       </c>
       <c r="B9" s="86" t="n">
         <f aca="false">Schedule!D9</f>
         <v>46663</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>908</v>
+        <v>939</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>909</v>
+        <v>940</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>755</v>
+        <v>786</v>
       </c>
       <c r="F9" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>910</v>
+        <v>941</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>911</v>
+        <v>942</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>827</v>
+        <v>858</v>
       </c>
       <c r="B10" s="86" t="n">
         <f aca="false">Schedule!D10</f>
         <v>46691</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>912</v>
+        <v>943</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>913</v>
+        <v>944</v>
       </c>
       <c r="E10" s="58" t="s">
         <v>100</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>914</v>
+        <v>945</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>915</v>
+        <v>946</v>
       </c>
       <c r="B12" s="54"/>
       <c r="C12" s="54"/>
@@ -7545,7 +7638,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>916</v>
+        <v>947</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7559,31 +7652,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>917</v>
+        <v>948</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>918</v>
+        <v>949</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>919</v>
+        <v>950</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>920</v>
+        <v>951</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>588</v>
+        <v>619</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>921</v>
+        <v>952</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>922</v>
+        <v>953</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>44</v>
@@ -7591,10 +7684,10 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="58" t="s">
-        <v>923</v>
+        <v>954</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>924</v>
+        <v>955</v>
       </c>
       <c r="C5" s="43" t="n">
         <v>3</v>
@@ -7607,27 +7700,27 @@
         <v>15</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>925</v>
+        <v>956</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="H5" s="58" t="s">
-        <v>812</v>
+        <v>843</v>
       </c>
       <c r="I5" s="58" t="s">
-        <v>926</v>
+        <v>957</v>
       </c>
       <c r="J5" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>928</v>
+        <v>959</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>929</v>
+        <v>960</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>3</v>
@@ -7640,27 +7733,27 @@
         <v>12</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>930</v>
+        <v>961</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>812</v>
+        <v>843</v>
       </c>
       <c r="I6" s="58" t="s">
-        <v>931</v>
+        <v>962</v>
       </c>
       <c r="J6" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="58" t="s">
-        <v>932</v>
+        <v>963</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>933</v>
+        <v>964</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>2</v>
@@ -7673,27 +7766,27 @@
         <v>8</v>
       </c>
       <c r="F7" s="58" t="s">
-        <v>934</v>
+        <v>965</v>
       </c>
       <c r="G7" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="H7" s="58" t="s">
-        <v>824</v>
+        <v>855</v>
       </c>
       <c r="I7" s="58" t="s">
-        <v>935</v>
+        <v>966</v>
       </c>
       <c r="J7" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>936</v>
+        <v>967</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>937</v>
+        <v>968</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>4</v>
@@ -7706,27 +7799,27 @@
         <v>12</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>938</v>
+        <v>969</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>816</v>
+        <v>847</v>
       </c>
       <c r="I8" s="58" t="s">
-        <v>939</v>
+        <v>970</v>
       </c>
       <c r="J8" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="58" t="s">
-        <v>940</v>
+        <v>971</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>941</v>
+        <v>972</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>2</v>
@@ -7739,27 +7832,27 @@
         <v>6</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>942</v>
+        <v>973</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>816</v>
+        <v>847</v>
       </c>
       <c r="I9" s="58" t="s">
-        <v>943</v>
+        <v>974</v>
       </c>
       <c r="J9" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>944</v>
+        <v>975</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>945</v>
+        <v>976</v>
       </c>
       <c r="C10" s="43" t="n">
         <v>2</v>
@@ -7772,27 +7865,27 @@
         <v>10</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>946</v>
+        <v>977</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>816</v>
+        <v>847</v>
       </c>
       <c r="I10" s="58" t="s">
-        <v>947</v>
+        <v>978</v>
       </c>
       <c r="J10" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="58" t="s">
-        <v>948</v>
+        <v>979</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>949</v>
+        <v>980</v>
       </c>
       <c r="C11" s="43" t="n">
         <v>3</v>
@@ -7805,27 +7898,27 @@
         <v>12</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>950</v>
+        <v>981</v>
       </c>
       <c r="G11" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H11" s="58" t="s">
-        <v>820</v>
+        <v>851</v>
       </c>
       <c r="I11" s="58" t="s">
-        <v>951</v>
+        <v>982</v>
       </c>
       <c r="J11" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>952</v>
+        <v>983</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>953</v>
+        <v>984</v>
       </c>
       <c r="C12" s="43" t="n">
         <v>2</v>
@@ -7838,27 +7931,27 @@
         <v>8</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>954</v>
+        <v>985</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>808</v>
+        <v>839</v>
       </c>
       <c r="I12" s="58" t="s">
-        <v>955</v>
+        <v>986</v>
       </c>
       <c r="J12" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="58" t="s">
-        <v>956</v>
+        <v>987</v>
       </c>
       <c r="B13" s="58" t="s">
-        <v>957</v>
+        <v>988</v>
       </c>
       <c r="C13" s="43" t="n">
         <v>2</v>
@@ -7871,27 +7964,27 @@
         <v>4</v>
       </c>
       <c r="F13" s="58" t="s">
+        <v>989</v>
+      </c>
+      <c r="G13" s="58" t="s">
+        <v>292</v>
+      </c>
+      <c r="H13" s="58" t="s">
+        <v>839</v>
+      </c>
+      <c r="I13" s="58" t="s">
+        <v>990</v>
+      </c>
+      <c r="J13" s="69" t="s">
         <v>958</v>
-      </c>
-      <c r="G13" s="58" t="s">
-        <v>261</v>
-      </c>
-      <c r="H13" s="58" t="s">
-        <v>808</v>
-      </c>
-      <c r="I13" s="58" t="s">
-        <v>959</v>
-      </c>
-      <c r="J13" s="69" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>960</v>
+        <v>991</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>961</v>
+        <v>992</v>
       </c>
       <c r="C14" s="43" t="n">
         <v>3</v>
@@ -7904,27 +7997,27 @@
         <v>12</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>962</v>
+        <v>993</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>820</v>
+        <v>851</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>963</v>
+        <v>994</v>
       </c>
       <c r="J14" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="58" t="s">
-        <v>964</v>
+        <v>995</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>965</v>
+        <v>996</v>
       </c>
       <c r="C15" s="43" t="n">
         <v>3</v>
@@ -7937,27 +8030,27 @@
         <v>15</v>
       </c>
       <c r="F15" s="58" t="s">
-        <v>966</v>
+        <v>997</v>
       </c>
       <c r="G15" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="H15" s="58" t="s">
-        <v>816</v>
+        <v>847</v>
       </c>
       <c r="I15" s="58" t="s">
-        <v>967</v>
+        <v>998</v>
       </c>
       <c r="J15" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>968</v>
+        <v>999</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>969</v>
+        <v>1000</v>
       </c>
       <c r="C16" s="43" t="n">
         <v>4</v>
@@ -7970,27 +8063,27 @@
         <v>16</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>970</v>
+        <v>1001</v>
       </c>
       <c r="G16" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>812</v>
+        <v>843</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>971</v>
+        <v>1002</v>
       </c>
       <c r="J16" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="58" t="s">
-        <v>972</v>
+        <v>1003</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>973</v>
+        <v>1004</v>
       </c>
       <c r="C17" s="43" t="n">
         <v>3</v>
@@ -8003,27 +8096,27 @@
         <v>12</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>974</v>
+        <v>1005</v>
       </c>
       <c r="G17" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="58" t="s">
-        <v>816</v>
+        <v>847</v>
       </c>
       <c r="I17" s="58" t="s">
-        <v>975</v>
+        <v>1006</v>
       </c>
       <c r="J17" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>976</v>
+        <v>1007</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>977</v>
+        <v>1008</v>
       </c>
       <c r="C18" s="43" t="n">
         <v>2</v>
@@ -8036,27 +8129,27 @@
         <v>6</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>978</v>
+        <v>1009</v>
       </c>
       <c r="G18" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="H18" s="58" t="s">
-        <v>824</v>
+        <v>855</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>979</v>
+        <v>1010</v>
       </c>
       <c r="J18" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="58" t="s">
-        <v>980</v>
+        <v>1011</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>981</v>
+        <v>1012</v>
       </c>
       <c r="C19" s="43" t="n">
         <v>2</v>
@@ -8069,27 +8162,27 @@
         <v>8</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>982</v>
+        <v>1013</v>
       </c>
       <c r="G19" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="H19" s="58" t="s">
-        <v>816</v>
+        <v>847</v>
       </c>
       <c r="I19" s="58" t="s">
-        <v>983</v>
+        <v>1014</v>
       </c>
       <c r="J19" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>984</v>
+        <v>1015</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>985</v>
+        <v>1016</v>
       </c>
       <c r="C20" s="43" t="n">
         <v>3</v>
@@ -8102,19 +8195,19 @@
         <v>15</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>986</v>
+        <v>1017</v>
       </c>
       <c r="G20" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H20" s="58" t="s">
-        <v>812</v>
+        <v>843</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>987</v>
+        <v>1018</v>
       </c>
       <c r="J20" s="69" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
     </row>
   </sheetData>
@@ -8192,7 +8285,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>988</v>
+        <v>1019</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8203,278 +8296,278 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>989</v>
+        <v>1020</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>990</v>
+        <v>1021</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>991</v>
+        <v>1022</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>992</v>
+        <v>1023</v>
       </c>
       <c r="E4" s="57" t="s">
         <v>95</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>588</v>
+        <v>619</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>993</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>994</v>
+        <v>1025</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>995</v>
+        <v>1026</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>996</v>
+        <v>1027</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>997</v>
+        <v>1028</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>998</v>
+        <v>1029</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>999</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>560</v>
+        <v>591</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1000</v>
+        <v>1031</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1001</v>
+        <v>1032</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>1002</v>
+        <v>1033</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>1003</v>
+        <v>1034</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>1004</v>
+        <v>1035</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>1005</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1006</v>
+        <v>1037</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1007</v>
+        <v>1038</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1008</v>
+        <v>1039</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1009</v>
+        <v>1040</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>1010</v>
+        <v>1041</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1005</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>1011</v>
+        <v>1042</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>1012</v>
+        <v>1043</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>1013</v>
+        <v>1044</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>1015</v>
+        <v>1046</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>1016</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>445</v>
+        <v>476</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1017</v>
+        <v>1048</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1018</v>
+        <v>1049</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1019</v>
+        <v>1050</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1020</v>
+        <v>1051</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1021</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1022</v>
+        <v>1053</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>1023</v>
+        <v>1054</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>758</v>
+        <v>789</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>1024</v>
+        <v>1055</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>1025</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>700</v>
+        <v>731</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1026</v>
+        <v>1057</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1027</v>
+        <v>1058</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1028</v>
+        <v>1059</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>1029</v>
+        <v>1060</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>700</v>
+        <v>731</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>1030</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>719</v>
+        <v>750</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1031</v>
+        <v>1062</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>1032</v>
+        <v>1063</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>1033</v>
+        <v>1064</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>1034</v>
+        <v>1065</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>1005</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1035</v>
+        <v>1066</v>
       </c>
       <c r="B13" s="27" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>631</v>
+      </c>
+      <c r="G13" s="27" t="s">
         <v>1036</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>1038</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>600</v>
-      </c>
-      <c r="G13" s="27" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1040</v>
+        <v>1071</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1041</v>
+        <v>1072</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1042</v>
+        <v>1073</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>1043</v>
+        <v>1074</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>1044</v>
+        <v>1075</v>
       </c>
       <c r="F14" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>1045</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1046</v>
+        <v>1077</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1047</v>
+        <v>1078</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1048</v>
+        <v>1079</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1049</v>
+        <v>1080</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>1050</v>
+        <v>1081</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>1051</v>
+        <v>1082</v>
       </c>
     </row>
   </sheetData>
@@ -8516,7 +8609,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1052</v>
+        <v>1083</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8527,24 +8620,24 @@
         <v>110</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1053</v>
+        <v>1084</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>1054</v>
+        <v>1085</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>588</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1055</v>
+        <v>1086</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1056</v>
+        <v>1087</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>808</v>
+        <v>839</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>100</v>
@@ -8552,55 +8645,55 @@
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>1057</v>
+        <v>1088</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1058</v>
+        <v>1089</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1059</v>
+        <v>1090</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1060</v>
+        <v>1091</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1061</v>
+        <v>1092</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>816</v>
+        <v>847</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>1062</v>
+        <v>1093</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>1063</v>
+        <v>1094</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>812</v>
+        <v>843</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1064</v>
+        <v>1095</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1065</v>
+        <v>1096</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>808</v>
+        <v>839</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>100</v>
@@ -8608,27 +8701,27 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>1066</v>
+        <v>1097</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1067</v>
+        <v>1098</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>816</v>
+        <v>847</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>1068</v>
+        <v>1099</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1069</v>
+        <v>1100</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>824</v>
+        <v>855</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>100</v>
@@ -8636,13 +8729,13 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>1070</v>
+        <v>1101</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1071</v>
+        <v>1102</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>827</v>
+        <v>858</v>
       </c>
       <c r="D12" s="58" t="s">
         <v>100</v>
@@ -8650,41 +8743,41 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1072</v>
+        <v>1103</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1073</v>
+        <v>1104</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>827</v>
+        <v>858</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>755</v>
+        <v>786</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1074</v>
+        <v>1105</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1075</v>
+        <v>1106</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1076</v>
+        <v>1107</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1077</v>
+        <v>1108</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1078</v>
+        <v>1109</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>812</v>
+        <v>843</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>100</v>
@@ -8692,14 +8785,14 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>1079</v>
+        <v>1110</v>
       </c>
       <c r="B16" s="58" t="str">
         <f aca="false">"Premium at $"&amp;TEXT(Assumptions!B69,"0.00")&amp;". Launch discount no deeper than the realized-price factor on Assumptions."</f>
         <v>Premium at $19.99. Launch discount no deeper than the realized-price factor on Assumptions.</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>820</v>
+        <v>851</v>
       </c>
       <c r="D16" s="58" t="s">
         <v>100</v>
@@ -8707,13 +8800,13 @@
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>1080</v>
+        <v>1111</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1081</v>
+        <v>1112</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>812</v>
+        <v>843</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>100</v>
@@ -8721,13 +8814,13 @@
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>802</v>
+        <v>833</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>1082</v>
+        <v>1113</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>820</v>
+        <v>851</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>100</v>
@@ -8735,27 +8828,27 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1083</v>
+        <v>1114</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1084</v>
+        <v>1115</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>824</v>
+        <v>855</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>1085</v>
+        <v>1116</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1086</v>
+        <v>1117</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>824</v>
+        <v>855</v>
       </c>
       <c r="D20" s="58" t="s">
         <v>100</v>
@@ -8763,27 +8856,27 @@
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>1087</v>
+        <v>1118</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1088</v>
+        <v>1119</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>824</v>
+        <v>855</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="58" t="s">
-        <v>1089</v>
+        <v>1120</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>1090</v>
+        <v>1121</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>827</v>
+        <v>858</v>
       </c>
       <c r="D22" s="58" t="s">
         <v>100</v>
@@ -8829,7 +8922,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1091</v>
+        <v>1122</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8837,16 +8930,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1092</v>
+        <v>1123</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1093</v>
+        <v>1124</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1094</v>
+        <v>1125</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1095</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8854,13 +8947,13 @@
         <v>46311</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1096</v>
+        <v>1127</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1097</v>
+        <v>1128</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1098</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8868,13 +8961,13 @@
         <v>46311</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1096</v>
+        <v>1127</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1099</v>
+        <v>1130</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>1100</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8882,13 +8975,13 @@
         <v>46311</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1096</v>
+        <v>1127</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1101</v>
+        <v>1132</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1102</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8896,13 +8989,13 @@
         <v>46311</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>862</v>
+        <v>893</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>1103</v>
+        <v>1134</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>1104</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8910,13 +9003,13 @@
         <v>46311</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1105</v>
+        <v>1136</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1106</v>
+        <v>1137</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1107</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8927,10 +9020,10 @@
         <v>53</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>1108</v>
+        <v>1139</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>1109</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8938,13 +9031,13 @@
         <v>46311</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1110</v>
+        <v>1141</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1111</v>
+        <v>1142</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1112</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8952,13 +9045,13 @@
         <v>46311</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>341</v>
+        <v>372</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>1113</v>
+        <v>1144</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>1114</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8966,13 +9059,13 @@
         <v>46311</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1115</v>
+        <v>1146</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1116</v>
+        <v>1147</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1117</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8980,13 +9073,13 @@
         <v>46311</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1118</v>
+        <v>1149</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1119</v>
+        <v>1150</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>1120</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8997,10 +9090,10 @@
         <v>58</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1121</v>
+        <v>1152</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1122</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9008,13 +9101,13 @@
         <v>46311</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>1123</v>
+        <v>1154</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>1124</v>
+        <v>1155</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>1125</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9025,10 +9118,10 @@
         <v>62</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1126</v>
+        <v>1157</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1127</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9036,13 +9129,13 @@
         <v>46311</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>375</v>
+        <v>406</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>1128</v>
+        <v>1159</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>1129</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9050,13 +9143,13 @@
         <v>46311</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>651</v>
+        <v>682</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1130</v>
+        <v>1161</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>1131</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9064,13 +9157,13 @@
         <v>46311</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1132</v>
+        <v>1163</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>1133</v>
+        <v>1164</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>1134</v>
+        <v>1165</v>
       </c>
     </row>
   </sheetData>
@@ -9094,7 +9187,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
@@ -10246,9 +10339,192 @@
         <v>250</v>
       </c>
     </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="B120" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C120" s="41" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="B122" s="24"/>
+      <c r="C122" s="24"/>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="B124" s="43" t="n">
+        <v>16</v>
+      </c>
+      <c r="C124" s="41" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="50" t="s">
+        <v>256</v>
+      </c>
+      <c r="B125" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="C125" s="41" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="B126" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="C126" s="41" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="50" t="s">
+        <v>260</v>
+      </c>
+      <c r="B127" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="C127" s="41" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="B128" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C128" s="41" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="B129" s="51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C129" s="41" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="42" t="s">
+        <v>266</v>
+      </c>
+      <c r="B130" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C130" s="41" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="50" t="s">
+        <v>268</v>
+      </c>
+      <c r="B131" s="43" t="n">
+        <v>213</v>
+      </c>
+      <c r="C131" s="41" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="B132" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C132" s="41" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="50" t="s">
+        <v>272</v>
+      </c>
+      <c r="B133" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C133" s="41" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="B134" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" s="41" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="B135" s="43" t="n">
+        <v>244</v>
+      </c>
+      <c r="C135" s="41" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="B136" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C136" s="41" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="50" t="s">
+        <v>280</v>
+      </c>
+      <c r="B137" s="43" t="n">
+        <v>540</v>
+      </c>
+      <c r="C137" s="41" t="s">
+        <v>281</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A15:C21"/>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:B4"/>
@@ -10268,6 +10544,7 @@
     <mergeCell ref="A91:C91"/>
     <mergeCell ref="A92:C92"/>
     <mergeCell ref="A94:C94"/>
+    <mergeCell ref="A122:C122"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10308,7 +10585,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -10317,160 +10594,160 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>281</v>
+        <v>312</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -10479,16 +10756,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>95</v>
@@ -10496,58 +10773,58 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="E16" s="59" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="58" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="E17" s="58" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="24"/>
@@ -10556,87 +10833,87 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>311</v>
+        <v>342</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>315</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="58" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="C23" s="58" t="s">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="D23" s="58" t="s">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="E23" s="58" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="58" t="s">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="B25" s="58" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="C25" s="58" t="s">
-        <v>332</v>
+        <v>363</v>
       </c>
       <c r="D25" s="58" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="E25" s="58" t="s">
-        <v>334</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -10689,7 +10966,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>335</v>
+        <v>366</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -10700,33 +10977,33 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>339</v>
+        <v>370</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>340</v>
+        <v>371</v>
       </c>
       <c r="F4" s="57" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>341</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>342</v>
+        <v>373</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>343</v>
+        <v>374</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>134</v>
@@ -10736,37 +11013,37 @@
         <v>24</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>344</v>
+        <v>375</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>347</v>
+        <v>378</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>348</v>
+        <v>379</v>
       </c>
       <c r="D6" s="60" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>349</v>
+        <v>380</v>
       </c>
       <c r="F6" s="58" t="s">
         <v>98</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>350</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10774,71 +11051,71 @@
         <v>228</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="D7" s="60" t="n">
         <f aca="false">Assumptions!B44</f>
         <v>120</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>353</v>
+        <v>384</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>355</v>
+        <v>386</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>357</v>
+        <v>388</v>
       </c>
       <c r="D8" s="60" t="n">
         <f aca="false">Assumptions!B46</f>
         <v>400</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>358</v>
+        <v>389</v>
       </c>
       <c r="F8" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>359</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>360</v>
+        <v>391</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>361</v>
+        <v>392</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>362</v>
+        <v>393</v>
       </c>
       <c r="D9" s="60" t="n">
         <f aca="false">Assumptions!B45</f>
         <v>120</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>363</v>
+        <v>394</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10846,151 +11123,151 @@
         <v>219</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>365</v>
+        <v>396</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>367</v>
+        <v>398</v>
       </c>
       <c r="F10" s="58" t="s">
         <v>98</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>368</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>370</v>
+        <v>401</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>372</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>373</v>
+        <v>404</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>374</v>
+        <v>405</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>375</v>
+        <v>406</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>376</v>
+        <v>407</v>
       </c>
       <c r="F12" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>378</v>
+        <v>409</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>379</v>
+        <v>410</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>380</v>
+        <v>411</v>
       </c>
       <c r="D13" s="60" t="n">
         <f aca="false">Assumptions!B43</f>
         <v>168</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>382</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>383</v>
+        <v>414</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>384</v>
+        <v>415</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>385</v>
+        <v>416</v>
       </c>
       <c r="D14" s="60" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>386</v>
+        <v>417</v>
       </c>
       <c r="F14" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>387</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>388</v>
+        <v>419</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>389</v>
+        <v>420</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>390</v>
+        <v>421</v>
       </c>
       <c r="D15" s="60" t="n">
         <f aca="false">Assumptions!B50</f>
         <v>5</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>391</v>
+        <v>422</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>392</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>393</v>
+        <v>424</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>394</v>
+        <v>425</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>395</v>
+        <v>426</v>
       </c>
       <c r="D16" s="60" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -11003,78 +11280,78 @@
         <v>102</v>
       </c>
       <c r="G16" s="58" t="s">
-        <v>396</v>
+        <v>427</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>397</v>
+        <v>428</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>398</v>
+        <v>429</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>399</v>
+        <v>430</v>
       </c>
       <c r="D17" s="60" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="F17" s="27" t="s">
         <v>102</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>403</v>
+        <v>434</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>404</v>
+        <v>435</v>
       </c>
       <c r="F18" s="58" t="s">
         <v>104</v>
       </c>
       <c r="G18" s="58" t="s">
-        <v>405</v>
+        <v>436</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>406</v>
+        <v>437</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>407</v>
+        <v>438</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>408</v>
+        <v>439</v>
       </c>
       <c r="D19" s="60" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>409</v>
+        <v>440</v>
       </c>
       <c r="F19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>410</v>
+        <v>441</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11082,46 +11359,46 @@
         <v>224</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>411</v>
+        <v>442</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>412</v>
+        <v>443</v>
       </c>
       <c r="F20" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G20" s="58" t="s">
-        <v>413</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>414</v>
+        <v>445</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>415</v>
+        <v>446</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>348</v>
+        <v>379</v>
       </c>
       <c r="D21" s="60" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>416</v>
+        <v>447</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>417</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11129,55 +11406,55 @@
         <v>236</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>418</v>
+        <v>449</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>419</v>
+        <v>450</v>
       </c>
       <c r="D22" s="60" t="n">
         <f aca="false">Assumptions!B57</f>
         <v>2</v>
       </c>
       <c r="E22" s="58" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="F22" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G22" s="58" t="s">
-        <v>421</v>
+        <v>452</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>422</v>
+        <v>453</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>423</v>
+        <v>454</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>385</v>
+        <v>416</v>
       </c>
       <c r="D23" s="60" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>424</v>
+        <v>455</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>425</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="58" t="s">
-        <v>426</v>
+        <v>457</v>
       </c>
       <c r="B24" s="58" t="s">
-        <v>427</v>
+        <v>458</v>
       </c>
       <c r="C24" s="58" t="s">
         <v>134</v>
@@ -11187,13 +11464,13 @@
         <v>24</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>428</v>
+        <v>459</v>
       </c>
       <c r="F24" s="58" t="s">
         <v>98</v>
       </c>
       <c r="G24" s="58" t="s">
-        <v>429</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -11239,7 +11516,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>430</v>
+        <v>461</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11248,7 +11525,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>431</v>
+        <v>462</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -11263,21 +11540,21 @@
         <v>42</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>432</v>
+        <v>463</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>433</v>
+        <v>464</v>
       </c>
       <c r="B6" s="61" t="n">
         <f aca="false">Assumptions!B62</f>
         <v>1200</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>434</v>
+        <v>465</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
@@ -11291,21 +11568,21 @@
         <v>120</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>435</v>
+        <v>466</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>436</v>
+        <v>467</v>
       </c>
       <c r="B8" s="62" t="n">
         <f aca="false">IF(B7=0,0,B6/B7)</f>
         <v>10</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>437</v>
+        <v>468</v>
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="33"/>
@@ -11319,7 +11596,7 @@
         <v>1.3</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>438</v>
+        <v>469</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
@@ -11333,14 +11610,14 @@
         <v>13</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>439</v>
+        <v>470</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>440</v>
+        <v>471</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -11349,24 +11626,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>441</v>
+        <v>472</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>442</v>
+        <v>473</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>443</v>
+        <v>474</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>444</v>
+        <v>475</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>445</v>
+        <v>476</v>
       </c>
       <c r="B14" s="60" t="n">
         <f aca="false">Assumptions!B42</f>
@@ -11381,12 +11658,12 @@
         <v>9.6</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>446</v>
+        <v>477</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="B15" s="60" t="n">
         <f aca="false">Assumptions!B57</f>
@@ -11401,12 +11678,12 @@
         <v>3</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>449</v>
+        <v>480</v>
       </c>
       <c r="B16" s="60" t="n">
         <f aca="false">Assumptions!B58</f>
@@ -11424,7 +11701,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="B17" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B43,0)</f>
@@ -11438,12 +11715,12 @@
         <v>2</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>450</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>451</v>
+        <v>482</v>
       </c>
       <c r="B18" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B44,0)</f>
@@ -11457,12 +11734,12 @@
         <v>3</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>452</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>453</v>
+        <v>484</v>
       </c>
       <c r="B19" s="32" t="n">
         <f aca="false">ROUNDUP((B15+B16*Assumptions!B60)*$B$10/Assumptions!B59,0)</f>
@@ -11476,12 +11753,12 @@
         <v>2</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="B20" s="60" t="n">
         <f aca="false">Assumptions!B61</f>
@@ -11500,7 +11777,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -11512,7 +11789,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>457</v>
+        <v>488</v>
       </c>
       <c r="D22" s="64" t="n">
         <f aca="false">Assumptions!B41</f>
@@ -11521,7 +11798,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="66" t="s">
-        <v>458</v>
+        <v>489</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
@@ -11536,7 +11813,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>459</v>
+        <v>490</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -11545,24 +11822,24 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>441</v>
+        <v>472</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>442</v>
+        <v>473</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>443</v>
+        <v>474</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>444</v>
+        <v>475</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="B27" s="60" t="n">
         <f aca="false">Assumptions!B64</f>
@@ -11582,7 +11859,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="58" t="s">
-        <v>461</v>
+        <v>492</v>
       </c>
       <c r="B28" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B43,0)</f>
@@ -11596,12 +11873,12 @@
         <v>1</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>462</v>
+        <v>493</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>463</v>
+        <v>494</v>
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B44,0)</f>
@@ -11618,7 +11895,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="D30" s="62" t="n">
         <f aca="false">SUM(D27:D29)</f>
@@ -11627,7 +11904,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>465</v>
+        <v>496</v>
       </c>
       <c r="D31" s="62" t="n">
         <f aca="false">Assumptions!B41-D30</f>
@@ -11636,7 +11913,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="D32" s="32" t="n">
         <f aca="false">INT(D31/Assumptions!B65)</f>
@@ -11645,7 +11922,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>467</v>
+        <v>498</v>
       </c>
       <c r="D33" s="60" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -11654,7 +11931,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="66" t="s">
-        <v>393</v>
+        <v>424</v>
       </c>
       <c r="B34" s="66"/>
       <c r="C34" s="66"/>
@@ -11669,7 +11946,7 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="54" t="s">
-        <v>468</v>
+        <v>499</v>
       </c>
       <c r="B36" s="54"/>
       <c r="C36" s="54"/>
@@ -11750,7 +12027,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>469</v>
+        <v>500</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11765,392 +12042,392 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="B4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>470</v>
+        <v>501</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>471</v>
+        <v>502</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>472</v>
+        <v>503</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>473</v>
+        <v>504</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>474</v>
+        <v>505</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>475</v>
+        <v>506</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>341</v>
+        <v>372</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>476</v>
+        <v>507</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>477</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>478</v>
+        <v>509</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>479</v>
+        <v>510</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>480</v>
+        <v>511</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>481</v>
+        <v>512</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>482</v>
+        <v>513</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>483</v>
+        <v>514</v>
       </c>
       <c r="H5" s="69" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>485</v>
+        <v>516</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>486</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>487</v>
+        <v>518</v>
       </c>
       <c r="B6" s="58" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>488</v>
+        <v>519</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>489</v>
+        <v>520</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>490</v>
+        <v>521</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>491</v>
+        <v>522</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="H6" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="58" t="s">
-        <v>493</v>
+        <v>524</v>
       </c>
       <c r="J6" s="58" t="s">
-        <v>494</v>
+        <v>525</v>
       </c>
       <c r="K6" s="58" t="s">
-        <v>495</v>
+        <v>526</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>496</v>
+        <v>527</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>497</v>
+        <v>528</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>498</v>
+        <v>529</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>499</v>
+        <v>530</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>501</v>
+        <v>532</v>
       </c>
       <c r="H7" s="69" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>502</v>
+        <v>533</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>503</v>
+        <v>534</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>504</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>505</v>
+        <v>536</v>
       </c>
       <c r="B8" s="58" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>507</v>
+        <v>538</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>508</v>
+        <v>539</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>509</v>
+        <v>540</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>510</v>
+        <v>541</v>
       </c>
       <c r="H8" s="69" t="n">
         <v>3</v>
       </c>
       <c r="I8" s="58" t="s">
-        <v>511</v>
+        <v>542</v>
       </c>
       <c r="J8" s="58" t="s">
-        <v>512</v>
+        <v>543</v>
       </c>
       <c r="K8" s="58" t="s">
-        <v>513</v>
+        <v>544</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>514</v>
+        <v>545</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>516</v>
+        <v>547</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>517</v>
+        <v>548</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>519</v>
+        <v>550</v>
       </c>
       <c r="H9" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>520</v>
+        <v>551</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>521</v>
+        <v>552</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>522</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>523</v>
+        <v>554</v>
       </c>
       <c r="B10" s="58" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>524</v>
+        <v>555</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>526</v>
+        <v>557</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>528</v>
+        <v>559</v>
       </c>
       <c r="H10" s="69" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="58" t="s">
-        <v>529</v>
+        <v>560</v>
       </c>
       <c r="J10" s="58" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="K10" s="58" t="s">
-        <v>531</v>
+        <v>562</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>532</v>
+        <v>563</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>533</v>
+        <v>564</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>534</v>
+        <v>565</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>535</v>
+        <v>566</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>536</v>
+        <v>567</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>537</v>
+        <v>568</v>
       </c>
       <c r="H11" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>538</v>
+        <v>569</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>539</v>
+        <v>570</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>540</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>541</v>
+        <v>572</v>
       </c>
       <c r="B12" s="58" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>542</v>
+        <v>573</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
       <c r="H12" s="69" t="n">
         <v>3</v>
       </c>
       <c r="I12" s="58" t="s">
-        <v>547</v>
+        <v>578</v>
       </c>
       <c r="J12" s="58" t="s">
-        <v>548</v>
+        <v>579</v>
       </c>
       <c r="K12" s="58" t="s">
-        <v>549</v>
+        <v>580</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>551</v>
+        <v>582</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>552</v>
+        <v>583</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>554</v>
+        <v>585</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>555</v>
+        <v>586</v>
       </c>
       <c r="H13" s="69" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>556</v>
+        <v>587</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>557</v>
+        <v>588</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>558</v>
+        <v>589</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>559</v>
+        <v>590</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>560</v>
+        <v>591</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>561</v>
+        <v>592</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>562</v>
+        <v>593</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>563</v>
+        <v>594</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>564</v>
+        <v>595</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>565</v>
+        <v>596</v>
       </c>
       <c r="H14" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="J14" s="58" t="s">
-        <v>567</v>
+        <v>598</v>
       </c>
       <c r="K14" s="58" t="s">
-        <v>568</v>
+        <v>599</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>569</v>
+        <v>600</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
@@ -12162,10 +12439,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>570</v>
+        <v>601</v>
       </c>
       <c r="B17" s="70" t="s">
-        <v>571</v>
+        <v>602</v>
       </c>
       <c r="C17" s="70"/>
       <c r="D17" s="70"/>
@@ -12176,10 +12453,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>572</v>
+        <v>603</v>
       </c>
       <c r="B18" s="70" t="s">
-        <v>573</v>
+        <v>604</v>
       </c>
       <c r="C18" s="70"/>
       <c r="D18" s="70"/>
@@ -12190,10 +12467,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>574</v>
+        <v>605</v>
       </c>
       <c r="B19" s="70" t="s">
-        <v>575</v>
+        <v>606</v>
       </c>
       <c r="C19" s="70"/>
       <c r="D19" s="70"/>
@@ -12204,10 +12481,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>576</v>
+        <v>607</v>
       </c>
       <c r="B20" s="70" t="s">
-        <v>577</v>
+        <v>608</v>
       </c>
       <c r="C20" s="70"/>
       <c r="D20" s="70"/>
@@ -12218,10 +12495,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>578</v>
+        <v>609</v>
       </c>
       <c r="B21" s="70" t="s">
-        <v>579</v>
+        <v>610</v>
       </c>
       <c r="C21" s="70"/>
       <c r="D21" s="70"/>
@@ -12232,10 +12509,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>580</v>
+        <v>611</v>
       </c>
       <c r="B22" s="70" t="s">
-        <v>581</v>
+        <v>612</v>
       </c>
       <c r="C22" s="70"/>
       <c r="D22" s="70"/>
@@ -12246,10 +12523,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>582</v>
+        <v>613</v>
       </c>
       <c r="B23" s="70" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
       <c r="C23" s="70"/>
       <c r="D23" s="70"/>
@@ -12260,7 +12537,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="71" t="s">
-        <v>584</v>
+        <v>615</v>
       </c>
     </row>
   </sheetData>
@@ -12324,7 +12601,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>585</v>
+        <v>616</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12338,42 +12615,42 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>586</v>
+        <v>617</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>587</v>
+        <v>618</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>588</v>
+        <v>619</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>589</v>
+        <v>620</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>590</v>
+        <v>621</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>592</v>
+        <v>623</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>593</v>
+        <v>624</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
@@ -12382,190 +12659,190 @@
         <v>96</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G5" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="I5" s="69" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="D6" s="58" t="s">
         <v>96</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G6" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>592</v>
+        <v>623</v>
       </c>
       <c r="I6" s="69" t="s">
-        <v>601</v>
+        <v>632</v>
       </c>
       <c r="J6" s="58" t="s">
-        <v>602</v>
+        <v>633</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>603</v>
+        <v>634</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G7" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="I7" s="69" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>605</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>606</v>
+        <v>637</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>607</v>
+        <v>638</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="D8" s="58" t="s">
         <v>96</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="G8" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="I8" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J8" s="58" t="s">
-        <v>610</v>
+        <v>641</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>611</v>
+        <v>642</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>612</v>
+        <v>643</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G9" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="I9" s="69" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>613</v>
+        <v>644</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>614</v>
+        <v>645</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>615</v>
+        <v>646</v>
       </c>
       <c r="D10" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G10" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="I10" s="69" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="J10" s="58" t="s">
-        <v>616</v>
+        <v>647</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>617</v>
+        <v>648</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>23</v>
@@ -12574,30 +12851,30 @@
         <v>98</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G11" s="43" t="n">
         <v>12</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="I11" s="69" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>618</v>
+        <v>649</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>493</v>
+        <v>524</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>619</v>
+        <v>650</v>
       </c>
       <c r="C12" s="58" t="s">
         <v>23</v>
@@ -12606,30 +12883,30 @@
         <v>98</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G12" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
       <c r="I12" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J12" s="58" t="s">
-        <v>620</v>
+        <v>651</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>502</v>
+        <v>533</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>621</v>
+        <v>652</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>26</v>
@@ -12638,62 +12915,62 @@
         <v>98</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G13" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="I13" s="69" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>622</v>
+        <v>653</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>623</v>
+        <v>654</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>624</v>
+        <v>655</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="D14" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G14" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="I14" s="69" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="J14" s="58" t="s">
-        <v>625</v>
+        <v>656</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>538</v>
+        <v>569</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>626</v>
+        <v>657</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>35</v>
@@ -12702,263 +12979,263 @@
         <v>98</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G15" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>623</v>
+        <v>654</v>
       </c>
       <c r="I15" s="69" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="J15" s="27" t="s">
-        <v>627</v>
+        <v>658</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>628</v>
+        <v>659</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>629</v>
+        <v>660</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>471</v>
+        <v>502</v>
       </c>
       <c r="D16" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G16" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
       <c r="I16" s="69" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="J16" s="58" t="s">
-        <v>630</v>
+        <v>661</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>410</v>
+        <v>441</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>631</v>
+        <v>662</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>632</v>
+        <v>663</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G17" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="I17" s="69" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>633</v>
+        <v>664</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>634</v>
+        <v>665</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="G18" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H18" s="58" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="I18" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J18" s="58" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>612</v>
+        <v>643</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G19" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="I19" s="69" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>368</v>
+        <v>399</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>640</v>
+        <v>671</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>615</v>
+        <v>646</v>
       </c>
       <c r="D20" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G20" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H20" s="58" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
       <c r="I20" s="69" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="J20" s="58" t="s">
-        <v>641</v>
+        <v>672</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>642</v>
+        <v>673</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>643</v>
+        <v>674</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>644</v>
+        <v>675</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G21" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="I21" s="69" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="J21" s="27" t="s">
-        <v>645</v>
+        <v>676</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="58" t="s">
-        <v>646</v>
+        <v>677</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>647</v>
+        <v>678</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>471</v>
+        <v>502</v>
       </c>
       <c r="D22" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E22" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F22" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G22" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="58" t="s">
-        <v>628</v>
+        <v>659</v>
       </c>
       <c r="I22" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J22" s="58" t="s">
-        <v>648</v>
+        <v>679</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>649</v>
+        <v>680</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>650</v>
+        <v>681</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>651</v>
+        <v>682</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>652</v>
+        <v>683</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
@@ -12967,117 +13244,117 @@
         <v>3</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>606</v>
+        <v>637</v>
       </c>
       <c r="I23" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>653</v>
+        <v>684</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="58" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="B24" s="58" t="s">
-        <v>373</v>
+        <v>404</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>615</v>
+        <v>646</v>
       </c>
       <c r="D24" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F24" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G24" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H24" s="58" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="I24" s="69" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="J24" s="58" t="s">
-        <v>654</v>
+        <v>685</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>561</v>
+        <v>592</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>615</v>
+        <v>646</v>
       </c>
       <c r="D25" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G25" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="I25" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J25" s="27" t="s">
-        <v>655</v>
+        <v>686</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="58" t="s">
-        <v>656</v>
+        <v>687</v>
       </c>
       <c r="B26" s="58" t="s">
-        <v>657</v>
+        <v>688</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>615</v>
+        <v>646</v>
       </c>
       <c r="D26" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F26" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G26" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H26" s="58" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="I26" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J26" s="58" t="s">
-        <v>658</v>
+        <v>689</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>520</v>
+        <v>551</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="C27" s="27" t="s">
         <v>29</v>
@@ -13086,30 +13363,30 @@
         <v>100</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G27" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>623</v>
+        <v>654</v>
       </c>
       <c r="I27" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J27" s="27" t="s">
-        <v>659</v>
+        <v>690</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="58" t="s">
-        <v>529</v>
+        <v>560</v>
       </c>
       <c r="B28" s="58" t="s">
-        <v>660</v>
+        <v>691</v>
       </c>
       <c r="C28" s="58" t="s">
         <v>32</v>
@@ -13118,30 +13395,30 @@
         <v>100</v>
       </c>
       <c r="E28" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F28" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G28" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H28" s="58" t="s">
-        <v>623</v>
+        <v>654</v>
       </c>
       <c r="I28" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J28" s="58" t="s">
-        <v>661</v>
+        <v>692</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>511</v>
+        <v>542</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>662</v>
+        <v>693</v>
       </c>
       <c r="C29" s="27" t="s">
         <v>26</v>
@@ -13150,94 +13427,94 @@
         <v>100</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>652</v>
+        <v>683</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G29" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>502</v>
+        <v>533</v>
       </c>
       <c r="I29" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>663</v>
+        <v>694</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="58" t="s">
-        <v>556</v>
+        <v>587</v>
       </c>
       <c r="B30" s="58" t="s">
-        <v>664</v>
+        <v>695</v>
       </c>
       <c r="C30" s="58" t="s">
-        <v>612</v>
+        <v>643</v>
       </c>
       <c r="D30" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F30" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G30" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="58" t="s">
-        <v>502</v>
+        <v>533</v>
       </c>
       <c r="I30" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J30" s="58" t="s">
-        <v>665</v>
+        <v>696</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="s">
-        <v>421</v>
+        <v>452</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>666</v>
+        <v>697</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="D31" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G31" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="I31" s="69" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="J31" s="27" t="s">
-        <v>667</v>
+        <v>698</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="58" t="s">
-        <v>668</v>
+        <v>699</v>
       </c>
       <c r="B32" s="58" t="s">
-        <v>669</v>
+        <v>700</v>
       </c>
       <c r="C32" s="58" t="s">
         <v>35</v>
@@ -13246,30 +13523,30 @@
         <v>100</v>
       </c>
       <c r="E32" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F32" s="58" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="G32" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H32" s="58" t="s">
-        <v>538</v>
+        <v>569</v>
       </c>
       <c r="I32" s="69" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="J32" s="58" t="s">
-        <v>670</v>
+        <v>701</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>547</v>
+        <v>578</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>671</v>
+        <v>702</v>
       </c>
       <c r="C33" s="27" t="s">
         <v>35</v>
@@ -13278,487 +13555,487 @@
         <v>100</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G33" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>538</v>
+        <v>569</v>
       </c>
       <c r="I33" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J33" s="27" t="s">
-        <v>672</v>
+        <v>703</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="58" t="s">
-        <v>673</v>
+        <v>704</v>
       </c>
       <c r="B34" s="58" t="s">
-        <v>674</v>
+        <v>705</v>
       </c>
       <c r="C34" s="58" t="s">
-        <v>675</v>
+        <v>706</v>
       </c>
       <c r="D34" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F34" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G34" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H34" s="58" t="s">
-        <v>421</v>
+        <v>452</v>
       </c>
       <c r="I34" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J34" s="58" t="s">
-        <v>676</v>
+        <v>707</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>677</v>
+        <v>708</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>678</v>
+        <v>709</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>675</v>
+        <v>706</v>
       </c>
       <c r="D35" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G35" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>673</v>
+        <v>704</v>
       </c>
       <c r="I35" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J35" s="27" t="s">
-        <v>679</v>
+        <v>710</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="58" t="s">
-        <v>680</v>
+        <v>711</v>
       </c>
       <c r="B36" s="58" t="s">
-        <v>681</v>
+        <v>712</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>675</v>
+        <v>706</v>
       </c>
       <c r="D36" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F36" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G36" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H36" s="58" t="s">
-        <v>677</v>
+        <v>708</v>
       </c>
       <c r="I36" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J36" s="58" t="s">
-        <v>682</v>
+        <v>713</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="27" t="s">
-        <v>683</v>
+        <v>714</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>684</v>
+        <v>715</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>685</v>
+        <v>716</v>
       </c>
       <c r="D37" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>652</v>
+        <v>683</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G37" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H37" s="27" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="I37" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J37" s="27" t="s">
-        <v>686</v>
+        <v>717</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="58" t="s">
-        <v>687</v>
+        <v>718</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>688</v>
+        <v>719</v>
       </c>
       <c r="C38" s="58" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="D38" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="58" t="s">
-        <v>652</v>
+        <v>683</v>
       </c>
       <c r="F38" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G38" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="58" t="s">
-        <v>683</v>
+        <v>714</v>
       </c>
       <c r="I38" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J38" s="58" t="s">
-        <v>689</v>
+        <v>720</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="27" t="s">
-        <v>413</v>
+        <v>444</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>690</v>
+        <v>721</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>632</v>
+        <v>663</v>
       </c>
       <c r="D39" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G39" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="I39" s="69" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="J39" s="27" t="s">
-        <v>691</v>
+        <v>722</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="58" t="s">
-        <v>417</v>
+        <v>448</v>
       </c>
       <c r="B40" s="58" t="s">
-        <v>414</v>
+        <v>445</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="D40" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F40" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G40" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H40" s="58" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="I40" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J40" s="58" t="s">
-        <v>692</v>
+        <v>723</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>425</v>
+        <v>456</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>693</v>
+        <v>724</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="D41" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G41" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>421</v>
+        <v>452</v>
       </c>
       <c r="I41" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J41" s="27" t="s">
-        <v>694</v>
+        <v>725</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="58" t="s">
-        <v>695</v>
+        <v>726</v>
       </c>
       <c r="B42" s="58" t="s">
-        <v>696</v>
+        <v>727</v>
       </c>
       <c r="C42" s="58" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="D42" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="58" t="s">
-        <v>652</v>
+        <v>683</v>
       </c>
       <c r="F42" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G42" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="58" t="s">
-        <v>687</v>
+        <v>718</v>
       </c>
       <c r="I42" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J42" s="58" t="s">
-        <v>697</v>
+        <v>728</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
-        <v>698</v>
+        <v>729</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>699</v>
+        <v>730</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>700</v>
+        <v>731</v>
       </c>
       <c r="D43" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>700</v>
+        <v>731</v>
       </c>
       <c r="G43" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H43" s="27" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="I43" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J43" s="27" t="s">
-        <v>701</v>
+        <v>732</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="58" t="s">
-        <v>702</v>
+        <v>733</v>
       </c>
       <c r="B44" s="58" t="s">
-        <v>703</v>
+        <v>734</v>
       </c>
       <c r="C44" s="58" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="D44" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E44" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F44" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G44" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H44" s="58" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="I44" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J44" s="58" t="s">
-        <v>704</v>
+        <v>735</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="27" t="s">
-        <v>705</v>
+        <v>736</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>706</v>
+        <v>737</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="D45" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G45" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H45" s="27" t="s">
-        <v>634</v>
+        <v>665</v>
       </c>
       <c r="I45" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J45" s="27" t="s">
-        <v>707</v>
+        <v>738</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="58" t="s">
-        <v>708</v>
+        <v>739</v>
       </c>
       <c r="B46" s="58" t="s">
-        <v>709</v>
+        <v>740</v>
       </c>
       <c r="C46" s="58" t="s">
-        <v>471</v>
+        <v>502</v>
       </c>
       <c r="D46" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E46" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F46" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G46" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H46" s="58" t="s">
-        <v>628</v>
+        <v>659</v>
       </c>
       <c r="I46" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J46" s="58" t="s">
-        <v>710</v>
+        <v>741</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
-        <v>711</v>
+        <v>742</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>712</v>
+        <v>743</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>685</v>
+        <v>716</v>
       </c>
       <c r="D47" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G47" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H47" s="27" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="I47" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J47" s="27" t="s">
-        <v>713</v>
+        <v>744</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="58" t="s">
-        <v>714</v>
+        <v>745</v>
       </c>
       <c r="B48" s="58" t="s">
-        <v>715</v>
+        <v>746</v>
       </c>
       <c r="C48" s="58" t="s">
-        <v>375</v>
+        <v>406</v>
       </c>
       <c r="D48" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E48" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F48" s="58" t="s">
         <v>100</v>
@@ -13767,62 +14044,62 @@
         <v>3</v>
       </c>
       <c r="H48" s="58" t="s">
-        <v>677</v>
+        <v>708</v>
       </c>
       <c r="I48" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J48" s="58" t="s">
-        <v>716</v>
+        <v>747</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="27" t="s">
-        <v>717</v>
+        <v>748</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>718</v>
+        <v>749</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>719</v>
+        <v>750</v>
       </c>
       <c r="D49" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>652</v>
+        <v>683</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G49" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H49" s="27" t="s">
-        <v>705</v>
+        <v>736</v>
       </c>
       <c r="I49" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J49" s="27" t="s">
-        <v>720</v>
+        <v>751</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="58" t="s">
-        <v>721</v>
+        <v>752</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>722</v>
+        <v>753</v>
       </c>
       <c r="C50" s="58" t="s">
-        <v>723</v>
+        <v>754</v>
       </c>
       <c r="D50" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E50" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F50" s="58" t="s">
         <v>100</v>
@@ -13831,181 +14108,181 @@
         <v>4</v>
       </c>
       <c r="H50" s="58" t="s">
-        <v>642</v>
+        <v>673</v>
       </c>
       <c r="I50" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J50" s="58" t="s">
-        <v>724</v>
+        <v>755</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
-        <v>725</v>
+        <v>756</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>726</v>
+        <v>757</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>727</v>
+        <v>758</v>
       </c>
       <c r="D51" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G51" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H51" s="27" t="s">
-        <v>656</v>
+        <v>687</v>
       </c>
       <c r="I51" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J51" s="27" t="s">
-        <v>728</v>
+        <v>759</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="58" t="s">
-        <v>729</v>
+        <v>760</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>730</v>
+        <v>761</v>
       </c>
       <c r="C52" s="58" t="s">
-        <v>727</v>
+        <v>758</v>
       </c>
       <c r="D52" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E52" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F52" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G52" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H52" s="58" t="s">
-        <v>547</v>
+        <v>578</v>
       </c>
       <c r="I52" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J52" s="58" t="s">
-        <v>731</v>
+        <v>762</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="27" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>732</v>
+        <v>763</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>727</v>
+        <v>758</v>
       </c>
       <c r="D53" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F53" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G53" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H53" s="27" t="s">
-        <v>729</v>
+        <v>760</v>
       </c>
       <c r="I53" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J53" s="27" t="s">
-        <v>733</v>
+        <v>764</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="58" t="s">
-        <v>734</v>
+        <v>765</v>
       </c>
       <c r="B54" s="58" t="s">
-        <v>735</v>
+        <v>766</v>
       </c>
       <c r="C54" s="58" t="s">
-        <v>615</v>
+        <v>646</v>
       </c>
       <c r="D54" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E54" s="58" t="s">
-        <v>652</v>
+        <v>683</v>
       </c>
       <c r="F54" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G54" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H54" s="58" t="s">
-        <v>656</v>
+        <v>687</v>
       </c>
       <c r="I54" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J54" s="58" t="s">
-        <v>736</v>
+        <v>767</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
-        <v>737</v>
+        <v>768</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>738</v>
+        <v>769</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="D55" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>739</v>
+        <v>770</v>
       </c>
       <c r="F55" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G55" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>680</v>
+        <v>711</v>
       </c>
       <c r="I55" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J55" s="27" t="s">
-        <v>740</v>
+        <v>771</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="58" t="s">
-        <v>741</v>
+        <v>772</v>
       </c>
       <c r="B56" s="58" t="s">
-        <v>742</v>
+        <v>773</v>
       </c>
       <c r="C56" s="58" t="s">
         <v>26</v>
@@ -14014,359 +14291,359 @@
         <v>102</v>
       </c>
       <c r="E56" s="58" t="s">
-        <v>739</v>
+        <v>770</v>
       </c>
       <c r="F56" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G56" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H56" s="58" t="s">
-        <v>502</v>
+        <v>533</v>
       </c>
       <c r="I56" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J56" s="58" t="s">
-        <v>743</v>
+        <v>774</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
-        <v>744</v>
+        <v>775</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>745</v>
+        <v>776</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>685</v>
+        <v>716</v>
       </c>
       <c r="D57" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G57" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H57" s="27" t="s">
-        <v>725</v>
+        <v>756</v>
       </c>
       <c r="I57" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J57" s="27" t="s">
-        <v>746</v>
+        <v>777</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="58" t="s">
-        <v>747</v>
+        <v>778</v>
       </c>
       <c r="B58" s="58" t="s">
-        <v>748</v>
+        <v>779</v>
       </c>
       <c r="C58" s="58" t="s">
-        <v>471</v>
+        <v>502</v>
       </c>
       <c r="D58" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E58" s="58" t="s">
-        <v>652</v>
+        <v>683</v>
       </c>
       <c r="F58" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G58" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H58" s="58" t="s">
-        <v>628</v>
+        <v>659</v>
       </c>
       <c r="I58" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J58" s="58" t="s">
-        <v>749</v>
+        <v>780</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="27" t="s">
-        <v>750</v>
+        <v>781</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>751</v>
+        <v>782</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>612</v>
+        <v>643</v>
       </c>
       <c r="D59" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E59" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G59" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H59" s="27" t="s">
-        <v>642</v>
+        <v>673</v>
       </c>
       <c r="I59" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J59" s="27" t="s">
-        <v>752</v>
+        <v>783</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="58" t="s">
-        <v>753</v>
+        <v>784</v>
       </c>
       <c r="B60" s="58" t="s">
-        <v>754</v>
+        <v>785</v>
       </c>
       <c r="C60" s="58" t="s">
-        <v>755</v>
+        <v>786</v>
       </c>
       <c r="D60" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E60" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F60" s="58" t="s">
-        <v>755</v>
+        <v>786</v>
       </c>
       <c r="G60" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H60" s="58" t="s">
-        <v>744</v>
+        <v>775</v>
       </c>
       <c r="I60" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J60" s="58" t="s">
-        <v>756</v>
+        <v>787</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="27" t="s">
-        <v>757</v>
+        <v>788</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>758</v>
+        <v>789</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>685</v>
+        <v>716</v>
       </c>
       <c r="D61" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G61" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H61" s="27" t="s">
-        <v>744</v>
+        <v>775</v>
       </c>
       <c r="I61" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J61" s="27" t="s">
-        <v>759</v>
+        <v>790</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="58" t="s">
-        <v>760</v>
+        <v>791</v>
       </c>
       <c r="B62" s="58" t="s">
-        <v>761</v>
+        <v>792</v>
       </c>
       <c r="C62" s="58" t="s">
-        <v>471</v>
+        <v>502</v>
       </c>
       <c r="D62" s="58" t="s">
         <v>104</v>
       </c>
       <c r="E62" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F62" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G62" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H62" s="58" t="s">
-        <v>628</v>
+        <v>659</v>
       </c>
       <c r="I62" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J62" s="58" t="s">
-        <v>762</v>
+        <v>793</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="27" t="s">
-        <v>763</v>
+        <v>794</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="C63" s="27" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="D63" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E63" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G63" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H63" s="27" t="s">
-        <v>744</v>
+        <v>775</v>
       </c>
       <c r="I63" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J63" s="27" t="s">
-        <v>766</v>
+        <v>797</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="58" t="s">
-        <v>767</v>
+        <v>798</v>
       </c>
       <c r="B64" s="58" t="s">
-        <v>768</v>
+        <v>799</v>
       </c>
       <c r="C64" s="58" t="s">
-        <v>719</v>
+        <v>750</v>
       </c>
       <c r="D64" s="58" t="s">
         <v>104</v>
       </c>
       <c r="E64" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F64" s="58" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G64" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H64" s="58" t="s">
-        <v>757</v>
+        <v>788</v>
       </c>
       <c r="I64" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J64" s="58" t="s">
-        <v>769</v>
+        <v>800</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="27" t="s">
-        <v>770</v>
+        <v>801</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>771</v>
+        <v>802</v>
       </c>
       <c r="C65" s="27" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="D65" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E65" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G65" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H65" s="27" t="s">
-        <v>744</v>
+        <v>775</v>
       </c>
       <c r="I65" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J65" s="27" t="s">
-        <v>772</v>
+        <v>803</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="58" t="s">
-        <v>773</v>
+        <v>804</v>
       </c>
       <c r="B66" s="58" t="s">
-        <v>774</v>
+        <v>805</v>
       </c>
       <c r="C66" s="58" t="s">
-        <v>651</v>
+        <v>682</v>
       </c>
       <c r="D66" s="58" t="s">
         <v>104</v>
       </c>
       <c r="E66" s="58" t="s">
-        <v>652</v>
+        <v>683</v>
       </c>
       <c r="F66" s="58" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G66" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H66" s="58" t="s">
-        <v>702</v>
+        <v>733</v>
       </c>
       <c r="I66" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J66" s="58" t="s">
-        <v>775</v>
+        <v>806</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="27" t="s">
-        <v>776</v>
+        <v>807</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>777</v>
+        <v>808</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>651</v>
+        <v>682</v>
       </c>
       <c r="D67" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F67" s="27" t="s">
         <v>100</v>
@@ -14375,30 +14652,30 @@
         <v>5</v>
       </c>
       <c r="H67" s="27" t="s">
-        <v>757</v>
+        <v>788</v>
       </c>
       <c r="I67" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J67" s="27" t="s">
-        <v>778</v>
+        <v>809</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="58" t="s">
-        <v>779</v>
+        <v>810</v>
       </c>
       <c r="B68" s="58" t="s">
-        <v>780</v>
+        <v>811</v>
       </c>
       <c r="C68" s="58" t="s">
-        <v>651</v>
+        <v>682</v>
       </c>
       <c r="D68" s="58" t="s">
         <v>106</v>
       </c>
       <c r="E68" s="58" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F68" s="58" t="s">
         <v>100</v>
@@ -14407,45 +14684,45 @@
         <v>1</v>
       </c>
       <c r="H68" s="58" t="s">
-        <v>776</v>
+        <v>807</v>
       </c>
       <c r="I68" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J68" s="58" t="s">
-        <v>781</v>
+        <v>812</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="27" t="s">
-        <v>782</v>
+        <v>813</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>783</v>
+        <v>814</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>651</v>
+        <v>682</v>
       </c>
       <c r="D69" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E69" s="27" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F69" s="27" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="G69" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H69" s="27" t="s">
-        <v>770</v>
+        <v>801</v>
       </c>
       <c r="I69" s="69" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="J69" s="27" t="s">
-        <v>784</v>
+        <v>815</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14582,7 +14859,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D82" s="72" t="s">
-        <v>785</v>
+        <v>816</v>
       </c>
       <c r="E82" s="72"/>
       <c r="F82" s="72"/>
@@ -14593,7 +14870,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D83" s="73" t="s">
-        <v>786</v>
+        <v>817</v>
       </c>
       <c r="E83" s="73"/>
       <c r="F83" s="73"/>
@@ -14604,7 +14881,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D84" s="73" t="s">
-        <v>787</v>
+        <v>818</v>
       </c>
       <c r="E84" s="73"/>
       <c r="F84" s="73"/>
@@ -14615,7 +14892,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D85" s="73" t="s">
-        <v>788</v>
+        <v>819</v>
       </c>
       <c r="E85" s="73"/>
       <c r="F85" s="73"/>
@@ -14626,7 +14903,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D86" s="73" t="s">
-        <v>789</v>
+        <v>820</v>
       </c>
       <c r="E86" s="73"/>
       <c r="F86" s="73"/>
@@ -14637,7 +14914,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>790</v>
+        <v>821</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -14651,25 +14928,25 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>588</v>
+        <v>619</v>
       </c>
       <c r="B90" s="9"/>
       <c r="C90" s="9" t="s">
-        <v>791</v>
+        <v>822</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>792</v>
+        <v>823</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>793</v>
+        <v>824</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>794</v>
+        <v>825</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="75" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="B91" s="75"/>
       <c r="C91" s="32" t="n">
@@ -14691,7 +14968,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="75" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="B92" s="75"/>
       <c r="C92" s="32" t="n">
@@ -14713,7 +14990,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="75" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="B93" s="75"/>
       <c r="C93" s="32" t="n">
@@ -14735,7 +15012,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="75" t="s">
-        <v>700</v>
+        <v>731</v>
       </c>
       <c r="B94" s="75"/>
       <c r="C94" s="32" t="n">
@@ -14757,7 +15034,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="75" t="s">
-        <v>755</v>
+        <v>786</v>
       </c>
       <c r="B95" s="75"/>
       <c r="C95" s="32" t="n">
@@ -14801,7 +15078,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="72" t="s">
-        <v>795</v>
+        <v>826</v>
       </c>
       <c r="B97" s="72"/>
       <c r="C97" s="21" t="n">
@@ -14827,16 +15104,16 @@
       </c>
       <c r="B99" s="29"/>
       <c r="C99" s="9" t="s">
-        <v>791</v>
+        <v>822</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>796</v>
+        <v>827</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>793</v>
+        <v>824</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>794</v>
+        <v>825</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14979,7 +15256,7 @@
     </row>
     <row r="107" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="54" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
       <c r="B107" s="54"/>
       <c r="C107" s="54"/>
@@ -15113,7 +15390,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>798</v>
+        <v>829</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -15131,22 +15408,22 @@
         <v>6</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>799</v>
+        <v>830</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>800</v>
+        <v>831</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>801</v>
+        <v>832</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>802</v>
+        <v>833</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>803</v>
+        <v>834</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>804</v>
+        <v>835</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15167,16 +15444,16 @@
         <v>46383</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>805</v>
+        <v>836</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>806</v>
+        <v>837</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>807</v>
+        <v>838</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>808</v>
+        <v>839</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15197,16 +15474,16 @@
         <v>46453</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>809</v>
+        <v>840</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>810</v>
+        <v>841</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>811</v>
+        <v>842</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>812</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15227,16 +15504,16 @@
         <v>46579</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>813</v>
+        <v>844</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>814</v>
+        <v>845</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>815</v>
+        <v>846</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>816</v>
+        <v>847</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15257,16 +15534,16 @@
         <v>46621</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>817</v>
+        <v>848</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>818</v>
+        <v>849</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>819</v>
+        <v>850</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>820</v>
+        <v>851</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15287,16 +15564,16 @@
         <v>46663</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>822</v>
+        <v>853</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>823</v>
+        <v>854</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>824</v>
+        <v>855</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15317,21 +15594,21 @@
         <v>46691</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>826</v>
+        <v>857</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>827</v>
+        <v>858</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>828</v>
+        <v>859</v>
       </c>
       <c r="B12" s="81" t="n">
         <f aca="false">D10</f>
@@ -15341,7 +15618,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="B13" s="82" t="n">
         <f aca="false">B12-Assumptions!B7</f>
@@ -15351,7 +15628,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>830</v>
+        <v>861</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="24"/>
@@ -15363,7 +15640,7 @@
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
-        <v>831</v>
+        <v>862</v>
       </c>
       <c r="B15" s="54"/>
       <c r="C15" s="54"/>
@@ -15375,7 +15652,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="54" t="s">
-        <v>832</v>
+        <v>863</v>
       </c>
       <c r="B16" s="54"/>
       <c r="C16" s="54"/>
@@ -15455,7 +15732,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>833</v>
+        <v>864</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -15489,13 +15766,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>834</v>
+        <v>865</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>799</v>
+        <v>830</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>800</v>
+        <v>831</v>
       </c>
       <c r="D4" s="83" t="n">
         <v>1</v>
@@ -15680,7 +15957,7 @@
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>835</v>
+        <v>866</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -15927,7 +16204,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>836</v>
+        <v>867</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -17698,7 +17975,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>837</v>
+        <v>868</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -17945,7 +18222,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>838</v>
+        <v>869</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>

--- a/docs/Vinland_Game_Development_Plan.xlsx
+++ b/docs/Vinland_Game_Development_Plan.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="1166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="1167">
   <si>
     <t xml:space="preserve">VINLAND</t>
   </si>
@@ -2479,7 +2479,7 @@
     <t xml:space="preserve">Polish</t>
   </si>
   <si>
-    <t xml:space="preserve">Forgiveness tuned from playtest 2 logs.</t>
+    <t xml:space="preserve">Forgiveness tuned from playtest 2 logs.  [Difficulty levels and novice-player tests in place from the first playtest; tune again from real play logs.]</t>
   </si>
   <si>
     <t xml:space="preserve">F56</t>
@@ -2956,25 +2956,28 @@
     <t xml:space="preserve">Star ring is not fun</t>
   </si>
   <si>
-    <t xml:space="preserve">Stop at the slice. Retune forgiveness before any other verb.</t>
+    <t xml:space="preserve">Stop at the slice. Retune forgiveness before any other verb. [17 Oct 2026: first playtest failed every mini-game. Retuned: Forgiving / Standard / Hard difficulty, guided prompts, keyboard wind-up, novice-player bots now gate every build.]</t>
   </si>
   <si>
     <t xml:space="preserve">Table testers stop seating stars after three tries</t>
   </si>
   <si>
+    <t xml:space="preserve">Watching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold math is trivial or cruel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log every slice run. Tune food coverage on Assumptions, not in code literals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slice runs end with the hold always full or never touched</t>
+  </si>
+  <si>
     <t xml:space="preserve">Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hold math is trivial or cruel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log every slice run. Tune food coverage on Assumptions, not in code literals.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slice runs end with the hold always full or never touched</t>
   </si>
   <si>
     <t xml:space="preserve">R3</t>
@@ -4788,11 +4791,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="73134574"/>
-        <c:axId val="63984756"/>
+        <c:axId val="98654844"/>
+        <c:axId val="96776336"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="73134574"/>
+        <c:axId val="98654844"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4824,7 +4827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63984756"/>
+        <c:crossAx val="96776336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4832,7 +4835,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="63984756"/>
+        <c:axId val="96776336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4908,7 +4911,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73134574"/>
+        <c:crossAx val="98654844"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4947,9 +4950,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>744120</xdr:colOff>
+      <xdr:colOff>743760</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>60480</xdr:rowOff>
+      <xdr:rowOff>60120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4958,7 +4961,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="6562800"/>
-        <a:ext cx="5396040" cy="2156040"/>
+        <a:ext cx="5395680" cy="2155680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7745,15 +7748,15 @@
         <v>962</v>
       </c>
       <c r="J6" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="58" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>2</v>
@@ -7766,7 +7769,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="58" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="G7" s="58" t="s">
         <v>631</v>
@@ -7775,18 +7778,18 @@
         <v>855</v>
       </c>
       <c r="I7" s="58" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="J7" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>4</v>
@@ -7799,7 +7802,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>100</v>
@@ -7808,18 +7811,18 @@
         <v>847</v>
       </c>
       <c r="I8" s="58" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="J8" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="58" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>2</v>
@@ -7832,7 +7835,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="G9" s="58" t="s">
         <v>639</v>
@@ -7841,18 +7844,18 @@
         <v>847</v>
       </c>
       <c r="I9" s="58" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="J9" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C10" s="43" t="n">
         <v>2</v>
@@ -7865,7 +7868,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G10" s="58" t="s">
         <v>292</v>
@@ -7874,18 +7877,18 @@
         <v>847</v>
       </c>
       <c r="I10" s="58" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="J10" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="58" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C11" s="43" t="n">
         <v>3</v>
@@ -7898,7 +7901,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="G11" s="58" t="s">
         <v>100</v>
@@ -7907,18 +7910,18 @@
         <v>851</v>
       </c>
       <c r="I11" s="58" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="J11" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C12" s="43" t="n">
         <v>2</v>
@@ -7931,7 +7934,7 @@
         <v>8</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G12" s="58" t="s">
         <v>631</v>
@@ -7940,18 +7943,18 @@
         <v>839</v>
       </c>
       <c r="I12" s="58" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="J12" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="58" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B13" s="58" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C13" s="43" t="n">
         <v>2</v>
@@ -7964,7 +7967,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="58" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="G13" s="58" t="s">
         <v>292</v>
@@ -7973,18 +7976,18 @@
         <v>839</v>
       </c>
       <c r="I13" s="58" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="J13" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C14" s="43" t="n">
         <v>3</v>
@@ -7997,7 +8000,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G14" s="58" t="s">
         <v>292</v>
@@ -8006,18 +8009,18 @@
         <v>851</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="J14" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="58" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C15" s="43" t="n">
         <v>3</v>
@@ -8030,7 +8033,7 @@
         <v>15</v>
       </c>
       <c r="F15" s="58" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="G15" s="58" t="s">
         <v>292</v>
@@ -8039,18 +8042,18 @@
         <v>847</v>
       </c>
       <c r="I15" s="58" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="J15" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C16" s="43" t="n">
         <v>4</v>
@@ -8063,7 +8066,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="G16" s="58" t="s">
         <v>100</v>
@@ -8072,18 +8075,18 @@
         <v>843</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="J16" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="58" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C17" s="43" t="n">
         <v>3</v>
@@ -8096,7 +8099,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="G17" s="58" t="s">
         <v>100</v>
@@ -8105,18 +8108,18 @@
         <v>847</v>
       </c>
       <c r="I17" s="58" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="J17" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C18" s="43" t="n">
         <v>2</v>
@@ -8129,7 +8132,7 @@
         <v>6</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="G18" s="58" t="s">
         <v>292</v>
@@ -8138,18 +8141,18 @@
         <v>855</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="J18" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="58" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C19" s="43" t="n">
         <v>2</v>
@@ -8162,7 +8165,7 @@
         <v>8</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G19" s="58" t="s">
         <v>631</v>
@@ -8171,18 +8174,18 @@
         <v>847</v>
       </c>
       <c r="I19" s="58" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="J19" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C20" s="43" t="n">
         <v>3</v>
@@ -8195,7 +8198,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="G20" s="58" t="s">
         <v>100</v>
@@ -8204,10 +8207,10 @@
         <v>843</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="J20" s="69" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
   </sheetData>
@@ -8285,7 +8288,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8296,16 +8299,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="E4" s="57" t="s">
         <v>95</v>
@@ -8314,30 +8317,30 @@
         <v>619</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>639</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8345,68 +8348,68 @@
         <v>591</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>639</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F8" s="58" t="s">
         <v>639</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8414,22 +8417,22 @@
         <v>476</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>639</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8437,22 +8440,22 @@
         <v>667</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D10" s="58" t="s">
         <v>789</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F10" s="58" t="s">
         <v>639</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8460,22 +8463,22 @@
         <v>731</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>731</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8483,91 +8486,91 @@
         <v>750</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F12" s="58" t="s">
         <v>292</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>631</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F14" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
   </sheetData>
@@ -8609,7 +8612,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8620,10 +8623,10 @@
         <v>110</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D4" s="57" t="s">
         <v>619</v>
@@ -8631,10 +8634,10 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>839</v>
@@ -8645,13 +8648,13 @@
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D6" s="58" t="s">
         <v>631</v>
@@ -8659,10 +8662,10 @@
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C7" s="27" t="s">
         <v>847</v>
@@ -8673,10 +8676,10 @@
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C8" s="58" t="s">
         <v>843</v>
@@ -8687,10 +8690,10 @@
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C9" s="27" t="s">
         <v>839</v>
@@ -8701,10 +8704,10 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C10" s="58" t="s">
         <v>847</v>
@@ -8715,10 +8718,10 @@
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>855</v>
@@ -8729,10 +8732,10 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C12" s="58" t="s">
         <v>858</v>
@@ -8743,10 +8746,10 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>858</v>
@@ -8757,13 +8760,13 @@
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D14" s="58" t="s">
         <v>292</v>
@@ -8771,10 +8774,10 @@
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>843</v>
@@ -8785,7 +8788,7 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B16" s="58" t="str">
         <f aca="false">"Premium at $"&amp;TEXT(Assumptions!B69,"0.00")&amp;". Launch discount no deeper than the realized-price factor on Assumptions."</f>
@@ -8800,10 +8803,10 @@
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C17" s="27" t="s">
         <v>843</v>
@@ -8817,7 +8820,7 @@
         <v>833</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C18" s="58" t="s">
         <v>851</v>
@@ -8828,10 +8831,10 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C19" s="27" t="s">
         <v>855</v>
@@ -8842,10 +8845,10 @@
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C20" s="58" t="s">
         <v>855</v>
@@ -8856,10 +8859,10 @@
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C21" s="27" t="s">
         <v>855</v>
@@ -8870,10 +8873,10 @@
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="58" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C22" s="58" t="s">
         <v>858</v>
@@ -8922,7 +8925,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8930,16 +8933,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8947,13 +8950,13 @@
         <v>46311</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8961,13 +8964,13 @@
         <v>46311</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8975,13 +8978,13 @@
         <v>46311</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8992,10 +8995,10 @@
         <v>893</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9003,13 +9006,13 @@
         <v>46311</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9020,10 +9023,10 @@
         <v>53</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9031,13 +9034,13 @@
         <v>46311</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9048,10 +9051,10 @@
         <v>372</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9059,13 +9062,13 @@
         <v>46311</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9073,13 +9076,13 @@
         <v>46311</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9090,10 +9093,10 @@
         <v>58</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9101,13 +9104,13 @@
         <v>46311</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9118,10 +9121,10 @@
         <v>62</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9132,10 +9135,10 @@
         <v>406</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9146,10 +9149,10 @@
         <v>682</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9157,13 +9160,13 @@
         <v>46311</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
   </sheetData>
@@ -10500,7 +10503,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="42" t="s">
         <v>278</v>
       </c>
@@ -10511,7 +10514,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="50" t="s">
         <v>280</v>
       </c>
@@ -14527,7 +14530,7 @@
         <v>775</v>
       </c>
       <c r="I63" s="69" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="J63" s="27" t="s">
         <v>797</v>

--- a/docs/Vinland_Game_Development_Plan.xlsx
+++ b/docs/Vinland_Game_Development_Plan.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="1167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="1197">
   <si>
     <t xml:space="preserve">VINLAND</t>
   </si>
@@ -889,7 +889,7 @@
     <t xml:space="preserve">Hay cut per worker-day (units)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hay, from 1 August</t>
+    <t xml:space="preserve">Hay, 1 August to mid-October</t>
   </si>
   <si>
     <t xml:space="preserve">First hay day (day of year)</t>
@@ -916,10 +916,10 @@
     <t xml:space="preserve">Tend the sick</t>
   </si>
   <si>
-    <t xml:space="preserve">Slice ends (day of year)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical slice runs to 1 September</t>
+    <t xml:space="preserve">Camp build ends (day of year, second year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This build ends at the second spring; the return voyage comes in Alpha</t>
   </si>
   <si>
     <t xml:space="preserve">Booth plots at the camp</t>
@@ -932,6 +932,96 @@
   </si>
   <si>
     <t xml:space="preserve">Build queue: the hall that gets the camp through winter (F17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First snow (day of year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter: 1 November. Forage closes, fishing and building slow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spring thaw (day of year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter ends: 20 April</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forage and hay season ends (day of year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid-October</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drying per worker-day (person-days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoke rack: surplus fresh fish becomes stores (F15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dried fish yield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of person-days kept when fish is dried</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter shore fishing factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice and short days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter building factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frozen ground, short days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter milk factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cows dry off in winter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter sickness factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Booth shelter in winter (share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Booths are summer shelter; the longhouse holds everyone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsheltered winter sickness multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter exposure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Death chance per exposed sick person-day in winter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold kills the sick without a roof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hay per head of cattle per winter day (units)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A sheep eats the sheep fodder share of this</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hay needed without a byre (multiplier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cattle out in the cold eat more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work to raise the byre (builder-days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build queue after the longhouse (F17)</t>
   </si>
   <si>
     <t xml:space="preserve">Pillars, fantasy, clocks, and the win</t>
@@ -4791,11 +4881,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="98654844"/>
-        <c:axId val="96776336"/>
+        <c:axId val="22413173"/>
+        <c:axId val="37001983"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="98654844"/>
+        <c:axId val="22413173"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4827,7 +4917,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96776336"/>
+        <c:crossAx val="37001983"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4835,7 +4925,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="96776336"/>
+        <c:axId val="37001983"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4911,7 +5001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98654844"/>
+        <c:crossAx val="22413173"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4950,9 +5040,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>743760</xdr:colOff>
+      <xdr:colOff>743400</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>60120</xdr:rowOff>
+      <xdr:rowOff>59760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4961,7 +5051,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="6562800"/>
-        <a:ext cx="5395680" cy="2155680"/>
+        <a:ext cx="5395320" cy="2155320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6043,7 +6133,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -6055,10 +6145,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>871</v>
+        <v>901</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>872</v>
+        <v>902</v>
       </c>
       <c r="C4" s="57" t="s">
         <v>96</v>
@@ -6079,7 +6169,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="57" t="s">
-        <v>873</v>
+        <v>903</v>
       </c>
       <c r="J4" s="57" t="s">
         <v>7</v>
@@ -6087,7 +6177,7 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="B5" s="89" t="n">
         <f aca="false">Assumptions!B26</f>
@@ -6122,7 +6212,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="B6" s="89" t="n">
         <f aca="false">Assumptions!B27</f>
@@ -6157,7 +6247,7 @@
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="B7" s="89" t="n">
         <f aca="false">Assumptions!B28</f>
@@ -6192,7 +6282,7 @@
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>731</v>
+        <v>761</v>
       </c>
       <c r="B8" s="89" t="n">
         <f aca="false">Assumptions!B29</f>
@@ -6227,7 +6317,7 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="B9" s="89" t="n">
         <f aca="false">Assumptions!B30</f>
@@ -6297,10 +6387,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="71" t="s">
-        <v>874</v>
+        <v>904</v>
       </c>
       <c r="B11" s="71" t="s">
-        <v>875</v>
+        <v>905</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -6337,10 +6427,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="71" t="s">
-        <v>876</v>
+        <v>906</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>877</v>
+        <v>907</v>
       </c>
       <c r="C12" s="62" t="n">
         <f aca="false">IF(Assumptions!B16=0,0,C11/Assumptions!B16)</f>
@@ -6373,7 +6463,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>878</v>
+        <v>908</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -6388,28 +6478,28 @@
         <v>5</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>879</v>
+        <v>909</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>731</v>
+        <v>761</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>100</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>873</v>
+        <v>903</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>7</v>
@@ -6669,7 +6759,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>880</v>
+        <v>910</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -6686,7 +6776,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="50" t="s">
-        <v>881</v>
+        <v>911</v>
       </c>
       <c r="B22" s="50"/>
       <c r="C22" s="50"/>
@@ -6706,7 +6796,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="50" t="s">
-        <v>882</v>
+        <v>912</v>
       </c>
       <c r="B23" s="50"/>
       <c r="C23" s="50"/>
@@ -6723,7 +6813,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="50" t="s">
-        <v>883</v>
+        <v>913</v>
       </c>
       <c r="B24" s="50"/>
       <c r="C24" s="50"/>
@@ -6791,7 +6881,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="50" t="s">
-        <v>884</v>
+        <v>914</v>
       </c>
       <c r="B28" s="50"/>
       <c r="C28" s="50"/>
@@ -6808,7 +6898,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>885</v>
+        <v>915</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
@@ -6845,7 +6935,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="66" t="s">
-        <v>886</v>
+        <v>916</v>
       </c>
       <c r="B31" s="66"/>
       <c r="C31" s="66"/>
@@ -6863,12 +6953,12 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="71" t="s">
-        <v>887</v>
+        <v>917</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="95" t="s">
-        <v>888</v>
+        <v>918</v>
       </c>
       <c r="B34" s="95"/>
       <c r="C34" s="95"/>
@@ -6882,7 +6972,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>880</v>
+        <v>910</v>
       </c>
       <c r="B35" s="90" t="n">
         <f aca="false">J21</f>
@@ -6891,7 +6981,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>889</v>
+        <v>919</v>
       </c>
       <c r="B36" s="90" t="n">
         <f aca="false">J31</f>
@@ -6900,7 +6990,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>890</v>
+        <v>920</v>
       </c>
       <c r="B37" s="90" t="n">
         <f aca="false">SUM(J22:J28)*(1+I30)</f>
@@ -6952,7 +7042,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>891</v>
+        <v>921</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -6961,7 +7051,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>892</v>
+        <v>922</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -6976,7 +7066,7 @@
         <v>42</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>463</v>
+        <v>493</v>
       </c>
       <c r="D5" s="29"/>
       <c r="E5" s="29"/>
@@ -6990,28 +7080,28 @@
         <v>19.99</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>893</v>
+        <v>923</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>894</v>
+        <v>924</v>
       </c>
       <c r="B7" s="97" t="n">
         <f aca="false">B6*Assumptions!B70</f>
         <v>15.992</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>895</v>
+        <v>925</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>896</v>
+        <v>926</v>
       </c>
       <c r="B8" s="97" t="n">
         <f aca="false">B7*(1-Assumptions!B71)</f>
@@ -7023,35 +7113,35 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>897</v>
+        <v>927</v>
       </c>
       <c r="B9" s="74" t="n">
         <f aca="false">Assumptions!B72*(1-Assumptions!B74)+Assumptions!B73*Assumptions!B74</f>
         <v>0.29</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>898</v>
+        <v>928</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>899</v>
+        <v>929</v>
       </c>
       <c r="B10" s="98" t="n">
         <f aca="false">B8*(1-B9)</f>
         <v>10.4459744</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>900</v>
+        <v>930</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>901</v>
+        <v>931</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -7066,7 +7156,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>463</v>
+        <v>493</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="29"/>
@@ -7080,70 +7170,70 @@
         <v>460504.8</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>902</v>
+        <v>932</v>
       </c>
       <c r="D14" s="33"/>
       <c r="E14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="66" t="s">
-        <v>903</v>
+        <v>933</v>
       </c>
       <c r="B15" s="99" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B14/B10,0))</f>
         <v>44085</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>904</v>
+        <v>934</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>905</v>
+        <v>935</v>
       </c>
       <c r="B16" s="89" t="n">
         <f aca="false">TeamBudget!B37</f>
         <v>98632.8</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>906</v>
+        <v>936</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="66" t="s">
-        <v>907</v>
+        <v>937</v>
       </c>
       <c r="B17" s="99" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B16/B10,0))</f>
         <v>9443</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>908</v>
+        <v>938</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>909</v>
+        <v>939</v>
       </c>
       <c r="B18" s="90" t="n">
         <f aca="false">B15*B6</f>
         <v>881259.15</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>910</v>
+        <v>940</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>911</v>
+        <v>941</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -7152,19 +7242,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>912</v>
+        <v>942</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>913</v>
+        <v>943</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>914</v>
+        <v>944</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>915</v>
+        <v>945</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>825</v>
+        <v>855</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7279,7 +7369,7 @@
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="54" t="s">
-        <v>916</v>
+        <v>946</v>
       </c>
       <c r="B28" s="54"/>
       <c r="C28" s="54"/>
@@ -7361,7 +7451,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>917</v>
+        <v>947</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7373,195 +7463,195 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>835</v>
+        <v>865</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>918</v>
+        <v>948</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>919</v>
+        <v>949</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>920</v>
+        <v>950</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>619</v>
+        <v>649</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>921</v>
+        <v>951</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>922</v>
+        <v>952</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>839</v>
+        <v>869</v>
       </c>
       <c r="B5" s="86" t="n">
         <f aca="false">Schedule!D5</f>
         <v>46383</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>923</v>
+        <v>953</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>924</v>
+        <v>954</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="F5" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>925</v>
+        <v>955</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>926</v>
+        <v>956</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>843</v>
+        <v>873</v>
       </c>
       <c r="B6" s="86" t="n">
         <f aca="false">Schedule!D6</f>
         <v>46453</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>927</v>
+        <v>957</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>928</v>
+        <v>958</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>929</v>
+        <v>959</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>930</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>847</v>
+        <v>877</v>
       </c>
       <c r="B7" s="86" t="n">
         <f aca="false">Schedule!D7</f>
         <v>46579</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>931</v>
+        <v>961</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>932</v>
+        <v>962</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="F7" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>933</v>
+        <v>963</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>934</v>
+        <v>964</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>851</v>
+        <v>881</v>
       </c>
       <c r="B8" s="86" t="n">
         <f aca="false">Schedule!D8</f>
         <v>46621</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>935</v>
+        <v>965</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>936</v>
+        <v>966</v>
       </c>
       <c r="E8" s="58" t="s">
         <v>100</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>937</v>
+        <v>967</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>938</v>
+        <v>968</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>855</v>
+        <v>885</v>
       </c>
       <c r="B9" s="86" t="n">
         <f aca="false">Schedule!D9</f>
         <v>46663</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>939</v>
+        <v>969</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>940</v>
+        <v>970</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="F9" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>941</v>
+        <v>971</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>942</v>
+        <v>972</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>858</v>
+        <v>888</v>
       </c>
       <c r="B10" s="86" t="n">
         <f aca="false">Schedule!D10</f>
         <v>46691</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>943</v>
+        <v>973</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>944</v>
+        <v>974</v>
       </c>
       <c r="E10" s="58" t="s">
         <v>100</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>945</v>
+        <v>975</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>946</v>
+        <v>976</v>
       </c>
       <c r="B12" s="54"/>
       <c r="C12" s="54"/>
@@ -7641,7 +7731,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>947</v>
+        <v>977</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7655,31 +7745,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>948</v>
+        <v>978</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>949</v>
+        <v>979</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>951</v>
+        <v>981</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>619</v>
+        <v>649</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>952</v>
+        <v>982</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>953</v>
+        <v>983</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>44</v>
@@ -7687,10 +7777,10 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="58" t="s">
-        <v>954</v>
+        <v>984</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>955</v>
+        <v>985</v>
       </c>
       <c r="C5" s="43" t="n">
         <v>3</v>
@@ -7703,27 +7793,27 @@
         <v>15</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>956</v>
+        <v>986</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="H5" s="58" t="s">
-        <v>843</v>
+        <v>873</v>
       </c>
       <c r="I5" s="58" t="s">
-        <v>957</v>
+        <v>987</v>
       </c>
       <c r="J5" s="69" t="s">
-        <v>958</v>
+        <v>988</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>959</v>
+        <v>989</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>960</v>
+        <v>990</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>3</v>
@@ -7736,27 +7826,27 @@
         <v>12</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>961</v>
+        <v>991</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>843</v>
+        <v>873</v>
       </c>
       <c r="I6" s="58" t="s">
-        <v>962</v>
+        <v>992</v>
       </c>
       <c r="J6" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="58" t="s">
-        <v>964</v>
+        <v>994</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>965</v>
+        <v>995</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>2</v>
@@ -7769,27 +7859,27 @@
         <v>8</v>
       </c>
       <c r="F7" s="58" t="s">
-        <v>966</v>
+        <v>996</v>
       </c>
       <c r="G7" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="H7" s="58" t="s">
-        <v>855</v>
+        <v>885</v>
       </c>
       <c r="I7" s="58" t="s">
-        <v>967</v>
+        <v>997</v>
       </c>
       <c r="J7" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>968</v>
+        <v>998</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>969</v>
+        <v>999</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>4</v>
@@ -7802,27 +7892,27 @@
         <v>12</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>847</v>
+        <v>877</v>
       </c>
       <c r="I8" s="58" t="s">
-        <v>971</v>
+        <v>1001</v>
       </c>
       <c r="J8" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="58" t="s">
-        <v>972</v>
+        <v>1002</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>973</v>
+        <v>1003</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>2</v>
@@ -7835,27 +7925,27 @@
         <v>6</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>974</v>
+        <v>1004</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>847</v>
+        <v>877</v>
       </c>
       <c r="I9" s="58" t="s">
-        <v>975</v>
+        <v>1005</v>
       </c>
       <c r="J9" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>976</v>
+        <v>1006</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>977</v>
+        <v>1007</v>
       </c>
       <c r="C10" s="43" t="n">
         <v>2</v>
@@ -7868,27 +7958,27 @@
         <v>10</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>978</v>
+        <v>1008</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>847</v>
+        <v>877</v>
       </c>
       <c r="I10" s="58" t="s">
-        <v>979</v>
+        <v>1009</v>
       </c>
       <c r="J10" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="58" t="s">
-        <v>980</v>
+        <v>1010</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="C11" s="43" t="n">
         <v>3</v>
@@ -7901,27 +7991,27 @@
         <v>12</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>982</v>
+        <v>1012</v>
       </c>
       <c r="G11" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H11" s="58" t="s">
-        <v>851</v>
+        <v>881</v>
       </c>
       <c r="I11" s="58" t="s">
-        <v>983</v>
+        <v>1013</v>
       </c>
       <c r="J11" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>984</v>
+        <v>1014</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>985</v>
+        <v>1015</v>
       </c>
       <c r="C12" s="43" t="n">
         <v>2</v>
@@ -7934,27 +8024,27 @@
         <v>8</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>986</v>
+        <v>1016</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>839</v>
+        <v>869</v>
       </c>
       <c r="I12" s="58" t="s">
-        <v>987</v>
+        <v>1017</v>
       </c>
       <c r="J12" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="58" t="s">
-        <v>988</v>
+        <v>1018</v>
       </c>
       <c r="B13" s="58" t="s">
-        <v>989</v>
+        <v>1019</v>
       </c>
       <c r="C13" s="43" t="n">
         <v>2</v>
@@ -7967,27 +8057,27 @@
         <v>4</v>
       </c>
       <c r="F13" s="58" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="G13" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="H13" s="58" t="s">
-        <v>839</v>
+        <v>869</v>
       </c>
       <c r="I13" s="58" t="s">
-        <v>991</v>
+        <v>1021</v>
       </c>
       <c r="J13" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>992</v>
+        <v>1022</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>993</v>
+        <v>1023</v>
       </c>
       <c r="C14" s="43" t="n">
         <v>3</v>
@@ -8000,27 +8090,27 @@
         <v>12</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>994</v>
+        <v>1024</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>851</v>
+        <v>881</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>995</v>
+        <v>1025</v>
       </c>
       <c r="J14" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="58" t="s">
-        <v>996</v>
+        <v>1026</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>997</v>
+        <v>1027</v>
       </c>
       <c r="C15" s="43" t="n">
         <v>3</v>
@@ -8033,27 +8123,27 @@
         <v>15</v>
       </c>
       <c r="F15" s="58" t="s">
-        <v>998</v>
+        <v>1028</v>
       </c>
       <c r="G15" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="H15" s="58" t="s">
-        <v>847</v>
+        <v>877</v>
       </c>
       <c r="I15" s="58" t="s">
-        <v>999</v>
+        <v>1029</v>
       </c>
       <c r="J15" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>1001</v>
+        <v>1031</v>
       </c>
       <c r="C16" s="43" t="n">
         <v>4</v>
@@ -8066,27 +8156,27 @@
         <v>16</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>1002</v>
+        <v>1032</v>
       </c>
       <c r="G16" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>843</v>
+        <v>873</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>1003</v>
+        <v>1033</v>
       </c>
       <c r="J16" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="58" t="s">
-        <v>1004</v>
+        <v>1034</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>1005</v>
+        <v>1035</v>
       </c>
       <c r="C17" s="43" t="n">
         <v>3</v>
@@ -8099,27 +8189,27 @@
         <v>12</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>1006</v>
+        <v>1036</v>
       </c>
       <c r="G17" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="58" t="s">
-        <v>847</v>
+        <v>877</v>
       </c>
       <c r="I17" s="58" t="s">
-        <v>1007</v>
+        <v>1037</v>
       </c>
       <c r="J17" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>1008</v>
+        <v>1038</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>1009</v>
+        <v>1039</v>
       </c>
       <c r="C18" s="43" t="n">
         <v>2</v>
@@ -8132,27 +8222,27 @@
         <v>6</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>1010</v>
+        <v>1040</v>
       </c>
       <c r="G18" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="H18" s="58" t="s">
-        <v>855</v>
+        <v>885</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>1011</v>
+        <v>1041</v>
       </c>
       <c r="J18" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="58" t="s">
-        <v>1012</v>
+        <v>1042</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>1013</v>
+        <v>1043</v>
       </c>
       <c r="C19" s="43" t="n">
         <v>2</v>
@@ -8165,27 +8255,27 @@
         <v>8</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>1014</v>
+        <v>1044</v>
       </c>
       <c r="G19" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="H19" s="58" t="s">
-        <v>847</v>
+        <v>877</v>
       </c>
       <c r="I19" s="58" t="s">
-        <v>1015</v>
+        <v>1045</v>
       </c>
       <c r="J19" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>1016</v>
+        <v>1046</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1017</v>
+        <v>1047</v>
       </c>
       <c r="C20" s="43" t="n">
         <v>3</v>
@@ -8198,19 +8288,19 @@
         <v>15</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>1018</v>
+        <v>1048</v>
       </c>
       <c r="G20" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H20" s="58" t="s">
-        <v>843</v>
+        <v>873</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>1019</v>
+        <v>1049</v>
       </c>
       <c r="J20" s="69" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
     </row>
   </sheetData>
@@ -8288,7 +8378,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1020</v>
+        <v>1050</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8299,278 +8389,278 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>1021</v>
+        <v>1051</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1022</v>
+        <v>1052</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>1023</v>
+        <v>1053</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>1024</v>
+        <v>1054</v>
       </c>
       <c r="E4" s="57" t="s">
         <v>95</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>619</v>
+        <v>649</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1025</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1026</v>
+        <v>1056</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1027</v>
+        <v>1057</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1028</v>
+        <v>1058</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1029</v>
+        <v>1059</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>1030</v>
+        <v>1060</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1031</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1032</v>
+        <v>1062</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1033</v>
+        <v>1063</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>1034</v>
+        <v>1064</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>1035</v>
+        <v>1065</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>1036</v>
+        <v>1066</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>1037</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1038</v>
+        <v>1068</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1039</v>
+        <v>1069</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1040</v>
+        <v>1070</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1041</v>
+        <v>1071</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>1042</v>
+        <v>1072</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1037</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>1043</v>
+        <v>1073</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>1044</v>
+        <v>1074</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>1045</v>
+        <v>1075</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>1046</v>
+        <v>1076</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>1047</v>
+        <v>1077</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>1048</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1049</v>
+        <v>1079</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1050</v>
+        <v>1080</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1051</v>
+        <v>1081</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1052</v>
+        <v>1082</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1053</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>667</v>
+        <v>697</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1054</v>
+        <v>1084</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>1055</v>
+        <v>1085</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>789</v>
+        <v>819</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>1056</v>
+        <v>1086</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>1057</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>731</v>
+        <v>761</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1058</v>
+        <v>1088</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1059</v>
+        <v>1089</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1060</v>
+        <v>1090</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>1061</v>
+        <v>1091</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>731</v>
+        <v>761</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>1062</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1063</v>
+        <v>1093</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>1064</v>
+        <v>1094</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>1065</v>
+        <v>1095</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>1066</v>
+        <v>1096</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>1037</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>661</v>
+      </c>
+      <c r="G13" s="27" t="s">
         <v>1067</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>1070</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>1071</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>631</v>
-      </c>
-      <c r="G13" s="27" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1072</v>
+        <v>1102</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1073</v>
+        <v>1103</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1074</v>
+        <v>1104</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>1075</v>
+        <v>1105</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>1076</v>
+        <v>1106</v>
       </c>
       <c r="F14" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>1077</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1078</v>
+        <v>1108</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1079</v>
+        <v>1109</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1080</v>
+        <v>1110</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1081</v>
+        <v>1111</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>1082</v>
+        <v>1112</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>1083</v>
+        <v>1113</v>
       </c>
     </row>
   </sheetData>
@@ -8612,7 +8702,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1084</v>
+        <v>1114</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8623,24 +8713,24 @@
         <v>110</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1085</v>
+        <v>1115</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>1086</v>
+        <v>1116</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>619</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1087</v>
+        <v>1117</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1088</v>
+        <v>1118</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>839</v>
+        <v>869</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>100</v>
@@ -8648,55 +8738,55 @@
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>1089</v>
+        <v>1119</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1090</v>
+        <v>1120</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1091</v>
+        <v>1121</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1092</v>
+        <v>1122</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1093</v>
+        <v>1123</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>847</v>
+        <v>877</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>1094</v>
+        <v>1124</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>1095</v>
+        <v>1125</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>843</v>
+        <v>873</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1096</v>
+        <v>1126</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1097</v>
+        <v>1127</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>839</v>
+        <v>869</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>100</v>
@@ -8704,27 +8794,27 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>1098</v>
+        <v>1128</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1099</v>
+        <v>1129</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>847</v>
+        <v>877</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>1100</v>
+        <v>1130</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1101</v>
+        <v>1131</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>855</v>
+        <v>885</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>100</v>
@@ -8732,13 +8822,13 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>1102</v>
+        <v>1132</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1103</v>
+        <v>1133</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>858</v>
+        <v>888</v>
       </c>
       <c r="D12" s="58" t="s">
         <v>100</v>
@@ -8746,41 +8836,41 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1104</v>
+        <v>1134</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1105</v>
+        <v>1135</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>858</v>
+        <v>888</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>786</v>
+        <v>816</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1106</v>
+        <v>1136</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1107</v>
+        <v>1137</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1108</v>
+        <v>1138</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1109</v>
+        <v>1139</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1110</v>
+        <v>1140</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>843</v>
+        <v>873</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>100</v>
@@ -8788,14 +8878,14 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>1111</v>
+        <v>1141</v>
       </c>
       <c r="B16" s="58" t="str">
         <f aca="false">"Premium at $"&amp;TEXT(Assumptions!B69,"0.00")&amp;". Launch discount no deeper than the realized-price factor on Assumptions."</f>
         <v>Premium at $19.99. Launch discount no deeper than the realized-price factor on Assumptions.</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>851</v>
+        <v>881</v>
       </c>
       <c r="D16" s="58" t="s">
         <v>100</v>
@@ -8803,13 +8893,13 @@
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>1112</v>
+        <v>1142</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1113</v>
+        <v>1143</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>843</v>
+        <v>873</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>100</v>
@@ -8817,13 +8907,13 @@
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>833</v>
+        <v>863</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>1114</v>
+        <v>1144</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>851</v>
+        <v>881</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>100</v>
@@ -8831,27 +8921,27 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1115</v>
+        <v>1145</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1116</v>
+        <v>1146</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>855</v>
+        <v>885</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>1117</v>
+        <v>1147</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1118</v>
+        <v>1148</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>855</v>
+        <v>885</v>
       </c>
       <c r="D20" s="58" t="s">
         <v>100</v>
@@ -8859,27 +8949,27 @@
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>1119</v>
+        <v>1149</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1120</v>
+        <v>1150</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>855</v>
+        <v>885</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="58" t="s">
-        <v>1121</v>
+        <v>1151</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>1122</v>
+        <v>1152</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>858</v>
+        <v>888</v>
       </c>
       <c r="D22" s="58" t="s">
         <v>100</v>
@@ -8925,7 +9015,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1123</v>
+        <v>1153</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8933,16 +9023,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1124</v>
+        <v>1154</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1125</v>
+        <v>1155</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1126</v>
+        <v>1156</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1127</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8950,13 +9040,13 @@
         <v>46311</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1128</v>
+        <v>1158</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1129</v>
+        <v>1159</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8964,13 +9054,13 @@
         <v>46311</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1128</v>
+        <v>1158</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>1132</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8978,13 +9068,13 @@
         <v>46311</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1128</v>
+        <v>1158</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1133</v>
+        <v>1163</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1134</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8992,13 +9082,13 @@
         <v>46311</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>893</v>
+        <v>923</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>1135</v>
+        <v>1165</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>1136</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9006,13 +9096,13 @@
         <v>46311</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1137</v>
+        <v>1167</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1138</v>
+        <v>1168</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1139</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9023,10 +9113,10 @@
         <v>53</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>1140</v>
+        <v>1170</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>1141</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9034,13 +9124,13 @@
         <v>46311</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1142</v>
+        <v>1172</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9048,13 +9138,13 @@
         <v>46311</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>1146</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9062,13 +9152,13 @@
         <v>46311</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1147</v>
+        <v>1177</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1148</v>
+        <v>1178</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1149</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9076,13 +9166,13 @@
         <v>46311</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1150</v>
+        <v>1180</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1151</v>
+        <v>1181</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>1152</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9093,10 +9183,10 @@
         <v>58</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1153</v>
+        <v>1183</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1154</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9104,13 +9194,13 @@
         <v>46311</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>1155</v>
+        <v>1185</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>1156</v>
+        <v>1186</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>1157</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9121,10 +9211,10 @@
         <v>62</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1158</v>
+        <v>1188</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1159</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9132,13 +9222,13 @@
         <v>46311</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>406</v>
+        <v>436</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>1160</v>
+        <v>1190</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>1161</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9146,13 +9236,13 @@
         <v>46311</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>682</v>
+        <v>712</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1162</v>
+        <v>1192</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9160,13 +9250,13 @@
         <v>46311</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>1165</v>
+        <v>1195</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>1166</v>
+        <v>1196</v>
       </c>
     </row>
   </sheetData>
@@ -9190,7 +9280,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
@@ -10442,7 +10532,7 @@
         <v>266</v>
       </c>
       <c r="B130" s="51" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="C130" s="41" t="s">
         <v>267</v>
@@ -10497,7 +10587,7 @@
         <v>276</v>
       </c>
       <c r="B135" s="43" t="n">
-        <v>244</v>
+        <v>145</v>
       </c>
       <c r="C135" s="41" t="s">
         <v>277</v>
@@ -10523,6 +10613,171 @@
       </c>
       <c r="C137" s="41" t="s">
         <v>281</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="B138" s="43" t="n">
+        <v>305</v>
+      </c>
+      <c r="C138" s="41" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="42" t="s">
+        <v>284</v>
+      </c>
+      <c r="B139" s="43" t="n">
+        <v>110</v>
+      </c>
+      <c r="C139" s="41" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="50" t="s">
+        <v>286</v>
+      </c>
+      <c r="B140" s="43" t="n">
+        <v>290</v>
+      </c>
+      <c r="C140" s="41" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="B141" s="43" t="n">
+        <v>15</v>
+      </c>
+      <c r="C141" s="41" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="B142" s="51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C142" s="41" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="42" t="s">
+        <v>292</v>
+      </c>
+      <c r="B143" s="51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C143" s="41" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="B144" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C144" s="41" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="42" t="s">
+        <v>296</v>
+      </c>
+      <c r="B145" s="51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C145" s="41" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="50" t="s">
+        <v>298</v>
+      </c>
+      <c r="B146" s="51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C146" s="41" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="B147" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C147" s="41" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="B148" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C148" s="41" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="42" t="s">
+        <v>304</v>
+      </c>
+      <c r="B149" s="51" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C149" s="41" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="50" t="s">
+        <v>306</v>
+      </c>
+      <c r="B150" s="51" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C150" s="41" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="42" t="s">
+        <v>308</v>
+      </c>
+      <c r="B151" s="51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C151" s="41" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="50" t="s">
+        <v>310</v>
+      </c>
+      <c r="B152" s="43" t="n">
+        <v>160</v>
+      </c>
+      <c r="C152" s="41" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -10588,7 +10843,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -10597,160 +10852,160 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -10759,16 +11014,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>95</v>
@@ -10776,58 +11031,58 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="E16" s="59" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="58" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="E17" s="58" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="24"/>
@@ -10836,87 +11091,87 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="58" t="s">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="C23" s="58" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="D23" s="58" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="E23" s="58" t="s">
-        <v>356</v>
+        <v>386</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>361</v>
+        <v>391</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="58" t="s">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="B25" s="58" t="s">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="C25" s="58" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="D25" s="58" t="s">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="E25" s="58" t="s">
-        <v>365</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -10969,7 +11224,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>366</v>
+        <v>396</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -10980,33 +11235,33 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="F4" s="57" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>373</v>
+        <v>403</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>134</v>
@@ -11016,37 +11271,37 @@
         <v>24</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>377</v>
+        <v>407</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>378</v>
+        <v>408</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="D6" s="60" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="F6" s="58" t="s">
         <v>98</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11054,71 +11309,71 @@
         <v>228</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
       <c r="D7" s="60" t="n">
         <f aca="false">Assumptions!B44</f>
         <v>120</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>384</v>
+        <v>414</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>385</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>387</v>
+        <v>417</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="D8" s="60" t="n">
         <f aca="false">Assumptions!B46</f>
         <v>400</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
       <c r="F8" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
       <c r="D9" s="60" t="n">
         <f aca="false">Assumptions!B45</f>
         <v>120</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>394</v>
+        <v>424</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11126,151 +11381,151 @@
         <v>219</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="F10" s="58" t="s">
         <v>98</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>402</v>
+        <v>432</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>403</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>405</v>
+        <v>435</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>406</v>
+        <v>436</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>407</v>
+        <v>437</v>
       </c>
       <c r="F12" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>409</v>
+        <v>439</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>410</v>
+        <v>440</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>411</v>
+        <v>441</v>
       </c>
       <c r="D13" s="60" t="n">
         <f aca="false">Assumptions!B43</f>
         <v>168</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>413</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>414</v>
+        <v>444</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>416</v>
+        <v>446</v>
       </c>
       <c r="D14" s="60" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>417</v>
+        <v>447</v>
       </c>
       <c r="F14" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>419</v>
+        <v>449</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="D15" s="60" t="n">
         <f aca="false">Assumptions!B50</f>
         <v>5</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>423</v>
+        <v>453</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="D16" s="60" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -11283,78 +11538,78 @@
         <v>102</v>
       </c>
       <c r="G16" s="58" t="s">
-        <v>427</v>
+        <v>457</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="D17" s="60" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>431</v>
+        <v>461</v>
       </c>
       <c r="F17" s="27" t="s">
         <v>102</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>432</v>
+        <v>462</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="F18" s="58" t="s">
         <v>104</v>
       </c>
       <c r="G18" s="58" t="s">
-        <v>436</v>
+        <v>466</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>437</v>
+        <v>467</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>438</v>
+        <v>468</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="D19" s="60" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="F19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>441</v>
+        <v>471</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11362,46 +11617,46 @@
         <v>224</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="F20" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G20" s="58" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="D21" s="60" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>447</v>
+        <v>477</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11409,55 +11664,55 @@
         <v>236</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="D22" s="60" t="n">
         <f aca="false">Assumptions!B57</f>
         <v>2</v>
       </c>
       <c r="E22" s="58" t="s">
-        <v>451</v>
+        <v>481</v>
       </c>
       <c r="F22" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G22" s="58" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>454</v>
+        <v>484</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>416</v>
+        <v>446</v>
       </c>
       <c r="D23" s="60" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>456</v>
+        <v>486</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="58" t="s">
-        <v>457</v>
+        <v>487</v>
       </c>
       <c r="B24" s="58" t="s">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="C24" s="58" t="s">
         <v>134</v>
@@ -11467,13 +11722,13 @@
         <v>24</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="F24" s="58" t="s">
         <v>98</v>
       </c>
       <c r="G24" s="58" t="s">
-        <v>460</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -11519,7 +11774,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>461</v>
+        <v>491</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11528,7 +11783,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -11543,21 +11798,21 @@
         <v>42</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>463</v>
+        <v>493</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="B6" s="61" t="n">
         <f aca="false">Assumptions!B62</f>
         <v>1200</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>465</v>
+        <v>495</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
@@ -11571,21 +11826,21 @@
         <v>120</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>466</v>
+        <v>496</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="B8" s="62" t="n">
         <f aca="false">IF(B7=0,0,B6/B7)</f>
         <v>10</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="33"/>
@@ -11599,7 +11854,7 @@
         <v>1.3</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
@@ -11613,14 +11868,14 @@
         <v>13</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>471</v>
+        <v>501</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -11629,24 +11884,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>472</v>
+        <v>502</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>473</v>
+        <v>503</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>475</v>
+        <v>505</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="B14" s="60" t="n">
         <f aca="false">Assumptions!B42</f>
@@ -11661,12 +11916,12 @@
         <v>9.6</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>477</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="B15" s="60" t="n">
         <f aca="false">Assumptions!B57</f>
@@ -11681,12 +11936,12 @@
         <v>3</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>479</v>
+        <v>509</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="B16" s="60" t="n">
         <f aca="false">Assumptions!B58</f>
@@ -11704,7 +11959,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="B17" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B43,0)</f>
@@ -11718,12 +11973,12 @@
         <v>2</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>481</v>
+        <v>511</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="B18" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B44,0)</f>
@@ -11737,12 +11992,12 @@
         <v>3</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>483</v>
+        <v>513</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>484</v>
+        <v>514</v>
       </c>
       <c r="B19" s="32" t="n">
         <f aca="false">ROUNDUP((B15+B16*Assumptions!B60)*$B$10/Assumptions!B59,0)</f>
@@ -11756,12 +12011,12 @@
         <v>2</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>485</v>
+        <v>515</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>486</v>
+        <v>516</v>
       </c>
       <c r="B20" s="60" t="n">
         <f aca="false">Assumptions!B61</f>
@@ -11780,7 +12035,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -11792,7 +12047,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>488</v>
+        <v>518</v>
       </c>
       <c r="D22" s="64" t="n">
         <f aca="false">Assumptions!B41</f>
@@ -11801,7 +12056,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="66" t="s">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
@@ -11816,7 +12071,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -11825,24 +12080,24 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>472</v>
+        <v>502</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>473</v>
+        <v>503</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>475</v>
+        <v>505</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>491</v>
+        <v>521</v>
       </c>
       <c r="B27" s="60" t="n">
         <f aca="false">Assumptions!B64</f>
@@ -11862,7 +12117,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="58" t="s">
-        <v>492</v>
+        <v>522</v>
       </c>
       <c r="B28" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B43,0)</f>
@@ -11876,12 +12131,12 @@
         <v>1</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>494</v>
+        <v>524</v>
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B44,0)</f>
@@ -11898,7 +12153,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>495</v>
+        <v>525</v>
       </c>
       <c r="D30" s="62" t="n">
         <f aca="false">SUM(D27:D29)</f>
@@ -11907,7 +12162,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>496</v>
+        <v>526</v>
       </c>
       <c r="D31" s="62" t="n">
         <f aca="false">Assumptions!B41-D30</f>
@@ -11916,7 +12171,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>497</v>
+        <v>527</v>
       </c>
       <c r="D32" s="32" t="n">
         <f aca="false">INT(D31/Assumptions!B65)</f>
@@ -11925,7 +12180,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>498</v>
+        <v>528</v>
       </c>
       <c r="D33" s="60" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -11934,7 +12189,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="66" t="s">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="B34" s="66"/>
       <c r="C34" s="66"/>
@@ -11949,7 +12204,7 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="54" t="s">
-        <v>499</v>
+        <v>529</v>
       </c>
       <c r="B36" s="54"/>
       <c r="C36" s="54"/>
@@ -12030,7 +12285,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12045,392 +12300,392 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="B4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>501</v>
+        <v>531</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>503</v>
+        <v>533</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>504</v>
+        <v>534</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>505</v>
+        <v>535</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>506</v>
+        <v>536</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>507</v>
+        <v>537</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>508</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>509</v>
+        <v>539</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>511</v>
+        <v>541</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>512</v>
+        <v>542</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>513</v>
+        <v>543</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>514</v>
+        <v>544</v>
       </c>
       <c r="H5" s="69" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>515</v>
+        <v>545</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>517</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>518</v>
+        <v>548</v>
       </c>
       <c r="B6" s="58" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>519</v>
+        <v>549</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>521</v>
+        <v>551</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>522</v>
+        <v>552</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="H6" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="58" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="J6" s="58" t="s">
-        <v>525</v>
+        <v>555</v>
       </c>
       <c r="K6" s="58" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>527</v>
+        <v>557</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>528</v>
+        <v>558</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>531</v>
+        <v>561</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>532</v>
+        <v>562</v>
       </c>
       <c r="H7" s="69" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>533</v>
+        <v>563</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>534</v>
+        <v>564</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>535</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>536</v>
+        <v>566</v>
       </c>
       <c r="B8" s="58" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>537</v>
+        <v>567</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>538</v>
+        <v>568</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>539</v>
+        <v>569</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>540</v>
+        <v>570</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>541</v>
+        <v>571</v>
       </c>
       <c r="H8" s="69" t="n">
         <v>3</v>
       </c>
       <c r="I8" s="58" t="s">
-        <v>542</v>
+        <v>572</v>
       </c>
       <c r="J8" s="58" t="s">
-        <v>543</v>
+        <v>573</v>
       </c>
       <c r="K8" s="58" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>545</v>
+        <v>575</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>546</v>
+        <v>576</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>547</v>
+        <v>577</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>548</v>
+        <v>578</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>549</v>
+        <v>579</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="H9" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>552</v>
+        <v>582</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>554</v>
+        <v>584</v>
       </c>
       <c r="B10" s="58" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>555</v>
+        <v>585</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>557</v>
+        <v>587</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>558</v>
+        <v>588</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>559</v>
+        <v>589</v>
       </c>
       <c r="H10" s="69" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="58" t="s">
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="J10" s="58" t="s">
-        <v>561</v>
+        <v>591</v>
       </c>
       <c r="K10" s="58" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>563</v>
+        <v>593</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>564</v>
+        <v>594</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>565</v>
+        <v>595</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>566</v>
+        <v>596</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>568</v>
+        <v>598</v>
       </c>
       <c r="H11" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>569</v>
+        <v>599</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>570</v>
+        <v>600</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>571</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>572</v>
+        <v>602</v>
       </c>
       <c r="B12" s="58" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>573</v>
+        <v>603</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>574</v>
+        <v>604</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>575</v>
+        <v>605</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>576</v>
+        <v>606</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>577</v>
+        <v>607</v>
       </c>
       <c r="H12" s="69" t="n">
         <v>3</v>
       </c>
       <c r="I12" s="58" t="s">
-        <v>578</v>
+        <v>608</v>
       </c>
       <c r="J12" s="58" t="s">
-        <v>579</v>
+        <v>609</v>
       </c>
       <c r="K12" s="58" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>581</v>
+        <v>611</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>582</v>
+        <v>612</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>583</v>
+        <v>613</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>584</v>
+        <v>614</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>585</v>
+        <v>615</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>586</v>
+        <v>616</v>
       </c>
       <c r="H13" s="69" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>587</v>
+        <v>617</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>588</v>
+        <v>618</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>589</v>
+        <v>619</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>590</v>
+        <v>620</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>592</v>
+        <v>622</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>593</v>
+        <v>623</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>594</v>
+        <v>624</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>595</v>
+        <v>625</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>596</v>
+        <v>626</v>
       </c>
       <c r="H14" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>597</v>
+        <v>627</v>
       </c>
       <c r="J14" s="58" t="s">
-        <v>598</v>
+        <v>628</v>
       </c>
       <c r="K14" s="58" t="s">
-        <v>599</v>
+        <v>629</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
@@ -12442,10 +12697,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>601</v>
+        <v>631</v>
       </c>
       <c r="B17" s="70" t="s">
-        <v>602</v>
+        <v>632</v>
       </c>
       <c r="C17" s="70"/>
       <c r="D17" s="70"/>
@@ -12456,10 +12711,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>603</v>
+        <v>633</v>
       </c>
       <c r="B18" s="70" t="s">
-        <v>604</v>
+        <v>634</v>
       </c>
       <c r="C18" s="70"/>
       <c r="D18" s="70"/>
@@ -12470,10 +12725,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>605</v>
+        <v>635</v>
       </c>
       <c r="B19" s="70" t="s">
-        <v>606</v>
+        <v>636</v>
       </c>
       <c r="C19" s="70"/>
       <c r="D19" s="70"/>
@@ -12484,10 +12739,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>607</v>
+        <v>637</v>
       </c>
       <c r="B20" s="70" t="s">
-        <v>608</v>
+        <v>638</v>
       </c>
       <c r="C20" s="70"/>
       <c r="D20" s="70"/>
@@ -12498,10 +12753,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>609</v>
+        <v>639</v>
       </c>
       <c r="B21" s="70" t="s">
-        <v>610</v>
+        <v>640</v>
       </c>
       <c r="C21" s="70"/>
       <c r="D21" s="70"/>
@@ -12512,10 +12767,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>611</v>
+        <v>641</v>
       </c>
       <c r="B22" s="70" t="s">
-        <v>612</v>
+        <v>642</v>
       </c>
       <c r="C22" s="70"/>
       <c r="D22" s="70"/>
@@ -12526,10 +12781,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>613</v>
+        <v>643</v>
       </c>
       <c r="B23" s="70" t="s">
-        <v>614</v>
+        <v>644</v>
       </c>
       <c r="C23" s="70"/>
       <c r="D23" s="70"/>
@@ -12540,7 +12795,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="71" t="s">
-        <v>615</v>
+        <v>645</v>
       </c>
     </row>
   </sheetData>
@@ -12604,7 +12859,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>616</v>
+        <v>646</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12618,42 +12873,42 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>617</v>
+        <v>647</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>618</v>
+        <v>648</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>619</v>
+        <v>649</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>620</v>
+        <v>650</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>621</v>
+        <v>651</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>622</v>
+        <v>652</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>623</v>
+        <v>653</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>624</v>
+        <v>654</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
@@ -12662,190 +12917,190 @@
         <v>96</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G5" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="I5" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>627</v>
+        <v>657</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>628</v>
+        <v>658</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>629</v>
+        <v>659</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="D6" s="58" t="s">
         <v>96</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G6" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>623</v>
+        <v>653</v>
       </c>
       <c r="I6" s="69" t="s">
-        <v>632</v>
+        <v>662</v>
       </c>
       <c r="J6" s="58" t="s">
-        <v>633</v>
+        <v>663</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>634</v>
+        <v>664</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>635</v>
+        <v>665</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G7" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>628</v>
+        <v>658</v>
       </c>
       <c r="I7" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>636</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>637</v>
+        <v>667</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>638</v>
+        <v>668</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="D8" s="58" t="s">
         <v>96</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="G8" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="I8" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J8" s="58" t="s">
-        <v>641</v>
+        <v>671</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>642</v>
+        <v>672</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>643</v>
+        <v>673</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G9" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="I9" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>644</v>
+        <v>674</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>645</v>
+        <v>675</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>646</v>
+        <v>676</v>
       </c>
       <c r="D10" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G10" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="I10" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J10" s="58" t="s">
-        <v>647</v>
+        <v>677</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>515</v>
+        <v>545</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>648</v>
+        <v>678</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>23</v>
@@ -12854,30 +13109,30 @@
         <v>98</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G11" s="43" t="n">
         <v>12</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="I11" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>649</v>
+        <v>679</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="C12" s="58" t="s">
         <v>23</v>
@@ -12886,30 +13141,30 @@
         <v>98</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G12" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>515</v>
+        <v>545</v>
       </c>
       <c r="I12" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J12" s="58" t="s">
-        <v>651</v>
+        <v>681</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>533</v>
+        <v>563</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>652</v>
+        <v>682</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>26</v>
@@ -12918,62 +13173,62 @@
         <v>98</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G13" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="I13" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>653</v>
+        <v>683</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>654</v>
+        <v>684</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>655</v>
+        <v>685</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="D14" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G14" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="I14" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J14" s="58" t="s">
-        <v>656</v>
+        <v>686</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>569</v>
+        <v>599</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>657</v>
+        <v>687</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>35</v>
@@ -12982,263 +13237,263 @@
         <v>98</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G15" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>654</v>
+        <v>684</v>
       </c>
       <c r="I15" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J15" s="27" t="s">
-        <v>658</v>
+        <v>688</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>659</v>
+        <v>689</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="D16" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G16" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>515</v>
+        <v>545</v>
       </c>
       <c r="I16" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J16" s="58" t="s">
-        <v>661</v>
+        <v>691</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>441</v>
+        <v>471</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>662</v>
+        <v>692</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>663</v>
+        <v>693</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G17" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="I17" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>664</v>
+        <v>694</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>665</v>
+        <v>695</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>666</v>
+        <v>696</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>667</v>
+        <v>697</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="G18" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H18" s="58" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="I18" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J18" s="58" t="s">
-        <v>668</v>
+        <v>698</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>669</v>
+        <v>699</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>643</v>
+        <v>673</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G19" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="I19" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>670</v>
+        <v>700</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>671</v>
+        <v>701</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>646</v>
+        <v>676</v>
       </c>
       <c r="D20" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G20" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H20" s="58" t="s">
-        <v>515</v>
+        <v>545</v>
       </c>
       <c r="I20" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J20" s="58" t="s">
-        <v>672</v>
+        <v>702</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>673</v>
+        <v>703</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>674</v>
+        <v>704</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>675</v>
+        <v>705</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G21" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="I21" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J21" s="27" t="s">
-        <v>676</v>
+        <v>706</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="58" t="s">
-        <v>677</v>
+        <v>707</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>678</v>
+        <v>708</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="D22" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E22" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F22" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G22" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="58" t="s">
-        <v>659</v>
+        <v>689</v>
       </c>
       <c r="I22" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J22" s="58" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>680</v>
+        <v>710</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>681</v>
+        <v>711</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>682</v>
+        <v>712</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>683</v>
+        <v>713</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
@@ -13247,117 +13502,117 @@
         <v>3</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>637</v>
+        <v>667</v>
       </c>
       <c r="I23" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>684</v>
+        <v>714</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="58" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="B24" s="58" t="s">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>646</v>
+        <v>676</v>
       </c>
       <c r="D24" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F24" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G24" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H24" s="58" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="I24" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J24" s="58" t="s">
-        <v>685</v>
+        <v>715</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>597</v>
+        <v>627</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>592</v>
+        <v>622</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>646</v>
+        <v>676</v>
       </c>
       <c r="D25" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G25" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="I25" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J25" s="27" t="s">
-        <v>686</v>
+        <v>716</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="58" t="s">
-        <v>687</v>
+        <v>717</v>
       </c>
       <c r="B26" s="58" t="s">
-        <v>688</v>
+        <v>718</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>646</v>
+        <v>676</v>
       </c>
       <c r="D26" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F26" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G26" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H26" s="58" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="I26" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J26" s="58" t="s">
-        <v>689</v>
+        <v>719</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>546</v>
+        <v>576</v>
       </c>
       <c r="C27" s="27" t="s">
         <v>29</v>
@@ -13366,30 +13621,30 @@
         <v>100</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G27" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>654</v>
+        <v>684</v>
       </c>
       <c r="I27" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J27" s="27" t="s">
-        <v>690</v>
+        <v>720</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="58" t="s">
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="B28" s="58" t="s">
-        <v>691</v>
+        <v>721</v>
       </c>
       <c r="C28" s="58" t="s">
         <v>32</v>
@@ -13398,30 +13653,30 @@
         <v>100</v>
       </c>
       <c r="E28" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F28" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G28" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H28" s="58" t="s">
-        <v>654</v>
+        <v>684</v>
       </c>
       <c r="I28" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J28" s="58" t="s">
-        <v>692</v>
+        <v>722</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>542</v>
+        <v>572</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>693</v>
+        <v>723</v>
       </c>
       <c r="C29" s="27" t="s">
         <v>26</v>
@@ -13430,94 +13685,94 @@
         <v>100</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>683</v>
+        <v>713</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G29" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>533</v>
+        <v>563</v>
       </c>
       <c r="I29" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>694</v>
+        <v>724</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="58" t="s">
-        <v>587</v>
+        <v>617</v>
       </c>
       <c r="B30" s="58" t="s">
-        <v>695</v>
+        <v>725</v>
       </c>
       <c r="C30" s="58" t="s">
-        <v>643</v>
+        <v>673</v>
       </c>
       <c r="D30" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F30" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G30" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="58" t="s">
-        <v>533</v>
+        <v>563</v>
       </c>
       <c r="I30" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J30" s="58" t="s">
-        <v>696</v>
+        <v>726</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>697</v>
+        <v>727</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="D31" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G31" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="I31" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J31" s="27" t="s">
-        <v>698</v>
+        <v>728</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="58" t="s">
-        <v>699</v>
+        <v>729</v>
       </c>
       <c r="B32" s="58" t="s">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="C32" s="58" t="s">
         <v>35</v>
@@ -13526,30 +13781,30 @@
         <v>100</v>
       </c>
       <c r="E32" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F32" s="58" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="G32" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H32" s="58" t="s">
-        <v>569</v>
+        <v>599</v>
       </c>
       <c r="I32" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J32" s="58" t="s">
-        <v>701</v>
+        <v>731</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>578</v>
+        <v>608</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>702</v>
+        <v>732</v>
       </c>
       <c r="C33" s="27" t="s">
         <v>35</v>
@@ -13558,487 +13813,487 @@
         <v>100</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G33" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>569</v>
+        <v>599</v>
       </c>
       <c r="I33" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J33" s="27" t="s">
-        <v>703</v>
+        <v>733</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="58" t="s">
-        <v>704</v>
+        <v>734</v>
       </c>
       <c r="B34" s="58" t="s">
-        <v>705</v>
+        <v>735</v>
       </c>
       <c r="C34" s="58" t="s">
-        <v>706</v>
+        <v>736</v>
       </c>
       <c r="D34" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F34" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G34" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H34" s="58" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="I34" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J34" s="58" t="s">
-        <v>707</v>
+        <v>737</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>708</v>
+        <v>738</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>709</v>
+        <v>739</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>706</v>
+        <v>736</v>
       </c>
       <c r="D35" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G35" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>704</v>
+        <v>734</v>
       </c>
       <c r="I35" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J35" s="27" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="58" t="s">
-        <v>711</v>
+        <v>741</v>
       </c>
       <c r="B36" s="58" t="s">
-        <v>712</v>
+        <v>742</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>706</v>
+        <v>736</v>
       </c>
       <c r="D36" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F36" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G36" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H36" s="58" t="s">
-        <v>708</v>
+        <v>738</v>
       </c>
       <c r="I36" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J36" s="58" t="s">
-        <v>713</v>
+        <v>743</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="27" t="s">
-        <v>714</v>
+        <v>744</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>715</v>
+        <v>745</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>716</v>
+        <v>746</v>
       </c>
       <c r="D37" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>683</v>
+        <v>713</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G37" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H37" s="27" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="I37" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J37" s="27" t="s">
-        <v>717</v>
+        <v>747</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="58" t="s">
-        <v>718</v>
+        <v>748</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>719</v>
+        <v>749</v>
       </c>
       <c r="C38" s="58" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="D38" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="58" t="s">
-        <v>683</v>
+        <v>713</v>
       </c>
       <c r="F38" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G38" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="58" t="s">
-        <v>714</v>
+        <v>744</v>
       </c>
       <c r="I38" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J38" s="58" t="s">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="27" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>721</v>
+        <v>751</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>663</v>
+        <v>693</v>
       </c>
       <c r="D39" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G39" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="I39" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J39" s="27" t="s">
-        <v>722</v>
+        <v>752</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="58" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B40" s="58" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="D40" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F40" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G40" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H40" s="58" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="I40" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J40" s="58" t="s">
-        <v>723</v>
+        <v>753</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>456</v>
+        <v>486</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>724</v>
+        <v>754</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="D41" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G41" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="I41" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J41" s="27" t="s">
-        <v>725</v>
+        <v>755</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="58" t="s">
-        <v>726</v>
+        <v>756</v>
       </c>
       <c r="B42" s="58" t="s">
-        <v>727</v>
+        <v>757</v>
       </c>
       <c r="C42" s="58" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="D42" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="58" t="s">
-        <v>683</v>
+        <v>713</v>
       </c>
       <c r="F42" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G42" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="58" t="s">
-        <v>718</v>
+        <v>748</v>
       </c>
       <c r="I42" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J42" s="58" t="s">
-        <v>728</v>
+        <v>758</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
-        <v>729</v>
+        <v>759</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>730</v>
+        <v>760</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>731</v>
+        <v>761</v>
       </c>
       <c r="D43" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>731</v>
+        <v>761</v>
       </c>
       <c r="G43" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H43" s="27" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="I43" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J43" s="27" t="s">
-        <v>732</v>
+        <v>762</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="58" t="s">
-        <v>733</v>
+        <v>763</v>
       </c>
       <c r="B44" s="58" t="s">
-        <v>734</v>
+        <v>764</v>
       </c>
       <c r="C44" s="58" t="s">
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="D44" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E44" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F44" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G44" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H44" s="58" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="I44" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J44" s="58" t="s">
-        <v>735</v>
+        <v>765</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="27" t="s">
-        <v>736</v>
+        <v>766</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>737</v>
+        <v>767</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>667</v>
+        <v>697</v>
       </c>
       <c r="D45" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G45" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H45" s="27" t="s">
-        <v>665</v>
+        <v>695</v>
       </c>
       <c r="I45" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J45" s="27" t="s">
-        <v>738</v>
+        <v>768</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="58" t="s">
-        <v>739</v>
+        <v>769</v>
       </c>
       <c r="B46" s="58" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="C46" s="58" t="s">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="D46" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E46" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F46" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G46" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H46" s="58" t="s">
-        <v>659</v>
+        <v>689</v>
       </c>
       <c r="I46" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J46" s="58" t="s">
-        <v>741</v>
+        <v>771</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
-        <v>742</v>
+        <v>772</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>743</v>
+        <v>773</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>716</v>
+        <v>746</v>
       </c>
       <c r="D47" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G47" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H47" s="27" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="I47" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J47" s="27" t="s">
-        <v>744</v>
+        <v>774</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="58" t="s">
-        <v>745</v>
+        <v>775</v>
       </c>
       <c r="B48" s="58" t="s">
-        <v>746</v>
+        <v>776</v>
       </c>
       <c r="C48" s="58" t="s">
-        <v>406</v>
+        <v>436</v>
       </c>
       <c r="D48" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E48" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F48" s="58" t="s">
         <v>100</v>
@@ -14047,62 +14302,62 @@
         <v>3</v>
       </c>
       <c r="H48" s="58" t="s">
-        <v>708</v>
+        <v>738</v>
       </c>
       <c r="I48" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J48" s="58" t="s">
-        <v>747</v>
+        <v>777</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="27" t="s">
-        <v>748</v>
+        <v>778</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>749</v>
+        <v>779</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="D49" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>683</v>
+        <v>713</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G49" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H49" s="27" t="s">
-        <v>736</v>
+        <v>766</v>
       </c>
       <c r="I49" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J49" s="27" t="s">
-        <v>751</v>
+        <v>781</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="58" t="s">
-        <v>752</v>
+        <v>782</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>753</v>
+        <v>783</v>
       </c>
       <c r="C50" s="58" t="s">
-        <v>754</v>
+        <v>784</v>
       </c>
       <c r="D50" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E50" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F50" s="58" t="s">
         <v>100</v>
@@ -14111,181 +14366,181 @@
         <v>4</v>
       </c>
       <c r="H50" s="58" t="s">
-        <v>673</v>
+        <v>703</v>
       </c>
       <c r="I50" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J50" s="58" t="s">
-        <v>755</v>
+        <v>785</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
-        <v>756</v>
+        <v>786</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>757</v>
+        <v>787</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>758</v>
+        <v>788</v>
       </c>
       <c r="D51" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G51" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H51" s="27" t="s">
-        <v>687</v>
+        <v>717</v>
       </c>
       <c r="I51" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J51" s="27" t="s">
-        <v>759</v>
+        <v>789</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="58" t="s">
-        <v>760</v>
+        <v>790</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>761</v>
+        <v>791</v>
       </c>
       <c r="C52" s="58" t="s">
-        <v>758</v>
+        <v>788</v>
       </c>
       <c r="D52" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E52" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F52" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G52" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H52" s="58" t="s">
-        <v>578</v>
+        <v>608</v>
       </c>
       <c r="I52" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J52" s="58" t="s">
-        <v>762</v>
+        <v>792</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="27" t="s">
-        <v>432</v>
+        <v>462</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>763</v>
+        <v>793</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>758</v>
+        <v>788</v>
       </c>
       <c r="D53" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F53" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G53" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H53" s="27" t="s">
-        <v>760</v>
+        <v>790</v>
       </c>
       <c r="I53" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J53" s="27" t="s">
-        <v>764</v>
+        <v>794</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="58" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="B54" s="58" t="s">
-        <v>766</v>
+        <v>796</v>
       </c>
       <c r="C54" s="58" t="s">
-        <v>646</v>
+        <v>676</v>
       </c>
       <c r="D54" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E54" s="58" t="s">
-        <v>683</v>
+        <v>713</v>
       </c>
       <c r="F54" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G54" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H54" s="58" t="s">
-        <v>687</v>
+        <v>717</v>
       </c>
       <c r="I54" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J54" s="58" t="s">
-        <v>767</v>
+        <v>797</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
-        <v>768</v>
+        <v>798</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>769</v>
+        <v>799</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="D55" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>770</v>
+        <v>800</v>
       </c>
       <c r="F55" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G55" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>711</v>
+        <v>741</v>
       </c>
       <c r="I55" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J55" s="27" t="s">
-        <v>771</v>
+        <v>801</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="58" t="s">
-        <v>772</v>
+        <v>802</v>
       </c>
       <c r="B56" s="58" t="s">
-        <v>773</v>
+        <v>803</v>
       </c>
       <c r="C56" s="58" t="s">
         <v>26</v>
@@ -14294,359 +14549,359 @@
         <v>102</v>
       </c>
       <c r="E56" s="58" t="s">
-        <v>770</v>
+        <v>800</v>
       </c>
       <c r="F56" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G56" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H56" s="58" t="s">
-        <v>533</v>
+        <v>563</v>
       </c>
       <c r="I56" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J56" s="58" t="s">
-        <v>774</v>
+        <v>804</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
-        <v>775</v>
+        <v>805</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>776</v>
+        <v>806</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>716</v>
+        <v>746</v>
       </c>
       <c r="D57" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G57" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H57" s="27" t="s">
-        <v>756</v>
+        <v>786</v>
       </c>
       <c r="I57" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J57" s="27" t="s">
-        <v>777</v>
+        <v>807</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="58" t="s">
-        <v>778</v>
+        <v>808</v>
       </c>
       <c r="B58" s="58" t="s">
-        <v>779</v>
+        <v>809</v>
       </c>
       <c r="C58" s="58" t="s">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="D58" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E58" s="58" t="s">
-        <v>683</v>
+        <v>713</v>
       </c>
       <c r="F58" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G58" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H58" s="58" t="s">
-        <v>659</v>
+        <v>689</v>
       </c>
       <c r="I58" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J58" s="58" t="s">
-        <v>780</v>
+        <v>810</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="27" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>782</v>
+        <v>812</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>643</v>
+        <v>673</v>
       </c>
       <c r="D59" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E59" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G59" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H59" s="27" t="s">
-        <v>673</v>
+        <v>703</v>
       </c>
       <c r="I59" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J59" s="27" t="s">
-        <v>783</v>
+        <v>813</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="58" t="s">
-        <v>784</v>
+        <v>814</v>
       </c>
       <c r="B60" s="58" t="s">
-        <v>785</v>
+        <v>815</v>
       </c>
       <c r="C60" s="58" t="s">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="D60" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E60" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F60" s="58" t="s">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="G60" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H60" s="58" t="s">
-        <v>775</v>
+        <v>805</v>
       </c>
       <c r="I60" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J60" s="58" t="s">
-        <v>787</v>
+        <v>817</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="27" t="s">
-        <v>788</v>
+        <v>818</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>789</v>
+        <v>819</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>716</v>
+        <v>746</v>
       </c>
       <c r="D61" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G61" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H61" s="27" t="s">
-        <v>775</v>
+        <v>805</v>
       </c>
       <c r="I61" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J61" s="27" t="s">
-        <v>790</v>
+        <v>820</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="58" t="s">
-        <v>791</v>
+        <v>821</v>
       </c>
       <c r="B62" s="58" t="s">
-        <v>792</v>
+        <v>822</v>
       </c>
       <c r="C62" s="58" t="s">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="D62" s="58" t="s">
         <v>104</v>
       </c>
       <c r="E62" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F62" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G62" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H62" s="58" t="s">
-        <v>659</v>
+        <v>689</v>
       </c>
       <c r="I62" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J62" s="58" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="27" t="s">
-        <v>794</v>
+        <v>824</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>795</v>
+        <v>825</v>
       </c>
       <c r="C63" s="27" t="s">
-        <v>796</v>
+        <v>826</v>
       </c>
       <c r="D63" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E63" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G63" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H63" s="27" t="s">
-        <v>775</v>
+        <v>805</v>
       </c>
       <c r="I63" s="69" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="J63" s="27" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="58" t="s">
-        <v>798</v>
+        <v>828</v>
       </c>
       <c r="B64" s="58" t="s">
-        <v>799</v>
+        <v>829</v>
       </c>
       <c r="C64" s="58" t="s">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="D64" s="58" t="s">
         <v>104</v>
       </c>
       <c r="E64" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F64" s="58" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G64" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H64" s="58" t="s">
-        <v>788</v>
+        <v>818</v>
       </c>
       <c r="I64" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J64" s="58" t="s">
-        <v>800</v>
+        <v>830</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="27" t="s">
-        <v>801</v>
+        <v>831</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>802</v>
+        <v>832</v>
       </c>
       <c r="C65" s="27" t="s">
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="D65" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E65" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G65" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H65" s="27" t="s">
-        <v>775</v>
+        <v>805</v>
       </c>
       <c r="I65" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J65" s="27" t="s">
-        <v>803</v>
+        <v>833</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="58" t="s">
-        <v>804</v>
+        <v>834</v>
       </c>
       <c r="B66" s="58" t="s">
-        <v>805</v>
+        <v>835</v>
       </c>
       <c r="C66" s="58" t="s">
-        <v>682</v>
+        <v>712</v>
       </c>
       <c r="D66" s="58" t="s">
         <v>104</v>
       </c>
       <c r="E66" s="58" t="s">
-        <v>683</v>
+        <v>713</v>
       </c>
       <c r="F66" s="58" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G66" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H66" s="58" t="s">
-        <v>733</v>
+        <v>763</v>
       </c>
       <c r="I66" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J66" s="58" t="s">
-        <v>806</v>
+        <v>836</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="27" t="s">
-        <v>807</v>
+        <v>837</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>808</v>
+        <v>838</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>682</v>
+        <v>712</v>
       </c>
       <c r="D67" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F67" s="27" t="s">
         <v>100</v>
@@ -14655,30 +14910,30 @@
         <v>5</v>
       </c>
       <c r="H67" s="27" t="s">
-        <v>788</v>
+        <v>818</v>
       </c>
       <c r="I67" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J67" s="27" t="s">
-        <v>809</v>
+        <v>839</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="58" t="s">
-        <v>810</v>
+        <v>840</v>
       </c>
       <c r="B68" s="58" t="s">
-        <v>811</v>
+        <v>841</v>
       </c>
       <c r="C68" s="58" t="s">
-        <v>682</v>
+        <v>712</v>
       </c>
       <c r="D68" s="58" t="s">
         <v>106</v>
       </c>
       <c r="E68" s="58" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F68" s="58" t="s">
         <v>100</v>
@@ -14687,45 +14942,45 @@
         <v>1</v>
       </c>
       <c r="H68" s="58" t="s">
-        <v>807</v>
+        <v>837</v>
       </c>
       <c r="I68" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J68" s="58" t="s">
-        <v>812</v>
+        <v>842</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="27" t="s">
-        <v>813</v>
+        <v>843</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>814</v>
+        <v>844</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>682</v>
+        <v>712</v>
       </c>
       <c r="D69" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E69" s="27" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F69" s="27" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="G69" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H69" s="27" t="s">
-        <v>801</v>
+        <v>831</v>
       </c>
       <c r="I69" s="69" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="J69" s="27" t="s">
-        <v>815</v>
+        <v>845</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14862,7 +15117,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D82" s="72" t="s">
-        <v>816</v>
+        <v>846</v>
       </c>
       <c r="E82" s="72"/>
       <c r="F82" s="72"/>
@@ -14873,7 +15128,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D83" s="73" t="s">
-        <v>817</v>
+        <v>847</v>
       </c>
       <c r="E83" s="73"/>
       <c r="F83" s="73"/>
@@ -14884,7 +15139,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D84" s="73" t="s">
-        <v>818</v>
+        <v>848</v>
       </c>
       <c r="E84" s="73"/>
       <c r="F84" s="73"/>
@@ -14895,7 +15150,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D85" s="73" t="s">
-        <v>819</v>
+        <v>849</v>
       </c>
       <c r="E85" s="73"/>
       <c r="F85" s="73"/>
@@ -14906,7 +15161,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D86" s="73" t="s">
-        <v>820</v>
+        <v>850</v>
       </c>
       <c r="E86" s="73"/>
       <c r="F86" s="73"/>
@@ -14917,7 +15172,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -14931,25 +15186,25 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>619</v>
+        <v>649</v>
       </c>
       <c r="B90" s="9"/>
       <c r="C90" s="9" t="s">
-        <v>822</v>
+        <v>852</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>823</v>
+        <v>853</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>824</v>
+        <v>854</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>825</v>
+        <v>855</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="75" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="B91" s="75"/>
       <c r="C91" s="32" t="n">
@@ -14971,7 +15226,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="75" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="B92" s="75"/>
       <c r="C92" s="32" t="n">
@@ -14993,7 +15248,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="75" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="B93" s="75"/>
       <c r="C93" s="32" t="n">
@@ -15015,7 +15270,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="75" t="s">
-        <v>731</v>
+        <v>761</v>
       </c>
       <c r="B94" s="75"/>
       <c r="C94" s="32" t="n">
@@ -15037,7 +15292,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="75" t="s">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="B95" s="75"/>
       <c r="C95" s="32" t="n">
@@ -15081,7 +15336,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="72" t="s">
-        <v>826</v>
+        <v>856</v>
       </c>
       <c r="B97" s="72"/>
       <c r="C97" s="21" t="n">
@@ -15107,16 +15362,16 @@
       </c>
       <c r="B99" s="29"/>
       <c r="C99" s="9" t="s">
-        <v>822</v>
+        <v>852</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>827</v>
+        <v>857</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>824</v>
+        <v>854</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>825</v>
+        <v>855</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15259,7 +15514,7 @@
     </row>
     <row r="107" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="54" t="s">
-        <v>828</v>
+        <v>858</v>
       </c>
       <c r="B107" s="54"/>
       <c r="C107" s="54"/>
@@ -15393,7 +15648,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>829</v>
+        <v>859</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -15411,22 +15666,22 @@
         <v>6</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>830</v>
+        <v>860</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>831</v>
+        <v>861</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>832</v>
+        <v>862</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>833</v>
+        <v>863</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>834</v>
+        <v>864</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>835</v>
+        <v>865</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15447,16 +15702,16 @@
         <v>46383</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>836</v>
+        <v>866</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>837</v>
+        <v>867</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>838</v>
+        <v>868</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>839</v>
+        <v>869</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15477,16 +15732,16 @@
         <v>46453</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>840</v>
+        <v>870</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>841</v>
+        <v>871</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>843</v>
+        <v>873</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15507,16 +15762,16 @@
         <v>46579</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>844</v>
+        <v>874</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>845</v>
+        <v>875</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>846</v>
+        <v>876</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>847</v>
+        <v>877</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15537,16 +15792,16 @@
         <v>46621</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>848</v>
+        <v>878</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>849</v>
+        <v>879</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>850</v>
+        <v>880</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>851</v>
+        <v>881</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15567,16 +15822,16 @@
         <v>46663</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>852</v>
+        <v>882</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>853</v>
+        <v>883</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>854</v>
+        <v>884</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>855</v>
+        <v>885</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15597,21 +15852,21 @@
         <v>46691</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>857</v>
+        <v>887</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>858</v>
+        <v>888</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>859</v>
+        <v>889</v>
       </c>
       <c r="B12" s="81" t="n">
         <f aca="false">D10</f>
@@ -15621,7 +15876,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="B13" s="82" t="n">
         <f aca="false">B12-Assumptions!B7</f>
@@ -15631,7 +15886,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>861</v>
+        <v>891</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="24"/>
@@ -15643,7 +15898,7 @@
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
-        <v>862</v>
+        <v>892</v>
       </c>
       <c r="B15" s="54"/>
       <c r="C15" s="54"/>
@@ -15655,7 +15910,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="54" t="s">
-        <v>863</v>
+        <v>893</v>
       </c>
       <c r="B16" s="54"/>
       <c r="C16" s="54"/>
@@ -15735,7 +15990,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>864</v>
+        <v>894</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -15769,13 +16024,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>865</v>
+        <v>895</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>830</v>
+        <v>860</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>831</v>
+        <v>861</v>
       </c>
       <c r="D4" s="83" t="n">
         <v>1</v>
@@ -15960,7 +16215,7 @@
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>866</v>
+        <v>896</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -16207,7 +16462,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>867</v>
+        <v>897</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -17978,7 +18233,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>868</v>
+        <v>898</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -18225,7 +18480,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>869</v>
+        <v>899</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>

--- a/docs/Vinland_Game_Development_Plan.xlsx
+++ b/docs/Vinland_Game_Development_Plan.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="1198">
   <si>
     <t xml:space="preserve">VINLAND</t>
   </si>
@@ -2056,60 +2056,60 @@
     <t xml:space="preserve">Must</t>
   </si>
   <si>
+    <t xml:space="preserve">Done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Someone who did not design it finds a fix and argues about the hold.  [Digital ring prototype stood in for the paper test.]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engine bake-off: ring prototype in both engines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engine chosen by week 2 on ring feel and haptic API, not feature lists.  [Godot 4.3 chosen 17 Oct 2026 without a bake-off: free, exports PC and web, builds headless for automated tests.]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source control, build pipeline, tagged builds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every playtest build is reproducible from a tag.  [Repo, tagged-quality builds, headless tests, Windows and Web exports.]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art style target: one sea, one camp, one UI frame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three paintovers approved: wood, wool, and a ring, not chrome.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold and ration model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economy</t>
+  </si>
+  <si>
     <t xml:space="preserve">In progress</t>
   </si>
   <si>
-    <t xml:space="preserve">Someone who did not design it finds a fix and argues about the hold.  [Digital ring prototype stands in for the paper test; needs a tester who did not design it.]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engine bake-off: ring prototype in both engines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engine chosen by week 2 on ring feel and haptic API, not feature lists.  [Godot 4.3 chosen 17 Oct 2026 without a bake-off: free, exports PC and web, builds headless for automated tests.]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source control, build pipeline, tagged builds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every playtest build is reproducible from a tag.  [Git repo, tagged builds, headless tests and Windows/Web exports work. Push to GitHub waits on repo access.]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Art style target: one sea, one camp, one UI frame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not started</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Three paintovers approved: wood, wool, and a ring, not chrome.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hold and ration model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economy</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cargo units, rations, and spoilage read from Assumptions knobs; no literals in code.  [Hold, rations, spoilage and animal fodder run from knobs; HoldCheck arithmetic reproduced and tested.]</t>
   </si>
   <si>
@@ -2125,7 +2125,7 @@
     <t xml:space="preserve">Star ring mini-game</t>
   </si>
   <si>
-    <t xml:space="preserve">Fix result (clean, partial, none) feeds drift; playable with haptics off.  [Prototype playable: 5 conditions, haptics with visual twin, run log CSV. Needs human playtests.]</t>
+    <t xml:space="preserve">Fix result (clean, partial, none) feeds drift; playable with haptics off.  [Star ring passed the slice playtest after the difficulty retune.]</t>
   </si>
   <si>
     <t xml:space="preserve">Sun board mini-game</t>
@@ -2137,7 +2137,7 @@
     <t xml:space="preserve">Hand-line fishing</t>
   </si>
   <si>
-    <t xml:space="preserve">A bite reads through the trigger; a cut line keeps the hook.  [Playable: depth by stick, nibbles, two-beat bite, set on the ease, haul under line strain, snap, cut; hooks are a stock. Bots: skilled watch ~19.5 person-days.]</t>
+    <t xml:space="preserve">A bite reads through the trigger; a cut line keeps the hook.  [Hand line passed the slice playtest after the difficulty retune.]</t>
   </si>
   <si>
     <t xml:space="preserve">F06</t>
@@ -2146,13 +2146,13 @@
     <t xml:space="preserve">One camp day loop</t>
   </si>
   <si>
-    <t xml:space="preserve">Morning job queue, one verb, evening tally that changes the hold.  [Playable: morning job board, you play the joint or the hand line, evening tally, a week at a time, G1 checklist at autumn.]</t>
+    <t xml:space="preserve">Morning job queue, one verb, evening tally that changes the hold.  [Camp day loop shipped in the slice and extended to a full year.]</t>
   </si>
   <si>
     <t xml:space="preserve">Joint construction</t>
   </si>
   <si>
-    <t xml:space="preserve">Grain reported on RT; a split log costs the day.  [Playable: brace, set the peg, drive by trigger depth; rain lowers the grain cap. Bots: steady 100%, full force 0%, timid 0%, no brace 22%.]</t>
+    <t xml:space="preserve">Grain reported on RT; a split log costs the day.  [Joint passed the slice playtest after the difficulty retune.]</t>
   </si>
   <si>
     <t xml:space="preserve">F08</t>
@@ -2236,7 +2236,7 @@
     <t xml:space="preserve">Seven cards shuffled per leg; each card offers a verb or takes one away.  [Seven cards plus fair wind, weighted per leg; card shown at each dawn.]</t>
   </si>
   <si>
-    <t xml:space="preserve">No sky game in a storm: hull check, then bail rhythm.</t>
+    <t xml:space="preserve">No sky game in a storm: hull check, then bail rhythm.  [Playable: find the leak, bail on the beat, wave sets with early rumble. Novice keyboard holds 100/92/42% (Forgiving/Standard/Hard).]</t>
   </si>
   <si>
     <t xml:space="preserve">F11</t>
@@ -2266,13 +2266,13 @@
     <t xml:space="preserve">Drying and smoke rack</t>
   </si>
   <si>
-    <t xml:space="preserve">Two fair days turn fresh fish into a food unit.</t>
+    <t xml:space="preserve">Two fair days turn fresh fish into a food unit.  [Smoke-and-dry job turns surplus fresh fish into stores on fair days (90% kept). Rack mini-game (MG9) still to come.]</t>
   </si>
   <si>
     <t xml:space="preserve">Livestock, milk, hay</t>
   </si>
   <si>
-    <t xml:space="preserve">Hay cut in late summer or the byre is a tomb.  [Milk from fed cows; hay job opens 1 August. Byre and winter feeding still to come.]</t>
+    <t xml:space="preserve">Hay cut in late summer or the byre is a tomb.  [Milk from fed cows; hay cut August to mid-October; herd eats hay all winter; no hay kills animals.]</t>
   </si>
   <si>
     <t xml:space="preserve">F17</t>
@@ -2281,7 +2281,7 @@
     <t xml:space="preserve">Byre, longhouse, booths</t>
   </si>
   <si>
-    <t xml:space="preserve">Three buildings raised with the joint and lift verbs; no tech tree.  [Booth plots and the longhouse as a build queue with visible stages (placeholder drawings).]</t>
+    <t xml:space="preserve">Three buildings raised with the joint and lift verbs; no tech tree.  [Build queue: three booths, the longhouse (540 builder-days), the byre (160). Placeholder drawings.]</t>
   </si>
   <si>
     <t xml:space="preserve">Lift and slipway</t>
@@ -2353,7 +2353,7 @@
     <t xml:space="preserve">Winter camp loop and starvation check</t>
   </si>
   <si>
-    <t xml:space="preserve">Each winter week checks hay, food, and shelter; starvation ends the run.</t>
+    <t xml:space="preserve">Each winter week checks hay, food, and shelter; starvation ends the run.  [Seasons and years; first snow 1 Nov, thaw 20 Apr; winter shelter, work, sickness and cold deaths. Year sweeps: a planning camp loses no one, a summer-only camp about 8.]</t>
   </si>
   <si>
     <t xml:space="preserve">F48</t>
@@ -2383,7 +2383,7 @@
     <t xml:space="preserve">Save system</t>
   </si>
   <si>
-    <t xml:space="preserve">Watch-level autosave at sea, day-level in camp, three rolling slots.</t>
+    <t xml:space="preserve">Watch-level autosave at sea, day-level in camp, three rolling slots.  [Autosave every watch at sea and every day ashore, three rolling slots written via temp file, exact-replay loads, Continue on the title.]</t>
   </si>
   <si>
     <t xml:space="preserve">F51</t>
@@ -2950,7 +2950,10 @@
     <t xml:space="preserve">Pillars signed. Paper prototype of the ring judged fun by someone who did not design it.</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes from the table session</t>
+    <t xml:space="preserve">Digital ring prototype, 17 Oct 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passed</t>
   </si>
   <si>
     <t xml:space="preserve">F41, F42, F43, F44</t>
@@ -2962,7 +2965,7 @@
     <t xml:space="preserve">Slice: leave a fjord, miss a fix, fish, dry nothing, build one joint, see the hold change.</t>
   </si>
   <si>
-    <t xml:space="preserve">Build tag slice-1</t>
+    <t xml:space="preserve">Slice build v2, playtest 17 Oct 2026 ("much better")</t>
   </si>
   <si>
     <t xml:space="preserve">F01, F02, F03, F04, F05, F06, F07, F08, F35, F36, F37, F38, F39, F40, F61</t>
@@ -4881,11 +4884,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="22413173"/>
-        <c:axId val="37001983"/>
+        <c:axId val="58729634"/>
+        <c:axId val="67663476"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="22413173"/>
+        <c:axId val="58729634"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4917,7 +4920,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37001983"/>
+        <c:crossAx val="67663476"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4925,7 +4928,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37001983"/>
+        <c:axId val="67663476"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5001,7 +5004,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22413173"/>
+        <c:crossAx val="58729634"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5040,9 +5043,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>743400</xdr:colOff>
+      <xdr:colOff>743040</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>59760</xdr:rowOff>
+      <xdr:rowOff>59400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5051,7 +5054,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="6562800"/>
-        <a:ext cx="5395320" cy="2155320"/>
+        <a:ext cx="5394960" cy="2154960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5966,7 +5969,7 @@
       </c>
       <c r="B55" s="5" t="str">
         <f aca="false">COUNTIF(Backlog!I5:I80,"Done")&amp;" of "&amp;COUNTA(Backlog!A5:A80)</f>
-        <v>1 of 65</v>
+        <v>7 of 65</v>
       </c>
       <c r="C55" s="31" t="s">
         <v>68</v>
@@ -5988,7 +5991,7 @@
       </c>
       <c r="B56" s="38" t="n">
         <f aca="false">Backlog!G86</f>
-        <v>0.0261437908496732</v>
+        <v>0.169934640522876</v>
       </c>
       <c r="C56" s="34" t="s">
         <v>71</v>
@@ -6010,7 +6013,7 @@
       </c>
       <c r="B57" s="5" t="str">
         <f aca="false">COUNTIF(Milestones!F5:F10,"Passed")&amp;" of 6"</f>
-        <v>0 of 6</v>
+        <v>2 of 6</v>
       </c>
       <c r="C57" s="31" t="s">
         <v>73</v>
@@ -6247,7 +6250,7 @@
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B7" s="89" t="n">
         <f aca="false">Assumptions!B28</f>
@@ -6487,7 +6490,7 @@
         <v>661</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>761</v>
@@ -7505,13 +7508,13 @@
         <v>322</v>
       </c>
       <c r="F5" s="69" t="s">
-        <v>670</v>
+        <v>955</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7523,22 +7526,22 @@
         <v>46453</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="E6" s="58" t="s">
         <v>661</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>670</v>
+        <v>955</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7550,22 +7553,22 @@
         <v>46579</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>322</v>
       </c>
       <c r="F7" s="69" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7577,22 +7580,22 @@
         <v>46621</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="E8" s="58" t="s">
         <v>100</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7604,22 +7607,22 @@
         <v>46663</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>816</v>
       </c>
       <c r="F9" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7631,19 +7634,19 @@
         <v>46691</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="E10" s="58" t="s">
         <v>100</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H10" s="58" t="s">
         <v>427</v>
@@ -7651,7 +7654,7 @@
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B12" s="54"/>
       <c r="C12" s="54"/>
@@ -7731,7 +7734,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7748,28 +7751,28 @@
         <v>313</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E4" s="57" t="s">
         <v>463</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="G4" s="57" t="s">
         <v>649</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>44</v>
@@ -7777,10 +7780,10 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="58" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C5" s="43" t="n">
         <v>3</v>
@@ -7793,7 +7796,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="G5" s="58" t="s">
         <v>322</v>
@@ -7802,18 +7805,18 @@
         <v>873</v>
       </c>
       <c r="I5" s="58" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="J5" s="69" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>3</v>
@@ -7826,7 +7829,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="G6" s="58" t="s">
         <v>322</v>
@@ -7835,18 +7838,18 @@
         <v>873</v>
       </c>
       <c r="I6" s="58" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="J6" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="58" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>2</v>
@@ -7859,7 +7862,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="58" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G7" s="58" t="s">
         <v>661</v>
@@ -7868,18 +7871,18 @@
         <v>885</v>
       </c>
       <c r="I7" s="58" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="J7" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>4</v>
@@ -7892,7 +7895,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>100</v>
@@ -7901,18 +7904,18 @@
         <v>877</v>
       </c>
       <c r="I8" s="58" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="J8" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="58" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>2</v>
@@ -7925,27 +7928,27 @@
         <v>6</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H9" s="58" t="s">
         <v>877</v>
       </c>
       <c r="I9" s="58" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="J9" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C10" s="43" t="n">
         <v>2</v>
@@ -7958,7 +7961,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="G10" s="58" t="s">
         <v>322</v>
@@ -7967,18 +7970,18 @@
         <v>877</v>
       </c>
       <c r="I10" s="58" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="J10" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="58" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C11" s="43" t="n">
         <v>3</v>
@@ -7991,7 +7994,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="G11" s="58" t="s">
         <v>100</v>
@@ -8000,18 +8003,18 @@
         <v>881</v>
       </c>
       <c r="I11" s="58" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="J11" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C12" s="43" t="n">
         <v>2</v>
@@ -8024,7 +8027,7 @@
         <v>8</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G12" s="58" t="s">
         <v>661</v>
@@ -8033,18 +8036,18 @@
         <v>869</v>
       </c>
       <c r="I12" s="58" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="J12" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="58" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B13" s="58" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C13" s="43" t="n">
         <v>2</v>
@@ -8057,7 +8060,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="58" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="G13" s="58" t="s">
         <v>322</v>
@@ -8066,18 +8069,18 @@
         <v>869</v>
       </c>
       <c r="I13" s="58" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="J13" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C14" s="43" t="n">
         <v>3</v>
@@ -8090,7 +8093,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="G14" s="58" t="s">
         <v>322</v>
@@ -8099,18 +8102,18 @@
         <v>881</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="J14" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="58" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C15" s="43" t="n">
         <v>3</v>
@@ -8123,7 +8126,7 @@
         <v>15</v>
       </c>
       <c r="F15" s="58" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="G15" s="58" t="s">
         <v>322</v>
@@ -8132,18 +8135,18 @@
         <v>877</v>
       </c>
       <c r="I15" s="58" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="J15" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C16" s="43" t="n">
         <v>4</v>
@@ -8156,7 +8159,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="G16" s="58" t="s">
         <v>100</v>
@@ -8165,18 +8168,18 @@
         <v>873</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="J16" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="58" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C17" s="43" t="n">
         <v>3</v>
@@ -8189,7 +8192,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="G17" s="58" t="s">
         <v>100</v>
@@ -8198,18 +8201,18 @@
         <v>877</v>
       </c>
       <c r="I17" s="58" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="J17" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C18" s="43" t="n">
         <v>2</v>
@@ -8222,7 +8225,7 @@
         <v>6</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="G18" s="58" t="s">
         <v>322</v>
@@ -8231,18 +8234,18 @@
         <v>885</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="J18" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="58" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C19" s="43" t="n">
         <v>2</v>
@@ -8255,7 +8258,7 @@
         <v>8</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G19" s="58" t="s">
         <v>661</v>
@@ -8264,18 +8267,18 @@
         <v>877</v>
       </c>
       <c r="I19" s="58" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="J19" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C20" s="43" t="n">
         <v>3</v>
@@ -8288,7 +8291,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="G20" s="58" t="s">
         <v>100</v>
@@ -8297,10 +8300,10 @@
         <v>873</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="J20" s="69" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
   </sheetData>
@@ -8378,7 +8381,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8389,16 +8392,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E4" s="57" t="s">
         <v>95</v>
@@ -8407,30 +8410,30 @@
         <v>649</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8438,68 +8441,68 @@
         <v>621</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>668</v>
+      </c>
+      <c r="G7" s="27" t="s">
         <v>1068</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>1072</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>669</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8507,22 +8510,22 @@
         <v>506</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8530,22 +8533,22 @@
         <v>697</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D10" s="58" t="s">
         <v>819</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8553,22 +8556,22 @@
         <v>761</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>761</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8576,91 +8579,91 @@
         <v>780</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F12" s="58" t="s">
         <v>322</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>661</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F14" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
   </sheetData>
@@ -8702,7 +8705,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8713,10 +8716,10 @@
         <v>110</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D4" s="57" t="s">
         <v>649</v>
@@ -8724,10 +8727,10 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>869</v>
@@ -8738,13 +8741,13 @@
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D6" s="58" t="s">
         <v>661</v>
@@ -8752,10 +8755,10 @@
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C7" s="27" t="s">
         <v>877</v>
@@ -8766,10 +8769,10 @@
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C8" s="58" t="s">
         <v>873</v>
@@ -8780,10 +8783,10 @@
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C9" s="27" t="s">
         <v>869</v>
@@ -8794,10 +8797,10 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C10" s="58" t="s">
         <v>877</v>
@@ -8808,10 +8811,10 @@
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>885</v>
@@ -8822,10 +8825,10 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C12" s="58" t="s">
         <v>888</v>
@@ -8836,10 +8839,10 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>888</v>
@@ -8850,13 +8853,13 @@
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D14" s="58" t="s">
         <v>322</v>
@@ -8864,10 +8867,10 @@
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>873</v>
@@ -8878,7 +8881,7 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B16" s="58" t="str">
         <f aca="false">"Premium at $"&amp;TEXT(Assumptions!B69,"0.00")&amp;". Launch discount no deeper than the realized-price factor on Assumptions."</f>
@@ -8893,10 +8896,10 @@
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C17" s="27" t="s">
         <v>873</v>
@@ -8910,7 +8913,7 @@
         <v>863</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C18" s="58" t="s">
         <v>881</v>
@@ -8921,10 +8924,10 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C19" s="27" t="s">
         <v>885</v>
@@ -8935,10 +8938,10 @@
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C20" s="58" t="s">
         <v>885</v>
@@ -8949,10 +8952,10 @@
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C21" s="27" t="s">
         <v>885</v>
@@ -8963,10 +8966,10 @@
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="58" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C22" s="58" t="s">
         <v>888</v>
@@ -9015,7 +9018,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9023,16 +9026,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9040,13 +9043,13 @@
         <v>46311</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9054,13 +9057,13 @@
         <v>46311</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9068,13 +9071,13 @@
         <v>46311</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9085,10 +9088,10 @@
         <v>923</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9096,13 +9099,13 @@
         <v>46311</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9113,10 +9116,10 @@
         <v>53</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9124,13 +9127,13 @@
         <v>46311</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9141,10 +9144,10 @@
         <v>402</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9152,13 +9155,13 @@
         <v>46311</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9166,13 +9169,13 @@
         <v>46311</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9183,10 +9186,10 @@
         <v>58</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9194,13 +9197,13 @@
         <v>46311</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9211,10 +9214,10 @@
         <v>62</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9225,10 +9228,10 @@
         <v>436</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9239,10 +9242,10 @@
         <v>712</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9250,13 +9253,13 @@
         <v>46311</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
   </sheetData>
@@ -10615,7 +10618,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="50" t="s">
         <v>282</v>
       </c>
@@ -10626,7 +10629,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="42" t="s">
         <v>284</v>
       </c>
@@ -10637,7 +10640,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="50" t="s">
         <v>286</v>
       </c>
@@ -10648,7 +10651,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="42" t="s">
         <v>288</v>
       </c>
@@ -10659,7 +10662,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="50" t="s">
         <v>290</v>
       </c>
@@ -10670,7 +10673,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="42" t="s">
         <v>292</v>
       </c>
@@ -10681,7 +10684,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="50" t="s">
         <v>294</v>
       </c>
@@ -10692,7 +10695,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="42" t="s">
         <v>296</v>
       </c>
@@ -10703,7 +10706,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="50" t="s">
         <v>298</v>
       </c>
@@ -10714,7 +10717,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="42" t="s">
         <v>300</v>
       </c>
@@ -10725,7 +10728,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="50" t="s">
         <v>302</v>
       </c>
@@ -10736,7 +10739,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="42" t="s">
         <v>304</v>
       </c>
@@ -10747,7 +10750,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="50" t="s">
         <v>306</v>
       </c>
@@ -10758,7 +10761,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="42" t="s">
         <v>308</v>
       </c>
@@ -10769,7 +10772,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="50" t="s">
         <v>310</v>
       </c>
@@ -12961,18 +12964,18 @@
         <v>653</v>
       </c>
       <c r="I6" s="69" t="s">
+        <v>656</v>
+      </c>
+      <c r="J6" s="58" t="s">
         <v>662</v>
-      </c>
-      <c r="J6" s="58" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
+        <v>663</v>
+      </c>
+      <c r="B7" s="27" t="s">
         <v>664</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>665</v>
       </c>
       <c r="C7" s="27" t="s">
         <v>660</v>
@@ -12996,18 +12999,18 @@
         <v>656</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
+        <v>666</v>
+      </c>
+      <c r="B8" s="58" t="s">
         <v>667</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="C8" s="58" t="s">
         <v>668</v>
-      </c>
-      <c r="C8" s="58" t="s">
-        <v>669</v>
       </c>
       <c r="D8" s="58" t="s">
         <v>96</v>
@@ -13016,7 +13019,7 @@
         <v>655</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G8" s="43" t="n">
         <v>5</v>
@@ -13025,10 +13028,10 @@
         <v>427</v>
       </c>
       <c r="I8" s="69" t="s">
+        <v>669</v>
+      </c>
+      <c r="J8" s="58" t="s">
         <v>670</v>
-      </c>
-      <c r="J8" s="58" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13036,10 +13039,10 @@
         <v>406</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>671</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>672</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>673</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>98</v>
@@ -13057,7 +13060,7 @@
         <v>427</v>
       </c>
       <c r="I9" s="69" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="J9" s="27" t="s">
         <v>674</v>
@@ -13089,7 +13092,7 @@
         <v>406</v>
       </c>
       <c r="I10" s="69" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="J10" s="58" t="s">
         <v>677</v>
@@ -13153,7 +13156,7 @@
         <v>545</v>
       </c>
       <c r="I12" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J12" s="58" t="s">
         <v>681</v>
@@ -13281,7 +13284,7 @@
         <v>545</v>
       </c>
       <c r="I16" s="69" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="J16" s="58" t="s">
         <v>691</v>
@@ -13313,7 +13316,7 @@
         <v>425</v>
       </c>
       <c r="I17" s="69" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="J17" s="27" t="s">
         <v>694</v>
@@ -13336,7 +13339,7 @@
         <v>655</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G18" s="43" t="n">
         <v>5</v>
@@ -13345,7 +13348,7 @@
         <v>406</v>
       </c>
       <c r="I18" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J18" s="58" t="s">
         <v>698</v>
@@ -13359,7 +13362,7 @@
         <v>699</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>98</v>
@@ -13377,7 +13380,7 @@
         <v>406</v>
       </c>
       <c r="I19" s="69" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="J19" s="27" t="s">
         <v>700</v>
@@ -13409,7 +13412,7 @@
         <v>545</v>
       </c>
       <c r="I20" s="69" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="J20" s="58" t="s">
         <v>702</v>
@@ -13441,7 +13444,7 @@
         <v>425</v>
       </c>
       <c r="I21" s="69" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="J21" s="27" t="s">
         <v>706</v>
@@ -13473,7 +13476,7 @@
         <v>689</v>
       </c>
       <c r="I22" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J22" s="58" t="s">
         <v>709</v>
@@ -13502,10 +13505,10 @@
         <v>3</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I23" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J23" s="27" t="s">
         <v>714</v>
@@ -13537,7 +13540,7 @@
         <v>425</v>
       </c>
       <c r="I24" s="69" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="J24" s="58" t="s">
         <v>715</v>
@@ -13569,7 +13572,7 @@
         <v>438</v>
       </c>
       <c r="I25" s="69" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="J25" s="27" t="s">
         <v>716</v>
@@ -13601,7 +13604,7 @@
         <v>438</v>
       </c>
       <c r="I26" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J26" s="58" t="s">
         <v>719</v>
@@ -13633,7 +13636,7 @@
         <v>684</v>
       </c>
       <c r="I27" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J27" s="27" t="s">
         <v>720</v>
@@ -13665,7 +13668,7 @@
         <v>684</v>
       </c>
       <c r="I28" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J28" s="58" t="s">
         <v>722</v>
@@ -13697,7 +13700,7 @@
         <v>563</v>
       </c>
       <c r="I29" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J29" s="27" t="s">
         <v>724</v>
@@ -13711,7 +13714,7 @@
         <v>725</v>
       </c>
       <c r="C30" s="58" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D30" s="58" t="s">
         <v>100</v>
@@ -13729,7 +13732,7 @@
         <v>563</v>
       </c>
       <c r="I30" s="69" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="J30" s="58" t="s">
         <v>726</v>
@@ -13761,7 +13764,7 @@
         <v>406</v>
       </c>
       <c r="I31" s="69" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="J31" s="27" t="s">
         <v>728</v>
@@ -13784,7 +13787,7 @@
         <v>655</v>
       </c>
       <c r="F32" s="58" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G32" s="43" t="n">
         <v>8</v>
@@ -13793,7 +13796,7 @@
         <v>599</v>
       </c>
       <c r="I32" s="69" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="J32" s="58" t="s">
         <v>731</v>
@@ -13825,7 +13828,7 @@
         <v>599</v>
       </c>
       <c r="I33" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J33" s="27" t="s">
         <v>733</v>
@@ -13857,7 +13860,7 @@
         <v>482</v>
       </c>
       <c r="I34" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J34" s="58" t="s">
         <v>737</v>
@@ -13889,7 +13892,7 @@
         <v>734</v>
       </c>
       <c r="I35" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J35" s="27" t="s">
         <v>740</v>
@@ -13921,7 +13924,7 @@
         <v>738</v>
       </c>
       <c r="I36" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J36" s="58" t="s">
         <v>743</v>
@@ -13953,7 +13956,7 @@
         <v>406</v>
       </c>
       <c r="I37" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J37" s="27" t="s">
         <v>747</v>
@@ -13985,7 +13988,7 @@
         <v>744</v>
       </c>
       <c r="I38" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J38" s="58" t="s">
         <v>750</v>
@@ -14017,7 +14020,7 @@
         <v>438</v>
       </c>
       <c r="I39" s="69" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="J39" s="27" t="s">
         <v>752</v>
@@ -14049,7 +14052,7 @@
         <v>406</v>
       </c>
       <c r="I40" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J40" s="58" t="s">
         <v>753</v>
@@ -14081,7 +14084,7 @@
         <v>482</v>
       </c>
       <c r="I41" s="69" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="J41" s="27" t="s">
         <v>755</v>
@@ -14113,7 +14116,7 @@
         <v>748</v>
       </c>
       <c r="I42" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J42" s="58" t="s">
         <v>758</v>
@@ -14145,7 +14148,7 @@
         <v>425</v>
       </c>
       <c r="I43" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J43" s="27" t="s">
         <v>762</v>
@@ -14177,7 +14180,7 @@
         <v>425</v>
       </c>
       <c r="I44" s="69" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="J44" s="58" t="s">
         <v>765</v>
@@ -14209,7 +14212,7 @@
         <v>695</v>
       </c>
       <c r="I45" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J45" s="27" t="s">
         <v>768</v>
@@ -14241,7 +14244,7 @@
         <v>689</v>
       </c>
       <c r="I46" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J46" s="58" t="s">
         <v>771</v>
@@ -14273,7 +14276,7 @@
         <v>406</v>
       </c>
       <c r="I47" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J47" s="27" t="s">
         <v>774</v>
@@ -14305,7 +14308,7 @@
         <v>738</v>
       </c>
       <c r="I48" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J48" s="58" t="s">
         <v>777</v>
@@ -14337,7 +14340,7 @@
         <v>766</v>
       </c>
       <c r="I49" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J49" s="27" t="s">
         <v>781</v>
@@ -14369,7 +14372,7 @@
         <v>703</v>
       </c>
       <c r="I50" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J50" s="58" t="s">
         <v>785</v>
@@ -14401,7 +14404,7 @@
         <v>717</v>
       </c>
       <c r="I51" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J51" s="27" t="s">
         <v>789</v>
@@ -14433,7 +14436,7 @@
         <v>608</v>
       </c>
       <c r="I52" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J52" s="58" t="s">
         <v>792</v>
@@ -14465,7 +14468,7 @@
         <v>790</v>
       </c>
       <c r="I53" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J53" s="27" t="s">
         <v>794</v>
@@ -14497,7 +14500,7 @@
         <v>717</v>
       </c>
       <c r="I54" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J54" s="58" t="s">
         <v>797</v>
@@ -14529,7 +14532,7 @@
         <v>741</v>
       </c>
       <c r="I55" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J55" s="27" t="s">
         <v>801</v>
@@ -14561,7 +14564,7 @@
         <v>563</v>
       </c>
       <c r="I56" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J56" s="58" t="s">
         <v>804</v>
@@ -14593,7 +14596,7 @@
         <v>786</v>
       </c>
       <c r="I57" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J57" s="27" t="s">
         <v>807</v>
@@ -14625,7 +14628,7 @@
         <v>689</v>
       </c>
       <c r="I58" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J58" s="58" t="s">
         <v>810</v>
@@ -14639,7 +14642,7 @@
         <v>812</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D59" s="27" t="s">
         <v>102</v>
@@ -14657,7 +14660,7 @@
         <v>703</v>
       </c>
       <c r="I59" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J59" s="27" t="s">
         <v>813</v>
@@ -14689,7 +14692,7 @@
         <v>805</v>
       </c>
       <c r="I60" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J60" s="58" t="s">
         <v>817</v>
@@ -14721,7 +14724,7 @@
         <v>805</v>
       </c>
       <c r="I61" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J61" s="27" t="s">
         <v>820</v>
@@ -14753,7 +14756,7 @@
         <v>689</v>
       </c>
       <c r="I62" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J62" s="58" t="s">
         <v>823</v>
@@ -14785,7 +14788,7 @@
         <v>805</v>
       </c>
       <c r="I63" s="69" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="J63" s="27" t="s">
         <v>827</v>
@@ -14817,7 +14820,7 @@
         <v>818</v>
       </c>
       <c r="I64" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J64" s="58" t="s">
         <v>830</v>
@@ -14849,7 +14852,7 @@
         <v>805</v>
       </c>
       <c r="I65" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J65" s="27" t="s">
         <v>833</v>
@@ -14881,7 +14884,7 @@
         <v>763</v>
       </c>
       <c r="I66" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J66" s="58" t="s">
         <v>836</v>
@@ -14913,7 +14916,7 @@
         <v>818</v>
       </c>
       <c r="I67" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J67" s="27" t="s">
         <v>839</v>
@@ -14945,7 +14948,7 @@
         <v>837</v>
       </c>
       <c r="I68" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J68" s="58" t="s">
         <v>842</v>
@@ -14977,7 +14980,7 @@
         <v>831</v>
       </c>
       <c r="I69" s="69" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J69" s="27" t="s">
         <v>845</v>
@@ -15156,7 +15159,7 @@
       <c r="F85" s="73"/>
       <c r="G85" s="32" t="n">
         <f aca="false">SUMIF(I$5:I$80,"Done",G$5:G$80)</f>
-        <v>8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15167,7 +15170,7 @@
       <c r="F86" s="73"/>
       <c r="G86" s="74" t="n">
         <f aca="false">IF(G83=0,0,SUMIFS(G$5:G$80,E$5:E$80,"Must",I$5:I$80,"Done")/G83)</f>
-        <v>0.0261437908496732</v>
+        <v>0.169934640522876</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15248,7 +15251,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="75" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B93" s="75"/>
       <c r="C93" s="32" t="n">

--- a/docs/Vinland_Game_Development_Plan.xlsx
+++ b/docs/Vinland_Game_Development_Plan.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="1210">
   <si>
     <t xml:space="preserve">VINLAND</t>
   </si>
@@ -1024,6 +1024,42 @@
     <t xml:space="preserve">Build queue after the longhouse (F17)</t>
   </si>
   <si>
+    <t xml:space="preserve">Hunt kill chance per hunter-day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunt: about the yield of a fisher, but swingier, and it brings hides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meat per kill (person-days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunt: one caribou; spoils like fish unless dried</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Far grounds kill bonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunt: more caribou away from the camp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Far grounds fear chance per hunter-day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goodwill / fear: ranging far is seen (F19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter hunting factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunt: deep snow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stripped patch damage carried to the season (share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forage: greedy picking thins every patch until spring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pillars, fantasy, clocks, and the win</t>
   </si>
   <si>
@@ -2248,13 +2284,13 @@
     <t xml:space="preserve">Each leg has a landfall quality and a named failure.</t>
   </si>
   <si>
-    <t xml:space="preserve">One shot; ranging far can tick fear.</t>
+    <t xml:space="preserve">One shot; ranging far can tick fear.  [Playable: stalk, freeze when it watches, crouch, scent, draw, aim with sway, loose; near/far grounds with a fear tick. Novice kills 75-79% Forgiving, 50-63% Standard.]</t>
   </si>
   <si>
     <t xml:space="preserve">Forage patch</t>
   </si>
   <si>
-    <t xml:space="preserve">A greedy take strips next season's patch.</t>
+    <t xml:space="preserve">A greedy take strips next season's patch.  [Playable: pick ripe clumps, greedy picking strips the patch for the season; magnetic hand on easier settings. Novice 100% Forgiving/Standard. Bird-island noise still to come.]</t>
   </si>
   <si>
     <t xml:space="preserve">Net throw</t>
@@ -2299,7 +2335,7 @@
     <t xml:space="preserve">Trade</t>
   </si>
   <si>
-    <t xml:space="preserve">Trade raises goodwill; weapon sale, killing, palisade, loose bull raise fear toward the cap.</t>
+    <t xml:space="preserve">Trade raises goodwill; weapon sale, killing, palisade, loose bull raise fear toward the cap.  [Fear clock started: far hunting raises fear (cap 5). Goodwill and the market still to come.]</t>
   </si>
   <si>
     <t xml:space="preserve">F20</t>
@@ -4884,11 +4920,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="58729634"/>
-        <c:axId val="67663476"/>
+        <c:axId val="95196207"/>
+        <c:axId val="37331758"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="58729634"/>
+        <c:axId val="95196207"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4920,7 +4956,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67663476"/>
+        <c:crossAx val="37331758"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4928,7 +4964,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67663476"/>
+        <c:axId val="37331758"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5004,7 +5040,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58729634"/>
+        <c:crossAx val="95196207"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5043,9 +5079,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>743040</xdr:colOff>
+      <xdr:colOff>742320</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>59400</xdr:rowOff>
+      <xdr:rowOff>58680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5054,7 +5090,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="6562800"/>
-        <a:ext cx="5394960" cy="2154960"/>
+        <a:ext cx="5394240" cy="2154240"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6136,7 +6172,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>900</v>
+        <v>912</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -6148,10 +6184,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>901</v>
+        <v>913</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="C4" s="57" t="s">
         <v>96</v>
@@ -6172,7 +6208,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="57" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="J4" s="57" t="s">
         <v>7</v>
@@ -6180,7 +6216,7 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B5" s="89" t="n">
         <f aca="false">Assumptions!B26</f>
@@ -6215,7 +6251,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="B6" s="89" t="n">
         <f aca="false">Assumptions!B27</f>
@@ -6250,7 +6286,7 @@
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="B7" s="89" t="n">
         <f aca="false">Assumptions!B28</f>
@@ -6285,7 +6321,7 @@
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="B8" s="89" t="n">
         <f aca="false">Assumptions!B29</f>
@@ -6320,7 +6356,7 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="B9" s="89" t="n">
         <f aca="false">Assumptions!B30</f>
@@ -6390,10 +6426,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="71" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="B11" s="71" t="s">
-        <v>905</v>
+        <v>917</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -6430,10 +6466,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="71" t="s">
-        <v>906</v>
+        <v>918</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C12" s="62" t="n">
         <f aca="false">IF(Assumptions!B16=0,0,C11/Assumptions!B16)</f>
@@ -6466,7 +6502,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>908</v>
+        <v>920</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -6481,28 +6517,28 @@
         <v>5</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>909</v>
+        <v>921</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>100</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>7</v>
@@ -6762,7 +6798,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -6779,7 +6815,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="50" t="s">
-        <v>911</v>
+        <v>923</v>
       </c>
       <c r="B22" s="50"/>
       <c r="C22" s="50"/>
@@ -6799,7 +6835,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="50" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="B23" s="50"/>
       <c r="C23" s="50"/>
@@ -6816,7 +6852,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="50" t="s">
-        <v>913</v>
+        <v>925</v>
       </c>
       <c r="B24" s="50"/>
       <c r="C24" s="50"/>
@@ -6884,7 +6920,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="50" t="s">
-        <v>914</v>
+        <v>926</v>
       </c>
       <c r="B28" s="50"/>
       <c r="C28" s="50"/>
@@ -6901,7 +6937,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>915</v>
+        <v>927</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
@@ -6938,7 +6974,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="66" t="s">
-        <v>916</v>
+        <v>928</v>
       </c>
       <c r="B31" s="66"/>
       <c r="C31" s="66"/>
@@ -6956,12 +6992,12 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="71" t="s">
-        <v>917</v>
+        <v>929</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="95" t="s">
-        <v>918</v>
+        <v>930</v>
       </c>
       <c r="B34" s="95"/>
       <c r="C34" s="95"/>
@@ -6975,7 +7011,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="B35" s="90" t="n">
         <f aca="false">J21</f>
@@ -6984,7 +7020,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="B36" s="90" t="n">
         <f aca="false">J31</f>
@@ -6993,7 +7029,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>920</v>
+        <v>932</v>
       </c>
       <c r="B37" s="90" t="n">
         <f aca="false">SUM(J22:J28)*(1+I30)</f>
@@ -7045,7 +7081,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>921</v>
+        <v>933</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7054,7 +7090,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>922</v>
+        <v>934</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -7069,7 +7105,7 @@
         <v>42</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D5" s="29"/>
       <c r="E5" s="29"/>
@@ -7083,28 +7119,28 @@
         <v>19.99</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>923</v>
+        <v>935</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>924</v>
+        <v>936</v>
       </c>
       <c r="B7" s="97" t="n">
         <f aca="false">B6*Assumptions!B70</f>
         <v>15.992</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>925</v>
+        <v>937</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="B8" s="97" t="n">
         <f aca="false">B7*(1-Assumptions!B71)</f>
@@ -7116,35 +7152,35 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="B9" s="74" t="n">
         <f aca="false">Assumptions!B72*(1-Assumptions!B74)+Assumptions!B73*Assumptions!B74</f>
         <v>0.29</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>928</v>
+        <v>940</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>929</v>
+        <v>941</v>
       </c>
       <c r="B10" s="98" t="n">
         <f aca="false">B8*(1-B9)</f>
         <v>10.4459744</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>931</v>
+        <v>943</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -7159,7 +7195,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="29"/>
@@ -7173,70 +7209,70 @@
         <v>460504.8</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>932</v>
+        <v>944</v>
       </c>
       <c r="D14" s="33"/>
       <c r="E14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="66" t="s">
-        <v>933</v>
+        <v>945</v>
       </c>
       <c r="B15" s="99" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B14/B10,0))</f>
         <v>44085</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>934</v>
+        <v>946</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>935</v>
+        <v>947</v>
       </c>
       <c r="B16" s="89" t="n">
         <f aca="false">TeamBudget!B37</f>
         <v>98632.8</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="66" t="s">
-        <v>937</v>
+        <v>949</v>
       </c>
       <c r="B17" s="99" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B16/B10,0))</f>
         <v>9443</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>938</v>
+        <v>950</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>939</v>
+        <v>951</v>
       </c>
       <c r="B18" s="90" t="n">
         <f aca="false">B15*B6</f>
         <v>881259.15</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>940</v>
+        <v>952</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>941</v>
+        <v>953</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -7245,19 +7281,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>942</v>
+        <v>954</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>943</v>
+        <v>955</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>944</v>
+        <v>956</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>945</v>
+        <v>957</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7372,7 +7408,7 @@
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="54" t="s">
-        <v>946</v>
+        <v>958</v>
       </c>
       <c r="B28" s="54"/>
       <c r="C28" s="54"/>
@@ -7454,7 +7490,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7466,195 +7502,195 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>948</v>
+        <v>960</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>949</v>
+        <v>961</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>950</v>
+        <v>962</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>951</v>
+        <v>963</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>952</v>
+        <v>964</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="B5" s="86" t="n">
         <f aca="false">Schedule!D5</f>
         <v>46383</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>953</v>
+        <v>965</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>954</v>
+        <v>966</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F5" s="69" t="s">
-        <v>955</v>
+        <v>967</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>957</v>
+        <v>969</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="B6" s="86" t="n">
         <f aca="false">Schedule!D6</f>
         <v>46453</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>958</v>
+        <v>970</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>959</v>
+        <v>971</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>955</v>
+        <v>967</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>960</v>
+        <v>972</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>961</v>
+        <v>973</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="B7" s="86" t="n">
         <f aca="false">Schedule!D7</f>
         <v>46579</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F7" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>965</v>
+        <v>977</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="B8" s="86" t="n">
         <f aca="false">Schedule!D8</f>
         <v>46621</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>966</v>
+        <v>978</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>967</v>
+        <v>979</v>
       </c>
       <c r="E8" s="58" t="s">
         <v>100</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>968</v>
+        <v>980</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>969</v>
+        <v>981</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="B9" s="86" t="n">
         <f aca="false">Schedule!D9</f>
         <v>46663</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>970</v>
+        <v>982</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="F9" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>972</v>
+        <v>984</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>973</v>
+        <v>985</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="B10" s="86" t="n">
         <f aca="false">Schedule!D10</f>
         <v>46691</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>974</v>
+        <v>986</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>975</v>
+        <v>987</v>
       </c>
       <c r="E10" s="58" t="s">
         <v>100</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>976</v>
+        <v>988</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>977</v>
+        <v>989</v>
       </c>
       <c r="B12" s="54"/>
       <c r="C12" s="54"/>
@@ -7734,7 +7770,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>978</v>
+        <v>990</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7748,31 +7784,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>979</v>
+        <v>991</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>980</v>
+        <v>992</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>981</v>
+        <v>993</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>982</v>
+        <v>994</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>983</v>
+        <v>995</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>984</v>
+        <v>996</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>44</v>
@@ -7780,10 +7816,10 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="58" t="s">
-        <v>985</v>
+        <v>997</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>986</v>
+        <v>998</v>
       </c>
       <c r="C5" s="43" t="n">
         <v>3</v>
@@ -7796,27 +7832,27 @@
         <v>15</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="H5" s="58" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="I5" s="58" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="J5" s="69" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>3</v>
@@ -7829,27 +7865,27 @@
         <v>12</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>992</v>
+        <v>1004</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="I6" s="58" t="s">
-        <v>993</v>
+        <v>1005</v>
       </c>
       <c r="J6" s="69" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="58" t="s">
-        <v>995</v>
+        <v>1007</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>2</v>
@@ -7862,27 +7898,27 @@
         <v>8</v>
       </c>
       <c r="F7" s="58" t="s">
-        <v>997</v>
+        <v>1009</v>
       </c>
       <c r="G7" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="H7" s="58" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="I7" s="58" t="s">
-        <v>998</v>
+        <v>1010</v>
       </c>
       <c r="J7" s="69" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>1000</v>
+        <v>1012</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>4</v>
@@ -7895,27 +7931,27 @@
         <v>12</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>1001</v>
+        <v>1013</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="I8" s="58" t="s">
-        <v>1002</v>
+        <v>1014</v>
       </c>
       <c r="J8" s="69" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="58" t="s">
-        <v>1003</v>
+        <v>1015</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>1004</v>
+        <v>1016</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>2</v>
@@ -7928,27 +7964,27 @@
         <v>6</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="I9" s="58" t="s">
+        <v>1018</v>
+      </c>
+      <c r="J9" s="69" t="s">
         <v>1006</v>
-      </c>
-      <c r="J9" s="69" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>1007</v>
+        <v>1019</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1008</v>
+        <v>1020</v>
       </c>
       <c r="C10" s="43" t="n">
         <v>2</v>
@@ -7961,27 +7997,27 @@
         <v>10</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="I10" s="58" t="s">
-        <v>1010</v>
+        <v>1022</v>
       </c>
       <c r="J10" s="69" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="58" t="s">
-        <v>1011</v>
+        <v>1023</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>1012</v>
+        <v>1024</v>
       </c>
       <c r="C11" s="43" t="n">
         <v>3</v>
@@ -7994,27 +8030,27 @@
         <v>12</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>1013</v>
+        <v>1025</v>
       </c>
       <c r="G11" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H11" s="58" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="I11" s="58" t="s">
-        <v>1014</v>
+        <v>1026</v>
       </c>
       <c r="J11" s="69" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>1015</v>
+        <v>1027</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1016</v>
+        <v>1028</v>
       </c>
       <c r="C12" s="43" t="n">
         <v>2</v>
@@ -8027,27 +8063,27 @@
         <v>8</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>1017</v>
+        <v>1029</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="I12" s="58" t="s">
-        <v>1018</v>
+        <v>1030</v>
       </c>
       <c r="J12" s="69" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="58" t="s">
-        <v>1019</v>
+        <v>1031</v>
       </c>
       <c r="B13" s="58" t="s">
-        <v>1020</v>
+        <v>1032</v>
       </c>
       <c r="C13" s="43" t="n">
         <v>2</v>
@@ -8060,27 +8096,27 @@
         <v>4</v>
       </c>
       <c r="F13" s="58" t="s">
-        <v>1021</v>
+        <v>1033</v>
       </c>
       <c r="G13" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="H13" s="58" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="I13" s="58" t="s">
-        <v>1022</v>
+        <v>1034</v>
       </c>
       <c r="J13" s="69" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1023</v>
+        <v>1035</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1024</v>
+        <v>1036</v>
       </c>
       <c r="C14" s="43" t="n">
         <v>3</v>
@@ -8093,27 +8129,27 @@
         <v>12</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>1025</v>
+        <v>1037</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>1026</v>
+        <v>1038</v>
       </c>
       <c r="J14" s="69" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="58" t="s">
-        <v>1027</v>
+        <v>1039</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>1028</v>
+        <v>1040</v>
       </c>
       <c r="C15" s="43" t="n">
         <v>3</v>
@@ -8126,27 +8162,27 @@
         <v>15</v>
       </c>
       <c r="F15" s="58" t="s">
-        <v>1029</v>
+        <v>1041</v>
       </c>
       <c r="G15" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="H15" s="58" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="I15" s="58" t="s">
-        <v>1030</v>
+        <v>1042</v>
       </c>
       <c r="J15" s="69" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>1031</v>
+        <v>1043</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>1032</v>
+        <v>1044</v>
       </c>
       <c r="C16" s="43" t="n">
         <v>4</v>
@@ -8159,27 +8195,27 @@
         <v>16</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>1033</v>
+        <v>1045</v>
       </c>
       <c r="G16" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>1034</v>
+        <v>1046</v>
       </c>
       <c r="J16" s="69" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="58" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>1036</v>
+        <v>1048</v>
       </c>
       <c r="C17" s="43" t="n">
         <v>3</v>
@@ -8192,27 +8228,27 @@
         <v>12</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>1037</v>
+        <v>1049</v>
       </c>
       <c r="G17" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="58" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="I17" s="58" t="s">
-        <v>1038</v>
+        <v>1050</v>
       </c>
       <c r="J17" s="69" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>1039</v>
+        <v>1051</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="C18" s="43" t="n">
         <v>2</v>
@@ -8225,27 +8261,27 @@
         <v>6</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
       <c r="G18" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="H18" s="58" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>1042</v>
+        <v>1054</v>
       </c>
       <c r="J18" s="69" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="58" t="s">
-        <v>1043</v>
+        <v>1055</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>1044</v>
+        <v>1056</v>
       </c>
       <c r="C19" s="43" t="n">
         <v>2</v>
@@ -8258,27 +8294,27 @@
         <v>8</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>1045</v>
+        <v>1057</v>
       </c>
       <c r="G19" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="H19" s="58" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="I19" s="58" t="s">
-        <v>1046</v>
+        <v>1058</v>
       </c>
       <c r="J19" s="69" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>1047</v>
+        <v>1059</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1048</v>
+        <v>1060</v>
       </c>
       <c r="C20" s="43" t="n">
         <v>3</v>
@@ -8291,19 +8327,19 @@
         <v>15</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>1049</v>
+        <v>1061</v>
       </c>
       <c r="G20" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H20" s="58" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>1050</v>
+        <v>1062</v>
       </c>
       <c r="J20" s="69" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
   </sheetData>
@@ -8381,7 +8417,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1051</v>
+        <v>1063</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8392,278 +8428,278 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1053</v>
+        <v>1065</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>1054</v>
+        <v>1066</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>1055</v>
+        <v>1067</v>
       </c>
       <c r="E4" s="57" t="s">
         <v>95</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1056</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1057</v>
+        <v>1069</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1058</v>
+        <v>1070</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1059</v>
+        <v>1071</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>1061</v>
+        <v>1073</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1062</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1063</v>
+        <v>1075</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1064</v>
+        <v>1076</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>1067</v>
+        <v>1079</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>1068</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1069</v>
+        <v>1081</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1070</v>
+        <v>1082</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1071</v>
+        <v>1083</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1072</v>
+        <v>1084</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>1073</v>
+        <v>1085</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1068</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>1074</v>
+        <v>1086</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>1075</v>
+        <v>1087</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>1076</v>
+        <v>1088</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>1077</v>
+        <v>1089</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>1078</v>
+        <v>1090</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>1079</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1080</v>
+        <v>1092</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1081</v>
+        <v>1093</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1082</v>
+        <v>1094</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1083</v>
+        <v>1095</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1084</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1085</v>
+        <v>1097</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>1086</v>
+        <v>1098</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>1087</v>
+        <v>1099</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>1088</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1089</v>
+        <v>1101</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1090</v>
+        <v>1102</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1091</v>
+        <v>1103</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>1092</v>
+        <v>1104</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>1093</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1094</v>
+        <v>1106</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>1095</v>
+        <v>1107</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>1096</v>
+        <v>1108</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>1097</v>
+        <v>1109</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>1068</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1098</v>
+        <v>1110</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1099</v>
+        <v>1111</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1100</v>
+        <v>1112</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1101</v>
+        <v>1113</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>1102</v>
+        <v>1114</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>1068</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1103</v>
+        <v>1115</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1104</v>
+        <v>1116</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1105</v>
+        <v>1117</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>1106</v>
+        <v>1118</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>1107</v>
+        <v>1119</v>
       </c>
       <c r="F14" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>1108</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1110</v>
+        <v>1122</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1111</v>
+        <v>1123</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1112</v>
+        <v>1124</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>1113</v>
+        <v>1125</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>1114</v>
+        <v>1126</v>
       </c>
     </row>
   </sheetData>
@@ -8705,7 +8741,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1115</v>
+        <v>1127</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8716,24 +8752,24 @@
         <v>110</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1116</v>
+        <v>1128</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>1117</v>
+        <v>1129</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1118</v>
+        <v>1130</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1119</v>
+        <v>1131</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>100</v>
@@ -8741,55 +8777,55 @@
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>1120</v>
+        <v>1132</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1121</v>
+        <v>1133</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1122</v>
+        <v>1134</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1123</v>
+        <v>1135</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1124</v>
+        <v>1136</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>1125</v>
+        <v>1137</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>1126</v>
+        <v>1138</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1127</v>
+        <v>1139</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1128</v>
+        <v>1140</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>100</v>
@@ -8797,27 +8833,27 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>1129</v>
+        <v>1141</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>1131</v>
+        <v>1143</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1132</v>
+        <v>1144</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>100</v>
@@ -8825,13 +8861,13 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>1133</v>
+        <v>1145</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1134</v>
+        <v>1146</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="D12" s="58" t="s">
         <v>100</v>
@@ -8839,41 +8875,41 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1135</v>
+        <v>1147</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1136</v>
+        <v>1148</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1137</v>
+        <v>1149</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1138</v>
+        <v>1150</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1139</v>
+        <v>1151</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1140</v>
+        <v>1152</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1141</v>
+        <v>1153</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>100</v>
@@ -8881,14 +8917,14 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>1142</v>
+        <v>1154</v>
       </c>
       <c r="B16" s="58" t="str">
         <f aca="false">"Premium at $"&amp;TEXT(Assumptions!B69,"0.00")&amp;". Launch discount no deeper than the realized-price factor on Assumptions."</f>
         <v>Premium at $19.99. Launch discount no deeper than the realized-price factor on Assumptions.</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="D16" s="58" t="s">
         <v>100</v>
@@ -8896,13 +8932,13 @@
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>1143</v>
+        <v>1155</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1144</v>
+        <v>1156</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>100</v>
@@ -8910,13 +8946,13 @@
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>1145</v>
+        <v>1157</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>100</v>
@@ -8924,27 +8960,27 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1147</v>
+        <v>1159</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>1148</v>
+        <v>1160</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1149</v>
+        <v>1161</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="D20" s="58" t="s">
         <v>100</v>
@@ -8952,27 +8988,27 @@
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>1150</v>
+        <v>1162</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1151</v>
+        <v>1163</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="58" t="s">
-        <v>1152</v>
+        <v>1164</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>1153</v>
+        <v>1165</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="D22" s="58" t="s">
         <v>100</v>
@@ -9018,7 +9054,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1154</v>
+        <v>1166</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9026,16 +9062,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1155</v>
+        <v>1167</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1156</v>
+        <v>1168</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1157</v>
+        <v>1169</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1158</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9043,13 +9079,13 @@
         <v>46311</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1159</v>
+        <v>1171</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1160</v>
+        <v>1172</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1161</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9057,13 +9093,13 @@
         <v>46311</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1159</v>
+        <v>1171</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1162</v>
+        <v>1174</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>1163</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9071,13 +9107,13 @@
         <v>46311</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1159</v>
+        <v>1171</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1164</v>
+        <v>1176</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1165</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9085,13 +9121,13 @@
         <v>46311</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>923</v>
+        <v>935</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>1166</v>
+        <v>1178</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>1167</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9099,13 +9135,13 @@
         <v>46311</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1168</v>
+        <v>1180</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1169</v>
+        <v>1181</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1170</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9116,10 +9152,10 @@
         <v>53</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>1171</v>
+        <v>1183</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>1172</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9127,13 +9163,13 @@
         <v>46311</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1173</v>
+        <v>1185</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1174</v>
+        <v>1186</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1175</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9141,13 +9177,13 @@
         <v>46311</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>1176</v>
+        <v>1188</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>1177</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9155,13 +9191,13 @@
         <v>46311</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1178</v>
+        <v>1190</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1179</v>
+        <v>1191</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1180</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9169,13 +9205,13 @@
         <v>46311</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1181</v>
+        <v>1193</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1182</v>
+        <v>1194</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>1183</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9186,10 +9222,10 @@
         <v>58</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1184</v>
+        <v>1196</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1185</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9197,13 +9233,13 @@
         <v>46311</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>1186</v>
+        <v>1198</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9214,10 +9250,10 @@
         <v>62</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1189</v>
+        <v>1201</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1190</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9225,13 +9261,13 @@
         <v>46311</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>1191</v>
+        <v>1203</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>1192</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9239,13 +9275,13 @@
         <v>46311</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1193</v>
+        <v>1205</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>1194</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9253,13 +9289,13 @@
         <v>46311</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1195</v>
+        <v>1207</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>1196</v>
+        <v>1208</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>1197</v>
+        <v>1209</v>
       </c>
     </row>
   </sheetData>
@@ -9283,7 +9319,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F158"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
@@ -10781,6 +10817,72 @@
       </c>
       <c r="C152" s="41" t="s">
         <v>311</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="42" t="s">
+        <v>312</v>
+      </c>
+      <c r="B153" s="51" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="C153" s="41" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="B154" s="43" t="n">
+        <v>75</v>
+      </c>
+      <c r="C154" s="41" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="B155" s="51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C155" s="41" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="50" t="s">
+        <v>318</v>
+      </c>
+      <c r="B156" s="51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C156" s="41" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A157" s="42" t="s">
+        <v>320</v>
+      </c>
+      <c r="B157" s="51" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C157" s="41" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="50" t="s">
+        <v>322</v>
+      </c>
+      <c r="B158" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C158" s="41" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -10846,7 +10948,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -10855,160 +10957,160 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="D8" s="58" t="s">
+        <v>346</v>
+      </c>
+      <c r="E8" s="58" t="s">
         <v>334</v>
-      </c>
-      <c r="E8" s="58" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -11017,16 +11119,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>95</v>
@@ -11034,58 +11136,58 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="E16" s="59" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="58" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="E17" s="58" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="24"/>
@@ -11094,87 +11196,87 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="58" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C23" s="58" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D23" s="58" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="E23" s="58" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="58" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="B25" s="58" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="C25" s="58" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="D25" s="58" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="E25" s="58" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -11227,7 +11329,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11238,33 +11340,33 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F4" s="57" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>134</v>
@@ -11274,37 +11376,37 @@
         <v>24</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="D6" s="60" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F6" s="58" t="s">
         <v>98</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11312,71 +11414,71 @@
         <v>228</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="D7" s="60" t="n">
         <f aca="false">Assumptions!B44</f>
         <v>120</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="D8" s="60" t="n">
         <f aca="false">Assumptions!B46</f>
         <v>400</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="F8" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="D9" s="60" t="n">
         <f aca="false">Assumptions!B45</f>
         <v>120</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11384,151 +11486,151 @@
         <v>219</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="F10" s="58" t="s">
         <v>98</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="F12" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="D13" s="60" t="n">
         <f aca="false">Assumptions!B43</f>
         <v>168</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="D14" s="60" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="F14" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="D15" s="60" t="n">
         <f aca="false">Assumptions!B50</f>
         <v>5</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="D16" s="60" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -11541,78 +11643,78 @@
         <v>102</v>
       </c>
       <c r="G16" s="58" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="D17" s="60" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="F17" s="27" t="s">
         <v>102</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="F18" s="58" t="s">
         <v>104</v>
       </c>
       <c r="G18" s="58" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D19" s="60" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="F19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11620,46 +11722,46 @@
         <v>224</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="F20" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G20" s="58" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="D21" s="60" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11667,55 +11769,55 @@
         <v>236</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="D22" s="60" t="n">
         <f aca="false">Assumptions!B57</f>
         <v>2</v>
       </c>
       <c r="E22" s="58" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="F22" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G22" s="58" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="D23" s="60" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="58" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="B24" s="58" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="C24" s="58" t="s">
         <v>134</v>
@@ -11725,13 +11827,13 @@
         <v>24</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="F24" s="58" t="s">
         <v>98</v>
       </c>
       <c r="G24" s="58" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -11777,7 +11879,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11786,7 +11888,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -11801,21 +11903,21 @@
         <v>42</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="B6" s="61" t="n">
         <f aca="false">Assumptions!B62</f>
         <v>1200</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
@@ -11829,21 +11931,21 @@
         <v>120</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B8" s="62" t="n">
         <f aca="false">IF(B7=0,0,B6/B7)</f>
         <v>10</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="33"/>
@@ -11857,7 +11959,7 @@
         <v>1.3</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
@@ -11871,14 +11973,14 @@
         <v>13</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -11887,24 +11989,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="B14" s="60" t="n">
         <f aca="false">Assumptions!B42</f>
@@ -11919,12 +12021,12 @@
         <v>9.6</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="B15" s="60" t="n">
         <f aca="false">Assumptions!B57</f>
@@ -11939,12 +12041,12 @@
         <v>3</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B16" s="60" t="n">
         <f aca="false">Assumptions!B58</f>
@@ -11962,7 +12064,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B17" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B43,0)</f>
@@ -11976,12 +12078,12 @@
         <v>2</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="B18" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B44,0)</f>
@@ -11995,12 +12097,12 @@
         <v>3</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="B19" s="32" t="n">
         <f aca="false">ROUNDUP((B15+B16*Assumptions!B60)*$B$10/Assumptions!B59,0)</f>
@@ -12014,12 +12116,12 @@
         <v>2</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B20" s="60" t="n">
         <f aca="false">Assumptions!B61</f>
@@ -12038,7 +12140,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -12050,7 +12152,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="D22" s="64" t="n">
         <f aca="false">Assumptions!B41</f>
@@ -12059,7 +12161,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="66" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
@@ -12074,7 +12176,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -12083,24 +12185,24 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="B27" s="60" t="n">
         <f aca="false">Assumptions!B64</f>
@@ -12120,7 +12222,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="58" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="B28" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B43,0)</f>
@@ -12134,12 +12236,12 @@
         <v>1</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B44,0)</f>
@@ -12156,7 +12258,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="D30" s="62" t="n">
         <f aca="false">SUM(D27:D29)</f>
@@ -12165,7 +12267,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="D31" s="62" t="n">
         <f aca="false">Assumptions!B41-D30</f>
@@ -12174,7 +12276,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="D32" s="32" t="n">
         <f aca="false">INT(D31/Assumptions!B65)</f>
@@ -12183,7 +12285,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="D33" s="60" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -12192,7 +12294,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="66" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="B34" s="66"/>
       <c r="C34" s="66"/>
@@ -12207,7 +12309,7 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="54" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="B36" s="54"/>
       <c r="C36" s="54"/>
@@ -12288,7 +12390,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12303,392 +12405,392 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="H5" s="69" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B6" s="58" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="H6" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="58" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="J6" s="58" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="K6" s="58" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="H7" s="69" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="B8" s="58" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="H8" s="69" t="n">
         <v>3</v>
       </c>
       <c r="I8" s="58" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="J8" s="58" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="K8" s="58" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="H9" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="B10" s="58" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="H10" s="69" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="58" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="J10" s="58" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="K10" s="58" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="H11" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="B12" s="58" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="H12" s="69" t="n">
         <v>3</v>
       </c>
       <c r="I12" s="58" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="J12" s="58" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="K12" s="58" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="H13" s="69" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="H14" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="J14" s="58" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="K14" s="58" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
@@ -12700,10 +12802,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="B17" s="70" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="C17" s="70"/>
       <c r="D17" s="70"/>
@@ -12714,10 +12816,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="B18" s="70" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="C18" s="70"/>
       <c r="D18" s="70"/>
@@ -12728,10 +12830,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="B19" s="70" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="C19" s="70"/>
       <c r="D19" s="70"/>
@@ -12742,10 +12844,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
       <c r="B20" s="70" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="C20" s="70"/>
       <c r="D20" s="70"/>
@@ -12756,10 +12858,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="B21" s="70" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="C21" s="70"/>
       <c r="D21" s="70"/>
@@ -12770,10 +12872,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="B22" s="70" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="C22" s="70"/>
       <c r="D22" s="70"/>
@@ -12784,10 +12886,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="B23" s="70" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="C23" s="70"/>
       <c r="D23" s="70"/>
@@ -12798,7 +12900,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="71" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>
@@ -12862,7 +12964,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12876,42 +12978,42 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
@@ -12920,190 +13022,190 @@
         <v>96</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G5" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="I5" s="69" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="D6" s="58" t="s">
         <v>96</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G6" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="I6" s="69" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="J6" s="58" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G7" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="I7" s="69" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="D8" s="58" t="s">
         <v>96</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="G8" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="I8" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J8" s="58" t="s">
-        <v>670</v>
+        <v>682</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G9" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="I9" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="D10" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G10" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="I10" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J10" s="58" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>23</v>
@@ -13112,30 +13214,30 @@
         <v>98</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G11" s="43" t="n">
         <v>12</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="I11" s="69" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="C12" s="58" t="s">
         <v>23</v>
@@ -13144,30 +13246,30 @@
         <v>98</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G12" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="I12" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J12" s="58" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>26</v>
@@ -13176,62 +13278,62 @@
         <v>98</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G13" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="I13" s="69" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D14" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G14" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="I14" s="69" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="J14" s="58" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>35</v>
@@ -13240,263 +13342,263 @@
         <v>98</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G15" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="I15" s="69" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="J15" s="27" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="D16" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G16" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="I16" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J16" s="58" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G17" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="I17" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="G18" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H18" s="58" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="I18" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J18" s="58" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G19" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="I19" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="D20" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G20" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H20" s="58" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="I20" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J20" s="58" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G21" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="I21" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J21" s="27" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="58" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="D22" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E22" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F22" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G22" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="58" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="I22" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J22" s="58" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
@@ -13505,117 +13607,117 @@
         <v>3</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="I23" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="58" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B24" s="58" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="D24" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F24" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G24" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H24" s="58" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="I24" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J24" s="58" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="D25" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G25" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="I25" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J25" s="27" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="58" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="B26" s="58" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="D26" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F26" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G26" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H26" s="58" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="I26" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J26" s="58" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="C27" s="27" t="s">
         <v>29</v>
@@ -13624,30 +13726,30 @@
         <v>100</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G27" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="I27" s="69" t="s">
-        <v>669</v>
+        <v>685</v>
       </c>
       <c r="J27" s="27" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="58" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="B28" s="58" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="C28" s="58" t="s">
         <v>32</v>
@@ -13656,30 +13758,30 @@
         <v>100</v>
       </c>
       <c r="E28" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F28" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G28" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H28" s="58" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="I28" s="69" t="s">
-        <v>669</v>
+        <v>685</v>
       </c>
       <c r="J28" s="58" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="C29" s="27" t="s">
         <v>26</v>
@@ -13688,94 +13790,94 @@
         <v>100</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G29" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="I29" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="58" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="B30" s="58" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="C30" s="58" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="D30" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F30" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G30" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="58" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="I30" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J30" s="58" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D31" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G31" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="I31" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J31" s="27" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="58" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="B32" s="58" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="C32" s="58" t="s">
         <v>35</v>
@@ -13784,30 +13886,30 @@
         <v>100</v>
       </c>
       <c r="E32" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F32" s="58" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="G32" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H32" s="58" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="I32" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J32" s="58" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="C33" s="27" t="s">
         <v>35</v>
@@ -13816,487 +13918,487 @@
         <v>100</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G33" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="I33" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J33" s="27" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="58" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="B34" s="58" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="C34" s="58" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="D34" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F34" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G34" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H34" s="58" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="I34" s="69" t="s">
-        <v>669</v>
+        <v>685</v>
       </c>
       <c r="J34" s="58" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="D35" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G35" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="I35" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J35" s="27" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="58" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="B36" s="58" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="D36" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F36" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G36" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H36" s="58" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="I36" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J36" s="58" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="27" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="D37" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G37" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H37" s="27" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="I37" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J37" s="27" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="58" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="C38" s="58" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D38" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="58" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="F38" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G38" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="58" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="I38" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J38" s="58" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="27" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="D39" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G39" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="I39" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J39" s="27" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="58" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="B40" s="58" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D40" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F40" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G40" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H40" s="58" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="I40" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J40" s="58" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D41" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G41" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="I41" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J41" s="27" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="58" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="B42" s="58" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="C42" s="58" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D42" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="58" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="F42" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G42" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="58" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="I42" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J42" s="58" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="D43" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="G43" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H43" s="27" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="I43" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J43" s="27" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="58" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="B44" s="58" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="C44" s="58" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="D44" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E44" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F44" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G44" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H44" s="58" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="I44" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J44" s="58" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="27" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="D45" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G45" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H45" s="27" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="I45" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J45" s="27" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="58" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="B46" s="58" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="C46" s="58" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="D46" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E46" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F46" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G46" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H46" s="58" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="I46" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J46" s="58" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="D47" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G47" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H47" s="27" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="I47" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J47" s="27" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="58" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="B48" s="58" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="C48" s="58" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D48" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E48" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F48" s="58" t="s">
         <v>100</v>
@@ -14305,62 +14407,62 @@
         <v>3</v>
       </c>
       <c r="H48" s="58" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="I48" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J48" s="58" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="27" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="D49" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G49" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H49" s="27" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="I49" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J49" s="27" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="58" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="C50" s="58" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="D50" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E50" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F50" s="58" t="s">
         <v>100</v>
@@ -14369,181 +14471,181 @@
         <v>4</v>
       </c>
       <c r="H50" s="58" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="I50" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J50" s="58" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="D51" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G51" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H51" s="27" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="I51" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J51" s="27" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="58" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="C52" s="58" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="D52" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E52" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F52" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G52" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H52" s="58" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="I52" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J52" s="58" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="27" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="D53" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F53" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G53" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H53" s="27" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="I53" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J53" s="27" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="58" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="B54" s="58" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="C54" s="58" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="D54" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E54" s="58" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="F54" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G54" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H54" s="58" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="I54" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J54" s="58" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D55" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="F55" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G55" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="I55" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J55" s="27" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="58" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="B56" s="58" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="C56" s="58" t="s">
         <v>26</v>
@@ -14552,359 +14654,359 @@
         <v>102</v>
       </c>
       <c r="E56" s="58" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="F56" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G56" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H56" s="58" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="I56" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J56" s="58" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="D57" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G57" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H57" s="27" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="I57" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J57" s="27" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="58" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="B58" s="58" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="C58" s="58" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="D58" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E58" s="58" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="F58" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G58" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H58" s="58" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="I58" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J58" s="58" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="27" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="D59" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E59" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G59" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H59" s="27" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="I59" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J59" s="27" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="58" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="B60" s="58" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="C60" s="58" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="D60" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E60" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F60" s="58" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="G60" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H60" s="58" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="I60" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J60" s="58" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="27" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="D61" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G61" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H61" s="27" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="I61" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J61" s="27" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="58" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="B62" s="58" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="C62" s="58" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="D62" s="58" t="s">
         <v>104</v>
       </c>
       <c r="E62" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F62" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G62" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H62" s="58" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="I62" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J62" s="58" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="27" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
       <c r="C63" s="27" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="D63" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E63" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G63" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H63" s="27" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="I63" s="69" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="J63" s="27" t="s">
-        <v>827</v>
+        <v>839</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="58" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
       <c r="B64" s="58" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="C64" s="58" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="D64" s="58" t="s">
         <v>104</v>
       </c>
       <c r="E64" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F64" s="58" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G64" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H64" s="58" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="I64" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J64" s="58" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="27" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="C65" s="27" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="D65" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E65" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G65" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H65" s="27" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="I65" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J65" s="27" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="58" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="B66" s="58" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="C66" s="58" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="D66" s="58" t="s">
         <v>104</v>
       </c>
       <c r="E66" s="58" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="F66" s="58" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G66" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H66" s="58" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="I66" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J66" s="58" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="27" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="D67" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F67" s="27" t="s">
         <v>100</v>
@@ -14913,30 +15015,30 @@
         <v>5</v>
       </c>
       <c r="H67" s="27" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="I67" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J67" s="27" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="58" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="B68" s="58" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="C68" s="58" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="D68" s="58" t="s">
         <v>106</v>
       </c>
       <c r="E68" s="58" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F68" s="58" t="s">
         <v>100</v>
@@ -14945,45 +15047,45 @@
         <v>1</v>
       </c>
       <c r="H68" s="58" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="I68" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J68" s="58" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="27" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>844</v>
+        <v>856</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="D69" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E69" s="27" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F69" s="27" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G69" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H69" s="27" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="I69" s="69" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="J69" s="27" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15120,7 +15222,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D82" s="72" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
       <c r="E82" s="72"/>
       <c r="F82" s="72"/>
@@ -15131,7 +15233,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D83" s="73" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="E83" s="73"/>
       <c r="F83" s="73"/>
@@ -15142,7 +15244,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D84" s="73" t="s">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="E84" s="73"/>
       <c r="F84" s="73"/>
@@ -15153,7 +15255,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D85" s="73" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="E85" s="73"/>
       <c r="F85" s="73"/>
@@ -15164,7 +15266,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D86" s="73" t="s">
-        <v>850</v>
+        <v>862</v>
       </c>
       <c r="E86" s="73"/>
       <c r="F86" s="73"/>
@@ -15175,7 +15277,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -15189,25 +15291,25 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="B90" s="9"/>
       <c r="C90" s="9" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="75" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B91" s="75"/>
       <c r="C91" s="32" t="n">
@@ -15229,7 +15331,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="75" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="B92" s="75"/>
       <c r="C92" s="32" t="n">
@@ -15251,7 +15353,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="75" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="B93" s="75"/>
       <c r="C93" s="32" t="n">
@@ -15273,7 +15375,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="75" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="B94" s="75"/>
       <c r="C94" s="32" t="n">
@@ -15295,7 +15397,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="75" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="B95" s="75"/>
       <c r="C95" s="32" t="n">
@@ -15339,7 +15441,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="72" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="B97" s="72"/>
       <c r="C97" s="21" t="n">
@@ -15365,16 +15467,16 @@
       </c>
       <c r="B99" s="29"/>
       <c r="C99" s="9" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15517,7 +15619,7 @@
     </row>
     <row r="107" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="54" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="B107" s="54"/>
       <c r="C107" s="54"/>
@@ -15651,7 +15753,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>859</v>
+        <v>871</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -15669,22 +15771,22 @@
         <v>6</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15705,16 +15807,16 @@
         <v>46383</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>868</v>
+        <v>880</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15735,16 +15837,16 @@
         <v>46453</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>870</v>
+        <v>882</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15765,16 +15867,16 @@
         <v>46579</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>875</v>
+        <v>887</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15795,16 +15897,16 @@
         <v>46621</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15825,16 +15927,16 @@
         <v>46663</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15855,21 +15957,21 @@
         <v>46691</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>889</v>
+        <v>901</v>
       </c>
       <c r="B12" s="81" t="n">
         <f aca="false">D10</f>
@@ -15879,7 +15981,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>890</v>
+        <v>902</v>
       </c>
       <c r="B13" s="82" t="n">
         <f aca="false">B12-Assumptions!B7</f>
@@ -15889,7 +15991,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="24"/>
@@ -15901,7 +16003,7 @@
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="B15" s="54"/>
       <c r="C15" s="54"/>
@@ -15913,7 +16015,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="54" t="s">
-        <v>893</v>
+        <v>905</v>
       </c>
       <c r="B16" s="54"/>
       <c r="C16" s="54"/>
@@ -15993,7 +16095,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>894</v>
+        <v>906</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -16027,13 +16129,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>895</v>
+        <v>907</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="D4" s="83" t="n">
         <v>1</v>
@@ -16218,7 +16320,7 @@
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>896</v>
+        <v>908</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -16465,7 +16567,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>897</v>
+        <v>909</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -18236,7 +18338,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>898</v>
+        <v>910</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -18483,7 +18585,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>899</v>
+        <v>911</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>

--- a/docs/Vinland_Game_Development_Plan.xlsx
+++ b/docs/Vinland_Game_Development_Plan.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="1210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1973" uniqueCount="1247">
   <si>
     <t xml:space="preserve">VINLAND</t>
   </si>
@@ -1058,6 +1058,117 @@
   </si>
   <si>
     <t xml:space="preserve">Forage: greedy picking thins every patch until spring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARKET TUNING (GOODWILL, FEAR, TRADE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First market (days after landing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitors come once the camp is settled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market chance per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer and autumn only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market chance per point of goodwill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goodwill brings them back sooner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goodwill cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goodwill clock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelts the visitors bring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 to 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range per market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trade value for one pelt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before goodwill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price discount per point of goodwill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fair dealing makes trade easier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red cloth strips per trade unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One bolt of madder-red cloth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iron blades per trade unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One trade unit of iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milk per trade value (person-days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milk is the peace (Pillar P6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon request chance per market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Once goodwill reaches 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon sale pelt multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The temptation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fear from a weapon sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A weapon sale caps fear (Pillar P6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bull breaks loose chance (unpenned, no byre)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The saga bull (F21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fear from the bull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitors scatter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fear eased per quiet week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fear fades slowly when nothing happens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raid chance per week at the fear cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trade breaks; the herd and the crew are at risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelts per cargo unit</t>
   </si>
   <si>
     <t xml:space="preserve">Pillars, fantasy, clocks, and the win</t>
@@ -4920,11 +5031,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="95196207"/>
-        <c:axId val="37331758"/>
+        <c:axId val="34176278"/>
+        <c:axId val="17074735"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="95196207"/>
+        <c:axId val="34176278"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4956,7 +5067,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37331758"/>
+        <c:crossAx val="17074735"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4964,7 +5075,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37331758"/>
+        <c:axId val="17074735"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5040,7 +5151,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95196207"/>
+        <c:crossAx val="34176278"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5079,9 +5190,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>742320</xdr:colOff>
+      <xdr:colOff>741960</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>58680</xdr:rowOff>
+      <xdr:rowOff>58320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5090,7 +5201,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="6562800"/>
-        <a:ext cx="5394240" cy="2154240"/>
+        <a:ext cx="5393880" cy="2153880"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6172,7 +6283,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>912</v>
+        <v>949</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -6184,10 +6295,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>913</v>
+        <v>950</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>914</v>
+        <v>951</v>
       </c>
       <c r="C4" s="57" t="s">
         <v>96</v>
@@ -6208,7 +6319,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="57" t="s">
-        <v>915</v>
+        <v>952</v>
       </c>
       <c r="J4" s="57" t="s">
         <v>7</v>
@@ -6216,7 +6327,7 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="B5" s="89" t="n">
         <f aca="false">Assumptions!B26</f>
@@ -6251,7 +6362,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="B6" s="89" t="n">
         <f aca="false">Assumptions!B27</f>
@@ -6286,7 +6397,7 @@
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="B7" s="89" t="n">
         <f aca="false">Assumptions!B28</f>
@@ -6321,7 +6432,7 @@
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>773</v>
+        <v>810</v>
       </c>
       <c r="B8" s="89" t="n">
         <f aca="false">Assumptions!B29</f>
@@ -6356,7 +6467,7 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>828</v>
+        <v>865</v>
       </c>
       <c r="B9" s="89" t="n">
         <f aca="false">Assumptions!B30</f>
@@ -6426,10 +6537,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="71" t="s">
-        <v>916</v>
+        <v>953</v>
       </c>
       <c r="B11" s="71" t="s">
-        <v>917</v>
+        <v>954</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -6466,10 +6577,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="71" t="s">
-        <v>918</v>
+        <v>955</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>919</v>
+        <v>956</v>
       </c>
       <c r="C12" s="62" t="n">
         <f aca="false">IF(Assumptions!B16=0,0,C11/Assumptions!B16)</f>
@@ -6502,7 +6613,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>920</v>
+        <v>957</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -6517,28 +6628,28 @@
         <v>5</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>921</v>
+        <v>958</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>773</v>
+        <v>810</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>828</v>
+        <v>865</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>100</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>915</v>
+        <v>952</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>7</v>
@@ -6798,7 +6909,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>922</v>
+        <v>959</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -6815,7 +6926,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="50" t="s">
-        <v>923</v>
+        <v>960</v>
       </c>
       <c r="B22" s="50"/>
       <c r="C22" s="50"/>
@@ -6835,7 +6946,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="50" t="s">
-        <v>924</v>
+        <v>961</v>
       </c>
       <c r="B23" s="50"/>
       <c r="C23" s="50"/>
@@ -6852,7 +6963,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="50" t="s">
-        <v>925</v>
+        <v>962</v>
       </c>
       <c r="B24" s="50"/>
       <c r="C24" s="50"/>
@@ -6920,7 +7031,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="50" t="s">
-        <v>926</v>
+        <v>963</v>
       </c>
       <c r="B28" s="50"/>
       <c r="C28" s="50"/>
@@ -6937,7 +7048,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>927</v>
+        <v>964</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
@@ -6974,7 +7085,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="66" t="s">
-        <v>928</v>
+        <v>965</v>
       </c>
       <c r="B31" s="66"/>
       <c r="C31" s="66"/>
@@ -6992,12 +7103,12 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="71" t="s">
-        <v>929</v>
+        <v>966</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="95" t="s">
-        <v>930</v>
+        <v>967</v>
       </c>
       <c r="B34" s="95"/>
       <c r="C34" s="95"/>
@@ -7011,7 +7122,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>922</v>
+        <v>959</v>
       </c>
       <c r="B35" s="90" t="n">
         <f aca="false">J21</f>
@@ -7020,7 +7131,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>931</v>
+        <v>968</v>
       </c>
       <c r="B36" s="90" t="n">
         <f aca="false">J31</f>
@@ -7029,7 +7140,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>932</v>
+        <v>969</v>
       </c>
       <c r="B37" s="90" t="n">
         <f aca="false">SUM(J22:J28)*(1+I30)</f>
@@ -7081,7 +7192,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>933</v>
+        <v>970</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7090,7 +7201,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>934</v>
+        <v>971</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -7105,7 +7216,7 @@
         <v>42</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="D5" s="29"/>
       <c r="E5" s="29"/>
@@ -7119,28 +7230,28 @@
         <v>19.99</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>935</v>
+        <v>972</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>936</v>
+        <v>973</v>
       </c>
       <c r="B7" s="97" t="n">
         <f aca="false">B6*Assumptions!B70</f>
         <v>15.992</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>937</v>
+        <v>974</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>938</v>
+        <v>975</v>
       </c>
       <c r="B8" s="97" t="n">
         <f aca="false">B7*(1-Assumptions!B71)</f>
@@ -7152,35 +7263,35 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>939</v>
+        <v>976</v>
       </c>
       <c r="B9" s="74" t="n">
         <f aca="false">Assumptions!B72*(1-Assumptions!B74)+Assumptions!B73*Assumptions!B74</f>
         <v>0.29</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>940</v>
+        <v>977</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>941</v>
+        <v>978</v>
       </c>
       <c r="B10" s="98" t="n">
         <f aca="false">B8*(1-B9)</f>
         <v>10.4459744</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>942</v>
+        <v>979</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>943</v>
+        <v>980</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -7195,7 +7306,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="29"/>
@@ -7209,70 +7320,70 @@
         <v>460504.8</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>944</v>
+        <v>981</v>
       </c>
       <c r="D14" s="33"/>
       <c r="E14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="66" t="s">
-        <v>945</v>
+        <v>982</v>
       </c>
       <c r="B15" s="99" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B14/B10,0))</f>
         <v>44085</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>946</v>
+        <v>983</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>947</v>
+        <v>984</v>
       </c>
       <c r="B16" s="89" t="n">
         <f aca="false">TeamBudget!B37</f>
         <v>98632.8</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>948</v>
+        <v>985</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="66" t="s">
-        <v>949</v>
+        <v>986</v>
       </c>
       <c r="B17" s="99" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B16/B10,0))</f>
         <v>9443</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>950</v>
+        <v>987</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>951</v>
+        <v>988</v>
       </c>
       <c r="B18" s="90" t="n">
         <f aca="false">B15*B6</f>
         <v>881259.15</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>952</v>
+        <v>989</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>953</v>
+        <v>990</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -7281,19 +7392,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>954</v>
+        <v>991</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>955</v>
+        <v>992</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>956</v>
+        <v>993</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>957</v>
+        <v>994</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>867</v>
+        <v>904</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7408,7 +7519,7 @@
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="54" t="s">
-        <v>958</v>
+        <v>995</v>
       </c>
       <c r="B28" s="54"/>
       <c r="C28" s="54"/>
@@ -7490,7 +7601,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>959</v>
+        <v>996</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7502,195 +7613,195 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>877</v>
+        <v>914</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>960</v>
+        <v>997</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>961</v>
+        <v>998</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>962</v>
+        <v>999</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>963</v>
+        <v>1000</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>964</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>881</v>
+        <v>918</v>
       </c>
       <c r="B5" s="86" t="n">
         <f aca="false">Schedule!D5</f>
         <v>46383</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>965</v>
+        <v>1002</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>966</v>
+        <v>1003</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="F5" s="69" t="s">
-        <v>967</v>
+        <v>1004</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>968</v>
+        <v>1005</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>969</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="B6" s="86" t="n">
         <f aca="false">Schedule!D6</f>
         <v>46453</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>970</v>
+        <v>1007</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>971</v>
+        <v>1008</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>967</v>
+        <v>1004</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>972</v>
+        <v>1009</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>973</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>889</v>
+        <v>926</v>
       </c>
       <c r="B7" s="86" t="n">
         <f aca="false">Schedule!D7</f>
         <v>46579</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>974</v>
+        <v>1011</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>975</v>
+        <v>1012</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="F7" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>976</v>
+        <v>1013</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>977</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>893</v>
+        <v>930</v>
       </c>
       <c r="B8" s="86" t="n">
         <f aca="false">Schedule!D8</f>
         <v>46621</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>978</v>
+        <v>1015</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>979</v>
+        <v>1016</v>
       </c>
       <c r="E8" s="58" t="s">
         <v>100</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>980</v>
+        <v>1017</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>981</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>897</v>
+        <v>934</v>
       </c>
       <c r="B9" s="86" t="n">
         <f aca="false">Schedule!D9</f>
         <v>46663</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>982</v>
+        <v>1019</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>983</v>
+        <v>1020</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>828</v>
+        <v>865</v>
       </c>
       <c r="F9" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>984</v>
+        <v>1021</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>985</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>900</v>
+        <v>937</v>
       </c>
       <c r="B10" s="86" t="n">
         <f aca="false">Schedule!D10</f>
         <v>46691</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>986</v>
+        <v>1023</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>987</v>
+        <v>1024</v>
       </c>
       <c r="E10" s="58" t="s">
         <v>100</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>988</v>
+        <v>1025</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>439</v>
+        <v>476</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>989</v>
+        <v>1026</v>
       </c>
       <c r="B12" s="54"/>
       <c r="C12" s="54"/>
@@ -7770,7 +7881,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>990</v>
+        <v>1027</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7784,31 +7895,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>991</v>
+        <v>1028</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>992</v>
+        <v>1029</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>993</v>
+        <v>1030</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>994</v>
+        <v>1031</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>995</v>
+        <v>1032</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>996</v>
+        <v>1033</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>44</v>
@@ -7816,10 +7927,10 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="58" t="s">
-        <v>997</v>
+        <v>1034</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>998</v>
+        <v>1035</v>
       </c>
       <c r="C5" s="43" t="n">
         <v>3</v>
@@ -7832,27 +7943,27 @@
         <v>15</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>999</v>
+        <v>1036</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="H5" s="58" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="I5" s="58" t="s">
-        <v>1000</v>
+        <v>1037</v>
       </c>
       <c r="J5" s="69" t="s">
-        <v>1001</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>1002</v>
+        <v>1039</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1003</v>
+        <v>1040</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>3</v>
@@ -7865,27 +7976,27 @@
         <v>12</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>1004</v>
+        <v>1041</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="I6" s="58" t="s">
-        <v>1005</v>
+        <v>1042</v>
       </c>
       <c r="J6" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="58" t="s">
-        <v>1007</v>
+        <v>1044</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>1008</v>
+        <v>1045</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>2</v>
@@ -7898,27 +8009,27 @@
         <v>8</v>
       </c>
       <c r="F7" s="58" t="s">
-        <v>1009</v>
+        <v>1046</v>
       </c>
       <c r="G7" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="H7" s="58" t="s">
-        <v>897</v>
+        <v>934</v>
       </c>
       <c r="I7" s="58" t="s">
-        <v>1010</v>
+        <v>1047</v>
       </c>
       <c r="J7" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>1011</v>
+        <v>1048</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>1012</v>
+        <v>1049</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>4</v>
@@ -7931,27 +8042,27 @@
         <v>12</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>1013</v>
+        <v>1050</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>889</v>
+        <v>926</v>
       </c>
       <c r="I8" s="58" t="s">
-        <v>1014</v>
+        <v>1051</v>
       </c>
       <c r="J8" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="58" t="s">
-        <v>1015</v>
+        <v>1052</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>1016</v>
+        <v>1053</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>2</v>
@@ -7964,27 +8075,27 @@
         <v>6</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>1017</v>
+        <v>1054</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>889</v>
+        <v>926</v>
       </c>
       <c r="I9" s="58" t="s">
-        <v>1018</v>
+        <v>1055</v>
       </c>
       <c r="J9" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>1019</v>
+        <v>1056</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1020</v>
+        <v>1057</v>
       </c>
       <c r="C10" s="43" t="n">
         <v>2</v>
@@ -7997,27 +8108,27 @@
         <v>10</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>1021</v>
+        <v>1058</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>889</v>
+        <v>926</v>
       </c>
       <c r="I10" s="58" t="s">
-        <v>1022</v>
+        <v>1059</v>
       </c>
       <c r="J10" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="58" t="s">
-        <v>1023</v>
+        <v>1060</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>1024</v>
+        <v>1061</v>
       </c>
       <c r="C11" s="43" t="n">
         <v>3</v>
@@ -8030,27 +8141,27 @@
         <v>12</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>1025</v>
+        <v>1062</v>
       </c>
       <c r="G11" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H11" s="58" t="s">
-        <v>893</v>
+        <v>930</v>
       </c>
       <c r="I11" s="58" t="s">
-        <v>1026</v>
+        <v>1063</v>
       </c>
       <c r="J11" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>1027</v>
+        <v>1064</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1028</v>
+        <v>1065</v>
       </c>
       <c r="C12" s="43" t="n">
         <v>2</v>
@@ -8063,27 +8174,27 @@
         <v>8</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>1029</v>
+        <v>1066</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>881</v>
+        <v>918</v>
       </c>
       <c r="I12" s="58" t="s">
-        <v>1030</v>
+        <v>1067</v>
       </c>
       <c r="J12" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="58" t="s">
-        <v>1031</v>
+        <v>1068</v>
       </c>
       <c r="B13" s="58" t="s">
-        <v>1032</v>
+        <v>1069</v>
       </c>
       <c r="C13" s="43" t="n">
         <v>2</v>
@@ -8096,27 +8207,27 @@
         <v>4</v>
       </c>
       <c r="F13" s="58" t="s">
-        <v>1033</v>
+        <v>1070</v>
       </c>
       <c r="G13" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="H13" s="58" t="s">
-        <v>881</v>
+        <v>918</v>
       </c>
       <c r="I13" s="58" t="s">
-        <v>1034</v>
+        <v>1071</v>
       </c>
       <c r="J13" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1035</v>
+        <v>1072</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1036</v>
+        <v>1073</v>
       </c>
       <c r="C14" s="43" t="n">
         <v>3</v>
@@ -8129,27 +8240,27 @@
         <v>12</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>1037</v>
+        <v>1074</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>893</v>
+        <v>930</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>1038</v>
+        <v>1075</v>
       </c>
       <c r="J14" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="58" t="s">
-        <v>1039</v>
+        <v>1076</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>1040</v>
+        <v>1077</v>
       </c>
       <c r="C15" s="43" t="n">
         <v>3</v>
@@ -8162,27 +8273,27 @@
         <v>15</v>
       </c>
       <c r="F15" s="58" t="s">
-        <v>1041</v>
+        <v>1078</v>
       </c>
       <c r="G15" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="H15" s="58" t="s">
-        <v>889</v>
+        <v>926</v>
       </c>
       <c r="I15" s="58" t="s">
-        <v>1042</v>
+        <v>1079</v>
       </c>
       <c r="J15" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>1043</v>
+        <v>1080</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>1044</v>
+        <v>1081</v>
       </c>
       <c r="C16" s="43" t="n">
         <v>4</v>
@@ -8195,27 +8306,27 @@
         <v>16</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>1045</v>
+        <v>1082</v>
       </c>
       <c r="G16" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>1046</v>
+        <v>1083</v>
       </c>
       <c r="J16" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="58" t="s">
-        <v>1047</v>
+        <v>1084</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>1048</v>
+        <v>1085</v>
       </c>
       <c r="C17" s="43" t="n">
         <v>3</v>
@@ -8228,27 +8339,27 @@
         <v>12</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>1049</v>
+        <v>1086</v>
       </c>
       <c r="G17" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="58" t="s">
-        <v>889</v>
+        <v>926</v>
       </c>
       <c r="I17" s="58" t="s">
-        <v>1050</v>
+        <v>1087</v>
       </c>
       <c r="J17" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>1051</v>
+        <v>1088</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>1052</v>
+        <v>1089</v>
       </c>
       <c r="C18" s="43" t="n">
         <v>2</v>
@@ -8261,27 +8372,27 @@
         <v>6</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>1053</v>
+        <v>1090</v>
       </c>
       <c r="G18" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="H18" s="58" t="s">
-        <v>897</v>
+        <v>934</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>1054</v>
+        <v>1091</v>
       </c>
       <c r="J18" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="58" t="s">
-        <v>1055</v>
+        <v>1092</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>1056</v>
+        <v>1093</v>
       </c>
       <c r="C19" s="43" t="n">
         <v>2</v>
@@ -8294,27 +8405,27 @@
         <v>8</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>1057</v>
+        <v>1094</v>
       </c>
       <c r="G19" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="H19" s="58" t="s">
-        <v>889</v>
+        <v>926</v>
       </c>
       <c r="I19" s="58" t="s">
-        <v>1058</v>
+        <v>1095</v>
       </c>
       <c r="J19" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>1059</v>
+        <v>1096</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1060</v>
+        <v>1097</v>
       </c>
       <c r="C20" s="43" t="n">
         <v>3</v>
@@ -8327,19 +8438,19 @@
         <v>15</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>1061</v>
+        <v>1098</v>
       </c>
       <c r="G20" s="58" t="s">
         <v>100</v>
       </c>
       <c r="H20" s="58" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>1062</v>
+        <v>1099</v>
       </c>
       <c r="J20" s="69" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
     </row>
   </sheetData>
@@ -8417,7 +8528,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1063</v>
+        <v>1100</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8428,278 +8539,278 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>1064</v>
+        <v>1101</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1065</v>
+        <v>1102</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>1066</v>
+        <v>1103</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>1067</v>
+        <v>1104</v>
       </c>
       <c r="E4" s="57" t="s">
         <v>95</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1068</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1069</v>
+        <v>1106</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1070</v>
+        <v>1107</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1071</v>
+        <v>1108</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1072</v>
+        <v>1109</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>1073</v>
+        <v>1110</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1074</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>633</v>
+        <v>670</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1075</v>
+        <v>1112</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1076</v>
+        <v>1113</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>1077</v>
+        <v>1114</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>1078</v>
+        <v>1115</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>1079</v>
+        <v>1116</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>1080</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1081</v>
+        <v>1118</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1082</v>
+        <v>1119</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1083</v>
+        <v>1120</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1084</v>
+        <v>1121</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>1085</v>
+        <v>1122</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1080</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>1086</v>
+        <v>1123</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>1087</v>
+        <v>1124</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>1088</v>
+        <v>1125</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>1089</v>
+        <v>1126</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>1090</v>
+        <v>1127</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>1091</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>518</v>
+        <v>555</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1092</v>
+        <v>1129</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1093</v>
+        <v>1130</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1094</v>
+        <v>1131</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1095</v>
+        <v>1132</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1096</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>709</v>
+        <v>746</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1097</v>
+        <v>1134</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>1098</v>
+        <v>1135</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>831</v>
+        <v>868</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>1099</v>
+        <v>1136</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>1100</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>773</v>
+        <v>810</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1101</v>
+        <v>1138</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1102</v>
+        <v>1139</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1103</v>
+        <v>1140</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>1104</v>
+        <v>1141</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>773</v>
+        <v>810</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>1105</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1106</v>
+        <v>1143</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>1107</v>
+        <v>1144</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>1108</v>
+        <v>1145</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>1109</v>
+        <v>1146</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>1080</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1110</v>
+        <v>1147</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1111</v>
+        <v>1148</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1112</v>
+        <v>1149</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1113</v>
+        <v>1150</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>1114</v>
+        <v>1151</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>1080</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1115</v>
+        <v>1152</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1116</v>
+        <v>1153</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1117</v>
+        <v>1154</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>1118</v>
+        <v>1155</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>1119</v>
+        <v>1156</v>
       </c>
       <c r="F14" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>1120</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1121</v>
+        <v>1158</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1122</v>
+        <v>1159</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1123</v>
+        <v>1160</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1124</v>
+        <v>1161</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>1125</v>
+        <v>1162</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>1126</v>
+        <v>1163</v>
       </c>
     </row>
   </sheetData>
@@ -8741,7 +8852,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1127</v>
+        <v>1164</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8752,24 +8863,24 @@
         <v>110</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1128</v>
+        <v>1165</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>1129</v>
+        <v>1166</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1130</v>
+        <v>1167</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1131</v>
+        <v>1168</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>881</v>
+        <v>918</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>100</v>
@@ -8777,55 +8888,55 @@
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>1132</v>
+        <v>1169</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1133</v>
+        <v>1170</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1134</v>
+        <v>1171</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1135</v>
+        <v>1172</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1136</v>
+        <v>1173</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>889</v>
+        <v>926</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>1137</v>
+        <v>1174</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>1138</v>
+        <v>1175</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1139</v>
+        <v>1176</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1140</v>
+        <v>1177</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>881</v>
+        <v>918</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>100</v>
@@ -8833,27 +8944,27 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>1141</v>
+        <v>1178</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>1142</v>
+        <v>1179</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>889</v>
+        <v>926</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>1143</v>
+        <v>1180</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1144</v>
+        <v>1181</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>897</v>
+        <v>934</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>100</v>
@@ -8861,13 +8972,13 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>1145</v>
+        <v>1182</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>1146</v>
+        <v>1183</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>900</v>
+        <v>937</v>
       </c>
       <c r="D12" s="58" t="s">
         <v>100</v>
@@ -8875,41 +8986,41 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1147</v>
+        <v>1184</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1148</v>
+        <v>1185</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>900</v>
+        <v>937</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>828</v>
+        <v>865</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>1149</v>
+        <v>1186</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1150</v>
+        <v>1187</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1151</v>
+        <v>1188</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1152</v>
+        <v>1189</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1153</v>
+        <v>1190</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>100</v>
@@ -8917,14 +9028,14 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>1154</v>
+        <v>1191</v>
       </c>
       <c r="B16" s="58" t="str">
         <f aca="false">"Premium at $"&amp;TEXT(Assumptions!B69,"0.00")&amp;". Launch discount no deeper than the realized-price factor on Assumptions."</f>
         <v>Premium at $19.99. Launch discount no deeper than the realized-price factor on Assumptions.</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>893</v>
+        <v>930</v>
       </c>
       <c r="D16" s="58" t="s">
         <v>100</v>
@@ -8932,13 +9043,13 @@
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>1155</v>
+        <v>1192</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1156</v>
+        <v>1193</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>100</v>
@@ -8946,13 +9057,13 @@
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>875</v>
+        <v>912</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>1157</v>
+        <v>1194</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>893</v>
+        <v>930</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>100</v>
@@ -8960,27 +9071,27 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1158</v>
+        <v>1195</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1159</v>
+        <v>1196</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>897</v>
+        <v>934</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>1160</v>
+        <v>1197</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1161</v>
+        <v>1198</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>897</v>
+        <v>934</v>
       </c>
       <c r="D20" s="58" t="s">
         <v>100</v>
@@ -8988,27 +9099,27 @@
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>1162</v>
+        <v>1199</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1163</v>
+        <v>1200</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>897</v>
+        <v>934</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="58" t="s">
-        <v>1164</v>
+        <v>1201</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>1165</v>
+        <v>1202</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>900</v>
+        <v>937</v>
       </c>
       <c r="D22" s="58" t="s">
         <v>100</v>
@@ -9054,7 +9165,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1166</v>
+        <v>1203</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9062,16 +9173,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1167</v>
+        <v>1204</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1168</v>
+        <v>1205</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1169</v>
+        <v>1206</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1170</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9079,13 +9190,13 @@
         <v>46311</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1171</v>
+        <v>1208</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1172</v>
+        <v>1209</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1173</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9093,13 +9204,13 @@
         <v>46311</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>1171</v>
+        <v>1208</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1174</v>
+        <v>1211</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>1175</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9107,13 +9218,13 @@
         <v>46311</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1171</v>
+        <v>1208</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1176</v>
+        <v>1213</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1177</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9121,13 +9232,13 @@
         <v>46311</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>935</v>
+        <v>972</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>1178</v>
+        <v>1215</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>1179</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9135,13 +9246,13 @@
         <v>46311</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1180</v>
+        <v>1217</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1181</v>
+        <v>1218</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1182</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9152,10 +9263,10 @@
         <v>53</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>1183</v>
+        <v>1220</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>1184</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9163,13 +9274,13 @@
         <v>46311</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1185</v>
+        <v>1222</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1186</v>
+        <v>1223</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1187</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9177,13 +9288,13 @@
         <v>46311</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>414</v>
+        <v>451</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>1188</v>
+        <v>1225</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>1189</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9191,13 +9302,13 @@
         <v>46311</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1190</v>
+        <v>1227</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1191</v>
+        <v>1228</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1192</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9205,13 +9316,13 @@
         <v>46311</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>1193</v>
+        <v>1230</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1194</v>
+        <v>1231</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>1195</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9222,10 +9333,10 @@
         <v>58</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1196</v>
+        <v>1233</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1197</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9233,13 +9344,13 @@
         <v>46311</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>1198</v>
+        <v>1235</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>1199</v>
+        <v>1236</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>1200</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9250,10 +9361,10 @@
         <v>62</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1202</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9261,13 +9372,13 @@
         <v>46311</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>1203</v>
+        <v>1240</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>1204</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9275,13 +9386,13 @@
         <v>46311</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>724</v>
+        <v>761</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1205</v>
+        <v>1242</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>1206</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9289,13 +9400,13 @@
         <v>46311</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>1207</v>
+        <v>1244</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>1208</v>
+        <v>1245</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>1209</v>
+        <v>1246</v>
       </c>
     </row>
   </sheetData>
@@ -9319,7 +9430,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:F179"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
@@ -10885,9 +10996,225 @@
         <v>323</v>
       </c>
     </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="B160" s="24"/>
+      <c r="C160" s="24"/>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B161" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C161" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="42" t="s">
+        <v>325</v>
+      </c>
+      <c r="B162" s="43" t="n">
+        <v>15</v>
+      </c>
+      <c r="C162" s="41" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="B163" s="51" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C163" s="41" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="42" t="s">
+        <v>329</v>
+      </c>
+      <c r="B164" s="51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C164" s="41" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="50" t="s">
+        <v>331</v>
+      </c>
+      <c r="B165" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C165" s="41" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="B166" s="56" t="s">
+        <v>334</v>
+      </c>
+      <c r="C166" s="41" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="B167" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C167" s="41" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="42" t="s">
+        <v>338</v>
+      </c>
+      <c r="B168" s="51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C168" s="41" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="50" t="s">
+        <v>340</v>
+      </c>
+      <c r="B169" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C169" s="41" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="42" t="s">
+        <v>342</v>
+      </c>
+      <c r="B170" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="C170" s="41" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="50" t="s">
+        <v>344</v>
+      </c>
+      <c r="B171" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C171" s="41" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="B172" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C172" s="41" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="50" t="s">
+        <v>348</v>
+      </c>
+      <c r="B173" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C173" s="41" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="42" t="s">
+        <v>350</v>
+      </c>
+      <c r="B174" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C174" s="41" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="50" t="s">
+        <v>352</v>
+      </c>
+      <c r="B175" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C175" s="41" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="42" t="s">
+        <v>354</v>
+      </c>
+      <c r="B176" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C176" s="41" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="50" t="s">
+        <v>356</v>
+      </c>
+      <c r="B177" s="49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C177" s="41" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="B178" s="51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C178" s="41" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="50" t="s">
+        <v>360</v>
+      </c>
+      <c r="B179" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C179" s="41" t="s">
+        <v>177</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A15:C21"/>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:B4"/>
@@ -10908,6 +11235,7 @@
     <mergeCell ref="A92:C92"/>
     <mergeCell ref="A94:C94"/>
     <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A160:C160"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10948,7 +11276,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>324</v>
+        <v>361</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -10957,160 +11285,160 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>326</v>
+        <v>363</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>328</v>
+        <v>365</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>329</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>331</v>
+        <v>368</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>333</v>
+        <v>370</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>338</v>
+        <v>375</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>339</v>
+        <v>376</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>341</v>
+        <v>378</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>342</v>
+        <v>379</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>343</v>
+        <v>380</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>344</v>
+        <v>381</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>345</v>
+        <v>382</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>347</v>
+        <v>384</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>348</v>
+        <v>385</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>349</v>
+        <v>386</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>350</v>
+        <v>387</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>351</v>
+        <v>388</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>353</v>
+        <v>390</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>354</v>
+        <v>391</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>356</v>
+        <v>393</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>358</v>
+        <v>395</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>361</v>
+        <v>398</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>362</v>
+        <v>399</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>363</v>
+        <v>400</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -11119,16 +11447,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>364</v>
+        <v>401</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>366</v>
+        <v>403</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>95</v>
@@ -11136,58 +11464,58 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="E16" s="59" t="s">
-        <v>372</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="58" t="s">
-        <v>373</v>
+        <v>410</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>374</v>
+        <v>411</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>375</v>
+        <v>412</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="E17" s="58" t="s">
-        <v>377</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>380</v>
+        <v>417</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>381</v>
+        <v>418</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>382</v>
+        <v>419</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>383</v>
+        <v>420</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="24"/>
@@ -11196,87 +11524,87 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>385</v>
+        <v>422</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>386</v>
+        <v>423</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>387</v>
+        <v>424</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>388</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>389</v>
+        <v>426</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>390</v>
+        <v>427</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>391</v>
+        <v>428</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>392</v>
+        <v>429</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>393</v>
+        <v>430</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="58" t="s">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>395</v>
+        <v>432</v>
       </c>
       <c r="C23" s="58" t="s">
-        <v>396</v>
+        <v>433</v>
       </c>
       <c r="D23" s="58" t="s">
-        <v>397</v>
+        <v>434</v>
       </c>
       <c r="E23" s="58" t="s">
-        <v>398</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>399</v>
+        <v>436</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>400</v>
+        <v>437</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>401</v>
+        <v>438</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>402</v>
+        <v>439</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>403</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="58" t="s">
-        <v>404</v>
+        <v>441</v>
       </c>
       <c r="B25" s="58" t="s">
-        <v>400</v>
+        <v>437</v>
       </c>
       <c r="C25" s="58" t="s">
-        <v>405</v>
+        <v>442</v>
       </c>
       <c r="D25" s="58" t="s">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="E25" s="58" t="s">
-        <v>407</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -11329,7 +11657,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>408</v>
+        <v>445</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11340,33 +11668,33 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>411</v>
+        <v>448</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>412</v>
+        <v>449</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>413</v>
+        <v>450</v>
       </c>
       <c r="F4" s="57" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>414</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>415</v>
+        <v>452</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>416</v>
+        <v>453</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>134</v>
@@ -11376,37 +11704,37 @@
         <v>24</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>417</v>
+        <v>454</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>419</v>
+        <v>456</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>420</v>
+        <v>457</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>421</v>
+        <v>458</v>
       </c>
       <c r="D6" s="60" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>422</v>
+        <v>459</v>
       </c>
       <c r="F6" s="58" t="s">
         <v>98</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>423</v>
+        <v>460</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11414,71 +11742,71 @@
         <v>228</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>424</v>
+        <v>461</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="D7" s="60" t="n">
         <f aca="false">Assumptions!B44</f>
         <v>120</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>427</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>428</v>
+        <v>465</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>429</v>
+        <v>466</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>430</v>
+        <v>467</v>
       </c>
       <c r="D8" s="60" t="n">
         <f aca="false">Assumptions!B46</f>
         <v>400</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="F8" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>432</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>433</v>
+        <v>470</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>434</v>
+        <v>471</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="D9" s="60" t="n">
         <f aca="false">Assumptions!B45</f>
         <v>120</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11486,151 +11814,151 @@
         <v>219</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>439</v>
+        <v>476</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>440</v>
+        <v>477</v>
       </c>
       <c r="F10" s="58" t="s">
         <v>98</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>441</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>443</v>
+        <v>480</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>439</v>
+        <v>476</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>444</v>
+        <v>481</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>445</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>446</v>
+        <v>483</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>447</v>
+        <v>484</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>439</v>
+        <v>476</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>449</v>
+        <v>486</v>
       </c>
       <c r="F12" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="D13" s="60" t="n">
         <f aca="false">Assumptions!B43</f>
         <v>168</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>454</v>
+        <v>491</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>455</v>
+        <v>492</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>456</v>
+        <v>493</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>457</v>
+        <v>494</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>458</v>
+        <v>495</v>
       </c>
       <c r="D14" s="60" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>459</v>
+        <v>496</v>
       </c>
       <c r="F14" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>460</v>
+        <v>497</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>461</v>
+        <v>498</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>462</v>
+        <v>499</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D15" s="60" t="n">
         <f aca="false">Assumptions!B50</f>
         <v>5</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>464</v>
+        <v>501</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>465</v>
+        <v>502</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>467</v>
+        <v>504</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>468</v>
+        <v>505</v>
       </c>
       <c r="D16" s="60" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -11643,78 +11971,78 @@
         <v>102</v>
       </c>
       <c r="G16" s="58" t="s">
-        <v>469</v>
+        <v>506</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>470</v>
+        <v>507</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>471</v>
+        <v>508</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>472</v>
+        <v>509</v>
       </c>
       <c r="D17" s="60" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>473</v>
+        <v>510</v>
       </c>
       <c r="F17" s="27" t="s">
         <v>102</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>474</v>
+        <v>511</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="B18" s="58" t="s">
+        <v>513</v>
+      </c>
+      <c r="C18" s="58" t="s">
         <v>476</v>
       </c>
-      <c r="C18" s="58" t="s">
-        <v>439</v>
-      </c>
       <c r="D18" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>477</v>
+        <v>514</v>
       </c>
       <c r="F18" s="58" t="s">
         <v>104</v>
       </c>
       <c r="G18" s="58" t="s">
-        <v>478</v>
+        <v>515</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>479</v>
+        <v>516</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>480</v>
+        <v>517</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="D19" s="60" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>482</v>
+        <v>519</v>
       </c>
       <c r="F19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>483</v>
+        <v>520</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11722,46 +12050,46 @@
         <v>224</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>484</v>
+        <v>521</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>439</v>
+        <v>476</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>485</v>
+        <v>522</v>
       </c>
       <c r="F20" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G20" s="58" t="s">
-        <v>486</v>
+        <v>523</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>488</v>
+        <v>525</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>421</v>
+        <v>458</v>
       </c>
       <c r="D21" s="60" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>489</v>
+        <v>526</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>490</v>
+        <v>527</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11769,55 +12097,55 @@
         <v>236</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>491</v>
+        <v>528</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="D22" s="60" t="n">
         <f aca="false">Assumptions!B57</f>
         <v>2</v>
       </c>
       <c r="E22" s="58" t="s">
-        <v>493</v>
+        <v>530</v>
       </c>
       <c r="F22" s="58" t="s">
         <v>100</v>
       </c>
       <c r="G22" s="58" t="s">
-        <v>494</v>
+        <v>531</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
+        <v>532</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>533</v>
+      </c>
+      <c r="C23" s="27" t="s">
         <v>495</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>496</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>458</v>
       </c>
       <c r="D23" s="60" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>497</v>
+        <v>534</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>498</v>
+        <v>535</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="58" t="s">
-        <v>499</v>
+        <v>536</v>
       </c>
       <c r="B24" s="58" t="s">
-        <v>500</v>
+        <v>537</v>
       </c>
       <c r="C24" s="58" t="s">
         <v>134</v>
@@ -11827,13 +12155,13 @@
         <v>24</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>501</v>
+        <v>538</v>
       </c>
       <c r="F24" s="58" t="s">
         <v>98</v>
       </c>
       <c r="G24" s="58" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -11879,7 +12207,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>503</v>
+        <v>540</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11888,7 +12216,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>504</v>
+        <v>541</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -11903,21 +12231,21 @@
         <v>42</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>506</v>
+        <v>543</v>
       </c>
       <c r="B6" s="61" t="n">
         <f aca="false">Assumptions!B62</f>
         <v>1200</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>507</v>
+        <v>544</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
@@ -11931,21 +12259,21 @@
         <v>120</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>508</v>
+        <v>545</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>509</v>
+        <v>546</v>
       </c>
       <c r="B8" s="62" t="n">
         <f aca="false">IF(B7=0,0,B6/B7)</f>
         <v>10</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>510</v>
+        <v>547</v>
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="33"/>
@@ -11959,7 +12287,7 @@
         <v>1.3</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>511</v>
+        <v>548</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
@@ -11973,14 +12301,14 @@
         <v>13</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>512</v>
+        <v>549</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>513</v>
+        <v>550</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -11989,24 +12317,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>514</v>
+        <v>551</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>515</v>
+        <v>552</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>516</v>
+        <v>553</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>517</v>
+        <v>554</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>410</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>518</v>
+        <v>555</v>
       </c>
       <c r="B14" s="60" t="n">
         <f aca="false">Assumptions!B42</f>
@@ -12021,12 +12349,12 @@
         <v>9.6</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>519</v>
+        <v>556</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>520</v>
+        <v>557</v>
       </c>
       <c r="B15" s="60" t="n">
         <f aca="false">Assumptions!B57</f>
@@ -12041,12 +12369,12 @@
         <v>3</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
       <c r="B16" s="60" t="n">
         <f aca="false">Assumptions!B58</f>
@@ -12064,7 +12392,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>454</v>
+        <v>491</v>
       </c>
       <c r="B17" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B43,0)</f>
@@ -12078,12 +12406,12 @@
         <v>2</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>523</v>
+        <v>560</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>524</v>
+        <v>561</v>
       </c>
       <c r="B18" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B44,0)</f>
@@ -12097,12 +12425,12 @@
         <v>3</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>525</v>
+        <v>562</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>526</v>
+        <v>563</v>
       </c>
       <c r="B19" s="32" t="n">
         <f aca="false">ROUNDUP((B15+B16*Assumptions!B60)*$B$10/Assumptions!B59,0)</f>
@@ -12116,12 +12444,12 @@
         <v>2</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>527</v>
+        <v>564</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>528</v>
+        <v>565</v>
       </c>
       <c r="B20" s="60" t="n">
         <f aca="false">Assumptions!B61</f>
@@ -12140,7 +12468,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>529</v>
+        <v>566</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -12152,7 +12480,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>530</v>
+        <v>567</v>
       </c>
       <c r="D22" s="64" t="n">
         <f aca="false">Assumptions!B41</f>
@@ -12161,7 +12489,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="66" t="s">
-        <v>531</v>
+        <v>568</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
@@ -12176,7 +12504,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>532</v>
+        <v>569</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -12185,24 +12513,24 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>514</v>
+        <v>551</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>515</v>
+        <v>552</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>516</v>
+        <v>553</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>517</v>
+        <v>554</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>410</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>533</v>
+        <v>570</v>
       </c>
       <c r="B27" s="60" t="n">
         <f aca="false">Assumptions!B64</f>
@@ -12222,7 +12550,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="58" t="s">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="B28" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B43,0)</f>
@@ -12236,12 +12564,12 @@
         <v>1</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>535</v>
+        <v>572</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>536</v>
+        <v>573</v>
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B44,0)</f>
@@ -12258,7 +12586,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>537</v>
+        <v>574</v>
       </c>
       <c r="D30" s="62" t="n">
         <f aca="false">SUM(D27:D29)</f>
@@ -12267,7 +12595,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>538</v>
+        <v>575</v>
       </c>
       <c r="D31" s="62" t="n">
         <f aca="false">Assumptions!B41-D30</f>
@@ -12276,7 +12604,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="D32" s="32" t="n">
         <f aca="false">INT(D31/Assumptions!B65)</f>
@@ -12285,7 +12613,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="D33" s="60" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -12294,7 +12622,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="66" t="s">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="B34" s="66"/>
       <c r="C34" s="66"/>
@@ -12309,7 +12637,7 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="54" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
       <c r="B36" s="54"/>
       <c r="C36" s="54"/>
@@ -12390,7 +12718,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>542</v>
+        <v>579</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12405,392 +12733,392 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="B4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>546</v>
+        <v>583</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>547</v>
+        <v>584</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>548</v>
+        <v>585</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>414</v>
+        <v>451</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>549</v>
+        <v>586</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>550</v>
+        <v>587</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>551</v>
+        <v>588</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>552</v>
+        <v>589</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>553</v>
+        <v>590</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>554</v>
+        <v>591</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>555</v>
+        <v>592</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
       <c r="H5" s="69" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>557</v>
+        <v>594</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>558</v>
+        <v>595</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>559</v>
+        <v>596</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>560</v>
+        <v>597</v>
       </c>
       <c r="B6" s="58" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>561</v>
+        <v>598</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>562</v>
+        <v>599</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>563</v>
+        <v>600</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>564</v>
+        <v>601</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>565</v>
+        <v>602</v>
       </c>
       <c r="H6" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="58" t="s">
-        <v>566</v>
+        <v>603</v>
       </c>
       <c r="J6" s="58" t="s">
-        <v>567</v>
+        <v>604</v>
       </c>
       <c r="K6" s="58" t="s">
-        <v>568</v>
+        <v>605</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>569</v>
+        <v>606</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>570</v>
+        <v>607</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>571</v>
+        <v>608</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>572</v>
+        <v>609</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>573</v>
+        <v>610</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>574</v>
+        <v>611</v>
       </c>
       <c r="H7" s="69" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>576</v>
+        <v>613</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>578</v>
+        <v>615</v>
       </c>
       <c r="B8" s="58" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>579</v>
+        <v>616</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>580</v>
+        <v>617</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>581</v>
+        <v>618</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>582</v>
+        <v>619</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>583</v>
+        <v>620</v>
       </c>
       <c r="H8" s="69" t="n">
         <v>3</v>
       </c>
       <c r="I8" s="58" t="s">
-        <v>584</v>
+        <v>621</v>
       </c>
       <c r="J8" s="58" t="s">
-        <v>585</v>
+        <v>622</v>
       </c>
       <c r="K8" s="58" t="s">
-        <v>586</v>
+        <v>623</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>587</v>
+        <v>624</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>588</v>
+        <v>625</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>589</v>
+        <v>626</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>590</v>
+        <v>627</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="H9" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>593</v>
+        <v>630</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>594</v>
+        <v>631</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>595</v>
+        <v>632</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>596</v>
+        <v>633</v>
       </c>
       <c r="B10" s="58" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>597</v>
+        <v>634</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>598</v>
+        <v>635</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>599</v>
+        <v>636</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>600</v>
+        <v>637</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>601</v>
+        <v>638</v>
       </c>
       <c r="H10" s="69" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="58" t="s">
-        <v>602</v>
+        <v>639</v>
       </c>
       <c r="J10" s="58" t="s">
-        <v>603</v>
+        <v>640</v>
       </c>
       <c r="K10" s="58" t="s">
-        <v>604</v>
+        <v>641</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>605</v>
+        <v>642</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>606</v>
+        <v>643</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>607</v>
+        <v>644</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>608</v>
+        <v>645</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>609</v>
+        <v>646</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>610</v>
+        <v>647</v>
       </c>
       <c r="H11" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>612</v>
+        <v>649</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>613</v>
+        <v>650</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>614</v>
+        <v>651</v>
       </c>
       <c r="B12" s="58" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>615</v>
+        <v>652</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>616</v>
+        <v>653</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>617</v>
+        <v>654</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>618</v>
+        <v>655</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>619</v>
+        <v>656</v>
       </c>
       <c r="H12" s="69" t="n">
         <v>3</v>
       </c>
       <c r="I12" s="58" t="s">
-        <v>620</v>
+        <v>657</v>
       </c>
       <c r="J12" s="58" t="s">
-        <v>621</v>
+        <v>658</v>
       </c>
       <c r="K12" s="58" t="s">
-        <v>622</v>
+        <v>659</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>624</v>
+        <v>661</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>625</v>
+        <v>662</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>626</v>
+        <v>663</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>627</v>
+        <v>664</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>628</v>
+        <v>665</v>
       </c>
       <c r="H13" s="69" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>629</v>
+        <v>666</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>630</v>
+        <v>667</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>631</v>
+        <v>668</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>632</v>
+        <v>669</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>633</v>
+        <v>670</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>634</v>
+        <v>671</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>635</v>
+        <v>672</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>636</v>
+        <v>673</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>637</v>
+        <v>674</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>638</v>
+        <v>675</v>
       </c>
       <c r="H14" s="69" t="n">
         <v>2</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>639</v>
+        <v>676</v>
       </c>
       <c r="J14" s="58" t="s">
-        <v>640</v>
+        <v>677</v>
       </c>
       <c r="K14" s="58" t="s">
-        <v>641</v>
+        <v>678</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>642</v>
+        <v>679</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
@@ -12802,10 +13130,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>643</v>
+        <v>680</v>
       </c>
       <c r="B17" s="70" t="s">
-        <v>644</v>
+        <v>681</v>
       </c>
       <c r="C17" s="70"/>
       <c r="D17" s="70"/>
@@ -12816,10 +13144,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>645</v>
+        <v>682</v>
       </c>
       <c r="B18" s="70" t="s">
-        <v>646</v>
+        <v>683</v>
       </c>
       <c r="C18" s="70"/>
       <c r="D18" s="70"/>
@@ -12830,10 +13158,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>647</v>
+        <v>684</v>
       </c>
       <c r="B19" s="70" t="s">
-        <v>648</v>
+        <v>685</v>
       </c>
       <c r="C19" s="70"/>
       <c r="D19" s="70"/>
@@ -12844,10 +13172,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>649</v>
+        <v>686</v>
       </c>
       <c r="B20" s="70" t="s">
-        <v>650</v>
+        <v>687</v>
       </c>
       <c r="C20" s="70"/>
       <c r="D20" s="70"/>
@@ -12858,10 +13186,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>651</v>
+        <v>688</v>
       </c>
       <c r="B21" s="70" t="s">
-        <v>652</v>
+        <v>689</v>
       </c>
       <c r="C21" s="70"/>
       <c r="D21" s="70"/>
@@ -12872,10 +13200,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>653</v>
+        <v>690</v>
       </c>
       <c r="B22" s="70" t="s">
-        <v>654</v>
+        <v>691</v>
       </c>
       <c r="C22" s="70"/>
       <c r="D22" s="70"/>
@@ -12886,10 +13214,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>655</v>
+        <v>692</v>
       </c>
       <c r="B23" s="70" t="s">
-        <v>656</v>
+        <v>693</v>
       </c>
       <c r="C23" s="70"/>
       <c r="D23" s="70"/>
@@ -12900,7 +13228,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="71" t="s">
-        <v>657</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -12964,7 +13292,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>658</v>
+        <v>695</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12978,42 +13306,42 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>659</v>
+        <v>696</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>660</v>
+        <v>697</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>662</v>
+        <v>699</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>664</v>
+        <v>701</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>665</v>
+        <v>702</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>666</v>
+        <v>703</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
@@ -13022,190 +13350,190 @@
         <v>96</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G5" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>439</v>
+        <v>476</v>
       </c>
       <c r="I5" s="69" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>669</v>
+        <v>706</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>670</v>
+        <v>707</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>671</v>
+        <v>708</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>672</v>
+        <v>709</v>
       </c>
       <c r="D6" s="58" t="s">
         <v>96</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G6" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>665</v>
+        <v>702</v>
       </c>
       <c r="I6" s="69" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="J6" s="58" t="s">
-        <v>674</v>
+        <v>711</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>675</v>
+        <v>712</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>676</v>
+        <v>713</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>672</v>
+        <v>709</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G7" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>670</v>
+        <v>707</v>
       </c>
       <c r="I7" s="69" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>677</v>
+        <v>714</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>678</v>
+        <v>715</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>679</v>
+        <v>716</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="D8" s="58" t="s">
         <v>96</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="G8" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>439</v>
+        <v>476</v>
       </c>
       <c r="I8" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J8" s="58" t="s">
-        <v>682</v>
+        <v>719</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>683</v>
+        <v>720</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>684</v>
+        <v>721</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G9" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>439</v>
+        <v>476</v>
       </c>
       <c r="I9" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>686</v>
+        <v>723</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>687</v>
+        <v>724</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>688</v>
+        <v>725</v>
       </c>
       <c r="D10" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G10" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="I10" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J10" s="58" t="s">
-        <v>689</v>
+        <v>726</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>557</v>
+        <v>594</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>690</v>
+        <v>727</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>23</v>
@@ -13214,30 +13542,30 @@
         <v>98</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G11" s="43" t="n">
         <v>12</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="I11" s="69" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>691</v>
+        <v>728</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>566</v>
+        <v>603</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>692</v>
+        <v>729</v>
       </c>
       <c r="C12" s="58" t="s">
         <v>23</v>
@@ -13246,30 +13574,30 @@
         <v>98</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G12" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>557</v>
+        <v>594</v>
       </c>
       <c r="I12" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J12" s="58" t="s">
-        <v>693</v>
+        <v>730</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>694</v>
+        <v>731</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>26</v>
@@ -13278,62 +13606,62 @@
         <v>98</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G13" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="I13" s="69" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>695</v>
+        <v>732</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>697</v>
+        <v>734</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="D14" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G14" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="I14" s="69" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="J14" s="58" t="s">
-        <v>698</v>
+        <v>735</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>699</v>
+        <v>736</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>35</v>
@@ -13342,263 +13670,263 @@
         <v>98</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G15" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
       <c r="I15" s="69" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="J15" s="27" t="s">
-        <v>700</v>
+        <v>737</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>701</v>
+        <v>738</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>702</v>
+        <v>739</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="D16" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G16" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>557</v>
+        <v>594</v>
       </c>
       <c r="I16" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J16" s="58" t="s">
-        <v>703</v>
+        <v>740</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>483</v>
+        <v>520</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>704</v>
+        <v>741</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>705</v>
+        <v>742</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G17" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="I17" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>706</v>
+        <v>743</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>707</v>
+        <v>744</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>708</v>
+        <v>745</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>709</v>
+        <v>746</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="G18" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H18" s="58" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="I18" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J18" s="58" t="s">
-        <v>710</v>
+        <v>747</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>427</v>
+        <v>464</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>711</v>
+        <v>748</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>684</v>
+        <v>721</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G19" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="I19" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>712</v>
+        <v>749</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>441</v>
+        <v>478</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>713</v>
+        <v>750</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>688</v>
+        <v>725</v>
       </c>
       <c r="D20" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G20" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H20" s="58" t="s">
-        <v>557</v>
+        <v>594</v>
       </c>
       <c r="I20" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J20" s="58" t="s">
-        <v>714</v>
+        <v>751</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>715</v>
+        <v>752</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>716</v>
+        <v>753</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>717</v>
+        <v>754</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G21" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="I21" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J21" s="27" t="s">
-        <v>718</v>
+        <v>755</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="58" t="s">
-        <v>719</v>
+        <v>756</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>720</v>
+        <v>757</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="D22" s="58" t="s">
         <v>98</v>
       </c>
       <c r="E22" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F22" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G22" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="58" t="s">
-        <v>701</v>
+        <v>738</v>
       </c>
       <c r="I22" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J22" s="58" t="s">
-        <v>721</v>
+        <v>758</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>722</v>
+        <v>759</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>723</v>
+        <v>760</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>724</v>
+        <v>761</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
@@ -13607,117 +13935,117 @@
         <v>3</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>678</v>
+        <v>715</v>
       </c>
       <c r="I23" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>726</v>
+        <v>763</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="58" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="B24" s="58" t="s">
-        <v>446</v>
+        <v>483</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>688</v>
+        <v>725</v>
       </c>
       <c r="D24" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F24" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G24" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H24" s="58" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="I24" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J24" s="58" t="s">
-        <v>727</v>
+        <v>764</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>639</v>
+        <v>676</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>634</v>
+        <v>671</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>688</v>
+        <v>725</v>
       </c>
       <c r="D25" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G25" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="I25" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J25" s="27" t="s">
-        <v>728</v>
+        <v>765</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="58" t="s">
-        <v>729</v>
+        <v>766</v>
       </c>
       <c r="B26" s="58" t="s">
-        <v>730</v>
+        <v>767</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>688</v>
+        <v>725</v>
       </c>
       <c r="D26" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F26" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G26" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H26" s="58" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="I26" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J26" s="58" t="s">
-        <v>731</v>
+        <v>768</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>593</v>
+        <v>630</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>588</v>
+        <v>625</v>
       </c>
       <c r="C27" s="27" t="s">
         <v>29</v>
@@ -13726,30 +14054,30 @@
         <v>100</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G27" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
       <c r="I27" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J27" s="27" t="s">
-        <v>732</v>
+        <v>769</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="58" t="s">
-        <v>602</v>
+        <v>639</v>
       </c>
       <c r="B28" s="58" t="s">
-        <v>733</v>
+        <v>770</v>
       </c>
       <c r="C28" s="58" t="s">
         <v>32</v>
@@ -13758,30 +14086,30 @@
         <v>100</v>
       </c>
       <c r="E28" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F28" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G28" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H28" s="58" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
       <c r="I28" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J28" s="58" t="s">
-        <v>734</v>
+        <v>771</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>584</v>
+        <v>621</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>735</v>
+        <v>772</v>
       </c>
       <c r="C29" s="27" t="s">
         <v>26</v>
@@ -13790,94 +14118,94 @@
         <v>100</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G29" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="I29" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>736</v>
+        <v>773</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="58" t="s">
-        <v>629</v>
+        <v>666</v>
       </c>
       <c r="B30" s="58" t="s">
-        <v>737</v>
+        <v>774</v>
       </c>
       <c r="C30" s="58" t="s">
-        <v>684</v>
+        <v>721</v>
       </c>
       <c r="D30" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F30" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G30" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="58" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="I30" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J30" s="58" t="s">
-        <v>738</v>
+        <v>775</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="s">
-        <v>494</v>
+        <v>531</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>739</v>
+        <v>776</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="D31" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G31" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="I31" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J31" s="27" t="s">
-        <v>740</v>
+        <v>777</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="58" t="s">
-        <v>741</v>
+        <v>778</v>
       </c>
       <c r="B32" s="58" t="s">
-        <v>742</v>
+        <v>779</v>
       </c>
       <c r="C32" s="58" t="s">
         <v>35</v>
@@ -13886,30 +14214,30 @@
         <v>100</v>
       </c>
       <c r="E32" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F32" s="58" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="G32" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H32" s="58" t="s">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="I32" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J32" s="58" t="s">
-        <v>743</v>
+        <v>780</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>620</v>
+        <v>657</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>744</v>
+        <v>781</v>
       </c>
       <c r="C33" s="27" t="s">
         <v>35</v>
@@ -13918,487 +14246,487 @@
         <v>100</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G33" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="I33" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J33" s="27" t="s">
-        <v>745</v>
+        <v>782</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="58" t="s">
-        <v>746</v>
+        <v>783</v>
       </c>
       <c r="B34" s="58" t="s">
-        <v>747</v>
+        <v>784</v>
       </c>
       <c r="C34" s="58" t="s">
-        <v>748</v>
+        <v>785</v>
       </c>
       <c r="D34" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F34" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G34" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H34" s="58" t="s">
-        <v>494</v>
+        <v>531</v>
       </c>
       <c r="I34" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J34" s="58" t="s">
-        <v>749</v>
+        <v>786</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>748</v>
+        <v>785</v>
       </c>
       <c r="D35" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G35" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>746</v>
+        <v>783</v>
       </c>
       <c r="I35" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J35" s="27" t="s">
-        <v>752</v>
+        <v>789</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="58" t="s">
-        <v>753</v>
+        <v>790</v>
       </c>
       <c r="B36" s="58" t="s">
-        <v>754</v>
+        <v>791</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>748</v>
+        <v>785</v>
       </c>
       <c r="D36" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F36" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G36" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H36" s="58" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="I36" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J36" s="58" t="s">
-        <v>755</v>
+        <v>792</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="27" t="s">
-        <v>756</v>
+        <v>793</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>757</v>
+        <v>794</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>758</v>
+        <v>795</v>
       </c>
       <c r="D37" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G37" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H37" s="27" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="I37" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J37" s="27" t="s">
-        <v>759</v>
+        <v>796</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="58" t="s">
-        <v>760</v>
+        <v>797</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>761</v>
+        <v>798</v>
       </c>
       <c r="C38" s="58" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="D38" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="58" t="s">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="F38" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G38" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="58" t="s">
-        <v>756</v>
+        <v>793</v>
       </c>
       <c r="I38" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J38" s="58" t="s">
-        <v>762</v>
+        <v>799</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="27" t="s">
-        <v>486</v>
+        <v>523</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>763</v>
+        <v>800</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>705</v>
+        <v>742</v>
       </c>
       <c r="D39" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G39" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="I39" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J39" s="27" t="s">
-        <v>764</v>
+        <v>801</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="58" t="s">
-        <v>490</v>
+        <v>527</v>
       </c>
       <c r="B40" s="58" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="D40" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F40" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G40" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H40" s="58" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="I40" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J40" s="58" t="s">
-        <v>765</v>
+        <v>802</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>498</v>
+        <v>535</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>766</v>
+        <v>803</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="D41" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G41" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>494</v>
+        <v>531</v>
       </c>
       <c r="I41" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J41" s="27" t="s">
-        <v>767</v>
+        <v>804</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="58" t="s">
-        <v>768</v>
+        <v>805</v>
       </c>
       <c r="B42" s="58" t="s">
-        <v>769</v>
+        <v>806</v>
       </c>
       <c r="C42" s="58" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="D42" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="58" t="s">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="F42" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G42" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="58" t="s">
-        <v>760</v>
+        <v>797</v>
       </c>
       <c r="I42" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J42" s="58" t="s">
-        <v>770</v>
+        <v>807</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
-        <v>771</v>
+        <v>808</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>773</v>
+        <v>810</v>
       </c>
       <c r="D43" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>773</v>
+        <v>810</v>
       </c>
       <c r="G43" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H43" s="27" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="I43" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J43" s="27" t="s">
-        <v>774</v>
+        <v>811</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="58" t="s">
-        <v>775</v>
+        <v>812</v>
       </c>
       <c r="B44" s="58" t="s">
-        <v>776</v>
+        <v>813</v>
       </c>
       <c r="C44" s="58" t="s">
-        <v>672</v>
+        <v>709</v>
       </c>
       <c r="D44" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E44" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F44" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G44" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H44" s="58" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="I44" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J44" s="58" t="s">
-        <v>777</v>
+        <v>814</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="27" t="s">
-        <v>778</v>
+        <v>815</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>779</v>
+        <v>816</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>709</v>
+        <v>746</v>
       </c>
       <c r="D45" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G45" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H45" s="27" t="s">
-        <v>707</v>
+        <v>744</v>
       </c>
       <c r="I45" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J45" s="27" t="s">
-        <v>780</v>
+        <v>817</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="58" t="s">
-        <v>781</v>
+        <v>818</v>
       </c>
       <c r="B46" s="58" t="s">
-        <v>782</v>
+        <v>819</v>
       </c>
       <c r="C46" s="58" t="s">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="D46" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E46" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F46" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G46" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H46" s="58" t="s">
-        <v>701</v>
+        <v>738</v>
       </c>
       <c r="I46" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J46" s="58" t="s">
-        <v>783</v>
+        <v>820</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
-        <v>784</v>
+        <v>821</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>785</v>
+        <v>822</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>758</v>
+        <v>795</v>
       </c>
       <c r="D47" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G47" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H47" s="27" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="I47" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J47" s="27" t="s">
-        <v>786</v>
+        <v>823</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="58" t="s">
-        <v>787</v>
+        <v>824</v>
       </c>
       <c r="B48" s="58" t="s">
-        <v>788</v>
+        <v>825</v>
       </c>
       <c r="C48" s="58" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="D48" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E48" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F48" s="58" t="s">
         <v>100</v>
@@ -14407,62 +14735,62 @@
         <v>3</v>
       </c>
       <c r="H48" s="58" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="I48" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J48" s="58" t="s">
-        <v>789</v>
+        <v>826</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="27" t="s">
-        <v>790</v>
+        <v>827</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>791</v>
+        <v>828</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="D49" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G49" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H49" s="27" t="s">
-        <v>778</v>
+        <v>815</v>
       </c>
       <c r="I49" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J49" s="27" t="s">
-        <v>793</v>
+        <v>830</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="58" t="s">
-        <v>794</v>
+        <v>831</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>795</v>
+        <v>832</v>
       </c>
       <c r="C50" s="58" t="s">
-        <v>796</v>
+        <v>833</v>
       </c>
       <c r="D50" s="58" t="s">
         <v>100</v>
       </c>
       <c r="E50" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F50" s="58" t="s">
         <v>100</v>
@@ -14471,181 +14799,181 @@
         <v>4</v>
       </c>
       <c r="H50" s="58" t="s">
-        <v>715</v>
+        <v>752</v>
       </c>
       <c r="I50" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J50" s="58" t="s">
-        <v>797</v>
+        <v>834</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
-        <v>798</v>
+        <v>835</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>799</v>
+        <v>836</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>800</v>
+        <v>837</v>
       </c>
       <c r="D51" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G51" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H51" s="27" t="s">
-        <v>729</v>
+        <v>766</v>
       </c>
       <c r="I51" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J51" s="27" t="s">
-        <v>801</v>
+        <v>838</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="58" t="s">
-        <v>802</v>
+        <v>839</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>803</v>
+        <v>840</v>
       </c>
       <c r="C52" s="58" t="s">
-        <v>800</v>
+        <v>837</v>
       </c>
       <c r="D52" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E52" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F52" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G52" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H52" s="58" t="s">
-        <v>620</v>
+        <v>657</v>
       </c>
       <c r="I52" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J52" s="58" t="s">
-        <v>804</v>
+        <v>841</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="27" t="s">
-        <v>474</v>
+        <v>511</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>805</v>
+        <v>842</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>800</v>
+        <v>837</v>
       </c>
       <c r="D53" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F53" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G53" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H53" s="27" t="s">
-        <v>802</v>
+        <v>839</v>
       </c>
       <c r="I53" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J53" s="27" t="s">
-        <v>806</v>
+        <v>843</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="58" t="s">
-        <v>807</v>
+        <v>844</v>
       </c>
       <c r="B54" s="58" t="s">
-        <v>808</v>
+        <v>845</v>
       </c>
       <c r="C54" s="58" t="s">
-        <v>688</v>
+        <v>725</v>
       </c>
       <c r="D54" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E54" s="58" t="s">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="F54" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G54" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H54" s="58" t="s">
-        <v>729</v>
+        <v>766</v>
       </c>
       <c r="I54" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J54" s="58" t="s">
-        <v>809</v>
+        <v>846</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
-        <v>810</v>
+        <v>847</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>811</v>
+        <v>848</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="D55" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>812</v>
+        <v>849</v>
       </c>
       <c r="F55" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G55" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>753</v>
+        <v>790</v>
       </c>
       <c r="I55" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J55" s="27" t="s">
-        <v>813</v>
+        <v>850</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="58" t="s">
-        <v>814</v>
+        <v>851</v>
       </c>
       <c r="B56" s="58" t="s">
-        <v>815</v>
+        <v>852</v>
       </c>
       <c r="C56" s="58" t="s">
         <v>26</v>
@@ -14654,359 +14982,359 @@
         <v>102</v>
       </c>
       <c r="E56" s="58" t="s">
-        <v>812</v>
+        <v>849</v>
       </c>
       <c r="F56" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G56" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H56" s="58" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="I56" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J56" s="58" t="s">
-        <v>816</v>
+        <v>853</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
-        <v>817</v>
+        <v>854</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>818</v>
+        <v>855</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>758</v>
+        <v>795</v>
       </c>
       <c r="D57" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G57" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H57" s="27" t="s">
-        <v>798</v>
+        <v>835</v>
       </c>
       <c r="I57" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J57" s="27" t="s">
-        <v>819</v>
+        <v>856</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="58" t="s">
-        <v>820</v>
+        <v>857</v>
       </c>
       <c r="B58" s="58" t="s">
-        <v>821</v>
+        <v>858</v>
       </c>
       <c r="C58" s="58" t="s">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="D58" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E58" s="58" t="s">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="F58" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G58" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H58" s="58" t="s">
-        <v>701</v>
+        <v>738</v>
       </c>
       <c r="I58" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J58" s="58" t="s">
-        <v>822</v>
+        <v>859</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="27" t="s">
-        <v>823</v>
+        <v>860</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>824</v>
+        <v>861</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>684</v>
+        <v>721</v>
       </c>
       <c r="D59" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E59" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G59" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H59" s="27" t="s">
-        <v>715</v>
+        <v>752</v>
       </c>
       <c r="I59" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J59" s="27" t="s">
-        <v>825</v>
+        <v>862</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="58" t="s">
-        <v>826</v>
+        <v>863</v>
       </c>
       <c r="B60" s="58" t="s">
-        <v>827</v>
+        <v>864</v>
       </c>
       <c r="C60" s="58" t="s">
-        <v>828</v>
+        <v>865</v>
       </c>
       <c r="D60" s="58" t="s">
         <v>102</v>
       </c>
       <c r="E60" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F60" s="58" t="s">
-        <v>828</v>
+        <v>865</v>
       </c>
       <c r="G60" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H60" s="58" t="s">
-        <v>817</v>
+        <v>854</v>
       </c>
       <c r="I60" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J60" s="58" t="s">
-        <v>829</v>
+        <v>866</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="27" t="s">
-        <v>830</v>
+        <v>867</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>831</v>
+        <v>868</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>758</v>
+        <v>795</v>
       </c>
       <c r="D61" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G61" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H61" s="27" t="s">
-        <v>817</v>
+        <v>854</v>
       </c>
       <c r="I61" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J61" s="27" t="s">
-        <v>832</v>
+        <v>869</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="58" t="s">
-        <v>833</v>
+        <v>870</v>
       </c>
       <c r="B62" s="58" t="s">
-        <v>834</v>
+        <v>871</v>
       </c>
       <c r="C62" s="58" t="s">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="D62" s="58" t="s">
         <v>104</v>
       </c>
       <c r="E62" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F62" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G62" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H62" s="58" t="s">
-        <v>701</v>
+        <v>738</v>
       </c>
       <c r="I62" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J62" s="58" t="s">
-        <v>835</v>
+        <v>872</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="27" t="s">
-        <v>836</v>
+        <v>873</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>837</v>
+        <v>874</v>
       </c>
       <c r="C63" s="27" t="s">
-        <v>838</v>
+        <v>875</v>
       </c>
       <c r="D63" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E63" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G63" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H63" s="27" t="s">
-        <v>817</v>
+        <v>854</v>
       </c>
       <c r="I63" s="69" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="J63" s="27" t="s">
-        <v>839</v>
+        <v>876</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="58" t="s">
-        <v>840</v>
+        <v>877</v>
       </c>
       <c r="B64" s="58" t="s">
-        <v>841</v>
+        <v>878</v>
       </c>
       <c r="C64" s="58" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="D64" s="58" t="s">
         <v>104</v>
       </c>
       <c r="E64" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F64" s="58" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G64" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H64" s="58" t="s">
-        <v>830</v>
+        <v>867</v>
       </c>
       <c r="I64" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J64" s="58" t="s">
-        <v>842</v>
+        <v>879</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="27" t="s">
-        <v>843</v>
+        <v>880</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="C65" s="27" t="s">
-        <v>672</v>
+        <v>709</v>
       </c>
       <c r="D65" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E65" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G65" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H65" s="27" t="s">
-        <v>817</v>
+        <v>854</v>
       </c>
       <c r="I65" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J65" s="27" t="s">
-        <v>845</v>
+        <v>882</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="58" t="s">
-        <v>846</v>
+        <v>883</v>
       </c>
       <c r="B66" s="58" t="s">
-        <v>847</v>
+        <v>884</v>
       </c>
       <c r="C66" s="58" t="s">
-        <v>724</v>
+        <v>761</v>
       </c>
       <c r="D66" s="58" t="s">
         <v>104</v>
       </c>
       <c r="E66" s="58" t="s">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="F66" s="58" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G66" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H66" s="58" t="s">
-        <v>775</v>
+        <v>812</v>
       </c>
       <c r="I66" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J66" s="58" t="s">
-        <v>848</v>
+        <v>885</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="27" t="s">
-        <v>849</v>
+        <v>886</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>850</v>
+        <v>887</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>724</v>
+        <v>761</v>
       </c>
       <c r="D67" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F67" s="27" t="s">
         <v>100</v>
@@ -15015,30 +15343,30 @@
         <v>5</v>
       </c>
       <c r="H67" s="27" t="s">
-        <v>830</v>
+        <v>867</v>
       </c>
       <c r="I67" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J67" s="27" t="s">
-        <v>851</v>
+        <v>888</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="58" t="s">
-        <v>852</v>
+        <v>889</v>
       </c>
       <c r="B68" s="58" t="s">
-        <v>853</v>
+        <v>890</v>
       </c>
       <c r="C68" s="58" t="s">
-        <v>724</v>
+        <v>761</v>
       </c>
       <c r="D68" s="58" t="s">
         <v>106</v>
       </c>
       <c r="E68" s="58" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F68" s="58" t="s">
         <v>100</v>
@@ -15047,45 +15375,45 @@
         <v>1</v>
       </c>
       <c r="H68" s="58" t="s">
-        <v>849</v>
+        <v>886</v>
       </c>
       <c r="I68" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J68" s="58" t="s">
-        <v>854</v>
+        <v>891</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="27" t="s">
-        <v>855</v>
+        <v>892</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>856</v>
+        <v>893</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>724</v>
+        <v>761</v>
       </c>
       <c r="D69" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E69" s="27" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="F69" s="27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G69" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H69" s="27" t="s">
-        <v>843</v>
+        <v>880</v>
       </c>
       <c r="I69" s="69" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="J69" s="27" t="s">
-        <v>857</v>
+        <v>894</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15222,7 +15550,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D82" s="72" t="s">
-        <v>858</v>
+        <v>895</v>
       </c>
       <c r="E82" s="72"/>
       <c r="F82" s="72"/>
@@ -15233,7 +15561,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D83" s="73" t="s">
-        <v>859</v>
+        <v>896</v>
       </c>
       <c r="E83" s="73"/>
       <c r="F83" s="73"/>
@@ -15244,7 +15572,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D84" s="73" t="s">
-        <v>860</v>
+        <v>897</v>
       </c>
       <c r="E84" s="73"/>
       <c r="F84" s="73"/>
@@ -15255,7 +15583,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D85" s="73" t="s">
-        <v>861</v>
+        <v>898</v>
       </c>
       <c r="E85" s="73"/>
       <c r="F85" s="73"/>
@@ -15266,7 +15594,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D86" s="73" t="s">
-        <v>862</v>
+        <v>899</v>
       </c>
       <c r="E86" s="73"/>
       <c r="F86" s="73"/>
@@ -15277,7 +15605,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>863</v>
+        <v>900</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -15291,25 +15619,25 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="B90" s="9"/>
       <c r="C90" s="9" t="s">
-        <v>864</v>
+        <v>901</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>865</v>
+        <v>902</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>866</v>
+        <v>903</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>867</v>
+        <v>904</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="75" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="B91" s="75"/>
       <c r="C91" s="32" t="n">
@@ -15331,7 +15659,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="75" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="B92" s="75"/>
       <c r="C92" s="32" t="n">
@@ -15353,7 +15681,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="75" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="B93" s="75"/>
       <c r="C93" s="32" t="n">
@@ -15375,7 +15703,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="75" t="s">
-        <v>773</v>
+        <v>810</v>
       </c>
       <c r="B94" s="75"/>
       <c r="C94" s="32" t="n">
@@ -15397,7 +15725,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="75" t="s">
-        <v>828</v>
+        <v>865</v>
       </c>
       <c r="B95" s="75"/>
       <c r="C95" s="32" t="n">
@@ -15441,7 +15769,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="72" t="s">
-        <v>868</v>
+        <v>905</v>
       </c>
       <c r="B97" s="72"/>
       <c r="C97" s="21" t="n">
@@ -15467,16 +15795,16 @@
       </c>
       <c r="B99" s="29"/>
       <c r="C99" s="9" t="s">
-        <v>864</v>
+        <v>901</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>869</v>
+        <v>906</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>866</v>
+        <v>903</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>867</v>
+        <v>904</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15619,7 +15947,7 @@
     </row>
     <row r="107" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="54" t="s">
-        <v>870</v>
+        <v>907</v>
       </c>
       <c r="B107" s="54"/>
       <c r="C107" s="54"/>
@@ -15753,7 +16081,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>871</v>
+        <v>908</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -15771,22 +16099,22 @@
         <v>6</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>872</v>
+        <v>909</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>873</v>
+        <v>910</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>874</v>
+        <v>911</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>875</v>
+        <v>912</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>876</v>
+        <v>913</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>877</v>
+        <v>914</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15807,16 +16135,16 @@
         <v>46383</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>878</v>
+        <v>915</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>879</v>
+        <v>916</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>880</v>
+        <v>917</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>881</v>
+        <v>918</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15837,16 +16165,16 @@
         <v>46453</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>882</v>
+        <v>919</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>883</v>
+        <v>920</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>884</v>
+        <v>921</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15867,16 +16195,16 @@
         <v>46579</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>886</v>
+        <v>923</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>887</v>
+        <v>924</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>888</v>
+        <v>925</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>889</v>
+        <v>926</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15897,16 +16225,16 @@
         <v>46621</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>890</v>
+        <v>927</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>891</v>
+        <v>928</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>892</v>
+        <v>929</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>893</v>
+        <v>930</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15927,16 +16255,16 @@
         <v>46663</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>894</v>
+        <v>931</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>895</v>
+        <v>932</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>896</v>
+        <v>933</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>897</v>
+        <v>934</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15957,21 +16285,21 @@
         <v>46691</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>898</v>
+        <v>935</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>373</v>
+        <v>410</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>899</v>
+        <v>936</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>900</v>
+        <v>937</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>901</v>
+        <v>938</v>
       </c>
       <c r="B12" s="81" t="n">
         <f aca="false">D10</f>
@@ -15981,7 +16309,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>902</v>
+        <v>939</v>
       </c>
       <c r="B13" s="82" t="n">
         <f aca="false">B12-Assumptions!B7</f>
@@ -15991,7 +16319,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>903</v>
+        <v>940</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="24"/>
@@ -16003,7 +16331,7 @@
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
-        <v>904</v>
+        <v>941</v>
       </c>
       <c r="B15" s="54"/>
       <c r="C15" s="54"/>
@@ -16015,7 +16343,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="54" t="s">
-        <v>905</v>
+        <v>942</v>
       </c>
       <c r="B16" s="54"/>
       <c r="C16" s="54"/>
@@ -16095,7 +16423,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>906</v>
+        <v>943</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -16129,13 +16457,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>907</v>
+        <v>944</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>872</v>
+        <v>909</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>873</v>
+        <v>910</v>
       </c>
       <c r="D4" s="83" t="n">
         <v>1</v>
@@ -16320,7 +16648,7 @@
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>908</v>
+        <v>945</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -16567,7 +16895,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>909</v>
+        <v>946</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -18338,7 +18666,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>910</v>
+        <v>947</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -18585,7 +18913,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>911</v>
+        <v>948</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>

--- a/docs/Vinland_Game_Development_Plan.xlsx
+++ b/docs/Vinland_Game_Development_Plan.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1973" uniqueCount="1247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="1249">
   <si>
     <t xml:space="preserve">VINLAND</t>
   </si>
@@ -2446,7 +2446,7 @@
     <t xml:space="preserve">Trade</t>
   </si>
   <si>
-    <t xml:space="preserve">Trade raises goodwill; weapon sale, killing, palisade, loose bull raise fear toward the cap.  [Fear clock started: far hunting raises fear (cap 5). Goodwill and the market still to come.]</t>
+    <t xml:space="preserve">Trade raises goodwill; weapon sale, killing, palisade, loose bull raise fear toward the cap.  [Built: goodwill 0-10 from trades (+2 for a generous one), fear 0-5 from far hunting, the bull and weapon sales; fear eases 0.5 a quiet week; at the cap trade stops and raids take animals or hurt a crew member.]</t>
   </si>
   <si>
     <t xml:space="preserve">F20</t>
@@ -2455,7 +2455,7 @@
     <t xml:space="preserve">Market day</t>
   </si>
   <si>
-    <t xml:space="preserve">Milk and red cloth trade; visitors have wants of their own and leave when fear rises.</t>
+    <t xml:space="preserve">Milk and red cloth trade; visitors have wants of their own and leave when fear rises.  [Built: visitors come on about 6% of summer days (more with goodwill), bring 3-8 pelts; offer red cloth and milk on a trade screen; goodwill lowers the price; sending them away costs goodwill; auto-resolved in week mode. Visitors are neutral placeholders pending F59.]</t>
   </si>
   <si>
     <t xml:space="preserve">F21</t>
@@ -2464,7 +2464,7 @@
     <t xml:space="preserve">Bull and weapon-sale events</t>
   </si>
   <si>
-    <t xml:space="preserve">Either event can break the market; neither is a cutscene.</t>
+    <t xml:space="preserve">Either event can break the market; neither is a cutscene.  [Built: an unpenned bull breaks loose 1 in 4 markets until the byre is up (fear +2, market ends); penning keeps one crew member back. At goodwill 2+ they may ask for iron: refusing costs 0.5 goodwill, selling two blades gives 6 pelts and fear +2.]</t>
   </si>
   <si>
     <t xml:space="preserve">F22</t>
@@ -2539,7 +2539,7 @@
     <t xml:space="preserve">Main menu, options, pause</t>
   </si>
   <si>
-    <t xml:space="preserve">Options cover remaps, haptic strength, text size, and ironman.</t>
+    <t xml:space="preserve">Options cover remaps, haptic strength, text size, and ironman.  [Built: pause menu on Back / P with resume, difficulty, vibration on/off, prompts auto/always/never, save and quit to title; settings persist in user://settings.json. Still to do: remaps, haptic strength, text size, ironman.]</t>
   </si>
   <si>
     <t xml:space="preserve">F52</t>
@@ -2557,7 +2557,7 @@
     <t xml:space="preserve">Eriksfjord loadout</t>
   </si>
   <si>
-    <t xml:space="preserve">Player picks people, animals, and goods against the hull before leaving.</t>
+    <t xml:space="preserve">Player picks people, animals, and goods against the hull before leaving.  [Built: Eriksfjord loadout screen: people, cattle, sheep, food, drink, fodder, red cloth, iron against the 24-unit hull with days-of-stores readouts and warnings; Y restores the HoldCheck load; an overloaded hull will not sail; cloth and iron carry into the camp market.]</t>
   </si>
   <si>
     <t xml:space="preserve">F59</t>
@@ -3827,6 +3827,12 @@
   </si>
   <si>
     <t xml:space="preserve">One page now shows scope load, hold math, revenue, risk, and gate status.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F19, F20, F21, F53 marked Done; F51 In progress with the pause and options menu built.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market at the shore, the Eriksfjord loadout and the pause menu are in the build with tests.</t>
   </si>
 </sst>
 </file>
@@ -5031,11 +5037,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="34176278"/>
-        <c:axId val="17074735"/>
+        <c:axId val="47226815"/>
+        <c:axId val="18458890"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="34176278"/>
+        <c:axId val="47226815"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5067,7 +5073,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17074735"/>
+        <c:crossAx val="18458890"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5075,7 +5081,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="17074735"/>
+        <c:axId val="18458890"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5151,7 +5157,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34176278"/>
+        <c:crossAx val="47226815"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5190,9 +5196,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>741960</xdr:colOff>
+      <xdr:colOff>741600</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>58320</xdr:rowOff>
+      <xdr:rowOff>57960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5201,7 +5207,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="6562800"/>
-        <a:ext cx="5393880" cy="2153880"/>
+        <a:ext cx="5393520" cy="2153520"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6116,7 +6122,7 @@
       </c>
       <c r="B55" s="5" t="str">
         <f aca="false">COUNTIF(Backlog!I5:I80,"Done")&amp;" of "&amp;COUNTA(Backlog!A5:A80)</f>
-        <v>7 of 65</v>
+        <v>11 of 65</v>
       </c>
       <c r="C55" s="31" t="s">
         <v>68</v>
@@ -6138,7 +6144,7 @@
       </c>
       <c r="B56" s="38" t="n">
         <f aca="false">Backlog!G86</f>
-        <v>0.169934640522876</v>
+        <v>0.23202614379085</v>
       </c>
       <c r="C56" s="34" t="s">
         <v>71</v>
@@ -9146,7 +9152,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -9407,6 +9413,20 @@
       </c>
       <c r="D20" s="58" t="s">
         <v>1246</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="102" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B21" s="58" t="s">
+        <v>451</v>
+      </c>
+      <c r="C21" s="58" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D21" s="58" t="s">
+        <v>1248</v>
       </c>
     </row>
   </sheetData>
@@ -10996,14 +11016,14 @@
         <v>323</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="24" t="s">
         <v>324</v>
       </c>
       <c r="B160" s="24"/>
       <c r="C160" s="24"/>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="9" t="s">
         <v>132</v>
       </c>
@@ -11014,7 +11034,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="42" t="s">
         <v>325</v>
       </c>
@@ -11025,7 +11045,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="50" t="s">
         <v>327</v>
       </c>
@@ -11036,7 +11056,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="42" t="s">
         <v>329</v>
       </c>
@@ -11047,7 +11067,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="50" t="s">
         <v>331</v>
       </c>
@@ -11058,7 +11078,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="42" t="s">
         <v>333</v>
       </c>
@@ -11069,7 +11089,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="50" t="s">
         <v>336</v>
       </c>
@@ -11080,7 +11100,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="42" t="s">
         <v>338</v>
       </c>
@@ -11091,7 +11111,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="50" t="s">
         <v>340</v>
       </c>
@@ -11102,7 +11122,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="42" t="s">
         <v>342</v>
       </c>
@@ -11113,7 +11133,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="50" t="s">
         <v>344</v>
       </c>
@@ -11124,7 +11144,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="42" t="s">
         <v>346</v>
       </c>
@@ -11135,7 +11155,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="50" t="s">
         <v>348</v>
       </c>
@@ -11146,7 +11166,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="42" t="s">
         <v>350</v>
       </c>
@@ -11157,7 +11177,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="50" t="s">
         <v>352</v>
       </c>
@@ -11168,7 +11188,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="42" t="s">
         <v>354</v>
       </c>
@@ -11179,7 +11199,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="50" t="s">
         <v>356</v>
       </c>
@@ -11190,7 +11210,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="42" t="s">
         <v>358</v>
       </c>
@@ -11201,7 +11221,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="50" t="s">
         <v>360</v>
       </c>
@@ -14290,7 +14310,7 @@
         <v>531</v>
       </c>
       <c r="I34" s="69" t="s">
-        <v>722</v>
+        <v>705</v>
       </c>
       <c r="J34" s="58" t="s">
         <v>786</v>
@@ -14322,7 +14342,7 @@
         <v>783</v>
       </c>
       <c r="I35" s="69" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="J35" s="27" t="s">
         <v>789</v>
@@ -14354,7 +14374,7 @@
         <v>787</v>
       </c>
       <c r="I36" s="69" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="J36" s="58" t="s">
         <v>792</v>
@@ -14642,7 +14662,7 @@
         <v>744</v>
       </c>
       <c r="I45" s="69" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="J45" s="27" t="s">
         <v>817</v>
@@ -14706,7 +14726,7 @@
         <v>455</v>
       </c>
       <c r="I47" s="69" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="J47" s="27" t="s">
         <v>823</v>
@@ -15589,7 +15609,7 @@
       <c r="F85" s="73"/>
       <c r="G85" s="32" t="n">
         <f aca="false">SUMIF(I$5:I$80,"Done",G$5:G$80)</f>
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15600,7 +15620,7 @@
       <c r="F86" s="73"/>
       <c r="G86" s="74" t="n">
         <f aca="false">IF(G83=0,0,SUMIFS(G$5:G$80,E$5:E$80,"Must",I$5:I$80,"Done")/G83)</f>
-        <v>0.169934640522876</v>
+        <v>0.23202614379085</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/Vinland_Game_Development_Plan.xlsx
+++ b/docs/Vinland_Game_Development_Plan.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="1267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="1270">
   <si>
     <t xml:space="preserve">VINLAND</t>
   </si>
@@ -2332,7 +2332,7 @@
     <t xml:space="preserve">Sun board mini-game</t>
   </si>
   <si>
-    <t xml:space="preserve">Overcast skips it; a snatched shadow keeps yesterday's error.</t>
+    <t xml:space="preserve">Overcast skips it; a snatched shadow keeps yesterday's error.  [Playable: noon sun board on sunny days (fair, calm, drift ice; a gap in low cloud 35%); turn the disk, set the peg, steady through the roll, take the reading; a snatched shadow is partial. The day uses the better of sun and stars. Novice keyboard/pad 100/100% Forgiving, 100/96% Standard, 42/79% Hard.]</t>
   </si>
   <si>
     <t xml:space="preserve">Hand-line fishing</t>
@@ -2461,13 +2461,13 @@
     <t xml:space="preserve">Net throw</t>
   </si>
   <si>
-    <t xml:space="preserve">An empty throw spends the day.</t>
+    <t xml:space="preserve">An empty throw spends the day.  [Playable in the camp (B on the Fish row): aim ahead of the school, cast, close with both triggers at the school depth; deeper in rain, hidden in fog until near; one throw a day (two on Forgiving), up to 48 person-days. Novice 96/100% Forgiving, 71/92% Standard.]</t>
   </si>
   <si>
     <t xml:space="preserve">Drying and smoke rack</t>
   </si>
   <si>
-    <t xml:space="preserve">Two fair days turn fresh fish into a food unit.  [Smoke-and-dry job turns surplus fresh fish into stores on fair days (90% kept). Rack mini-game (MG9) still to come.]</t>
+    <t xml:space="preserve">Two fair days turn fresh fish into a food unit.  [Smoke-and-dry job turns surplus fresh fish into stores on fair days (90% kept). Rack fire mini-game (MG9) built: steer the smoke under the rack through gusts, hold the heat in the band; your fire cures up to 1.5x a dryer at 60-100% yield, a case-hardened rack loses your share.]</t>
   </si>
   <si>
     <t xml:space="preserve">Livestock, milk, hay</t>
@@ -3887,6 +3887,15 @@
   </si>
   <si>
     <t xml:space="preserve">Market at the shore, the Eriksfjord loadout and the pause menu are in the build with tests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backlog, Assumptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F04 sun board, F14 net and the MG9 smoke rack built; new WORK MINI-GAME PAYOFFS knobs on Assumptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The sun board, net and smoke rack are playable, tested with expert bots and novice models, and tuned per difficulty.</t>
   </si>
 </sst>
 </file>
@@ -5095,11 +5104,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="81071095"/>
-        <c:axId val="38110597"/>
+        <c:axId val="79622641"/>
+        <c:axId val="37277396"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="81071095"/>
+        <c:axId val="79622641"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5131,7 +5140,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38110597"/>
+        <c:crossAx val="37277396"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5139,7 +5148,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38110597"/>
+        <c:axId val="37277396"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5215,7 +5224,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81071095"/>
+        <c:crossAx val="79622641"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5254,9 +5263,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>741240</xdr:colOff>
+      <xdr:colOff>740520</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>57600</xdr:rowOff>
+      <xdr:rowOff>56880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5265,7 +5274,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="6562800"/>
-        <a:ext cx="5393160" cy="2153160"/>
+        <a:ext cx="5392440" cy="2152440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -9210,7 +9219,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -9485,6 +9494,20 @@
       </c>
       <c r="D21" s="59" t="s">
         <v>1266</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="103" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B22" s="59" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C22" s="59" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D22" s="59" t="s">
+        <v>1269</v>
       </c>
     </row>
   </sheetData>
@@ -13768,7 +13791,7 @@
         <v>612</v>
       </c>
       <c r="I12" s="70" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="J12" s="59" t="s">
         <v>748</v>
@@ -14312,7 +14335,7 @@
         <v>630</v>
       </c>
       <c r="I29" s="70" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="J29" s="27" t="s">
         <v>791</v>

--- a/docs/Vinland_Game_Development_Plan.xlsx
+++ b/docs/Vinland_Game_Development_Plan.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="1270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="1311">
   <si>
     <t xml:space="preserve">VINLAND</t>
   </si>
@@ -1225,6 +1225,123 @@
     <t xml:space="preserve">Smoke rack (MG9): case-hardened fish rots inside</t>
   </si>
   <si>
+    <t xml:space="preserve">OUTFITS AND CREW ROLES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merchant: pelt price multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfits (F22): red cloth buys more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merchant: forage multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfits (F22): forage-poor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farm household: byre work multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfits (F22): the byre is easier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farm household: fodder and hay go further</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfits (F22): fodder skill, at sea and in the byre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farm household: milk multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfits (F22): cheese keeps the milk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter-boat: shore fishing multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfits (F22): fishing people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter-boat: goodwill gain multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfits (F22): weak diplomacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter-boat: building multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfits (F22): weak builders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipwright's kin: timber felled multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfits (F22): they know a good tree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipwright's kin: repair levels at a landfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfits (F22): hull repair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipwright's kin: forage multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfits (F22): poor foragers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role: speed without a skipper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles (F23): no one who knows her helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role: repair levels at a landfall with a shipwright</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles (F23): without one, no repairs ashore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role: hooks a smith makes from one iron blade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles (F23): the smith at the camp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role: hooks the camp keeps before the smith works iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles (F23): the smith works when hooks run short</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role: sick days saved by a healer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles (F23): sickness at sea and ashore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role: milk multiplier with a householder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles (F23): the dairy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role: kill chance multiplier with a hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles (F23): someone who reads the herd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role: fewest crew to sail a knarr home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles (F23): the return voyage (F24)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pillars, fantasy, clocks, and the win</t>
   </si>
   <si>
@@ -2530,7 +2647,7 @@
     <t xml:space="preserve">Meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Each outfit changes the starting hold and one verb's ease.</t>
+    <t xml:space="preserve">Each outfit changes the starting hold and one verb's ease.  [Built: Merchant (Karlsefni), Farm household, Hunter-boat, Shipwright's kin chosen on the Eriksfjord loadout. Each sets the starting hold (all fit 24 units with stores for the crossing), the kit (hooks, nets, spare sail), one or two mini-games a step easier or harder, and multipliers on the Assumptions sheet (OUTFITS AND CREW ROLES). Every outfit crosses (40/40 careful runs) and winters (0 deaths, 0 animals lost with a planning player; the farm herd wants five haymakers).]</t>
   </si>
   <si>
     <t xml:space="preserve">F23</t>
@@ -2539,7 +2656,7 @@
     <t xml:space="preserve">Named crew roles</t>
   </si>
   <si>
-    <t xml:space="preserve">Roles decide who can stand a watch, take a verb, or sail home.</t>
+    <t xml:space="preserve">Roles decide who can stand a watch, take a verb, or sail home.  [Built: every run has a named crew, about two in five women, with leaders per outfit and seven key roles. Skipper: without one she sails 10% slower. Pilot: without one the star ring and sun board are a step harder. Shipwright: landfall repairs (two levels for Shipwright's kin). Smith: beats trade iron into hooks. Healer: sickness a day shorter. Householder: more milk. Hunter: better kill chance. Deaths name who was lost. Who can sail home (skipper or pilot plus 10 crew) is ready for F24.]</t>
   </si>
   <si>
     <t xml:space="preserve">Ship strain and hull damage</t>
@@ -3896,6 +4013,12 @@
   </si>
   <si>
     <t xml:space="preserve">The sun board, net and smoke rack are playable, tested with expert bots and novice models, and tuned per difficulty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F22 four outfits and F23 named crew roles built; OUTFITS AND CREW ROLES knobs added.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfits now change the hold, the kit and how the verbs feel; roles make each death matter.</t>
   </si>
 </sst>
 </file>
@@ -5104,11 +5227,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="79622641"/>
-        <c:axId val="37277396"/>
+        <c:axId val="5451543"/>
+        <c:axId val="74781591"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="79622641"/>
+        <c:axId val="5451543"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5140,7 +5263,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37277396"/>
+        <c:crossAx val="74781591"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5148,7 +5271,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37277396"/>
+        <c:axId val="74781591"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5224,7 +5347,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79622641"/>
+        <c:crossAx val="5451543"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5263,9 +5386,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>740520</xdr:colOff>
+      <xdr:colOff>739800</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>56880</xdr:rowOff>
+      <xdr:rowOff>56160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5274,7 +5397,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="6562800"/>
-        <a:ext cx="5392440" cy="2152440"/>
+        <a:ext cx="5391720" cy="2151720"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6189,7 +6312,7 @@
       </c>
       <c r="B55" s="5" t="str">
         <f aca="false">COUNTIF(Backlog!I5:I80,"Done")&amp;" of "&amp;COUNTA(Backlog!A5:A80)</f>
-        <v>11 of 65</v>
+        <v>13 of 65</v>
       </c>
       <c r="C55" s="31" t="s">
         <v>68</v>
@@ -6356,7 +6479,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>967</v>
+        <v>1006</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -6368,10 +6491,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>968</v>
+        <v>1007</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>969</v>
+        <v>1008</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>96</v>
@@ -6392,7 +6515,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="58" t="s">
-        <v>970</v>
+        <v>1009</v>
       </c>
       <c r="J4" s="58" t="s">
         <v>7</v>
@@ -6400,7 +6523,7 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="B5" s="90" t="n">
         <f aca="false">Assumptions!B26</f>
@@ -6435,7 +6558,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="B6" s="90" t="n">
         <f aca="false">Assumptions!B27</f>
@@ -6470,7 +6593,7 @@
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>735</v>
+        <v>774</v>
       </c>
       <c r="B7" s="90" t="n">
         <f aca="false">Assumptions!B28</f>
@@ -6505,7 +6628,7 @@
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>828</v>
+        <v>867</v>
       </c>
       <c r="B8" s="90" t="n">
         <f aca="false">Assumptions!B29</f>
@@ -6540,7 +6663,7 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>883</v>
+        <v>922</v>
       </c>
       <c r="B9" s="90" t="n">
         <f aca="false">Assumptions!B30</f>
@@ -6610,10 +6733,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="72" t="s">
-        <v>971</v>
+        <v>1010</v>
       </c>
       <c r="B11" s="72" t="s">
-        <v>972</v>
+        <v>1011</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -6650,10 +6773,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="72" t="s">
-        <v>973</v>
+        <v>1012</v>
       </c>
       <c r="B12" s="72" t="s">
-        <v>974</v>
+        <v>1013</v>
       </c>
       <c r="C12" s="63" t="n">
         <f aca="false">IF(Assumptions!B16=0,0,C11/Assumptions!B16)</f>
@@ -6686,7 +6809,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>975</v>
+        <v>1014</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -6701,28 +6824,28 @@
         <v>5</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>976</v>
+        <v>1015</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>735</v>
+        <v>774</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>828</v>
+        <v>867</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>883</v>
+        <v>922</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>100</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>970</v>
+        <v>1009</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>7</v>
@@ -6982,7 +7105,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>977</v>
+        <v>1016</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -6999,7 +7122,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="50" t="s">
-        <v>978</v>
+        <v>1017</v>
       </c>
       <c r="B22" s="50"/>
       <c r="C22" s="50"/>
@@ -7019,7 +7142,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="50" t="s">
-        <v>979</v>
+        <v>1018</v>
       </c>
       <c r="B23" s="50"/>
       <c r="C23" s="50"/>
@@ -7036,7 +7159,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="50" t="s">
-        <v>980</v>
+        <v>1019</v>
       </c>
       <c r="B24" s="50"/>
       <c r="C24" s="50"/>
@@ -7104,7 +7227,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="50" t="s">
-        <v>981</v>
+        <v>1020</v>
       </c>
       <c r="B28" s="50"/>
       <c r="C28" s="50"/>
@@ -7121,7 +7244,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>982</v>
+        <v>1021</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
@@ -7158,7 +7281,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="67" t="s">
-        <v>983</v>
+        <v>1022</v>
       </c>
       <c r="B31" s="67"/>
       <c r="C31" s="67"/>
@@ -7176,12 +7299,12 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="72" t="s">
-        <v>984</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="96" t="s">
-        <v>985</v>
+        <v>1024</v>
       </c>
       <c r="B34" s="96"/>
       <c r="C34" s="96"/>
@@ -7195,7 +7318,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>977</v>
+        <v>1016</v>
       </c>
       <c r="B35" s="91" t="n">
         <f aca="false">J21</f>
@@ -7204,7 +7327,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>986</v>
+        <v>1025</v>
       </c>
       <c r="B36" s="91" t="n">
         <f aca="false">J31</f>
@@ -7213,7 +7336,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>987</v>
+        <v>1026</v>
       </c>
       <c r="B37" s="91" t="n">
         <f aca="false">SUM(J22:J28)*(1+I30)</f>
@@ -7265,7 +7388,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>988</v>
+        <v>1027</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7274,7 +7397,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>989</v>
+        <v>1028</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -7289,7 +7412,7 @@
         <v>42</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>560</v>
+        <v>599</v>
       </c>
       <c r="D5" s="29"/>
       <c r="E5" s="29"/>
@@ -7303,28 +7426,28 @@
         <v>19.99</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>990</v>
+        <v>1029</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>991</v>
+        <v>1030</v>
       </c>
       <c r="B7" s="98" t="n">
         <f aca="false">B6*Assumptions!B70</f>
         <v>15.992</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>992</v>
+        <v>1031</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>993</v>
+        <v>1032</v>
       </c>
       <c r="B8" s="98" t="n">
         <f aca="false">B7*(1-Assumptions!B71)</f>
@@ -7336,35 +7459,35 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>994</v>
+        <v>1033</v>
       </c>
       <c r="B9" s="75" t="n">
         <f aca="false">Assumptions!B72*(1-Assumptions!B74)+Assumptions!B73*Assumptions!B74</f>
         <v>0.29</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>995</v>
+        <v>1034</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>996</v>
+        <v>1035</v>
       </c>
       <c r="B10" s="99" t="n">
         <f aca="false">B8*(1-B9)</f>
         <v>10.4459744</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>997</v>
+        <v>1036</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>998</v>
+        <v>1037</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -7379,7 +7502,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>560</v>
+        <v>599</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="29"/>
@@ -7393,70 +7516,70 @@
         <v>460504.8</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>999</v>
+        <v>1038</v>
       </c>
       <c r="D14" s="33"/>
       <c r="E14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>1000</v>
+        <v>1039</v>
       </c>
       <c r="B15" s="100" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B14/B10,0))</f>
         <v>44085</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>1001</v>
+        <v>1040</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>1002</v>
+        <v>1041</v>
       </c>
       <c r="B16" s="90" t="n">
         <f aca="false">TeamBudget!B37</f>
         <v>98632.8</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>1003</v>
+        <v>1042</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="67" t="s">
-        <v>1004</v>
+        <v>1043</v>
       </c>
       <c r="B17" s="100" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B16/B10,0))</f>
         <v>9443</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>1005</v>
+        <v>1044</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>1006</v>
+        <v>1045</v>
       </c>
       <c r="B18" s="91" t="n">
         <f aca="false">B15*B6</f>
         <v>881259.15</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>1007</v>
+        <v>1046</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>1008</v>
+        <v>1047</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -7465,19 +7588,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>1009</v>
+        <v>1048</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1010</v>
+        <v>1049</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1011</v>
+        <v>1050</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1012</v>
+        <v>1051</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>922</v>
+        <v>961</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7592,7 +7715,7 @@
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="54" t="s">
-        <v>1013</v>
+        <v>1052</v>
       </c>
       <c r="B28" s="54"/>
       <c r="C28" s="54"/>
@@ -7674,7 +7797,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1014</v>
+        <v>1053</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7686,195 +7809,195 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>932</v>
+        <v>971</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1015</v>
+        <v>1054</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1016</v>
+        <v>1055</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1017</v>
+        <v>1056</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>716</v>
+        <v>755</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1018</v>
+        <v>1057</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>1019</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>936</v>
+        <v>975</v>
       </c>
       <c r="B5" s="87" t="n">
         <f aca="false">Schedule!D5</f>
         <v>46383</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1020</v>
+        <v>1059</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1021</v>
+        <v>1060</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="F5" s="70" t="s">
-        <v>1022</v>
+        <v>1061</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1023</v>
+        <v>1062</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>1024</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>940</v>
+        <v>979</v>
       </c>
       <c r="B6" s="87" t="n">
         <f aca="false">Schedule!D6</f>
         <v>46453</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1025</v>
+        <v>1064</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1026</v>
+        <v>1065</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="F6" s="70" t="s">
-        <v>1022</v>
+        <v>1061</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>1027</v>
+        <v>1066</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>1028</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>944</v>
+        <v>983</v>
       </c>
       <c r="B7" s="87" t="n">
         <f aca="false">Schedule!D7</f>
         <v>46579</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1029</v>
+        <v>1068</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1030</v>
+        <v>1069</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="F7" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1031</v>
+        <v>1070</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>1032</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>948</v>
+        <v>987</v>
       </c>
       <c r="B8" s="87" t="n">
         <f aca="false">Schedule!D8</f>
         <v>46621</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1033</v>
+        <v>1072</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1034</v>
+        <v>1073</v>
       </c>
       <c r="E8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="F8" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>1035</v>
+        <v>1074</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>1036</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>952</v>
+        <v>991</v>
       </c>
       <c r="B9" s="87" t="n">
         <f aca="false">Schedule!D9</f>
         <v>46663</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1037</v>
+        <v>1076</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1038</v>
+        <v>1077</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>883</v>
+        <v>922</v>
       </c>
       <c r="F9" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1039</v>
+        <v>1078</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>1040</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>955</v>
+        <v>994</v>
       </c>
       <c r="B10" s="87" t="n">
         <f aca="false">Schedule!D10</f>
         <v>46691</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1041</v>
+        <v>1080</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>1042</v>
+        <v>1081</v>
       </c>
       <c r="E10" s="59" t="s">
         <v>100</v>
       </c>
       <c r="F10" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>1043</v>
+        <v>1082</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>1044</v>
+        <v>1083</v>
       </c>
       <c r="B12" s="54"/>
       <c r="C12" s="54"/>
@@ -7954,7 +8077,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1045</v>
+        <v>1084</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7968,31 +8091,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>380</v>
+        <v>419</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1046</v>
+        <v>1085</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1047</v>
+        <v>1086</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1048</v>
+        <v>1087</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>530</v>
+        <v>569</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>1049</v>
+        <v>1088</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>716</v>
+        <v>755</v>
       </c>
       <c r="H4" s="58" t="s">
-        <v>1050</v>
+        <v>1089</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>1051</v>
+        <v>1090</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>44</v>
@@ -8000,10 +8123,10 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="59" t="s">
-        <v>1052</v>
+        <v>1091</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>1053</v>
+        <v>1092</v>
       </c>
       <c r="C5" s="43" t="n">
         <v>3</v>
@@ -8016,27 +8139,27 @@
         <v>15</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>1054</v>
+        <v>1093</v>
       </c>
       <c r="G5" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="H5" s="59" t="s">
-        <v>940</v>
+        <v>979</v>
       </c>
       <c r="I5" s="59" t="s">
-        <v>1055</v>
+        <v>1094</v>
       </c>
       <c r="J5" s="70" t="s">
-        <v>1056</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>1057</v>
+        <v>1096</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1058</v>
+        <v>1097</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>3</v>
@@ -8049,27 +8172,27 @@
         <v>12</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>1059</v>
+        <v>1098</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>940</v>
+        <v>979</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>1060</v>
+        <v>1099</v>
       </c>
       <c r="J6" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="59" t="s">
-        <v>1062</v>
+        <v>1101</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>1063</v>
+        <v>1102</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>2</v>
@@ -8082,27 +8205,27 @@
         <v>8</v>
       </c>
       <c r="F7" s="59" t="s">
-        <v>1064</v>
+        <v>1103</v>
       </c>
       <c r="G7" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="H7" s="59" t="s">
-        <v>952</v>
+        <v>991</v>
       </c>
       <c r="I7" s="59" t="s">
-        <v>1065</v>
+        <v>1104</v>
       </c>
       <c r="J7" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1066</v>
+        <v>1105</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1067</v>
+        <v>1106</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>4</v>
@@ -8115,27 +8238,27 @@
         <v>12</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>1068</v>
+        <v>1107</v>
       </c>
       <c r="G8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>944</v>
+        <v>983</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>1069</v>
+        <v>1108</v>
       </c>
       <c r="J8" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="59" t="s">
-        <v>1070</v>
+        <v>1109</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1071</v>
+        <v>1110</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>2</v>
@@ -8148,27 +8271,27 @@
         <v>6</v>
       </c>
       <c r="F9" s="59" t="s">
-        <v>1072</v>
+        <v>1111</v>
       </c>
       <c r="G9" s="59" t="s">
-        <v>735</v>
+        <v>774</v>
       </c>
       <c r="H9" s="59" t="s">
-        <v>944</v>
+        <v>983</v>
       </c>
       <c r="I9" s="59" t="s">
-        <v>1073</v>
+        <v>1112</v>
       </c>
       <c r="J9" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1074</v>
+        <v>1113</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1075</v>
+        <v>1114</v>
       </c>
       <c r="C10" s="43" t="n">
         <v>2</v>
@@ -8181,27 +8304,27 @@
         <v>10</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>1076</v>
+        <v>1115</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>944</v>
+        <v>983</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>1077</v>
+        <v>1116</v>
       </c>
       <c r="J10" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="59" t="s">
-        <v>1078</v>
+        <v>1117</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>1079</v>
+        <v>1118</v>
       </c>
       <c r="C11" s="43" t="n">
         <v>3</v>
@@ -8214,27 +8337,27 @@
         <v>12</v>
       </c>
       <c r="F11" s="59" t="s">
-        <v>1080</v>
+        <v>1119</v>
       </c>
       <c r="G11" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H11" s="59" t="s">
-        <v>948</v>
+        <v>987</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>1081</v>
+        <v>1120</v>
       </c>
       <c r="J11" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1082</v>
+        <v>1121</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1083</v>
+        <v>1122</v>
       </c>
       <c r="C12" s="43" t="n">
         <v>2</v>
@@ -8247,27 +8370,27 @@
         <v>8</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>1084</v>
+        <v>1123</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>936</v>
+        <v>975</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>1085</v>
+        <v>1124</v>
       </c>
       <c r="J12" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="59" t="s">
-        <v>1086</v>
+        <v>1125</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>1087</v>
+        <v>1126</v>
       </c>
       <c r="C13" s="43" t="n">
         <v>2</v>
@@ -8280,27 +8403,27 @@
         <v>4</v>
       </c>
       <c r="F13" s="59" t="s">
-        <v>1088</v>
+        <v>1127</v>
       </c>
       <c r="G13" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="H13" s="59" t="s">
-        <v>936</v>
+        <v>975</v>
       </c>
       <c r="I13" s="59" t="s">
-        <v>1089</v>
+        <v>1128</v>
       </c>
       <c r="J13" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1090</v>
+        <v>1129</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1091</v>
+        <v>1130</v>
       </c>
       <c r="C14" s="43" t="n">
         <v>3</v>
@@ -8313,27 +8436,27 @@
         <v>12</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>1092</v>
+        <v>1131</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="H14" s="59" t="s">
-        <v>948</v>
+        <v>987</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>1093</v>
+        <v>1132</v>
       </c>
       <c r="J14" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="59" t="s">
-        <v>1094</v>
+        <v>1133</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>1095</v>
+        <v>1134</v>
       </c>
       <c r="C15" s="43" t="n">
         <v>3</v>
@@ -8346,27 +8469,27 @@
         <v>15</v>
       </c>
       <c r="F15" s="59" t="s">
-        <v>1096</v>
+        <v>1135</v>
       </c>
       <c r="G15" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="H15" s="59" t="s">
-        <v>944</v>
+        <v>983</v>
       </c>
       <c r="I15" s="59" t="s">
-        <v>1097</v>
+        <v>1136</v>
       </c>
       <c r="J15" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>1098</v>
+        <v>1137</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>1099</v>
+        <v>1138</v>
       </c>
       <c r="C16" s="43" t="n">
         <v>4</v>
@@ -8379,27 +8502,27 @@
         <v>16</v>
       </c>
       <c r="F16" s="59" t="s">
-        <v>1100</v>
+        <v>1139</v>
       </c>
       <c r="G16" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H16" s="59" t="s">
-        <v>940</v>
+        <v>979</v>
       </c>
       <c r="I16" s="59" t="s">
-        <v>1101</v>
+        <v>1140</v>
       </c>
       <c r="J16" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="59" t="s">
-        <v>1102</v>
+        <v>1141</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>1103</v>
+        <v>1142</v>
       </c>
       <c r="C17" s="43" t="n">
         <v>3</v>
@@ -8412,27 +8535,27 @@
         <v>12</v>
       </c>
       <c r="F17" s="59" t="s">
-        <v>1104</v>
+        <v>1143</v>
       </c>
       <c r="G17" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="59" t="s">
-        <v>944</v>
+        <v>983</v>
       </c>
       <c r="I17" s="59" t="s">
-        <v>1105</v>
+        <v>1144</v>
       </c>
       <c r="J17" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>1106</v>
+        <v>1145</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1107</v>
+        <v>1146</v>
       </c>
       <c r="C18" s="43" t="n">
         <v>2</v>
@@ -8445,27 +8568,27 @@
         <v>6</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>1108</v>
+        <v>1147</v>
       </c>
       <c r="G18" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="H18" s="59" t="s">
-        <v>952</v>
+        <v>991</v>
       </c>
       <c r="I18" s="59" t="s">
-        <v>1109</v>
+        <v>1148</v>
       </c>
       <c r="J18" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="59" t="s">
-        <v>1110</v>
+        <v>1149</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>1111</v>
+        <v>1150</v>
       </c>
       <c r="C19" s="43" t="n">
         <v>2</v>
@@ -8478,27 +8601,27 @@
         <v>8</v>
       </c>
       <c r="F19" s="59" t="s">
-        <v>1112</v>
+        <v>1151</v>
       </c>
       <c r="G19" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="H19" s="59" t="s">
-        <v>944</v>
+        <v>983</v>
       </c>
       <c r="I19" s="59" t="s">
-        <v>1113</v>
+        <v>1152</v>
       </c>
       <c r="J19" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>1114</v>
+        <v>1153</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1115</v>
+        <v>1154</v>
       </c>
       <c r="C20" s="43" t="n">
         <v>3</v>
@@ -8511,19 +8634,19 @@
         <v>15</v>
       </c>
       <c r="F20" s="59" t="s">
-        <v>1116</v>
+        <v>1155</v>
       </c>
       <c r="G20" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>940</v>
+        <v>979</v>
       </c>
       <c r="I20" s="59" t="s">
-        <v>1117</v>
+        <v>1156</v>
       </c>
       <c r="J20" s="70" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
@@ -8601,7 +8724,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1118</v>
+        <v>1157</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8612,278 +8735,278 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>1119</v>
+        <v>1158</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1120</v>
+        <v>1159</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1121</v>
+        <v>1160</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1122</v>
+        <v>1161</v>
       </c>
       <c r="E4" s="58" t="s">
         <v>95</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>716</v>
+        <v>755</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1123</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1124</v>
+        <v>1163</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1125</v>
+        <v>1164</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1126</v>
+        <v>1165</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1127</v>
+        <v>1166</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>1128</v>
+        <v>1167</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>735</v>
+        <v>774</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1129</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>688</v>
+        <v>727</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1130</v>
+        <v>1169</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1131</v>
+        <v>1170</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1132</v>
+        <v>1171</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>1133</v>
+        <v>1172</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>1134</v>
+        <v>1173</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>1135</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1136</v>
+        <v>1175</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1137</v>
+        <v>1176</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1138</v>
+        <v>1177</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1139</v>
+        <v>1178</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>1140</v>
+        <v>1179</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>735</v>
+        <v>774</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1135</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1141</v>
+        <v>1180</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1142</v>
+        <v>1181</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1143</v>
+        <v>1182</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1144</v>
+        <v>1183</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>1145</v>
+        <v>1184</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>735</v>
+        <v>774</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>1146</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>573</v>
+        <v>612</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1147</v>
+        <v>1186</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1148</v>
+        <v>1187</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1149</v>
+        <v>1188</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1150</v>
+        <v>1189</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>735</v>
+        <v>774</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1151</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>764</v>
+        <v>803</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1152</v>
+        <v>1191</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1153</v>
+        <v>1192</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>886</v>
+        <v>925</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>1154</v>
+        <v>1193</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>735</v>
+        <v>774</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>1155</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>828</v>
+        <v>867</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1156</v>
+        <v>1195</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1157</v>
+        <v>1196</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1158</v>
+        <v>1197</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>1159</v>
+        <v>1198</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>828</v>
+        <v>867</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>1160</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>847</v>
+        <v>886</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1161</v>
+        <v>1200</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1162</v>
+        <v>1201</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>1163</v>
+        <v>1202</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>1164</v>
+        <v>1203</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>1135</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1165</v>
+        <v>1204</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1166</v>
+        <v>1205</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1167</v>
+        <v>1206</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1168</v>
+        <v>1207</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>1169</v>
+        <v>1208</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>1135</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1170</v>
+        <v>1209</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1171</v>
+        <v>1210</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1172</v>
+        <v>1211</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>1173</v>
+        <v>1212</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>1174</v>
+        <v>1213</v>
       </c>
       <c r="F14" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>1175</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1176</v>
+        <v>1215</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1177</v>
+        <v>1216</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1178</v>
+        <v>1217</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1179</v>
+        <v>1218</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>1180</v>
+        <v>1219</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>1181</v>
+        <v>1220</v>
       </c>
     </row>
   </sheetData>
@@ -8925,7 +9048,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1182</v>
+        <v>1221</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8936,24 +9059,24 @@
         <v>110</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1183</v>
+        <v>1222</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1184</v>
+        <v>1223</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>716</v>
+        <v>755</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1185</v>
+        <v>1224</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1186</v>
+        <v>1225</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>936</v>
+        <v>975</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>100</v>
@@ -8961,55 +9084,55 @@
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>1187</v>
+        <v>1226</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1188</v>
+        <v>1227</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1189</v>
+        <v>1228</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1190</v>
+        <v>1229</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1191</v>
+        <v>1230</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>944</v>
+        <v>983</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1192</v>
+        <v>1231</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1193</v>
+        <v>1232</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>940</v>
+        <v>979</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1194</v>
+        <v>1233</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1195</v>
+        <v>1234</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>936</v>
+        <v>975</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>100</v>
@@ -9017,27 +9140,27 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1196</v>
+        <v>1235</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1197</v>
+        <v>1236</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>944</v>
+        <v>983</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>1198</v>
+        <v>1237</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1199</v>
+        <v>1238</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>952</v>
+        <v>991</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>100</v>
@@ -9045,13 +9168,13 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1200</v>
+        <v>1239</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1201</v>
+        <v>1240</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>955</v>
+        <v>994</v>
       </c>
       <c r="D12" s="59" t="s">
         <v>100</v>
@@ -9059,41 +9182,41 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1202</v>
+        <v>1241</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1203</v>
+        <v>1242</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>955</v>
+        <v>994</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>883</v>
+        <v>922</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1204</v>
+        <v>1243</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1205</v>
+        <v>1244</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1206</v>
+        <v>1245</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1207</v>
+        <v>1246</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1208</v>
+        <v>1247</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>940</v>
+        <v>979</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>100</v>
@@ -9101,14 +9224,14 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>1209</v>
+        <v>1248</v>
       </c>
       <c r="B16" s="59" t="str">
         <f aca="false">"Premium at $"&amp;TEXT(Assumptions!B69,"0.00")&amp;". Launch discount no deeper than the realized-price factor on Assumptions."</f>
         <v>Premium at $19.99. Launch discount no deeper than the realized-price factor on Assumptions.</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>948</v>
+        <v>987</v>
       </c>
       <c r="D16" s="59" t="s">
         <v>100</v>
@@ -9116,13 +9239,13 @@
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>1210</v>
+        <v>1249</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1211</v>
+        <v>1250</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>940</v>
+        <v>979</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>100</v>
@@ -9130,13 +9253,13 @@
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>930</v>
+        <v>969</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1212</v>
+        <v>1251</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>948</v>
+        <v>987</v>
       </c>
       <c r="D18" s="59" t="s">
         <v>100</v>
@@ -9144,27 +9267,27 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1213</v>
+        <v>1252</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1214</v>
+        <v>1253</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>952</v>
+        <v>991</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>1215</v>
+        <v>1254</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1216</v>
+        <v>1255</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>952</v>
+        <v>991</v>
       </c>
       <c r="D20" s="59" t="s">
         <v>100</v>
@@ -9172,27 +9295,27 @@
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>1217</v>
+        <v>1256</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1218</v>
+        <v>1257</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>952</v>
+        <v>991</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="59" t="s">
-        <v>1219</v>
+        <v>1258</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1220</v>
+        <v>1259</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>955</v>
+        <v>994</v>
       </c>
       <c r="D22" s="59" t="s">
         <v>100</v>
@@ -9219,7 +9342,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -9238,7 +9361,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1221</v>
+        <v>1260</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9246,16 +9369,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1222</v>
+        <v>1261</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1223</v>
+        <v>1262</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1224</v>
+        <v>1263</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1225</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9263,13 +9386,13 @@
         <v>46311</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1226</v>
+        <v>1265</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1227</v>
+        <v>1266</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1228</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9277,13 +9400,13 @@
         <v>46311</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1226</v>
+        <v>1265</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1229</v>
+        <v>1268</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1230</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9291,13 +9414,13 @@
         <v>46311</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1226</v>
+        <v>1265</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1231</v>
+        <v>1270</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1232</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9305,13 +9428,13 @@
         <v>46311</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>990</v>
+        <v>1029</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1233</v>
+        <v>1272</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1234</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9319,13 +9442,13 @@
         <v>46311</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1235</v>
+        <v>1274</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1236</v>
+        <v>1275</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1237</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9336,10 +9459,10 @@
         <v>53</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1238</v>
+        <v>1277</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>1239</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9347,13 +9470,13 @@
         <v>46311</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1240</v>
+        <v>1279</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1241</v>
+        <v>1280</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1242</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9361,13 +9484,13 @@
         <v>46311</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>469</v>
+        <v>508</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1243</v>
+        <v>1282</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>1244</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9375,13 +9498,13 @@
         <v>46311</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1245</v>
+        <v>1284</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1246</v>
+        <v>1285</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1247</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9389,13 +9512,13 @@
         <v>46311</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1248</v>
+        <v>1287</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1249</v>
+        <v>1288</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>1250</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9406,10 +9529,10 @@
         <v>58</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1251</v>
+        <v>1290</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1252</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9417,13 +9540,13 @@
         <v>46311</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>1253</v>
+        <v>1292</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>1254</v>
+        <v>1293</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>1255</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9434,10 +9557,10 @@
         <v>62</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1256</v>
+        <v>1295</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1257</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9445,13 +9568,13 @@
         <v>46311</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>1258</v>
+        <v>1297</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>1259</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9459,13 +9582,13 @@
         <v>46311</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>779</v>
+        <v>818</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1260</v>
+        <v>1299</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>1261</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9473,13 +9596,13 @@
         <v>46311</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1262</v>
+        <v>1301</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>1263</v>
+        <v>1302</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>1264</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9487,13 +9610,13 @@
         <v>46313</v>
       </c>
       <c r="B21" s="59" t="s">
-        <v>469</v>
+        <v>508</v>
       </c>
       <c r="C21" s="59" t="s">
-        <v>1265</v>
+        <v>1304</v>
       </c>
       <c r="D21" s="59" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9501,13 +9624,27 @@
         <v>46313</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1267</v>
+        <v>1306</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>1268</v>
+        <v>1307</v>
       </c>
       <c r="D22" s="59" t="s">
-        <v>1269</v>
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="103" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B23" s="59" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C23" s="59" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D23" s="59" t="s">
+        <v>1310</v>
       </c>
     </row>
   </sheetData>
@@ -9531,7 +9668,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F190"/>
+  <dimension ref="A1:F212"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
@@ -11415,6 +11552,231 @@
       </c>
       <c r="C190" s="41" t="s">
         <v>378</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A192" s="57" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A193" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B193" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C193" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A194" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="B194" s="43" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C194" s="41" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A195" s="42" t="s">
+        <v>382</v>
+      </c>
+      <c r="B195" s="43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C195" s="41" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A196" s="42" t="s">
+        <v>384</v>
+      </c>
+      <c r="B196" s="43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C196" s="41" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A197" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="B197" s="43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C197" s="41" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A198" s="42" t="s">
+        <v>388</v>
+      </c>
+      <c r="B198" s="43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C198" s="41" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A199" s="42" t="s">
+        <v>390</v>
+      </c>
+      <c r="B199" s="43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C199" s="41" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A200" s="42" t="s">
+        <v>392</v>
+      </c>
+      <c r="B200" s="43" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C200" s="41" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A201" s="42" t="s">
+        <v>394</v>
+      </c>
+      <c r="B201" s="43" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C201" s="41" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A202" s="42" t="s">
+        <v>396</v>
+      </c>
+      <c r="B202" s="43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C202" s="41" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A203" s="42" t="s">
+        <v>398</v>
+      </c>
+      <c r="B203" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C203" s="41" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A204" s="42" t="s">
+        <v>400</v>
+      </c>
+      <c r="B204" s="43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C204" s="41" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A205" s="42" t="s">
+        <v>402</v>
+      </c>
+      <c r="B205" s="43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C205" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A206" s="42" t="s">
+        <v>404</v>
+      </c>
+      <c r="B206" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C206" s="41" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A207" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="B207" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C207" s="41" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A208" s="42" t="s">
+        <v>408</v>
+      </c>
+      <c r="B208" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C208" s="41" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A209" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="B209" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" s="41" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A210" s="42" t="s">
+        <v>412</v>
+      </c>
+      <c r="B210" s="43" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C210" s="41" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A211" s="42" t="s">
+        <v>414</v>
+      </c>
+      <c r="B211" s="43" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C211" s="41" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A212" s="42" t="s">
+        <v>416</v>
+      </c>
+      <c r="B212" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C212" s="41" t="s">
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -11481,7 +11843,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>379</v>
+        <v>418</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11490,160 +11852,160 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>380</v>
+        <v>419</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>381</v>
+        <v>420</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>383</v>
+        <v>422</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>384</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>385</v>
+        <v>424</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>386</v>
+        <v>425</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>387</v>
+        <v>426</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>388</v>
+        <v>427</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>390</v>
+        <v>429</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>391</v>
+        <v>430</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>392</v>
+        <v>431</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>393</v>
+        <v>432</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>394</v>
+        <v>433</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>395</v>
+        <v>434</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>396</v>
+        <v>435</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>397</v>
+        <v>436</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>398</v>
+        <v>437</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>400</v>
+        <v>439</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>401</v>
+        <v>440</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>402</v>
+        <v>441</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>403</v>
+        <v>442</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>404</v>
+        <v>443</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>405</v>
+        <v>444</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>406</v>
+        <v>445</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>414</v>
+        <v>453</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>415</v>
+        <v>454</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>416</v>
+        <v>455</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>417</v>
+        <v>456</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>418</v>
+        <v>457</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -11652,16 +12014,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>420</v>
+        <v>459</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>422</v>
+        <v>461</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>95</v>
@@ -11669,58 +12031,58 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="60" t="s">
-        <v>423</v>
+        <v>462</v>
       </c>
       <c r="B16" s="60" t="s">
-        <v>424</v>
+        <v>463</v>
       </c>
       <c r="C16" s="60" t="s">
-        <v>425</v>
+        <v>464</v>
       </c>
       <c r="D16" s="60" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
       <c r="E16" s="60" t="s">
-        <v>427</v>
+        <v>466</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="59" t="s">
-        <v>428</v>
+        <v>467</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>429</v>
+        <v>468</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>430</v>
+        <v>469</v>
       </c>
       <c r="D17" s="59" t="s">
-        <v>431</v>
+        <v>470</v>
       </c>
       <c r="E17" s="59" t="s">
-        <v>432</v>
+        <v>471</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="60" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="B18" s="60" t="s">
-        <v>434</v>
+        <v>473</v>
       </c>
       <c r="C18" s="60" t="s">
-        <v>435</v>
+        <v>474</v>
       </c>
       <c r="D18" s="60" t="s">
-        <v>436</v>
+        <v>475</v>
       </c>
       <c r="E18" s="60" t="s">
-        <v>437</v>
+        <v>476</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>438</v>
+        <v>477</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="24"/>
@@ -11729,87 +12091,87 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>439</v>
+        <v>478</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>440</v>
+        <v>479</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>441</v>
+        <v>480</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>442</v>
+        <v>481</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>443</v>
+        <v>482</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>444</v>
+        <v>483</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>445</v>
+        <v>484</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>446</v>
+        <v>485</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>447</v>
+        <v>486</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>448</v>
+        <v>487</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="59" t="s">
-        <v>449</v>
+        <v>488</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>450</v>
+        <v>489</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>451</v>
+        <v>490</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>452</v>
+        <v>491</v>
       </c>
       <c r="E23" s="59" t="s">
-        <v>453</v>
+        <v>492</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>454</v>
+        <v>493</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>456</v>
+        <v>495</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="59" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="B25" s="59" t="s">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>460</v>
+        <v>499</v>
       </c>
       <c r="D25" s="59" t="s">
-        <v>461</v>
+        <v>500</v>
       </c>
       <c r="E25" s="59" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -11862,7 +12224,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>463</v>
+        <v>502</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11873,33 +12235,33 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>464</v>
+        <v>503</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>465</v>
+        <v>504</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>466</v>
+        <v>505</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="F4" s="58" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>469</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>470</v>
+        <v>509</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>471</v>
+        <v>510</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>134</v>
@@ -11909,37 +12271,37 @@
         <v>24</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>472</v>
+        <v>511</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>474</v>
+        <v>513</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>475</v>
+        <v>514</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="D6" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>477</v>
+        <v>516</v>
       </c>
       <c r="F6" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>478</v>
+        <v>517</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11947,71 +12309,71 @@
         <v>228</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>479</v>
+        <v>518</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>480</v>
+        <v>519</v>
       </c>
       <c r="D7" s="61" t="n">
         <f aca="false">Assumptions!B44</f>
         <v>120</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>481</v>
+        <v>520</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>483</v>
+        <v>522</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>484</v>
+        <v>523</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>485</v>
+        <v>524</v>
       </c>
       <c r="D8" s="61" t="n">
         <f aca="false">Assumptions!B46</f>
         <v>400</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="F8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>487</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>488</v>
+        <v>527</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>489</v>
+        <v>528</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="D9" s="61" t="n">
         <f aca="false">Assumptions!B45</f>
         <v>120</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12019,151 +12381,151 @@
         <v>219</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>493</v>
+        <v>532</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>495</v>
+        <v>534</v>
       </c>
       <c r="F10" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>498</v>
+        <v>537</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>500</v>
+        <v>539</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="F12" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>506</v>
+        <v>545</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>507</v>
+        <v>546</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>508</v>
+        <v>547</v>
       </c>
       <c r="D13" s="61" t="n">
         <f aca="false">Assumptions!B43</f>
         <v>168</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>510</v>
+        <v>549</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>511</v>
+        <v>550</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>512</v>
+        <v>551</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>513</v>
+        <v>552</v>
       </c>
       <c r="D14" s="61" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="F14" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>516</v>
+        <v>555</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>517</v>
+        <v>556</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>518</v>
+        <v>557</v>
       </c>
       <c r="D15" s="61" t="n">
         <f aca="false">Assumptions!B50</f>
         <v>5</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>519</v>
+        <v>558</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>520</v>
+        <v>559</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>521</v>
+        <v>560</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>523</v>
+        <v>562</v>
       </c>
       <c r="D16" s="61" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -12176,78 +12538,78 @@
         <v>102</v>
       </c>
       <c r="G16" s="59" t="s">
-        <v>524</v>
+        <v>563</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>525</v>
+        <v>564</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>527</v>
+        <v>566</v>
       </c>
       <c r="D17" s="61" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>528</v>
+        <v>567</v>
       </c>
       <c r="F17" s="27" t="s">
         <v>102</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>530</v>
+        <v>569</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>531</v>
+        <v>570</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>532</v>
+        <v>571</v>
       </c>
       <c r="F18" s="59" t="s">
         <v>104</v>
       </c>
       <c r="G18" s="59" t="s">
-        <v>533</v>
+        <v>572</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>534</v>
+        <v>573</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>535</v>
+        <v>574</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>536</v>
+        <v>575</v>
       </c>
       <c r="D19" s="61" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>537</v>
+        <v>576</v>
       </c>
       <c r="F19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>538</v>
+        <v>577</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12255,46 +12617,46 @@
         <v>224</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>539</v>
+        <v>578</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="E20" s="59" t="s">
-        <v>540</v>
+        <v>579</v>
       </c>
       <c r="F20" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G20" s="59" t="s">
-        <v>541</v>
+        <v>580</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>542</v>
+        <v>581</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>543</v>
+        <v>582</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="D21" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>544</v>
+        <v>583</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>545</v>
+        <v>584</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12302,55 +12664,55 @@
         <v>236</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>546</v>
+        <v>585</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>547</v>
+        <v>586</v>
       </c>
       <c r="D22" s="61" t="n">
         <f aca="false">Assumptions!B57</f>
         <v>2</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>548</v>
+        <v>587</v>
       </c>
       <c r="F22" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G22" s="59" t="s">
-        <v>549</v>
+        <v>588</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>550</v>
+        <v>589</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>551</v>
+        <v>590</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>513</v>
+        <v>552</v>
       </c>
       <c r="D23" s="61" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>552</v>
+        <v>591</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>553</v>
+        <v>592</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="59" t="s">
-        <v>554</v>
+        <v>593</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>555</v>
+        <v>594</v>
       </c>
       <c r="C24" s="59" t="s">
         <v>134</v>
@@ -12360,13 +12722,13 @@
         <v>24</v>
       </c>
       <c r="E24" s="59" t="s">
-        <v>556</v>
+        <v>595</v>
       </c>
       <c r="F24" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G24" s="59" t="s">
-        <v>557</v>
+        <v>596</v>
       </c>
     </row>
   </sheetData>
@@ -12412,7 +12774,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>558</v>
+        <v>597</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12421,7 +12783,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>559</v>
+        <v>598</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -12436,21 +12798,21 @@
         <v>42</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>560</v>
+        <v>599</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>561</v>
+        <v>600</v>
       </c>
       <c r="B6" s="62" t="n">
         <f aca="false">Assumptions!B62</f>
         <v>1200</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>562</v>
+        <v>601</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
@@ -12464,21 +12826,21 @@
         <v>120</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>563</v>
+        <v>602</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>564</v>
+        <v>603</v>
       </c>
       <c r="B8" s="63" t="n">
         <f aca="false">IF(B7=0,0,B6/B7)</f>
         <v>10</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>565</v>
+        <v>604</v>
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="33"/>
@@ -12492,7 +12854,7 @@
         <v>1.3</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>566</v>
+        <v>605</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
@@ -12506,14 +12868,14 @@
         <v>13</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>567</v>
+        <v>606</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>568</v>
+        <v>607</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -12522,24 +12884,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>569</v>
+        <v>608</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>570</v>
+        <v>609</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>571</v>
+        <v>610</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>572</v>
+        <v>611</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>465</v>
+        <v>504</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>573</v>
+        <v>612</v>
       </c>
       <c r="B14" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
@@ -12554,12 +12916,12 @@
         <v>9.6</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>574</v>
+        <v>613</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>575</v>
+        <v>614</v>
       </c>
       <c r="B15" s="61" t="n">
         <f aca="false">Assumptions!B57</f>
@@ -12574,12 +12936,12 @@
         <v>3</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>576</v>
+        <v>615</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>577</v>
+        <v>616</v>
       </c>
       <c r="B16" s="61" t="n">
         <f aca="false">Assumptions!B58</f>
@@ -12597,7 +12959,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="B17" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B43,0)</f>
@@ -12611,12 +12973,12 @@
         <v>2</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>578</v>
+        <v>617</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>579</v>
+        <v>618</v>
       </c>
       <c r="B18" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B44,0)</f>
@@ -12630,12 +12992,12 @@
         <v>3</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>580</v>
+        <v>619</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>581</v>
+        <v>620</v>
       </c>
       <c r="B19" s="32" t="n">
         <f aca="false">ROUNDUP((B15+B16*Assumptions!B60)*$B$10/Assumptions!B59,0)</f>
@@ -12649,12 +13011,12 @@
         <v>2</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>582</v>
+        <v>621</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>583</v>
+        <v>622</v>
       </c>
       <c r="B20" s="61" t="n">
         <f aca="false">Assumptions!B61</f>
@@ -12673,7 +13035,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>584</v>
+        <v>623</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -12685,7 +13047,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>585</v>
+        <v>624</v>
       </c>
       <c r="D22" s="65" t="n">
         <f aca="false">Assumptions!B41</f>
@@ -12694,7 +13056,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="67" t="s">
-        <v>586</v>
+        <v>625</v>
       </c>
       <c r="B23" s="67"/>
       <c r="C23" s="67"/>
@@ -12709,7 +13071,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>587</v>
+        <v>626</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -12718,24 +13080,24 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>569</v>
+        <v>608</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>570</v>
+        <v>609</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>571</v>
+        <v>610</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>572</v>
+        <v>611</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>465</v>
+        <v>504</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>588</v>
+        <v>627</v>
       </c>
       <c r="B27" s="61" t="n">
         <f aca="false">Assumptions!B64</f>
@@ -12755,7 +13117,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="59" t="s">
-        <v>589</v>
+        <v>628</v>
       </c>
       <c r="B28" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B43,0)</f>
@@ -12769,12 +13131,12 @@
         <v>1</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>590</v>
+        <v>629</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>591</v>
+        <v>630</v>
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B44,0)</f>
@@ -12791,7 +13153,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>592</v>
+        <v>631</v>
       </c>
       <c r="D30" s="63" t="n">
         <f aca="false">SUM(D27:D29)</f>
@@ -12800,7 +13162,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>593</v>
+        <v>632</v>
       </c>
       <c r="D31" s="63" t="n">
         <f aca="false">Assumptions!B41-D30</f>
@@ -12809,7 +13171,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>594</v>
+        <v>633</v>
       </c>
       <c r="D32" s="32" t="n">
         <f aca="false">INT(D31/Assumptions!B65)</f>
@@ -12818,7 +13180,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>595</v>
+        <v>634</v>
       </c>
       <c r="D33" s="61" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -12827,7 +13189,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="67" t="s">
-        <v>521</v>
+        <v>560</v>
       </c>
       <c r="B34" s="67"/>
       <c r="C34" s="67"/>
@@ -12842,7 +13204,7 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="54" t="s">
-        <v>596</v>
+        <v>635</v>
       </c>
       <c r="B36" s="54"/>
       <c r="C36" s="54"/>
@@ -12923,7 +13285,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>597</v>
+        <v>636</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12938,392 +13300,392 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>380</v>
+        <v>419</v>
       </c>
       <c r="B4" s="58" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>598</v>
+        <v>637</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>599</v>
+        <v>638</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>600</v>
+        <v>639</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>601</v>
+        <v>640</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H4" s="58" t="s">
-        <v>603</v>
+        <v>642</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>469</v>
+        <v>508</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>604</v>
+        <v>643</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>606</v>
+        <v>645</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>608</v>
+        <v>647</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>609</v>
+        <v>648</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>610</v>
+        <v>649</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>611</v>
+        <v>650</v>
       </c>
       <c r="H5" s="70" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>612</v>
+        <v>651</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>613</v>
+        <v>652</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>614</v>
+        <v>653</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>615</v>
+        <v>654</v>
       </c>
       <c r="B6" s="59" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>616</v>
+        <v>655</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>617</v>
+        <v>656</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>618</v>
+        <v>657</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>619</v>
+        <v>658</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>620</v>
+        <v>659</v>
       </c>
       <c r="H6" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>621</v>
+        <v>660</v>
       </c>
       <c r="J6" s="59" t="s">
-        <v>622</v>
+        <v>661</v>
       </c>
       <c r="K6" s="59" t="s">
-        <v>623</v>
+        <v>662</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>624</v>
+        <v>663</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>625</v>
+        <v>664</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>626</v>
+        <v>665</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>627</v>
+        <v>666</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>628</v>
+        <v>667</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>629</v>
+        <v>668</v>
       </c>
       <c r="H7" s="70" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>630</v>
+        <v>669</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>631</v>
+        <v>670</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>632</v>
+        <v>671</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>633</v>
+        <v>672</v>
       </c>
       <c r="B8" s="59" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>634</v>
+        <v>673</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>635</v>
+        <v>674</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>636</v>
+        <v>675</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>637</v>
+        <v>676</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>638</v>
+        <v>677</v>
       </c>
       <c r="H8" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>639</v>
+        <v>678</v>
       </c>
       <c r="J8" s="59" t="s">
-        <v>640</v>
+        <v>679</v>
       </c>
       <c r="K8" s="59" t="s">
-        <v>641</v>
+        <v>680</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>642</v>
+        <v>681</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>643</v>
+        <v>682</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>644</v>
+        <v>683</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>645</v>
+        <v>684</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>646</v>
+        <v>685</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>647</v>
+        <v>686</v>
       </c>
       <c r="H9" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>648</v>
+        <v>687</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>649</v>
+        <v>688</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>650</v>
+        <v>689</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>651</v>
+        <v>690</v>
       </c>
       <c r="B10" s="59" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>652</v>
+        <v>691</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>653</v>
+        <v>692</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>654</v>
+        <v>693</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>655</v>
+        <v>694</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>656</v>
+        <v>695</v>
       </c>
       <c r="H10" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>657</v>
+        <v>696</v>
       </c>
       <c r="J10" s="59" t="s">
-        <v>658</v>
+        <v>697</v>
       </c>
       <c r="K10" s="59" t="s">
-        <v>659</v>
+        <v>698</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>660</v>
+        <v>699</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>661</v>
+        <v>700</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>662</v>
+        <v>701</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>663</v>
+        <v>702</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>664</v>
+        <v>703</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>665</v>
+        <v>704</v>
       </c>
       <c r="H11" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>666</v>
+        <v>705</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>667</v>
+        <v>706</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>668</v>
+        <v>707</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>669</v>
+        <v>708</v>
       </c>
       <c r="B12" s="59" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>670</v>
+        <v>709</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>671</v>
+        <v>710</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>672</v>
+        <v>711</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>673</v>
+        <v>712</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>674</v>
+        <v>713</v>
       </c>
       <c r="H12" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>675</v>
+        <v>714</v>
       </c>
       <c r="J12" s="59" t="s">
-        <v>676</v>
+        <v>715</v>
       </c>
       <c r="K12" s="59" t="s">
-        <v>677</v>
+        <v>716</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>678</v>
+        <v>717</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>679</v>
+        <v>718</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>680</v>
+        <v>719</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>681</v>
+        <v>720</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>682</v>
+        <v>721</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>683</v>
+        <v>722</v>
       </c>
       <c r="H13" s="70" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>684</v>
+        <v>723</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>686</v>
+        <v>725</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>687</v>
+        <v>726</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>688</v>
+        <v>727</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>689</v>
+        <v>728</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>690</v>
+        <v>729</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>691</v>
+        <v>730</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>692</v>
+        <v>731</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>693</v>
+        <v>732</v>
       </c>
       <c r="H14" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>694</v>
+        <v>733</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>695</v>
+        <v>734</v>
       </c>
       <c r="K14" s="59" t="s">
-        <v>696</v>
+        <v>735</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>697</v>
+        <v>736</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
@@ -13335,10 +13697,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>698</v>
+        <v>737</v>
       </c>
       <c r="B17" s="71" t="s">
-        <v>699</v>
+        <v>738</v>
       </c>
       <c r="C17" s="71"/>
       <c r="D17" s="71"/>
@@ -13349,10 +13711,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>700</v>
+        <v>739</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>701</v>
+        <v>740</v>
       </c>
       <c r="C18" s="71"/>
       <c r="D18" s="71"/>
@@ -13363,10 +13725,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>702</v>
+        <v>741</v>
       </c>
       <c r="B19" s="71" t="s">
-        <v>703</v>
+        <v>742</v>
       </c>
       <c r="C19" s="71"/>
       <c r="D19" s="71"/>
@@ -13377,10 +13739,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>704</v>
+        <v>743</v>
       </c>
       <c r="B20" s="71" t="s">
-        <v>705</v>
+        <v>744</v>
       </c>
       <c r="C20" s="71"/>
       <c r="D20" s="71"/>
@@ -13391,10 +13753,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>706</v>
+        <v>745</v>
       </c>
       <c r="B21" s="71" t="s">
-        <v>707</v>
+        <v>746</v>
       </c>
       <c r="C21" s="71"/>
       <c r="D21" s="71"/>
@@ -13405,10 +13767,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>708</v>
+        <v>747</v>
       </c>
       <c r="B22" s="71" t="s">
-        <v>709</v>
+        <v>748</v>
       </c>
       <c r="C22" s="71"/>
       <c r="D22" s="71"/>
@@ -13419,10 +13781,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>710</v>
+        <v>749</v>
       </c>
       <c r="B23" s="71" t="s">
-        <v>711</v>
+        <v>750</v>
       </c>
       <c r="C23" s="71"/>
       <c r="D23" s="71"/>
@@ -13433,7 +13795,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="72" t="s">
-        <v>712</v>
+        <v>751</v>
       </c>
     </row>
   </sheetData>
@@ -13497,7 +13859,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>713</v>
+        <v>752</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -13511,42 +13873,42 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>380</v>
+        <v>419</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>714</v>
+        <v>753</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>464</v>
+        <v>503</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>715</v>
+        <v>754</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>716</v>
+        <v>755</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>717</v>
+        <v>756</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>718</v>
+        <v>757</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>719</v>
+        <v>758</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>720</v>
+        <v>759</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
@@ -13555,190 +13917,190 @@
         <v>96</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G5" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="I5" s="70" t="s">
-        <v>723</v>
+        <v>762</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>724</v>
+        <v>763</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>725</v>
+        <v>764</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>726</v>
+        <v>765</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>727</v>
+        <v>766</v>
       </c>
       <c r="D6" s="59" t="s">
         <v>96</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G6" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>720</v>
+        <v>759</v>
       </c>
       <c r="I6" s="70" t="s">
-        <v>723</v>
+        <v>762</v>
       </c>
       <c r="J6" s="59" t="s">
-        <v>729</v>
+        <v>768</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>730</v>
+        <v>769</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>731</v>
+        <v>770</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>727</v>
+        <v>766</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G7" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>725</v>
+        <v>764</v>
       </c>
       <c r="I7" s="70" t="s">
-        <v>723</v>
+        <v>762</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>732</v>
+        <v>771</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>733</v>
+        <v>772</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>734</v>
+        <v>773</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>735</v>
+        <v>774</v>
       </c>
       <c r="D8" s="59" t="s">
         <v>96</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>735</v>
+        <v>774</v>
       </c>
       <c r="G8" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="I8" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J8" s="59" t="s">
-        <v>737</v>
+        <v>776</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>738</v>
+        <v>777</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>739</v>
+        <v>778</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G9" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="I9" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>741</v>
+        <v>780</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>742</v>
+        <v>781</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>743</v>
+        <v>782</v>
       </c>
       <c r="D10" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G10" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="I10" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J10" s="59" t="s">
-        <v>744</v>
+        <v>783</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>612</v>
+        <v>651</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>745</v>
+        <v>784</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>23</v>
@@ -13747,30 +14109,30 @@
         <v>98</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G11" s="43" t="n">
         <v>12</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="I11" s="70" t="s">
-        <v>723</v>
+        <v>762</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>746</v>
+        <v>785</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>621</v>
+        <v>660</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>747</v>
+        <v>786</v>
       </c>
       <c r="C12" s="59" t="s">
         <v>23</v>
@@ -13779,30 +14141,30 @@
         <v>98</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G12" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>612</v>
+        <v>651</v>
       </c>
       <c r="I12" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J12" s="59" t="s">
-        <v>748</v>
+        <v>787</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>630</v>
+        <v>669</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>749</v>
+        <v>788</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>26</v>
@@ -13811,62 +14173,62 @@
         <v>98</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G13" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="I13" s="70" t="s">
-        <v>723</v>
+        <v>762</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>750</v>
+        <v>789</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>751</v>
+        <v>790</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="D14" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G14" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H14" s="59" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="I14" s="70" t="s">
-        <v>723</v>
+        <v>762</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>753</v>
+        <v>792</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>666</v>
+        <v>705</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>754</v>
+        <v>793</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>35</v>
@@ -13875,263 +14237,263 @@
         <v>98</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G15" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>751</v>
+        <v>790</v>
       </c>
       <c r="I15" s="70" t="s">
-        <v>723</v>
+        <v>762</v>
       </c>
       <c r="J15" s="27" t="s">
-        <v>755</v>
+        <v>794</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>756</v>
+        <v>795</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>757</v>
+        <v>796</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>599</v>
+        <v>638</v>
       </c>
       <c r="D16" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E16" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F16" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G16" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H16" s="59" t="s">
-        <v>612</v>
+        <v>651</v>
       </c>
       <c r="I16" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J16" s="59" t="s">
-        <v>758</v>
+        <v>797</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>538</v>
+        <v>577</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>759</v>
+        <v>798</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>760</v>
+        <v>799</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G17" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="I17" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>761</v>
+        <v>800</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>762</v>
+        <v>801</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>763</v>
+        <v>802</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>764</v>
+        <v>803</v>
       </c>
       <c r="D18" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>735</v>
+        <v>774</v>
       </c>
       <c r="G18" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H18" s="59" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="I18" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J18" s="59" t="s">
-        <v>765</v>
+        <v>804</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>766</v>
+        <v>805</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>739</v>
+        <v>778</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G19" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="I19" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>767</v>
+        <v>806</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>768</v>
+        <v>807</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>743</v>
+        <v>782</v>
       </c>
       <c r="D20" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E20" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F20" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G20" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>612</v>
+        <v>651</v>
       </c>
       <c r="I20" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J20" s="59" t="s">
-        <v>769</v>
+        <v>808</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>770</v>
+        <v>809</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>771</v>
+        <v>810</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>772</v>
+        <v>811</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G21" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="I21" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J21" s="27" t="s">
-        <v>773</v>
+        <v>812</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="59" t="s">
-        <v>774</v>
+        <v>813</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>775</v>
+        <v>814</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>599</v>
+        <v>638</v>
       </c>
       <c r="D22" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F22" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G22" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="59" t="s">
-        <v>756</v>
+        <v>795</v>
       </c>
       <c r="I22" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J22" s="59" t="s">
-        <v>776</v>
+        <v>815</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>777</v>
+        <v>816</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>778</v>
+        <v>817</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>779</v>
+        <v>818</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>780</v>
+        <v>819</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
@@ -14140,117 +14502,117 @@
         <v>3</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>733</v>
+        <v>772</v>
       </c>
       <c r="I23" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>781</v>
+        <v>820</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="59" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="C24" s="59" t="s">
-        <v>743</v>
+        <v>782</v>
       </c>
       <c r="D24" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E24" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F24" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G24" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H24" s="59" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="I24" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J24" s="59" t="s">
-        <v>782</v>
+        <v>821</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>694</v>
+        <v>733</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>689</v>
+        <v>728</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>743</v>
+        <v>782</v>
       </c>
       <c r="D25" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G25" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="I25" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J25" s="27" t="s">
-        <v>783</v>
+        <v>822</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="59" t="s">
-        <v>784</v>
+        <v>823</v>
       </c>
       <c r="B26" s="59" t="s">
-        <v>785</v>
+        <v>824</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>743</v>
+        <v>782</v>
       </c>
       <c r="D26" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E26" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F26" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G26" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="I26" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J26" s="59" t="s">
-        <v>786</v>
+        <v>825</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>648</v>
+        <v>687</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>643</v>
+        <v>682</v>
       </c>
       <c r="C27" s="27" t="s">
         <v>29</v>
@@ -14259,30 +14621,30 @@
         <v>100</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G27" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>751</v>
+        <v>790</v>
       </c>
       <c r="I27" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J27" s="27" t="s">
-        <v>787</v>
+        <v>826</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="59" t="s">
-        <v>657</v>
+        <v>696</v>
       </c>
       <c r="B28" s="59" t="s">
-        <v>788</v>
+        <v>827</v>
       </c>
       <c r="C28" s="59" t="s">
         <v>32</v>
@@ -14291,30 +14653,30 @@
         <v>100</v>
       </c>
       <c r="E28" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F28" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G28" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H28" s="59" t="s">
-        <v>751</v>
+        <v>790</v>
       </c>
       <c r="I28" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J28" s="59" t="s">
-        <v>789</v>
+        <v>828</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>639</v>
+        <v>678</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>790</v>
+        <v>829</v>
       </c>
       <c r="C29" s="27" t="s">
         <v>26</v>
@@ -14323,94 +14685,94 @@
         <v>100</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>780</v>
+        <v>819</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G29" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>630</v>
+        <v>669</v>
       </c>
       <c r="I29" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>791</v>
+        <v>830</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="59" t="s">
-        <v>684</v>
+        <v>723</v>
       </c>
       <c r="B30" s="59" t="s">
-        <v>792</v>
+        <v>831</v>
       </c>
       <c r="C30" s="59" t="s">
-        <v>739</v>
+        <v>778</v>
       </c>
       <c r="D30" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F30" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G30" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="59" t="s">
-        <v>630</v>
+        <v>669</v>
       </c>
       <c r="I30" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J30" s="59" t="s">
-        <v>793</v>
+        <v>832</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="s">
-        <v>549</v>
+        <v>588</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>794</v>
+        <v>833</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="D31" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G31" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="I31" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J31" s="27" t="s">
-        <v>795</v>
+        <v>834</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="59" t="s">
-        <v>796</v>
+        <v>835</v>
       </c>
       <c r="B32" s="59" t="s">
-        <v>797</v>
+        <v>836</v>
       </c>
       <c r="C32" s="59" t="s">
         <v>35</v>
@@ -14419,30 +14781,30 @@
         <v>100</v>
       </c>
       <c r="E32" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F32" s="59" t="s">
-        <v>735</v>
+        <v>774</v>
       </c>
       <c r="G32" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H32" s="59" t="s">
-        <v>666</v>
+        <v>705</v>
       </c>
       <c r="I32" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J32" s="59" t="s">
-        <v>798</v>
+        <v>837</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>675</v>
+        <v>714</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>799</v>
+        <v>838</v>
       </c>
       <c r="C33" s="27" t="s">
         <v>35</v>
@@ -14451,487 +14813,487 @@
         <v>100</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G33" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>666</v>
+        <v>705</v>
       </c>
       <c r="I33" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J33" s="27" t="s">
-        <v>800</v>
+        <v>839</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="59" t="s">
-        <v>801</v>
+        <v>840</v>
       </c>
       <c r="B34" s="59" t="s">
-        <v>802</v>
+        <v>841</v>
       </c>
       <c r="C34" s="59" t="s">
-        <v>803</v>
+        <v>842</v>
       </c>
       <c r="D34" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F34" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G34" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H34" s="59" t="s">
-        <v>549</v>
+        <v>588</v>
       </c>
       <c r="I34" s="70" t="s">
-        <v>723</v>
+        <v>762</v>
       </c>
       <c r="J34" s="59" t="s">
-        <v>804</v>
+        <v>843</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>806</v>
+        <v>845</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>803</v>
+        <v>842</v>
       </c>
       <c r="D35" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G35" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>801</v>
+        <v>840</v>
       </c>
       <c r="I35" s="70" t="s">
-        <v>723</v>
+        <v>762</v>
       </c>
       <c r="J35" s="27" t="s">
-        <v>807</v>
+        <v>846</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="59" t="s">
-        <v>808</v>
+        <v>847</v>
       </c>
       <c r="B36" s="59" t="s">
-        <v>809</v>
+        <v>848</v>
       </c>
       <c r="C36" s="59" t="s">
-        <v>803</v>
+        <v>842</v>
       </c>
       <c r="D36" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F36" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G36" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H36" s="59" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
       <c r="I36" s="70" t="s">
-        <v>723</v>
+        <v>762</v>
       </c>
       <c r="J36" s="59" t="s">
-        <v>810</v>
+        <v>849</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="27" t="s">
-        <v>811</v>
+        <v>850</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>812</v>
+        <v>851</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>813</v>
+        <v>852</v>
       </c>
       <c r="D37" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>780</v>
+        <v>819</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G37" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H37" s="27" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="I37" s="70" t="s">
-        <v>736</v>
+        <v>762</v>
       </c>
       <c r="J37" s="27" t="s">
-        <v>814</v>
+        <v>853</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="59" t="s">
-        <v>815</v>
+        <v>854</v>
       </c>
       <c r="B38" s="59" t="s">
-        <v>816</v>
+        <v>855</v>
       </c>
       <c r="C38" s="59" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="D38" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="59" t="s">
-        <v>780</v>
+        <v>819</v>
       </c>
       <c r="F38" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G38" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="59" t="s">
-        <v>811</v>
+        <v>850</v>
       </c>
       <c r="I38" s="70" t="s">
-        <v>736</v>
+        <v>762</v>
       </c>
       <c r="J38" s="59" t="s">
-        <v>817</v>
+        <v>856</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="27" t="s">
-        <v>541</v>
+        <v>580</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>818</v>
+        <v>857</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>760</v>
+        <v>799</v>
       </c>
       <c r="D39" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G39" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="I39" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J39" s="27" t="s">
-        <v>819</v>
+        <v>858</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="59" t="s">
-        <v>545</v>
+        <v>584</v>
       </c>
       <c r="B40" s="59" t="s">
-        <v>542</v>
+        <v>581</v>
       </c>
       <c r="C40" s="59" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="D40" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F40" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G40" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H40" s="59" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="I40" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J40" s="59" t="s">
-        <v>820</v>
+        <v>859</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>553</v>
+        <v>592</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>821</v>
+        <v>860</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="D41" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G41" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>549</v>
+        <v>588</v>
       </c>
       <c r="I41" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J41" s="27" t="s">
-        <v>822</v>
+        <v>861</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="59" t="s">
-        <v>823</v>
+        <v>862</v>
       </c>
       <c r="B42" s="59" t="s">
-        <v>824</v>
+        <v>863</v>
       </c>
       <c r="C42" s="59" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="D42" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="59" t="s">
-        <v>780</v>
+        <v>819</v>
       </c>
       <c r="F42" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G42" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="59" t="s">
-        <v>815</v>
+        <v>854</v>
       </c>
       <c r="I42" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J42" s="59" t="s">
-        <v>825</v>
+        <v>864</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
-        <v>826</v>
+        <v>865</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>827</v>
+        <v>866</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>828</v>
+        <v>867</v>
       </c>
       <c r="D43" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>828</v>
+        <v>867</v>
       </c>
       <c r="G43" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H43" s="27" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="I43" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J43" s="27" t="s">
-        <v>829</v>
+        <v>868</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="59" t="s">
-        <v>830</v>
+        <v>869</v>
       </c>
       <c r="B44" s="59" t="s">
-        <v>831</v>
+        <v>870</v>
       </c>
       <c r="C44" s="59" t="s">
-        <v>727</v>
+        <v>766</v>
       </c>
       <c r="D44" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E44" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F44" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G44" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H44" s="59" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="I44" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J44" s="59" t="s">
-        <v>832</v>
+        <v>871</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="27" t="s">
-        <v>833</v>
+        <v>872</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>834</v>
+        <v>873</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>764</v>
+        <v>803</v>
       </c>
       <c r="D45" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G45" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H45" s="27" t="s">
-        <v>762</v>
+        <v>801</v>
       </c>
       <c r="I45" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J45" s="27" t="s">
-        <v>835</v>
+        <v>874</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="59" t="s">
-        <v>836</v>
+        <v>875</v>
       </c>
       <c r="B46" s="59" t="s">
-        <v>837</v>
+        <v>876</v>
       </c>
       <c r="C46" s="59" t="s">
-        <v>599</v>
+        <v>638</v>
       </c>
       <c r="D46" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E46" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F46" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G46" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H46" s="59" t="s">
-        <v>756</v>
+        <v>795</v>
       </c>
       <c r="I46" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J46" s="59" t="s">
-        <v>838</v>
+        <v>877</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
-        <v>839</v>
+        <v>878</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>840</v>
+        <v>879</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>813</v>
+        <v>852</v>
       </c>
       <c r="D47" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G47" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H47" s="27" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="I47" s="70" t="s">
-        <v>723</v>
+        <v>762</v>
       </c>
       <c r="J47" s="27" t="s">
-        <v>841</v>
+        <v>880</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="59" t="s">
-        <v>842</v>
+        <v>881</v>
       </c>
       <c r="B48" s="59" t="s">
-        <v>843</v>
+        <v>882</v>
       </c>
       <c r="C48" s="59" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="D48" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E48" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F48" s="59" t="s">
         <v>100</v>
@@ -14940,62 +15302,62 @@
         <v>3</v>
       </c>
       <c r="H48" s="59" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
       <c r="I48" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J48" s="59" t="s">
-        <v>844</v>
+        <v>883</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="27" t="s">
-        <v>845</v>
+        <v>884</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>846</v>
+        <v>885</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>847</v>
+        <v>886</v>
       </c>
       <c r="D49" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>780</v>
+        <v>819</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G49" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H49" s="27" t="s">
-        <v>833</v>
+        <v>872</v>
       </c>
       <c r="I49" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J49" s="27" t="s">
-        <v>848</v>
+        <v>887</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="59" t="s">
-        <v>849</v>
+        <v>888</v>
       </c>
       <c r="B50" s="59" t="s">
-        <v>850</v>
+        <v>889</v>
       </c>
       <c r="C50" s="59" t="s">
-        <v>851</v>
+        <v>890</v>
       </c>
       <c r="D50" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E50" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F50" s="59" t="s">
         <v>100</v>
@@ -15004,181 +15366,181 @@
         <v>4</v>
       </c>
       <c r="H50" s="59" t="s">
-        <v>770</v>
+        <v>809</v>
       </c>
       <c r="I50" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J50" s="59" t="s">
-        <v>852</v>
+        <v>891</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
-        <v>853</v>
+        <v>892</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>854</v>
+        <v>893</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>855</v>
+        <v>894</v>
       </c>
       <c r="D51" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G51" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H51" s="27" t="s">
-        <v>784</v>
+        <v>823</v>
       </c>
       <c r="I51" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J51" s="27" t="s">
-        <v>856</v>
+        <v>895</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="59" t="s">
-        <v>857</v>
+        <v>896</v>
       </c>
       <c r="B52" s="59" t="s">
-        <v>858</v>
+        <v>897</v>
       </c>
       <c r="C52" s="59" t="s">
-        <v>855</v>
+        <v>894</v>
       </c>
       <c r="D52" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E52" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F52" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G52" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H52" s="59" t="s">
-        <v>675</v>
+        <v>714</v>
       </c>
       <c r="I52" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J52" s="59" t="s">
-        <v>859</v>
+        <v>898</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="27" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>860</v>
+        <v>899</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>855</v>
+        <v>894</v>
       </c>
       <c r="D53" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F53" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G53" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H53" s="27" t="s">
-        <v>857</v>
+        <v>896</v>
       </c>
       <c r="I53" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J53" s="27" t="s">
-        <v>861</v>
+        <v>900</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="59" t="s">
-        <v>862</v>
+        <v>901</v>
       </c>
       <c r="B54" s="59" t="s">
-        <v>863</v>
+        <v>902</v>
       </c>
       <c r="C54" s="59" t="s">
-        <v>743</v>
+        <v>782</v>
       </c>
       <c r="D54" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E54" s="59" t="s">
-        <v>780</v>
+        <v>819</v>
       </c>
       <c r="F54" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G54" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H54" s="59" t="s">
-        <v>784</v>
+        <v>823</v>
       </c>
       <c r="I54" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J54" s="59" t="s">
-        <v>864</v>
+        <v>903</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
-        <v>865</v>
+        <v>904</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>866</v>
+        <v>905</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="D55" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>867</v>
+        <v>906</v>
       </c>
       <c r="F55" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G55" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>808</v>
+        <v>847</v>
       </c>
       <c r="I55" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J55" s="27" t="s">
-        <v>868</v>
+        <v>907</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="59" t="s">
-        <v>869</v>
+        <v>908</v>
       </c>
       <c r="B56" s="59" t="s">
-        <v>870</v>
+        <v>909</v>
       </c>
       <c r="C56" s="59" t="s">
         <v>26</v>
@@ -15187,359 +15549,359 @@
         <v>102</v>
       </c>
       <c r="E56" s="59" t="s">
-        <v>867</v>
+        <v>906</v>
       </c>
       <c r="F56" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G56" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H56" s="59" t="s">
-        <v>630</v>
+        <v>669</v>
       </c>
       <c r="I56" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J56" s="59" t="s">
-        <v>871</v>
+        <v>910</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
-        <v>872</v>
+        <v>911</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>873</v>
+        <v>912</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>813</v>
+        <v>852</v>
       </c>
       <c r="D57" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G57" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H57" s="27" t="s">
-        <v>853</v>
+        <v>892</v>
       </c>
       <c r="I57" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J57" s="27" t="s">
-        <v>874</v>
+        <v>913</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="59" t="s">
-        <v>875</v>
+        <v>914</v>
       </c>
       <c r="B58" s="59" t="s">
-        <v>876</v>
+        <v>915</v>
       </c>
       <c r="C58" s="59" t="s">
-        <v>599</v>
+        <v>638</v>
       </c>
       <c r="D58" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E58" s="59" t="s">
-        <v>780</v>
+        <v>819</v>
       </c>
       <c r="F58" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G58" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H58" s="59" t="s">
-        <v>756</v>
+        <v>795</v>
       </c>
       <c r="I58" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J58" s="59" t="s">
-        <v>877</v>
+        <v>916</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="27" t="s">
-        <v>878</v>
+        <v>917</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>879</v>
+        <v>918</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>739</v>
+        <v>778</v>
       </c>
       <c r="D59" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E59" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G59" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H59" s="27" t="s">
-        <v>770</v>
+        <v>809</v>
       </c>
       <c r="I59" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J59" s="27" t="s">
-        <v>880</v>
+        <v>919</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="59" t="s">
-        <v>881</v>
+        <v>920</v>
       </c>
       <c r="B60" s="59" t="s">
-        <v>882</v>
+        <v>921</v>
       </c>
       <c r="C60" s="59" t="s">
-        <v>883</v>
+        <v>922</v>
       </c>
       <c r="D60" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E60" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F60" s="59" t="s">
-        <v>883</v>
+        <v>922</v>
       </c>
       <c r="G60" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H60" s="59" t="s">
-        <v>872</v>
+        <v>911</v>
       </c>
       <c r="I60" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J60" s="59" t="s">
-        <v>884</v>
+        <v>923</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="27" t="s">
-        <v>885</v>
+        <v>924</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>886</v>
+        <v>925</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>813</v>
+        <v>852</v>
       </c>
       <c r="D61" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G61" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H61" s="27" t="s">
-        <v>872</v>
+        <v>911</v>
       </c>
       <c r="I61" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J61" s="27" t="s">
-        <v>887</v>
+        <v>926</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="59" t="s">
-        <v>888</v>
+        <v>927</v>
       </c>
       <c r="B62" s="59" t="s">
-        <v>889</v>
+        <v>928</v>
       </c>
       <c r="C62" s="59" t="s">
-        <v>599</v>
+        <v>638</v>
       </c>
       <c r="D62" s="59" t="s">
         <v>104</v>
       </c>
       <c r="E62" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F62" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G62" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H62" s="59" t="s">
-        <v>756</v>
+        <v>795</v>
       </c>
       <c r="I62" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J62" s="59" t="s">
-        <v>890</v>
+        <v>929</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="27" t="s">
-        <v>891</v>
+        <v>930</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>892</v>
+        <v>931</v>
       </c>
       <c r="C63" s="27" t="s">
-        <v>893</v>
+        <v>932</v>
       </c>
       <c r="D63" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E63" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G63" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H63" s="27" t="s">
-        <v>872</v>
+        <v>911</v>
       </c>
       <c r="I63" s="70" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J63" s="27" t="s">
-        <v>894</v>
+        <v>933</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="59" t="s">
-        <v>895</v>
+        <v>934</v>
       </c>
       <c r="B64" s="59" t="s">
-        <v>896</v>
+        <v>935</v>
       </c>
       <c r="C64" s="59" t="s">
-        <v>847</v>
+        <v>886</v>
       </c>
       <c r="D64" s="59" t="s">
         <v>104</v>
       </c>
       <c r="E64" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F64" s="59" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="G64" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H64" s="59" t="s">
-        <v>885</v>
+        <v>924</v>
       </c>
       <c r="I64" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J64" s="59" t="s">
-        <v>897</v>
+        <v>936</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="27" t="s">
-        <v>898</v>
+        <v>937</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>899</v>
+        <v>938</v>
       </c>
       <c r="C65" s="27" t="s">
-        <v>727</v>
+        <v>766</v>
       </c>
       <c r="D65" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E65" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G65" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H65" s="27" t="s">
-        <v>872</v>
+        <v>911</v>
       </c>
       <c r="I65" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J65" s="27" t="s">
-        <v>900</v>
+        <v>939</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="59" t="s">
-        <v>901</v>
+        <v>940</v>
       </c>
       <c r="B66" s="59" t="s">
-        <v>902</v>
+        <v>941</v>
       </c>
       <c r="C66" s="59" t="s">
-        <v>779</v>
+        <v>818</v>
       </c>
       <c r="D66" s="59" t="s">
         <v>104</v>
       </c>
       <c r="E66" s="59" t="s">
-        <v>780</v>
+        <v>819</v>
       </c>
       <c r="F66" s="59" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G66" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H66" s="59" t="s">
-        <v>830</v>
+        <v>869</v>
       </c>
       <c r="I66" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J66" s="59" t="s">
-        <v>903</v>
+        <v>942</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="27" t="s">
-        <v>904</v>
+        <v>943</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>905</v>
+        <v>944</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>779</v>
+        <v>818</v>
       </c>
       <c r="D67" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F67" s="27" t="s">
         <v>100</v>
@@ -15548,30 +15910,30 @@
         <v>5</v>
       </c>
       <c r="H67" s="27" t="s">
-        <v>885</v>
+        <v>924</v>
       </c>
       <c r="I67" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J67" s="27" t="s">
-        <v>906</v>
+        <v>945</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="59" t="s">
-        <v>907</v>
+        <v>946</v>
       </c>
       <c r="B68" s="59" t="s">
-        <v>908</v>
+        <v>947</v>
       </c>
       <c r="C68" s="59" t="s">
-        <v>779</v>
+        <v>818</v>
       </c>
       <c r="D68" s="59" t="s">
         <v>106</v>
       </c>
       <c r="E68" s="59" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F68" s="59" t="s">
         <v>100</v>
@@ -15580,45 +15942,45 @@
         <v>1</v>
       </c>
       <c r="H68" s="59" t="s">
-        <v>904</v>
+        <v>943</v>
       </c>
       <c r="I68" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J68" s="59" t="s">
-        <v>909</v>
+        <v>948</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="27" t="s">
-        <v>910</v>
+        <v>949</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>911</v>
+        <v>950</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>779</v>
+        <v>818</v>
       </c>
       <c r="D69" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E69" s="27" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="F69" s="27" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="G69" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H69" s="27" t="s">
-        <v>898</v>
+        <v>937</v>
       </c>
       <c r="I69" s="70" t="s">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="J69" s="27" t="s">
-        <v>912</v>
+        <v>951</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15755,7 +16117,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D82" s="73" t="s">
-        <v>913</v>
+        <v>952</v>
       </c>
       <c r="E82" s="73"/>
       <c r="F82" s="73"/>
@@ -15766,7 +16128,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D83" s="74" t="s">
-        <v>914</v>
+        <v>953</v>
       </c>
       <c r="E83" s="74"/>
       <c r="F83" s="74"/>
@@ -15777,7 +16139,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D84" s="74" t="s">
-        <v>915</v>
+        <v>954</v>
       </c>
       <c r="E84" s="74"/>
       <c r="F84" s="74"/>
@@ -15788,18 +16150,18 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D85" s="74" t="s">
-        <v>916</v>
+        <v>955</v>
       </c>
       <c r="E85" s="74"/>
       <c r="F85" s="74"/>
       <c r="G85" s="32" t="n">
         <f aca="false">SUMIF(I$5:I$80,"Done",G$5:G$80)</f>
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D86" s="74" t="s">
-        <v>917</v>
+        <v>956</v>
       </c>
       <c r="E86" s="74"/>
       <c r="F86" s="74"/>
@@ -15810,7 +16172,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>918</v>
+        <v>957</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -15824,25 +16186,25 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>716</v>
+        <v>755</v>
       </c>
       <c r="B90" s="9"/>
       <c r="C90" s="9" t="s">
-        <v>919</v>
+        <v>958</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>920</v>
+        <v>959</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>921</v>
+        <v>960</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>922</v>
+        <v>961</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="76" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="B91" s="76"/>
       <c r="C91" s="32" t="n">
@@ -15864,7 +16226,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="76" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="B92" s="76"/>
       <c r="C92" s="32" t="n">
@@ -15886,7 +16248,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="76" t="s">
-        <v>735</v>
+        <v>774</v>
       </c>
       <c r="B93" s="76"/>
       <c r="C93" s="32" t="n">
@@ -15908,7 +16270,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="76" t="s">
-        <v>828</v>
+        <v>867</v>
       </c>
       <c r="B94" s="76"/>
       <c r="C94" s="32" t="n">
@@ -15930,7 +16292,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="76" t="s">
-        <v>883</v>
+        <v>922</v>
       </c>
       <c r="B95" s="76"/>
       <c r="C95" s="32" t="n">
@@ -15974,7 +16336,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="73" t="s">
-        <v>923</v>
+        <v>962</v>
       </c>
       <c r="B97" s="73"/>
       <c r="C97" s="21" t="n">
@@ -16000,16 +16362,16 @@
       </c>
       <c r="B99" s="29"/>
       <c r="C99" s="9" t="s">
-        <v>919</v>
+        <v>958</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>924</v>
+        <v>963</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>921</v>
+        <v>960</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>922</v>
+        <v>961</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16152,7 +16514,7 @@
     </row>
     <row r="107" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="54" t="s">
-        <v>925</v>
+        <v>964</v>
       </c>
       <c r="B107" s="54"/>
       <c r="C107" s="54"/>
@@ -16286,7 +16648,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>926</v>
+        <v>965</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -16304,22 +16666,22 @@
         <v>6</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>927</v>
+        <v>966</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>928</v>
+        <v>967</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>929</v>
+        <v>968</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>930</v>
+        <v>969</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>931</v>
+        <v>970</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>932</v>
+        <v>971</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16340,16 +16702,16 @@
         <v>46383</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>933</v>
+        <v>972</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>934</v>
+        <v>973</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>935</v>
+        <v>974</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>936</v>
+        <v>975</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16370,16 +16732,16 @@
         <v>46453</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>937</v>
+        <v>976</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>938</v>
+        <v>977</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>939</v>
+        <v>978</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>940</v>
+        <v>979</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16400,16 +16762,16 @@
         <v>46579</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>941</v>
+        <v>980</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>942</v>
+        <v>981</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>943</v>
+        <v>982</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>944</v>
+        <v>983</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16430,16 +16792,16 @@
         <v>46621</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>945</v>
+        <v>984</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>946</v>
+        <v>985</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>947</v>
+        <v>986</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>948</v>
+        <v>987</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16460,16 +16822,16 @@
         <v>46663</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>949</v>
+        <v>988</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>950</v>
+        <v>989</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>951</v>
+        <v>990</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>952</v>
+        <v>991</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16490,21 +16852,21 @@
         <v>46691</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>953</v>
+        <v>992</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>428</v>
+        <v>467</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>954</v>
+        <v>993</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>955</v>
+        <v>994</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>956</v>
+        <v>995</v>
       </c>
       <c r="B12" s="82" t="n">
         <f aca="false">D10</f>
@@ -16514,7 +16876,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>957</v>
+        <v>996</v>
       </c>
       <c r="B13" s="83" t="n">
         <f aca="false">B12-Assumptions!B7</f>
@@ -16524,7 +16886,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>958</v>
+        <v>997</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="24"/>
@@ -16536,7 +16898,7 @@
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
-        <v>959</v>
+        <v>998</v>
       </c>
       <c r="B15" s="54"/>
       <c r="C15" s="54"/>
@@ -16548,7 +16910,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="54" t="s">
-        <v>960</v>
+        <v>999</v>
       </c>
       <c r="B16" s="54"/>
       <c r="C16" s="54"/>
@@ -16628,7 +16990,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>961</v>
+        <v>1000</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -16662,13 +17024,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>962</v>
+        <v>1001</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>927</v>
+        <v>966</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>928</v>
+        <v>967</v>
       </c>
       <c r="D4" s="84" t="n">
         <v>1</v>
@@ -16853,7 +17215,7 @@
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>963</v>
+        <v>1002</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -17100,7 +17462,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>964</v>
+        <v>1003</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -18871,7 +19233,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>965</v>
+        <v>1004</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -19118,7 +19480,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>966</v>
+        <v>1005</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>

--- a/docs/Vinland_Game_Development_Plan.xlsx
+++ b/docs/Vinland_Game_Development_Plan.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="1311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="1360">
   <si>
     <t xml:space="preserve">VINLAND</t>
   </si>
@@ -1342,6 +1342,147 @@
     <t xml:space="preserve">Roles (F23): the return voyage (F24)</t>
   </si>
   <si>
+    <t xml:space="preserve">RETURN VOYAGE, APPRAISAL AND RECRUITMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work to raise the boat shed (builder-days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return gate (F24): the knarr is readied under a roof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return window opens (day of year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return gate (F24): 1 June of the second summer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last sensible day to sail home (day of year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return gate (F24): 2 September; later is a gamble with October</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hull levels mended a week ashore with a shipwright</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return gate (F24): a seaworthy hull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autumn bias: foul weather weight multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return voyage (F24): fog, cloud, gales and storms come more often</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autumn bias: chance a fair day turns foul after 1 September</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return voyage (F24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autumn bias: sickness multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return voyage (F24): cold, wet watches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timber jettison chance when the bail fails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return voyage (F24): lighten her or lose her</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver per timber unit, sound grade (marks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appraisal (F25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime timber price multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appraisal (F25): mostly winter-felled, or a shipwright's eye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rough timber price multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appraisal (F25): green summer-felled wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter-felled share for prime timber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter-felled share below which timber is rough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver per pelt (marks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appraisal (F25): ten pelts are a cargo unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting silver, high (marks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfit silver (F22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting silver, medium (marks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting silver, low (marks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Story: points per person alive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recruitment (F26): at the camp and home again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Story: points per building raised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recruitment (F26): booths, longhouse, byre, boat shed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Story: points lost per death</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recruitment (F26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Story: points per point of goodwill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recruitment (F26): peace with the people of the land</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volunteers per point of story</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recruitment (F26): a true story recruits better than silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver to hire a recruit (marks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second hull price (marks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recruitment (F26): a knarr of your own for the relief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most volunteers in a winter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most people a relief hull carries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recruitment (F26): room left for stores and stock in 24 units</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pillars, fantasy, clocks, and the win</t>
   </si>
   <si>
@@ -2773,7 +2914,7 @@
     <t xml:space="preserve">Route</t>
   </si>
   <si>
-    <t xml:space="preserve">Autumn bias: longer nights and worse weather on the way home.</t>
+    <t xml:space="preserve">Autumn bias: longer nights and worse weather on the way home.  [Built: the knarr row on the camp board shows the return gate (second summer from 1 June, boat shed, hull mended to strained or better, 4+ timber, a skipper or pilot and 10 crew). The planner loads who sails, timber, pelts, food and drink against 24 units; the skipper and a pilot sail, the healer and smith stay. The voyage home runs the legs in reverse with 1.6x foul weather, fair days turning foul after 1 September, more sickness, and timber jettisoned when a bail fails. Careful captains bring her home 40/40.]</t>
   </si>
   <si>
     <t xml:space="preserve">F25</t>
@@ -2782,13 +2923,13 @@
     <t xml:space="preserve">Timber appraisal and cargo sale</t>
   </si>
   <si>
-    <t xml:space="preserve">Timber grade and amount set what the cargo buys at home.</t>
+    <t xml:space="preserve">Timber grade and amount set what the cargo buys at home.  [Built: the appraisal at Eriksfjord grades timber rough / sound / prime by the share felled in winter (Shipwright's kin one grade up) and sells it with the pelts for marks of silver on top of the outfit's silver.]</t>
   </si>
   <si>
     <t xml:space="preserve">Recruitment and second hull</t>
   </si>
   <si>
-    <t xml:space="preserve">A living crew and a true story recruit better than silver.</t>
+    <t xml:space="preserve">A living crew and a true story recruit better than silver.  [Built: the story (people alive in both places, buildings, deaths, goodwill) brings volunteers; silver hires more and can buy a second hull (40 marks); each hull carries 30. The relief sails in F30.]</t>
   </si>
   <si>
     <t xml:space="preserve">F27</t>
@@ -4019,6 +4160,12 @@
   </si>
   <si>
     <t xml:space="preserve">Outfits now change the hold, the kit and how the verbs feel; roles make each death matter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F24 return voyage and F25 appraisal done, F26 recruitment in progress; RETURN VOYAGE, APPRAISAL AND RECRUITMENT knobs added. The camp no longer ends at the second spring: that is now the G1 milestone card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha begins: the timber goes home and buys the relief.</t>
   </si>
 </sst>
 </file>
@@ -5227,11 +5374,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="5451543"/>
-        <c:axId val="74781591"/>
+        <c:axId val="71538381"/>
+        <c:axId val="28951518"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5451543"/>
+        <c:axId val="71538381"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5263,7 +5410,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74781591"/>
+        <c:crossAx val="28951518"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5271,7 +5418,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="74781591"/>
+        <c:axId val="28951518"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5347,7 +5494,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5451543"/>
+        <c:crossAx val="71538381"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5386,9 +5533,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>739800</xdr:colOff>
+      <xdr:colOff>738720</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>56160</xdr:rowOff>
+      <xdr:rowOff>55080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5397,7 +5544,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="6562800"/>
-        <a:ext cx="5391720" cy="2151720"/>
+        <a:ext cx="5390640" cy="2150640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6312,7 +6459,7 @@
       </c>
       <c r="B55" s="5" t="str">
         <f aca="false">COUNTIF(Backlog!I5:I80,"Done")&amp;" of "&amp;COUNTA(Backlog!A5:A80)</f>
-        <v>13 of 65</v>
+        <v>15 of 65</v>
       </c>
       <c r="C55" s="31" t="s">
         <v>68</v>
@@ -6334,7 +6481,7 @@
       </c>
       <c r="B56" s="38" t="n">
         <f aca="false">Backlog!G86</f>
-        <v>0.23202614379085</v>
+        <v>0.274509803921569</v>
       </c>
       <c r="C56" s="34" t="s">
         <v>71</v>
@@ -6479,7 +6626,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1006</v>
+        <v>1053</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -6491,10 +6638,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>1007</v>
+        <v>1054</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1008</v>
+        <v>1055</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>96</v>
@@ -6515,7 +6662,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="58" t="s">
-        <v>1009</v>
+        <v>1056</v>
       </c>
       <c r="J4" s="58" t="s">
         <v>7</v>
@@ -6523,7 +6670,7 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="B5" s="90" t="n">
         <f aca="false">Assumptions!B26</f>
@@ -6558,7 +6705,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="B6" s="90" t="n">
         <f aca="false">Assumptions!B27</f>
@@ -6593,7 +6740,7 @@
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="B7" s="90" t="n">
         <f aca="false">Assumptions!B28</f>
@@ -6628,7 +6775,7 @@
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>867</v>
+        <v>914</v>
       </c>
       <c r="B8" s="90" t="n">
         <f aca="false">Assumptions!B29</f>
@@ -6663,7 +6810,7 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>922</v>
+        <v>969</v>
       </c>
       <c r="B9" s="90" t="n">
         <f aca="false">Assumptions!B30</f>
@@ -6733,10 +6880,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="72" t="s">
-        <v>1010</v>
+        <v>1057</v>
       </c>
       <c r="B11" s="72" t="s">
-        <v>1011</v>
+        <v>1058</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -6773,10 +6920,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="72" t="s">
-        <v>1012</v>
+        <v>1059</v>
       </c>
       <c r="B12" s="72" t="s">
-        <v>1013</v>
+        <v>1060</v>
       </c>
       <c r="C12" s="63" t="n">
         <f aca="false">IF(Assumptions!B16=0,0,C11/Assumptions!B16)</f>
@@ -6809,7 +6956,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1014</v>
+        <v>1061</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -6824,28 +6971,28 @@
         <v>5</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1015</v>
+        <v>1062</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>867</v>
+        <v>914</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>922</v>
+        <v>969</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>100</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>1009</v>
+        <v>1056</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>7</v>
@@ -7105,7 +7252,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>1016</v>
+        <v>1063</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -7122,7 +7269,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="50" t="s">
-        <v>1017</v>
+        <v>1064</v>
       </c>
       <c r="B22" s="50"/>
       <c r="C22" s="50"/>
@@ -7142,7 +7289,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="50" t="s">
-        <v>1018</v>
+        <v>1065</v>
       </c>
       <c r="B23" s="50"/>
       <c r="C23" s="50"/>
@@ -7159,7 +7306,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="50" t="s">
-        <v>1019</v>
+        <v>1066</v>
       </c>
       <c r="B24" s="50"/>
       <c r="C24" s="50"/>
@@ -7227,7 +7374,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="50" t="s">
-        <v>1020</v>
+        <v>1067</v>
       </c>
       <c r="B28" s="50"/>
       <c r="C28" s="50"/>
@@ -7244,7 +7391,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>1021</v>
+        <v>1068</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
@@ -7281,7 +7428,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="67" t="s">
-        <v>1022</v>
+        <v>1069</v>
       </c>
       <c r="B31" s="67"/>
       <c r="C31" s="67"/>
@@ -7299,12 +7446,12 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="72" t="s">
-        <v>1023</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="96" t="s">
-        <v>1024</v>
+        <v>1071</v>
       </c>
       <c r="B34" s="96"/>
       <c r="C34" s="96"/>
@@ -7318,7 +7465,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>1016</v>
+        <v>1063</v>
       </c>
       <c r="B35" s="91" t="n">
         <f aca="false">J21</f>
@@ -7327,7 +7474,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>1025</v>
+        <v>1072</v>
       </c>
       <c r="B36" s="91" t="n">
         <f aca="false">J31</f>
@@ -7336,7 +7483,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>1026</v>
+        <v>1073</v>
       </c>
       <c r="B37" s="91" t="n">
         <f aca="false">SUM(J22:J28)*(1+I30)</f>
@@ -7388,7 +7535,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1027</v>
+        <v>1074</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7397,7 +7544,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1028</v>
+        <v>1075</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -7412,7 +7559,7 @@
         <v>42</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>599</v>
+        <v>646</v>
       </c>
       <c r="D5" s="29"/>
       <c r="E5" s="29"/>
@@ -7426,28 +7573,28 @@
         <v>19.99</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>1029</v>
+        <v>1076</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1030</v>
+        <v>1077</v>
       </c>
       <c r="B7" s="98" t="n">
         <f aca="false">B6*Assumptions!B70</f>
         <v>15.992</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>1031</v>
+        <v>1078</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>1032</v>
+        <v>1079</v>
       </c>
       <c r="B8" s="98" t="n">
         <f aca="false">B7*(1-Assumptions!B71)</f>
@@ -7459,35 +7606,35 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>1033</v>
+        <v>1080</v>
       </c>
       <c r="B9" s="75" t="n">
         <f aca="false">Assumptions!B72*(1-Assumptions!B74)+Assumptions!B73*Assumptions!B74</f>
         <v>0.29</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>1034</v>
+        <v>1081</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>1035</v>
+        <v>1082</v>
       </c>
       <c r="B10" s="99" t="n">
         <f aca="false">B8*(1-B9)</f>
         <v>10.4459744</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>1036</v>
+        <v>1083</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1037</v>
+        <v>1084</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -7502,7 +7649,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>599</v>
+        <v>646</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="29"/>
@@ -7516,70 +7663,70 @@
         <v>460504.8</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>1038</v>
+        <v>1085</v>
       </c>
       <c r="D14" s="33"/>
       <c r="E14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>1039</v>
+        <v>1086</v>
       </c>
       <c r="B15" s="100" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B14/B10,0))</f>
         <v>44085</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>1040</v>
+        <v>1087</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>1041</v>
+        <v>1088</v>
       </c>
       <c r="B16" s="90" t="n">
         <f aca="false">TeamBudget!B37</f>
         <v>98632.8</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>1042</v>
+        <v>1089</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="67" t="s">
-        <v>1043</v>
+        <v>1090</v>
       </c>
       <c r="B17" s="100" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B16/B10,0))</f>
         <v>9443</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>1044</v>
+        <v>1091</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>1045</v>
+        <v>1092</v>
       </c>
       <c r="B18" s="91" t="n">
         <f aca="false">B15*B6</f>
         <v>881259.15</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>1046</v>
+        <v>1093</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>1047</v>
+        <v>1094</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -7588,19 +7735,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>1048</v>
+        <v>1095</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1049</v>
+        <v>1096</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1050</v>
+        <v>1097</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1051</v>
+        <v>1098</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>961</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7715,7 +7862,7 @@
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="54" t="s">
-        <v>1052</v>
+        <v>1099</v>
       </c>
       <c r="B28" s="54"/>
       <c r="C28" s="54"/>
@@ -7797,7 +7944,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1053</v>
+        <v>1100</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7809,195 +7956,195 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>971</v>
+        <v>1018</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1054</v>
+        <v>1101</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1055</v>
+        <v>1102</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1056</v>
+        <v>1103</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>755</v>
+        <v>802</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1057</v>
+        <v>1104</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>1058</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>975</v>
+        <v>1022</v>
       </c>
       <c r="B5" s="87" t="n">
         <f aca="false">Schedule!D5</f>
         <v>46383</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1059</v>
+        <v>1106</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1060</v>
+        <v>1107</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="F5" s="70" t="s">
-        <v>1061</v>
+        <v>1108</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1062</v>
+        <v>1109</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>1063</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>979</v>
+        <v>1026</v>
       </c>
       <c r="B6" s="87" t="n">
         <f aca="false">Schedule!D6</f>
         <v>46453</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1064</v>
+        <v>1111</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1065</v>
+        <v>1112</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="F6" s="70" t="s">
-        <v>1061</v>
+        <v>1108</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>1066</v>
+        <v>1113</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>1067</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>983</v>
+        <v>1030</v>
       </c>
       <c r="B7" s="87" t="n">
         <f aca="false">Schedule!D7</f>
         <v>46579</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1068</v>
+        <v>1115</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1069</v>
+        <v>1116</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="F7" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1070</v>
+        <v>1117</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>1071</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>987</v>
+        <v>1034</v>
       </c>
       <c r="B8" s="87" t="n">
         <f aca="false">Schedule!D8</f>
         <v>46621</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1072</v>
+        <v>1119</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1073</v>
+        <v>1120</v>
       </c>
       <c r="E8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="F8" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>1074</v>
+        <v>1121</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>1075</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>991</v>
+        <v>1038</v>
       </c>
       <c r="B9" s="87" t="n">
         <f aca="false">Schedule!D9</f>
         <v>46663</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1076</v>
+        <v>1123</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1077</v>
+        <v>1124</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>922</v>
+        <v>969</v>
       </c>
       <c r="F9" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1078</v>
+        <v>1125</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>1079</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>994</v>
+        <v>1041</v>
       </c>
       <c r="B10" s="87" t="n">
         <f aca="false">Schedule!D10</f>
         <v>46691</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1080</v>
+        <v>1127</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>1081</v>
+        <v>1128</v>
       </c>
       <c r="E10" s="59" t="s">
         <v>100</v>
       </c>
       <c r="F10" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>1082</v>
+        <v>1129</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>1083</v>
+        <v>1130</v>
       </c>
       <c r="B12" s="54"/>
       <c r="C12" s="54"/>
@@ -8077,7 +8224,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1084</v>
+        <v>1131</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8091,31 +8238,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>419</v>
+        <v>466</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1085</v>
+        <v>1132</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1086</v>
+        <v>1133</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1087</v>
+        <v>1134</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>569</v>
+        <v>616</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>1088</v>
+        <v>1135</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>755</v>
+        <v>802</v>
       </c>
       <c r="H4" s="58" t="s">
-        <v>1089</v>
+        <v>1136</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>1090</v>
+        <v>1137</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>44</v>
@@ -8123,10 +8270,10 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="59" t="s">
-        <v>1091</v>
+        <v>1138</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>1092</v>
+        <v>1139</v>
       </c>
       <c r="C5" s="43" t="n">
         <v>3</v>
@@ -8139,27 +8286,27 @@
         <v>15</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>1093</v>
+        <v>1140</v>
       </c>
       <c r="G5" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="H5" s="59" t="s">
-        <v>979</v>
+        <v>1026</v>
       </c>
       <c r="I5" s="59" t="s">
-        <v>1094</v>
+        <v>1141</v>
       </c>
       <c r="J5" s="70" t="s">
-        <v>1095</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>1096</v>
+        <v>1143</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1097</v>
+        <v>1144</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>3</v>
@@ -8172,27 +8319,27 @@
         <v>12</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>1098</v>
+        <v>1145</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>979</v>
+        <v>1026</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>1099</v>
+        <v>1146</v>
       </c>
       <c r="J6" s="70" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="59" t="s">
-        <v>1101</v>
+        <v>1148</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>1102</v>
+        <v>1149</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>2</v>
@@ -8205,27 +8352,27 @@
         <v>8</v>
       </c>
       <c r="F7" s="59" t="s">
-        <v>1103</v>
+        <v>1150</v>
       </c>
       <c r="G7" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="H7" s="59" t="s">
-        <v>991</v>
+        <v>1038</v>
       </c>
       <c r="I7" s="59" t="s">
-        <v>1104</v>
+        <v>1151</v>
       </c>
       <c r="J7" s="70" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1105</v>
+        <v>1152</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1106</v>
+        <v>1153</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>4</v>
@@ -8238,27 +8385,27 @@
         <v>12</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>1107</v>
+        <v>1154</v>
       </c>
       <c r="G8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>983</v>
+        <v>1030</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>1108</v>
+        <v>1155</v>
       </c>
       <c r="J8" s="70" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="59" t="s">
-        <v>1109</v>
+        <v>1156</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1110</v>
+        <v>1157</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>2</v>
@@ -8271,27 +8418,27 @@
         <v>6</v>
       </c>
       <c r="F9" s="59" t="s">
-        <v>1111</v>
+        <v>1158</v>
       </c>
       <c r="G9" s="59" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="H9" s="59" t="s">
-        <v>983</v>
+        <v>1030</v>
       </c>
       <c r="I9" s="59" t="s">
-        <v>1112</v>
+        <v>1159</v>
       </c>
       <c r="J9" s="70" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1113</v>
+        <v>1160</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1114</v>
+        <v>1161</v>
       </c>
       <c r="C10" s="43" t="n">
         <v>2</v>
@@ -8304,27 +8451,27 @@
         <v>10</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>1115</v>
+        <v>1162</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>983</v>
+        <v>1030</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>1116</v>
+        <v>1163</v>
       </c>
       <c r="J10" s="70" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="59" t="s">
-        <v>1117</v>
+        <v>1164</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>1118</v>
+        <v>1165</v>
       </c>
       <c r="C11" s="43" t="n">
         <v>3</v>
@@ -8337,27 +8484,27 @@
         <v>12</v>
       </c>
       <c r="F11" s="59" t="s">
-        <v>1119</v>
+        <v>1166</v>
       </c>
       <c r="G11" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H11" s="59" t="s">
-        <v>987</v>
+        <v>1034</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>1120</v>
+        <v>1167</v>
       </c>
       <c r="J11" s="70" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1121</v>
+        <v>1168</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1122</v>
+        <v>1169</v>
       </c>
       <c r="C12" s="43" t="n">
         <v>2</v>
@@ -8370,27 +8517,27 @@
         <v>8</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>1123</v>
+        <v>1170</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>975</v>
+        <v>1022</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>1124</v>
+        <v>1171</v>
       </c>
       <c r="J12" s="70" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="59" t="s">
-        <v>1125</v>
+        <v>1172</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>1126</v>
+        <v>1173</v>
       </c>
       <c r="C13" s="43" t="n">
         <v>2</v>
@@ -8403,27 +8550,27 @@
         <v>4</v>
       </c>
       <c r="F13" s="59" t="s">
-        <v>1127</v>
+        <v>1174</v>
       </c>
       <c r="G13" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="H13" s="59" t="s">
-        <v>975</v>
+        <v>1022</v>
       </c>
       <c r="I13" s="59" t="s">
-        <v>1128</v>
+        <v>1175</v>
       </c>
       <c r="J13" s="70" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1129</v>
+        <v>1176</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1130</v>
+        <v>1177</v>
       </c>
       <c r="C14" s="43" t="n">
         <v>3</v>
@@ -8436,27 +8583,27 @@
         <v>12</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>1131</v>
+        <v>1178</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="H14" s="59" t="s">
-        <v>987</v>
+        <v>1034</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>1132</v>
+        <v>1179</v>
       </c>
       <c r="J14" s="70" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="59" t="s">
-        <v>1133</v>
+        <v>1180</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>1134</v>
+        <v>1181</v>
       </c>
       <c r="C15" s="43" t="n">
         <v>3</v>
@@ -8469,27 +8616,27 @@
         <v>15</v>
       </c>
       <c r="F15" s="59" t="s">
-        <v>1135</v>
+        <v>1182</v>
       </c>
       <c r="G15" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="H15" s="59" t="s">
-        <v>983</v>
+        <v>1030</v>
       </c>
       <c r="I15" s="59" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
       <c r="J15" s="70" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>1137</v>
+        <v>1184</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>1138</v>
+        <v>1185</v>
       </c>
       <c r="C16" s="43" t="n">
         <v>4</v>
@@ -8502,27 +8649,27 @@
         <v>16</v>
       </c>
       <c r="F16" s="59" t="s">
-        <v>1139</v>
+        <v>1186</v>
       </c>
       <c r="G16" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H16" s="59" t="s">
-        <v>979</v>
+        <v>1026</v>
       </c>
       <c r="I16" s="59" t="s">
-        <v>1140</v>
+        <v>1187</v>
       </c>
       <c r="J16" s="70" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="59" t="s">
-        <v>1141</v>
+        <v>1188</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>1142</v>
+        <v>1189</v>
       </c>
       <c r="C17" s="43" t="n">
         <v>3</v>
@@ -8535,27 +8682,27 @@
         <v>12</v>
       </c>
       <c r="F17" s="59" t="s">
-        <v>1143</v>
+        <v>1190</v>
       </c>
       <c r="G17" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="59" t="s">
-        <v>983</v>
+        <v>1030</v>
       </c>
       <c r="I17" s="59" t="s">
-        <v>1144</v>
+        <v>1191</v>
       </c>
       <c r="J17" s="70" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>1145</v>
+        <v>1192</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1146</v>
+        <v>1193</v>
       </c>
       <c r="C18" s="43" t="n">
         <v>2</v>
@@ -8568,27 +8715,27 @@
         <v>6</v>
       </c>
       <c r="F18" s="59" t="s">
+        <v>1194</v>
+      </c>
+      <c r="G18" s="59" t="s">
+        <v>475</v>
+      </c>
+      <c r="H18" s="59" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I18" s="59" t="s">
+        <v>1195</v>
+      </c>
+      <c r="J18" s="70" t="s">
         <v>1147</v>
-      </c>
-      <c r="G18" s="59" t="s">
-        <v>428</v>
-      </c>
-      <c r="H18" s="59" t="s">
-        <v>991</v>
-      </c>
-      <c r="I18" s="59" t="s">
-        <v>1148</v>
-      </c>
-      <c r="J18" s="70" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="59" t="s">
-        <v>1149</v>
+        <v>1196</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>1150</v>
+        <v>1197</v>
       </c>
       <c r="C19" s="43" t="n">
         <v>2</v>
@@ -8601,27 +8748,27 @@
         <v>8</v>
       </c>
       <c r="F19" s="59" t="s">
-        <v>1151</v>
+        <v>1198</v>
       </c>
       <c r="G19" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="H19" s="59" t="s">
-        <v>983</v>
+        <v>1030</v>
       </c>
       <c r="I19" s="59" t="s">
-        <v>1152</v>
+        <v>1199</v>
       </c>
       <c r="J19" s="70" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>1153</v>
+        <v>1200</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1154</v>
+        <v>1201</v>
       </c>
       <c r="C20" s="43" t="n">
         <v>3</v>
@@ -8634,19 +8781,19 @@
         <v>15</v>
       </c>
       <c r="F20" s="59" t="s">
-        <v>1155</v>
+        <v>1202</v>
       </c>
       <c r="G20" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>979</v>
+        <v>1026</v>
       </c>
       <c r="I20" s="59" t="s">
-        <v>1156</v>
+        <v>1203</v>
       </c>
       <c r="J20" s="70" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
   </sheetData>
@@ -8724,7 +8871,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1157</v>
+        <v>1204</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8735,278 +8882,278 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>1158</v>
+        <v>1205</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1159</v>
+        <v>1206</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1160</v>
+        <v>1207</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1161</v>
+        <v>1208</v>
       </c>
       <c r="E4" s="58" t="s">
         <v>95</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>755</v>
+        <v>802</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1162</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1163</v>
+        <v>1210</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1164</v>
+        <v>1211</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1165</v>
+        <v>1212</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1166</v>
+        <v>1213</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>1167</v>
+        <v>1214</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1168</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>727</v>
+        <v>774</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1169</v>
+        <v>1216</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1170</v>
+        <v>1217</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1171</v>
+        <v>1218</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>1172</v>
+        <v>1219</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>1173</v>
+        <v>1220</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>1174</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1175</v>
+        <v>1222</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1176</v>
+        <v>1223</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1177</v>
+        <v>1224</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1178</v>
+        <v>1225</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>1179</v>
+        <v>1226</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1174</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1180</v>
+        <v>1227</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1181</v>
+        <v>1228</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1182</v>
+        <v>1229</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1183</v>
+        <v>1230</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>1184</v>
+        <v>1231</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>1185</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>612</v>
+        <v>659</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1186</v>
+        <v>1233</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1187</v>
+        <v>1234</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1188</v>
+        <v>1235</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1189</v>
+        <v>1236</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1190</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>803</v>
+        <v>850</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1191</v>
+        <v>1238</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1192</v>
+        <v>1239</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>925</v>
+        <v>972</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>1193</v>
+        <v>1240</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>1194</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>867</v>
+        <v>914</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1195</v>
+        <v>1242</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1196</v>
+        <v>1243</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1197</v>
+        <v>1244</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>1198</v>
+        <v>1245</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>867</v>
+        <v>914</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>1199</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>886</v>
+        <v>933</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1200</v>
+        <v>1247</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1201</v>
+        <v>1248</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>1203</v>
+        <v>1250</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>1174</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1204</v>
+        <v>1251</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1205</v>
+        <v>1252</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1206</v>
+        <v>1253</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1207</v>
+        <v>1254</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>1208</v>
+        <v>1255</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>1174</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1209</v>
+        <v>1256</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1210</v>
+        <v>1257</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1211</v>
+        <v>1258</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>1212</v>
+        <v>1259</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>1213</v>
+        <v>1260</v>
       </c>
       <c r="F14" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>1214</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1215</v>
+        <v>1262</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1216</v>
+        <v>1263</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1217</v>
+        <v>1264</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1218</v>
+        <v>1265</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>1219</v>
+        <v>1266</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>1220</v>
+        <v>1267</v>
       </c>
     </row>
   </sheetData>
@@ -9048,7 +9195,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1221</v>
+        <v>1268</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9059,24 +9206,24 @@
         <v>110</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1222</v>
+        <v>1269</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1223</v>
+        <v>1270</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>755</v>
+        <v>802</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1224</v>
+        <v>1271</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1225</v>
+        <v>1272</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>975</v>
+        <v>1022</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>100</v>
@@ -9084,55 +9231,55 @@
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>1226</v>
+        <v>1273</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1227</v>
+        <v>1274</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1228</v>
+        <v>1275</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1229</v>
+        <v>1276</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1230</v>
+        <v>1277</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>983</v>
+        <v>1030</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1231</v>
+        <v>1278</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1232</v>
+        <v>1279</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>979</v>
+        <v>1026</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1233</v>
+        <v>1280</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1234</v>
+        <v>1281</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>975</v>
+        <v>1022</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>100</v>
@@ -9140,27 +9287,27 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1235</v>
+        <v>1282</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1236</v>
+        <v>1283</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>983</v>
+        <v>1030</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>1237</v>
+        <v>1284</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1238</v>
+        <v>1285</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>991</v>
+        <v>1038</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>100</v>
@@ -9168,13 +9315,13 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1239</v>
+        <v>1286</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1240</v>
+        <v>1287</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>994</v>
+        <v>1041</v>
       </c>
       <c r="D12" s="59" t="s">
         <v>100</v>
@@ -9182,41 +9329,41 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1241</v>
+        <v>1288</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1242</v>
+        <v>1289</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>994</v>
+        <v>1041</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>922</v>
+        <v>969</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1243</v>
+        <v>1290</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1244</v>
+        <v>1291</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1245</v>
+        <v>1292</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1246</v>
+        <v>1293</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1247</v>
+        <v>1294</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>979</v>
+        <v>1026</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>100</v>
@@ -9224,14 +9371,14 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>1248</v>
+        <v>1295</v>
       </c>
       <c r="B16" s="59" t="str">
         <f aca="false">"Premium at $"&amp;TEXT(Assumptions!B69,"0.00")&amp;". Launch discount no deeper than the realized-price factor on Assumptions."</f>
         <v>Premium at $19.99. Launch discount no deeper than the realized-price factor on Assumptions.</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>987</v>
+        <v>1034</v>
       </c>
       <c r="D16" s="59" t="s">
         <v>100</v>
@@ -9239,13 +9386,13 @@
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>1249</v>
+        <v>1296</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1250</v>
+        <v>1297</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>979</v>
+        <v>1026</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>100</v>
@@ -9253,13 +9400,13 @@
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>969</v>
+        <v>1016</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1251</v>
+        <v>1298</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>987</v>
+        <v>1034</v>
       </c>
       <c r="D18" s="59" t="s">
         <v>100</v>
@@ -9267,27 +9414,27 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1252</v>
+        <v>1299</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1253</v>
+        <v>1300</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>991</v>
+        <v>1038</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>1254</v>
+        <v>1301</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1255</v>
+        <v>1302</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>991</v>
+        <v>1038</v>
       </c>
       <c r="D20" s="59" t="s">
         <v>100</v>
@@ -9295,27 +9442,27 @@
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>1256</v>
+        <v>1303</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1257</v>
+        <v>1304</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>991</v>
+        <v>1038</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="59" t="s">
-        <v>1258</v>
+        <v>1305</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1259</v>
+        <v>1306</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>994</v>
+        <v>1041</v>
       </c>
       <c r="D22" s="59" t="s">
         <v>100</v>
@@ -9342,7 +9489,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -9361,7 +9508,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1260</v>
+        <v>1307</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9369,16 +9516,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1261</v>
+        <v>1308</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1262</v>
+        <v>1309</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1263</v>
+        <v>1310</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1264</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9386,13 +9533,13 @@
         <v>46311</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1265</v>
+        <v>1312</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1266</v>
+        <v>1313</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1267</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9400,13 +9547,13 @@
         <v>46311</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1265</v>
+        <v>1312</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1268</v>
+        <v>1315</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1269</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9414,13 +9561,13 @@
         <v>46311</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1265</v>
+        <v>1312</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1270</v>
+        <v>1317</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1271</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9428,13 +9575,13 @@
         <v>46311</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1029</v>
+        <v>1076</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1272</v>
+        <v>1319</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1273</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9442,13 +9589,13 @@
         <v>46311</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1274</v>
+        <v>1321</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1275</v>
+        <v>1322</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1276</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9459,10 +9606,10 @@
         <v>53</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1277</v>
+        <v>1324</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>1278</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9470,13 +9617,13 @@
         <v>46311</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1279</v>
+        <v>1326</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1280</v>
+        <v>1327</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1281</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9484,13 +9631,13 @@
         <v>46311</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1282</v>
+        <v>1329</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>1283</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9498,13 +9645,13 @@
         <v>46311</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1284</v>
+        <v>1331</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1285</v>
+        <v>1332</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1286</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9512,13 +9659,13 @@
         <v>46311</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1287</v>
+        <v>1334</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1288</v>
+        <v>1335</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>1289</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9529,10 +9676,10 @@
         <v>58</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1290</v>
+        <v>1337</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1291</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9540,13 +9687,13 @@
         <v>46311</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>1292</v>
+        <v>1339</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>1293</v>
+        <v>1340</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>1294</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9557,10 +9704,10 @@
         <v>62</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1295</v>
+        <v>1342</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1296</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9568,13 +9715,13 @@
         <v>46311</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>542</v>
+        <v>589</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>1297</v>
+        <v>1344</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>1298</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9582,13 +9729,13 @@
         <v>46311</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>818</v>
+        <v>865</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1299</v>
+        <v>1346</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>1300</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9596,13 +9743,13 @@
         <v>46311</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1301</v>
+        <v>1348</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>1302</v>
+        <v>1349</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>1303</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9610,13 +9757,13 @@
         <v>46313</v>
       </c>
       <c r="B21" s="59" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="C21" s="59" t="s">
-        <v>1304</v>
+        <v>1351</v>
       </c>
       <c r="D21" s="59" t="s">
-        <v>1305</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9624,27 +9771,41 @@
         <v>46313</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1306</v>
+        <v>1353</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>1307</v>
+        <v>1354</v>
       </c>
       <c r="D22" s="59" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="103" t="n">
         <v>46313</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>1306</v>
+        <v>1353</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>1309</v>
+        <v>1356</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>1310</v>
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="103" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B24" s="59" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C24" s="59" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D24" s="59" t="s">
+        <v>1359</v>
       </c>
     </row>
   </sheetData>
@@ -9668,7 +9829,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F212"/>
+  <dimension ref="A1:F241"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
@@ -11777,6 +11938,308 @@
       </c>
       <c r="C212" s="41" t="s">
         <v>417</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A214" s="57" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A215" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C215" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A216" s="42" t="s">
+        <v>419</v>
+      </c>
+      <c r="B216" s="43" t="n">
+        <v>80</v>
+      </c>
+      <c r="C216" s="41" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A217" s="42" t="s">
+        <v>421</v>
+      </c>
+      <c r="B217" s="43" t="n">
+        <v>152</v>
+      </c>
+      <c r="C217" s="41" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A218" s="42" t="s">
+        <v>423</v>
+      </c>
+      <c r="B218" s="43" t="n">
+        <v>245</v>
+      </c>
+      <c r="C218" s="41" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A219" s="42" t="s">
+        <v>425</v>
+      </c>
+      <c r="B219" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C219" s="41" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A220" s="42" t="s">
+        <v>427</v>
+      </c>
+      <c r="B220" s="43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C220" s="41" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A221" s="42" t="s">
+        <v>429</v>
+      </c>
+      <c r="B221" s="43" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C221" s="41" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A222" s="42" t="s">
+        <v>431</v>
+      </c>
+      <c r="B222" s="43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C222" s="41" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A223" s="42" t="s">
+        <v>433</v>
+      </c>
+      <c r="B223" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C223" s="41" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A224" s="42" t="s">
+        <v>435</v>
+      </c>
+      <c r="B224" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C224" s="41" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A225" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="B225" s="43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C225" s="41" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A226" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="B226" s="43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C226" s="41" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A227" s="42" t="s">
+        <v>441</v>
+      </c>
+      <c r="B227" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C227" s="41" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A228" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="B228" s="43" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C228" s="41" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A229" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="B229" s="43" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C229" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A230" s="42" t="s">
+        <v>445</v>
+      </c>
+      <c r="B230" s="43" t="n">
+        <v>12</v>
+      </c>
+      <c r="C230" s="41" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A231" s="42" t="s">
+        <v>447</v>
+      </c>
+      <c r="B231" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C231" s="41" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A232" s="42" t="s">
+        <v>448</v>
+      </c>
+      <c r="B232" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C232" s="41" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A233" s="42" t="s">
+        <v>449</v>
+      </c>
+      <c r="B233" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C233" s="41" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A234" s="42" t="s">
+        <v>451</v>
+      </c>
+      <c r="B234" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C234" s="41" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A235" s="42" t="s">
+        <v>453</v>
+      </c>
+      <c r="B235" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C235" s="41" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A236" s="42" t="s">
+        <v>455</v>
+      </c>
+      <c r="B236" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C236" s="41" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A237" s="42" t="s">
+        <v>457</v>
+      </c>
+      <c r="B237" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C237" s="41" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A238" s="42" t="s">
+        <v>459</v>
+      </c>
+      <c r="B238" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C238" s="41" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A239" s="42" t="s">
+        <v>460</v>
+      </c>
+      <c r="B239" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="C239" s="41" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A240" s="42" t="s">
+        <v>462</v>
+      </c>
+      <c r="B240" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="C240" s="41" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A241" s="42" t="s">
+        <v>463</v>
+      </c>
+      <c r="B241" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="C241" s="41" t="s">
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -11843,7 +12306,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>418</v>
+        <v>465</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11852,160 +12315,160 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>419</v>
+        <v>466</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>420</v>
+        <v>467</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>421</v>
+        <v>468</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>422</v>
+        <v>469</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>423</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>424</v>
+        <v>471</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>425</v>
+        <v>472</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>426</v>
+        <v>473</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>427</v>
+        <v>474</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>429</v>
+        <v>476</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>430</v>
+        <v>477</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>431</v>
+        <v>478</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>432</v>
+        <v>479</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>433</v>
+        <v>480</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>434</v>
+        <v>481</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>435</v>
+        <v>482</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>436</v>
+        <v>483</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>437</v>
+        <v>484</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>438</v>
+        <v>485</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>439</v>
+        <v>486</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>440</v>
+        <v>487</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>441</v>
+        <v>488</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>442</v>
+        <v>489</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>443</v>
+        <v>490</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>444</v>
+        <v>491</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>445</v>
+        <v>492</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>446</v>
+        <v>493</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>447</v>
+        <v>494</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>448</v>
+        <v>495</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>449</v>
+        <v>496</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>450</v>
+        <v>497</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>451</v>
+        <v>498</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>452</v>
+        <v>499</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>453</v>
+        <v>500</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>454</v>
+        <v>501</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>455</v>
+        <v>502</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>456</v>
+        <v>503</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>457</v>
+        <v>504</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -12014,16 +12477,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>458</v>
+        <v>505</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>459</v>
+        <v>506</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>460</v>
+        <v>507</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>461</v>
+        <v>508</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>95</v>
@@ -12031,58 +12494,58 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="60" t="s">
-        <v>462</v>
+        <v>509</v>
       </c>
       <c r="B16" s="60" t="s">
-        <v>463</v>
+        <v>510</v>
       </c>
       <c r="C16" s="60" t="s">
-        <v>464</v>
+        <v>511</v>
       </c>
       <c r="D16" s="60" t="s">
-        <v>465</v>
+        <v>512</v>
       </c>
       <c r="E16" s="60" t="s">
-        <v>466</v>
+        <v>513</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="59" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>468</v>
+        <v>515</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>469</v>
+        <v>516</v>
       </c>
       <c r="D17" s="59" t="s">
-        <v>470</v>
+        <v>517</v>
       </c>
       <c r="E17" s="59" t="s">
-        <v>471</v>
+        <v>518</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="60" t="s">
-        <v>472</v>
+        <v>519</v>
       </c>
       <c r="B18" s="60" t="s">
-        <v>473</v>
+        <v>520</v>
       </c>
       <c r="C18" s="60" t="s">
-        <v>474</v>
+        <v>521</v>
       </c>
       <c r="D18" s="60" t="s">
-        <v>475</v>
+        <v>522</v>
       </c>
       <c r="E18" s="60" t="s">
-        <v>476</v>
+        <v>523</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>477</v>
+        <v>524</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="24"/>
@@ -12091,87 +12554,87 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>478</v>
+        <v>525</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>479</v>
+        <v>526</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>480</v>
+        <v>527</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>481</v>
+        <v>528</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>482</v>
+        <v>529</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>483</v>
+        <v>530</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>484</v>
+        <v>531</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>485</v>
+        <v>532</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>486</v>
+        <v>533</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>487</v>
+        <v>534</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="59" t="s">
-        <v>488</v>
+        <v>535</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>489</v>
+        <v>536</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>490</v>
+        <v>537</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>491</v>
+        <v>538</v>
       </c>
       <c r="E23" s="59" t="s">
-        <v>492</v>
+        <v>539</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>493</v>
+        <v>540</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>494</v>
+        <v>541</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>495</v>
+        <v>542</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>496</v>
+        <v>543</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>497</v>
+        <v>544</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="59" t="s">
-        <v>498</v>
+        <v>545</v>
       </c>
       <c r="B25" s="59" t="s">
-        <v>494</v>
+        <v>541</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>499</v>
+        <v>546</v>
       </c>
       <c r="D25" s="59" t="s">
-        <v>500</v>
+        <v>547</v>
       </c>
       <c r="E25" s="59" t="s">
-        <v>501</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -12224,7 +12687,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>502</v>
+        <v>549</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12235,33 +12698,33 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>503</v>
+        <v>550</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>504</v>
+        <v>551</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>505</v>
+        <v>552</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>506</v>
+        <v>553</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>507</v>
+        <v>554</v>
       </c>
       <c r="F4" s="58" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>509</v>
+        <v>556</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>510</v>
+        <v>557</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>134</v>
@@ -12271,37 +12734,37 @@
         <v>24</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>511</v>
+        <v>558</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>512</v>
+        <v>559</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>514</v>
+        <v>561</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>515</v>
+        <v>562</v>
       </c>
       <c r="D6" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>516</v>
+        <v>563</v>
       </c>
       <c r="F6" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>517</v>
+        <v>564</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12309,71 +12772,71 @@
         <v>228</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>518</v>
+        <v>565</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>519</v>
+        <v>566</v>
       </c>
       <c r="D7" s="61" t="n">
         <f aca="false">Assumptions!B44</f>
         <v>120</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>520</v>
+        <v>567</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>521</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>522</v>
+        <v>569</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>523</v>
+        <v>570</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>524</v>
+        <v>571</v>
       </c>
       <c r="D8" s="61" t="n">
         <f aca="false">Assumptions!B46</f>
         <v>400</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>525</v>
+        <v>572</v>
       </c>
       <c r="F8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>526</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>527</v>
+        <v>574</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>528</v>
+        <v>575</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>529</v>
+        <v>576</v>
       </c>
       <c r="D9" s="61" t="n">
         <f aca="false">Assumptions!B45</f>
         <v>120</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12381,151 +12844,151 @@
         <v>219</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>532</v>
+        <v>579</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="F10" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>540</v>
+        <v>587</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>541</v>
+        <v>588</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>542</v>
+        <v>589</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>543</v>
+        <v>590</v>
       </c>
       <c r="F12" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>544</v>
+        <v>591</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>545</v>
+        <v>592</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>546</v>
+        <v>593</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>547</v>
+        <v>594</v>
       </c>
       <c r="D13" s="61" t="n">
         <f aca="false">Assumptions!B43</f>
         <v>168</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>548</v>
+        <v>595</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>549</v>
+        <v>596</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>550</v>
+        <v>597</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>551</v>
+        <v>598</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>552</v>
+        <v>599</v>
       </c>
       <c r="D14" s="61" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>553</v>
+        <v>600</v>
       </c>
       <c r="F14" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>555</v>
+        <v>602</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>556</v>
+        <v>603</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>557</v>
+        <v>604</v>
       </c>
       <c r="D15" s="61" t="n">
         <f aca="false">Assumptions!B50</f>
         <v>5</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>558</v>
+        <v>605</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>559</v>
+        <v>606</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>560</v>
+        <v>607</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>561</v>
+        <v>608</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>562</v>
+        <v>609</v>
       </c>
       <c r="D16" s="61" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -12538,78 +13001,78 @@
         <v>102</v>
       </c>
       <c r="G16" s="59" t="s">
-        <v>563</v>
+        <v>610</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>564</v>
+        <v>611</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>565</v>
+        <v>612</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>566</v>
+        <v>613</v>
       </c>
       <c r="D17" s="61" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>567</v>
+        <v>614</v>
       </c>
       <c r="F17" s="27" t="s">
         <v>102</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>568</v>
+        <v>615</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>569</v>
+        <v>616</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>570</v>
+        <v>617</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>571</v>
+        <v>618</v>
       </c>
       <c r="F18" s="59" t="s">
         <v>104</v>
       </c>
       <c r="G18" s="59" t="s">
-        <v>572</v>
+        <v>619</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>573</v>
+        <v>620</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>574</v>
+        <v>621</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>575</v>
+        <v>622</v>
       </c>
       <c r="D19" s="61" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>576</v>
+        <v>623</v>
       </c>
       <c r="F19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>577</v>
+        <v>624</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12617,46 +13080,46 @@
         <v>224</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>578</v>
+        <v>625</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="E20" s="59" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="F20" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G20" s="59" t="s">
-        <v>580</v>
+        <v>627</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>582</v>
+        <v>629</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>515</v>
+        <v>562</v>
       </c>
       <c r="D21" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>583</v>
+        <v>630</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>584</v>
+        <v>631</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12664,55 +13127,55 @@
         <v>236</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>585</v>
+        <v>632</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="D22" s="61" t="n">
         <f aca="false">Assumptions!B57</f>
         <v>2</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>587</v>
+        <v>634</v>
       </c>
       <c r="F22" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G22" s="59" t="s">
-        <v>588</v>
+        <v>635</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>589</v>
+        <v>636</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>590</v>
+        <v>637</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>552</v>
+        <v>599</v>
       </c>
       <c r="D23" s="61" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>591</v>
+        <v>638</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>592</v>
+        <v>639</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="59" t="s">
-        <v>593</v>
+        <v>640</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>594</v>
+        <v>641</v>
       </c>
       <c r="C24" s="59" t="s">
         <v>134</v>
@@ -12722,13 +13185,13 @@
         <v>24</v>
       </c>
       <c r="E24" s="59" t="s">
-        <v>595</v>
+        <v>642</v>
       </c>
       <c r="F24" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G24" s="59" t="s">
-        <v>596</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -12774,7 +13237,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>597</v>
+        <v>644</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12783,7 +13246,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>598</v>
+        <v>645</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -12798,21 +13261,21 @@
         <v>42</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>599</v>
+        <v>646</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>600</v>
+        <v>647</v>
       </c>
       <c r="B6" s="62" t="n">
         <f aca="false">Assumptions!B62</f>
         <v>1200</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>601</v>
+        <v>648</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
@@ -12826,21 +13289,21 @@
         <v>120</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>602</v>
+        <v>649</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>603</v>
+        <v>650</v>
       </c>
       <c r="B8" s="63" t="n">
         <f aca="false">IF(B7=0,0,B6/B7)</f>
         <v>10</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>604</v>
+        <v>651</v>
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="33"/>
@@ -12854,7 +13317,7 @@
         <v>1.3</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>605</v>
+        <v>652</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
@@ -12868,14 +13331,14 @@
         <v>13</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>606</v>
+        <v>653</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>607</v>
+        <v>654</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -12884,24 +13347,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>608</v>
+        <v>655</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>609</v>
+        <v>656</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>610</v>
+        <v>657</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>611</v>
+        <v>658</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>504</v>
+        <v>551</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>612</v>
+        <v>659</v>
       </c>
       <c r="B14" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
@@ -12916,12 +13379,12 @@
         <v>9.6</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>613</v>
+        <v>660</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>614</v>
+        <v>661</v>
       </c>
       <c r="B15" s="61" t="n">
         <f aca="false">Assumptions!B57</f>
@@ -12936,12 +13399,12 @@
         <v>3</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>615</v>
+        <v>662</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>616</v>
+        <v>663</v>
       </c>
       <c r="B16" s="61" t="n">
         <f aca="false">Assumptions!B58</f>
@@ -12959,7 +13422,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>548</v>
+        <v>595</v>
       </c>
       <c r="B17" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B43,0)</f>
@@ -12973,12 +13436,12 @@
         <v>2</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>617</v>
+        <v>664</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>618</v>
+        <v>665</v>
       </c>
       <c r="B18" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B44,0)</f>
@@ -12992,12 +13455,12 @@
         <v>3</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>619</v>
+        <v>666</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>620</v>
+        <v>667</v>
       </c>
       <c r="B19" s="32" t="n">
         <f aca="false">ROUNDUP((B15+B16*Assumptions!B60)*$B$10/Assumptions!B59,0)</f>
@@ -13011,12 +13474,12 @@
         <v>2</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>621</v>
+        <v>668</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>622</v>
+        <v>669</v>
       </c>
       <c r="B20" s="61" t="n">
         <f aca="false">Assumptions!B61</f>
@@ -13035,7 +13498,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>623</v>
+        <v>670</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -13047,7 +13510,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>624</v>
+        <v>671</v>
       </c>
       <c r="D22" s="65" t="n">
         <f aca="false">Assumptions!B41</f>
@@ -13056,7 +13519,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="67" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="B23" s="67"/>
       <c r="C23" s="67"/>
@@ -13071,7 +13534,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -13080,24 +13543,24 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>608</v>
+        <v>655</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>609</v>
+        <v>656</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>610</v>
+        <v>657</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>611</v>
+        <v>658</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>504</v>
+        <v>551</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>627</v>
+        <v>674</v>
       </c>
       <c r="B27" s="61" t="n">
         <f aca="false">Assumptions!B64</f>
@@ -13117,7 +13580,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="59" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="B28" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B43,0)</f>
@@ -13131,12 +13594,12 @@
         <v>1</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>629</v>
+        <v>676</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B44,0)</f>
@@ -13153,7 +13616,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>631</v>
+        <v>678</v>
       </c>
       <c r="D30" s="63" t="n">
         <f aca="false">SUM(D27:D29)</f>
@@ -13162,7 +13625,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="D31" s="63" t="n">
         <f aca="false">Assumptions!B41-D30</f>
@@ -13171,7 +13634,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>633</v>
+        <v>680</v>
       </c>
       <c r="D32" s="32" t="n">
         <f aca="false">INT(D31/Assumptions!B65)</f>
@@ -13180,7 +13643,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>634</v>
+        <v>681</v>
       </c>
       <c r="D33" s="61" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -13189,7 +13652,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="67" t="s">
-        <v>560</v>
+        <v>607</v>
       </c>
       <c r="B34" s="67"/>
       <c r="C34" s="67"/>
@@ -13204,7 +13667,7 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="54" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="B36" s="54"/>
       <c r="C36" s="54"/>
@@ -13285,7 +13748,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>636</v>
+        <v>683</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -13300,392 +13763,392 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>419</v>
+        <v>466</v>
       </c>
       <c r="B4" s="58" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>637</v>
+        <v>684</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>638</v>
+        <v>685</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>639</v>
+        <v>686</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>640</v>
+        <v>687</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>641</v>
+        <v>688</v>
       </c>
       <c r="H4" s="58" t="s">
-        <v>642</v>
+        <v>689</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>643</v>
+        <v>690</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>644</v>
+        <v>691</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>645</v>
+        <v>692</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>646</v>
+        <v>693</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>647</v>
+        <v>694</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>648</v>
+        <v>695</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>649</v>
+        <v>696</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>650</v>
+        <v>697</v>
       </c>
       <c r="H5" s="70" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>651</v>
+        <v>698</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>652</v>
+        <v>699</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>653</v>
+        <v>700</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>654</v>
+        <v>701</v>
       </c>
       <c r="B6" s="59" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>656</v>
+        <v>703</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>657</v>
+        <v>704</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>658</v>
+        <v>705</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>659</v>
+        <v>706</v>
       </c>
       <c r="H6" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>660</v>
+        <v>707</v>
       </c>
       <c r="J6" s="59" t="s">
-        <v>661</v>
+        <v>708</v>
       </c>
       <c r="K6" s="59" t="s">
-        <v>662</v>
+        <v>709</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>663</v>
+        <v>710</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>664</v>
+        <v>711</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>665</v>
+        <v>712</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>666</v>
+        <v>713</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>667</v>
+        <v>714</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>668</v>
+        <v>715</v>
       </c>
       <c r="H7" s="70" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>669</v>
+        <v>716</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>670</v>
+        <v>717</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>671</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>672</v>
+        <v>719</v>
       </c>
       <c r="B8" s="59" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>673</v>
+        <v>720</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>674</v>
+        <v>721</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>675</v>
+        <v>722</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>676</v>
+        <v>723</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>677</v>
+        <v>724</v>
       </c>
       <c r="H8" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>678</v>
+        <v>725</v>
       </c>
       <c r="J8" s="59" t="s">
-        <v>679</v>
+        <v>726</v>
       </c>
       <c r="K8" s="59" t="s">
-        <v>680</v>
+        <v>727</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>681</v>
+        <v>728</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>682</v>
+        <v>729</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>683</v>
+        <v>730</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>684</v>
+        <v>731</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>685</v>
+        <v>732</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>686</v>
+        <v>733</v>
       </c>
       <c r="H9" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>687</v>
+        <v>734</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>688</v>
+        <v>735</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>689</v>
+        <v>736</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>690</v>
+        <v>737</v>
       </c>
       <c r="B10" s="59" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>691</v>
+        <v>738</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>692</v>
+        <v>739</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>693</v>
+        <v>740</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>694</v>
+        <v>741</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>695</v>
+        <v>742</v>
       </c>
       <c r="H10" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>696</v>
+        <v>743</v>
       </c>
       <c r="J10" s="59" t="s">
-        <v>697</v>
+        <v>744</v>
       </c>
       <c r="K10" s="59" t="s">
-        <v>698</v>
+        <v>745</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>699</v>
+        <v>746</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>700</v>
+        <v>747</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>701</v>
+        <v>748</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>702</v>
+        <v>749</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>703</v>
+        <v>750</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>704</v>
+        <v>751</v>
       </c>
       <c r="H11" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>705</v>
+        <v>752</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>706</v>
+        <v>753</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>707</v>
+        <v>754</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>708</v>
+        <v>755</v>
       </c>
       <c r="B12" s="59" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>709</v>
+        <v>756</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>710</v>
+        <v>757</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>711</v>
+        <v>758</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>712</v>
+        <v>759</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>713</v>
+        <v>760</v>
       </c>
       <c r="H12" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>714</v>
+        <v>761</v>
       </c>
       <c r="J12" s="59" t="s">
-        <v>715</v>
+        <v>762</v>
       </c>
       <c r="K12" s="59" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>718</v>
+        <v>765</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>720</v>
+        <v>767</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>722</v>
+        <v>769</v>
       </c>
       <c r="H13" s="70" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>723</v>
+        <v>770</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>724</v>
+        <v>771</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>725</v>
+        <v>772</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>726</v>
+        <v>773</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>727</v>
+        <v>774</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>728</v>
+        <v>775</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>729</v>
+        <v>776</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>730</v>
+        <v>777</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>731</v>
+        <v>778</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>732</v>
+        <v>779</v>
       </c>
       <c r="H14" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>733</v>
+        <v>780</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>734</v>
+        <v>781</v>
       </c>
       <c r="K14" s="59" t="s">
-        <v>735</v>
+        <v>782</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>736</v>
+        <v>783</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
@@ -13697,10 +14160,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>737</v>
+        <v>784</v>
       </c>
       <c r="B17" s="71" t="s">
-        <v>738</v>
+        <v>785</v>
       </c>
       <c r="C17" s="71"/>
       <c r="D17" s="71"/>
@@ -13711,10 +14174,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>739</v>
+        <v>786</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>740</v>
+        <v>787</v>
       </c>
       <c r="C18" s="71"/>
       <c r="D18" s="71"/>
@@ -13725,10 +14188,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>741</v>
+        <v>788</v>
       </c>
       <c r="B19" s="71" t="s">
-        <v>742</v>
+        <v>789</v>
       </c>
       <c r="C19" s="71"/>
       <c r="D19" s="71"/>
@@ -13739,10 +14202,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>743</v>
+        <v>790</v>
       </c>
       <c r="B20" s="71" t="s">
-        <v>744</v>
+        <v>791</v>
       </c>
       <c r="C20" s="71"/>
       <c r="D20" s="71"/>
@@ -13753,10 +14216,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>745</v>
+        <v>792</v>
       </c>
       <c r="B21" s="71" t="s">
-        <v>746</v>
+        <v>793</v>
       </c>
       <c r="C21" s="71"/>
       <c r="D21" s="71"/>
@@ -13767,10 +14230,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>747</v>
+        <v>794</v>
       </c>
       <c r="B22" s="71" t="s">
-        <v>748</v>
+        <v>795</v>
       </c>
       <c r="C22" s="71"/>
       <c r="D22" s="71"/>
@@ -13781,10 +14244,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>749</v>
+        <v>796</v>
       </c>
       <c r="B23" s="71" t="s">
-        <v>750</v>
+        <v>797</v>
       </c>
       <c r="C23" s="71"/>
       <c r="D23" s="71"/>
@@ -13795,7 +14258,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="72" t="s">
-        <v>751</v>
+        <v>798</v>
       </c>
     </row>
   </sheetData>
@@ -13859,7 +14322,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>752</v>
+        <v>799</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -13873,42 +14336,42 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>419</v>
+        <v>466</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>753</v>
+        <v>800</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>503</v>
+        <v>550</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>754</v>
+        <v>801</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>755</v>
+        <v>802</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>756</v>
+        <v>803</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>757</v>
+        <v>804</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>758</v>
+        <v>805</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>759</v>
+        <v>806</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>760</v>
+        <v>807</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
@@ -13917,190 +14380,190 @@
         <v>96</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G5" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="I5" s="70" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>763</v>
+        <v>810</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>764</v>
+        <v>811</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>765</v>
+        <v>812</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>766</v>
+        <v>813</v>
       </c>
       <c r="D6" s="59" t="s">
         <v>96</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G6" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>759</v>
+        <v>806</v>
       </c>
       <c r="I6" s="70" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="J6" s="59" t="s">
-        <v>768</v>
+        <v>815</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>769</v>
+        <v>816</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>770</v>
+        <v>817</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>766</v>
+        <v>813</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G7" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>764</v>
+        <v>811</v>
       </c>
       <c r="I7" s="70" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>771</v>
+        <v>818</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>772</v>
+        <v>819</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>773</v>
+        <v>820</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="D8" s="59" t="s">
         <v>96</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="G8" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="I8" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J8" s="59" t="s">
-        <v>776</v>
+        <v>823</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>512</v>
+        <v>559</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>777</v>
+        <v>824</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>778</v>
+        <v>825</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G9" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="I9" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>780</v>
+        <v>827</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>781</v>
+        <v>828</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="D10" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G10" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>512</v>
+        <v>559</v>
       </c>
       <c r="I10" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J10" s="59" t="s">
-        <v>783</v>
+        <v>830</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>651</v>
+        <v>698</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>784</v>
+        <v>831</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>23</v>
@@ -14109,30 +14572,30 @@
         <v>98</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G11" s="43" t="n">
         <v>12</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="I11" s="70" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>785</v>
+        <v>832</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>660</v>
+        <v>707</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>786</v>
+        <v>833</v>
       </c>
       <c r="C12" s="59" t="s">
         <v>23</v>
@@ -14141,30 +14604,30 @@
         <v>98</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G12" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>651</v>
+        <v>698</v>
       </c>
       <c r="I12" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J12" s="59" t="s">
-        <v>787</v>
+        <v>834</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>669</v>
+        <v>716</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>788</v>
+        <v>835</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>26</v>
@@ -14173,62 +14636,62 @@
         <v>98</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G13" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="I13" s="70" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>789</v>
+        <v>836</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>790</v>
+        <v>837</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>791</v>
+        <v>838</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>472</v>
+        <v>519</v>
       </c>
       <c r="D14" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G14" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H14" s="59" t="s">
-        <v>512</v>
+        <v>559</v>
       </c>
       <c r="I14" s="70" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>792</v>
+        <v>839</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>705</v>
+        <v>752</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>793</v>
+        <v>840</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>35</v>
@@ -14237,263 +14700,263 @@
         <v>98</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G15" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>790</v>
+        <v>837</v>
       </c>
       <c r="I15" s="70" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="J15" s="27" t="s">
-        <v>794</v>
+        <v>841</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>795</v>
+        <v>842</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>638</v>
+        <v>685</v>
       </c>
       <c r="D16" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E16" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F16" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G16" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H16" s="59" t="s">
-        <v>651</v>
+        <v>698</v>
       </c>
       <c r="I16" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J16" s="59" t="s">
-        <v>797</v>
+        <v>844</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>577</v>
+        <v>624</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>798</v>
+        <v>845</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>799</v>
+        <v>846</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G17" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="I17" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>800</v>
+        <v>847</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>801</v>
+        <v>848</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>802</v>
+        <v>849</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>803</v>
+        <v>850</v>
       </c>
       <c r="D18" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="G18" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H18" s="59" t="s">
-        <v>512</v>
+        <v>559</v>
       </c>
       <c r="I18" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J18" s="59" t="s">
-        <v>804</v>
+        <v>851</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>521</v>
+        <v>568</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>805</v>
+        <v>852</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>778</v>
+        <v>825</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G19" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>512</v>
+        <v>559</v>
       </c>
       <c r="I19" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>806</v>
+        <v>853</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>807</v>
+        <v>854</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="D20" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E20" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F20" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G20" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>651</v>
+        <v>698</v>
       </c>
       <c r="I20" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J20" s="59" t="s">
-        <v>808</v>
+        <v>855</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>809</v>
+        <v>856</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>810</v>
+        <v>857</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>811</v>
+        <v>858</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G21" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="I21" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J21" s="27" t="s">
-        <v>812</v>
+        <v>859</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="59" t="s">
-        <v>813</v>
+        <v>860</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>814</v>
+        <v>861</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>638</v>
+        <v>685</v>
       </c>
       <c r="D22" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F22" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G22" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="59" t="s">
-        <v>795</v>
+        <v>842</v>
       </c>
       <c r="I22" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J22" s="59" t="s">
-        <v>815</v>
+        <v>862</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>816</v>
+        <v>863</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>817</v>
+        <v>864</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>818</v>
+        <v>865</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>819</v>
+        <v>866</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
@@ -14502,117 +14965,117 @@
         <v>3</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>772</v>
+        <v>819</v>
       </c>
       <c r="I23" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>820</v>
+        <v>867</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="59" t="s">
-        <v>544</v>
+        <v>591</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>540</v>
+        <v>587</v>
       </c>
       <c r="C24" s="59" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="D24" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E24" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F24" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G24" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H24" s="59" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="I24" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J24" s="59" t="s">
-        <v>821</v>
+        <v>868</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>733</v>
+        <v>780</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>728</v>
+        <v>775</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="D25" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G25" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>544</v>
+        <v>591</v>
       </c>
       <c r="I25" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J25" s="27" t="s">
-        <v>822</v>
+        <v>869</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="59" t="s">
-        <v>823</v>
+        <v>870</v>
       </c>
       <c r="B26" s="59" t="s">
-        <v>824</v>
+        <v>871</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="D26" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E26" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F26" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G26" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>544</v>
+        <v>591</v>
       </c>
       <c r="I26" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J26" s="59" t="s">
-        <v>825</v>
+        <v>872</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>687</v>
+        <v>734</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>682</v>
+        <v>729</v>
       </c>
       <c r="C27" s="27" t="s">
         <v>29</v>
@@ -14621,30 +15084,30 @@
         <v>100</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G27" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>790</v>
+        <v>837</v>
       </c>
       <c r="I27" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J27" s="27" t="s">
-        <v>826</v>
+        <v>873</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="59" t="s">
-        <v>696</v>
+        <v>743</v>
       </c>
       <c r="B28" s="59" t="s">
-        <v>827</v>
+        <v>874</v>
       </c>
       <c r="C28" s="59" t="s">
         <v>32</v>
@@ -14653,30 +15116,30 @@
         <v>100</v>
       </c>
       <c r="E28" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F28" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G28" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H28" s="59" t="s">
-        <v>790</v>
+        <v>837</v>
       </c>
       <c r="I28" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J28" s="59" t="s">
-        <v>828</v>
+        <v>875</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>678</v>
+        <v>725</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>829</v>
+        <v>876</v>
       </c>
       <c r="C29" s="27" t="s">
         <v>26</v>
@@ -14685,94 +15148,94 @@
         <v>100</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>819</v>
+        <v>866</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G29" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>669</v>
+        <v>716</v>
       </c>
       <c r="I29" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>830</v>
+        <v>877</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="59" t="s">
-        <v>723</v>
+        <v>770</v>
       </c>
       <c r="B30" s="59" t="s">
-        <v>831</v>
+        <v>878</v>
       </c>
       <c r="C30" s="59" t="s">
-        <v>778</v>
+        <v>825</v>
       </c>
       <c r="D30" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F30" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G30" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="59" t="s">
-        <v>669</v>
+        <v>716</v>
       </c>
       <c r="I30" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J30" s="59" t="s">
-        <v>832</v>
+        <v>879</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="s">
-        <v>588</v>
+        <v>635</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>833</v>
+        <v>880</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>472</v>
+        <v>519</v>
       </c>
       <c r="D31" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G31" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>512</v>
+        <v>559</v>
       </c>
       <c r="I31" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J31" s="27" t="s">
-        <v>834</v>
+        <v>881</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="59" t="s">
-        <v>835</v>
+        <v>882</v>
       </c>
       <c r="B32" s="59" t="s">
-        <v>836</v>
+        <v>883</v>
       </c>
       <c r="C32" s="59" t="s">
         <v>35</v>
@@ -14781,30 +15244,30 @@
         <v>100</v>
       </c>
       <c r="E32" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F32" s="59" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="G32" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H32" s="59" t="s">
-        <v>705</v>
+        <v>752</v>
       </c>
       <c r="I32" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J32" s="59" t="s">
-        <v>837</v>
+        <v>884</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>714</v>
+        <v>761</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>838</v>
+        <v>885</v>
       </c>
       <c r="C33" s="27" t="s">
         <v>35</v>
@@ -14813,487 +15276,487 @@
         <v>100</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G33" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>705</v>
+        <v>752</v>
       </c>
       <c r="I33" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J33" s="27" t="s">
-        <v>839</v>
+        <v>886</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="59" t="s">
-        <v>840</v>
+        <v>887</v>
       </c>
       <c r="B34" s="59" t="s">
-        <v>841</v>
+        <v>888</v>
       </c>
       <c r="C34" s="59" t="s">
-        <v>842</v>
+        <v>889</v>
       </c>
       <c r="D34" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F34" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G34" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H34" s="59" t="s">
-        <v>588</v>
+        <v>635</v>
       </c>
       <c r="I34" s="70" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="J34" s="59" t="s">
-        <v>843</v>
+        <v>890</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>844</v>
+        <v>891</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>845</v>
+        <v>892</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>842</v>
+        <v>889</v>
       </c>
       <c r="D35" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G35" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>840</v>
+        <v>887</v>
       </c>
       <c r="I35" s="70" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="J35" s="27" t="s">
-        <v>846</v>
+        <v>893</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="59" t="s">
-        <v>847</v>
+        <v>894</v>
       </c>
       <c r="B36" s="59" t="s">
-        <v>848</v>
+        <v>895</v>
       </c>
       <c r="C36" s="59" t="s">
-        <v>842</v>
+        <v>889</v>
       </c>
       <c r="D36" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F36" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G36" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H36" s="59" t="s">
-        <v>844</v>
+        <v>891</v>
       </c>
       <c r="I36" s="70" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="J36" s="59" t="s">
-        <v>849</v>
+        <v>896</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="27" t="s">
-        <v>850</v>
+        <v>897</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>851</v>
+        <v>898</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>852</v>
+        <v>899</v>
       </c>
       <c r="D37" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>819</v>
+        <v>866</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G37" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H37" s="27" t="s">
-        <v>512</v>
+        <v>559</v>
       </c>
       <c r="I37" s="70" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="J37" s="27" t="s">
-        <v>853</v>
+        <v>900</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="59" t="s">
-        <v>854</v>
+        <v>901</v>
       </c>
       <c r="B38" s="59" t="s">
-        <v>855</v>
+        <v>902</v>
       </c>
       <c r="C38" s="59" t="s">
-        <v>472</v>
+        <v>519</v>
       </c>
       <c r="D38" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="59" t="s">
-        <v>819</v>
+        <v>866</v>
       </c>
       <c r="F38" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G38" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="59" t="s">
-        <v>850</v>
+        <v>897</v>
       </c>
       <c r="I38" s="70" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="J38" s="59" t="s">
-        <v>856</v>
+        <v>903</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="27" t="s">
-        <v>580</v>
+        <v>627</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>857</v>
+        <v>904</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>799</v>
+        <v>846</v>
       </c>
       <c r="D39" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G39" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>544</v>
+        <v>591</v>
       </c>
       <c r="I39" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J39" s="27" t="s">
-        <v>858</v>
+        <v>905</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="59" t="s">
-        <v>584</v>
+        <v>631</v>
       </c>
       <c r="B40" s="59" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="C40" s="59" t="s">
-        <v>472</v>
+        <v>519</v>
       </c>
       <c r="D40" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F40" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G40" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H40" s="59" t="s">
-        <v>512</v>
+        <v>559</v>
       </c>
       <c r="I40" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J40" s="59" t="s">
-        <v>859</v>
+        <v>906</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>592</v>
+        <v>639</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>860</v>
+        <v>907</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>472</v>
+        <v>519</v>
       </c>
       <c r="D41" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G41" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>588</v>
+        <v>635</v>
       </c>
       <c r="I41" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J41" s="27" t="s">
-        <v>861</v>
+        <v>908</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="59" t="s">
-        <v>862</v>
+        <v>909</v>
       </c>
       <c r="B42" s="59" t="s">
-        <v>863</v>
+        <v>910</v>
       </c>
       <c r="C42" s="59" t="s">
-        <v>472</v>
+        <v>519</v>
       </c>
       <c r="D42" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="59" t="s">
-        <v>819</v>
+        <v>866</v>
       </c>
       <c r="F42" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G42" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="59" t="s">
-        <v>854</v>
+        <v>901</v>
       </c>
       <c r="I42" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J42" s="59" t="s">
-        <v>864</v>
+        <v>911</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
-        <v>865</v>
+        <v>912</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>866</v>
+        <v>913</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>867</v>
+        <v>914</v>
       </c>
       <c r="D43" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>867</v>
+        <v>914</v>
       </c>
       <c r="G43" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H43" s="27" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="I43" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J43" s="27" t="s">
-        <v>868</v>
+        <v>915</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="59" t="s">
-        <v>869</v>
+        <v>916</v>
       </c>
       <c r="B44" s="59" t="s">
-        <v>870</v>
+        <v>917</v>
       </c>
       <c r="C44" s="59" t="s">
-        <v>766</v>
+        <v>813</v>
       </c>
       <c r="D44" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E44" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F44" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G44" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H44" s="59" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="I44" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J44" s="59" t="s">
-        <v>871</v>
+        <v>918</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="27" t="s">
-        <v>872</v>
+        <v>919</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>873</v>
+        <v>920</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>803</v>
+        <v>850</v>
       </c>
       <c r="D45" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G45" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H45" s="27" t="s">
-        <v>801</v>
+        <v>848</v>
       </c>
       <c r="I45" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J45" s="27" t="s">
-        <v>874</v>
+        <v>921</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="59" t="s">
-        <v>875</v>
+        <v>922</v>
       </c>
       <c r="B46" s="59" t="s">
-        <v>876</v>
+        <v>923</v>
       </c>
       <c r="C46" s="59" t="s">
-        <v>638</v>
+        <v>685</v>
       </c>
       <c r="D46" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E46" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F46" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G46" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H46" s="59" t="s">
-        <v>795</v>
+        <v>842</v>
       </c>
       <c r="I46" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J46" s="59" t="s">
-        <v>877</v>
+        <v>924</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
-        <v>878</v>
+        <v>925</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>879</v>
+        <v>926</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>852</v>
+        <v>899</v>
       </c>
       <c r="D47" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G47" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H47" s="27" t="s">
-        <v>512</v>
+        <v>559</v>
       </c>
       <c r="I47" s="70" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="J47" s="27" t="s">
-        <v>880</v>
+        <v>927</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="59" t="s">
-        <v>881</v>
+        <v>928</v>
       </c>
       <c r="B48" s="59" t="s">
-        <v>882</v>
+        <v>929</v>
       </c>
       <c r="C48" s="59" t="s">
-        <v>542</v>
+        <v>589</v>
       </c>
       <c r="D48" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E48" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F48" s="59" t="s">
         <v>100</v>
@@ -15302,62 +15765,62 @@
         <v>3</v>
       </c>
       <c r="H48" s="59" t="s">
-        <v>844</v>
+        <v>891</v>
       </c>
       <c r="I48" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J48" s="59" t="s">
-        <v>883</v>
+        <v>930</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="27" t="s">
-        <v>884</v>
+        <v>931</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>885</v>
+        <v>932</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>886</v>
+        <v>933</v>
       </c>
       <c r="D49" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>819</v>
+        <v>866</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G49" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H49" s="27" t="s">
-        <v>872</v>
+        <v>919</v>
       </c>
       <c r="I49" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J49" s="27" t="s">
-        <v>887</v>
+        <v>934</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="59" t="s">
-        <v>888</v>
+        <v>935</v>
       </c>
       <c r="B50" s="59" t="s">
-        <v>889</v>
+        <v>936</v>
       </c>
       <c r="C50" s="59" t="s">
-        <v>890</v>
+        <v>937</v>
       </c>
       <c r="D50" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E50" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F50" s="59" t="s">
         <v>100</v>
@@ -15366,181 +15829,181 @@
         <v>4</v>
       </c>
       <c r="H50" s="59" t="s">
-        <v>809</v>
+        <v>856</v>
       </c>
       <c r="I50" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J50" s="59" t="s">
-        <v>891</v>
+        <v>938</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
-        <v>892</v>
+        <v>939</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>893</v>
+        <v>940</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>894</v>
+        <v>941</v>
       </c>
       <c r="D51" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G51" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H51" s="27" t="s">
-        <v>823</v>
+        <v>870</v>
       </c>
       <c r="I51" s="70" t="s">
-        <v>775</v>
+        <v>809</v>
       </c>
       <c r="J51" s="27" t="s">
-        <v>895</v>
+        <v>942</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="59" t="s">
-        <v>896</v>
+        <v>943</v>
       </c>
       <c r="B52" s="59" t="s">
-        <v>897</v>
+        <v>944</v>
       </c>
       <c r="C52" s="59" t="s">
-        <v>894</v>
+        <v>941</v>
       </c>
       <c r="D52" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E52" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F52" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G52" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H52" s="59" t="s">
-        <v>714</v>
+        <v>761</v>
       </c>
       <c r="I52" s="70" t="s">
-        <v>775</v>
+        <v>809</v>
       </c>
       <c r="J52" s="59" t="s">
-        <v>898</v>
+        <v>945</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="27" t="s">
-        <v>568</v>
+        <v>615</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>899</v>
+        <v>946</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>894</v>
+        <v>941</v>
       </c>
       <c r="D53" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F53" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G53" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H53" s="27" t="s">
-        <v>896</v>
+        <v>943</v>
       </c>
       <c r="I53" s="70" t="s">
-        <v>775</v>
+        <v>826</v>
       </c>
       <c r="J53" s="27" t="s">
-        <v>900</v>
+        <v>947</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="59" t="s">
-        <v>901</v>
+        <v>948</v>
       </c>
       <c r="B54" s="59" t="s">
-        <v>902</v>
+        <v>949</v>
       </c>
       <c r="C54" s="59" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="D54" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E54" s="59" t="s">
-        <v>819</v>
+        <v>866</v>
       </c>
       <c r="F54" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G54" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H54" s="59" t="s">
-        <v>823</v>
+        <v>870</v>
       </c>
       <c r="I54" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J54" s="59" t="s">
-        <v>903</v>
+        <v>950</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
-        <v>904</v>
+        <v>951</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>905</v>
+        <v>952</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>472</v>
+        <v>519</v>
       </c>
       <c r="D55" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>906</v>
+        <v>953</v>
       </c>
       <c r="F55" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G55" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>847</v>
+        <v>894</v>
       </c>
       <c r="I55" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J55" s="27" t="s">
-        <v>907</v>
+        <v>954</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="59" t="s">
-        <v>908</v>
+        <v>955</v>
       </c>
       <c r="B56" s="59" t="s">
-        <v>909</v>
+        <v>956</v>
       </c>
       <c r="C56" s="59" t="s">
         <v>26</v>
@@ -15549,359 +16012,359 @@
         <v>102</v>
       </c>
       <c r="E56" s="59" t="s">
-        <v>906</v>
+        <v>953</v>
       </c>
       <c r="F56" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G56" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H56" s="59" t="s">
-        <v>669</v>
+        <v>716</v>
       </c>
       <c r="I56" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J56" s="59" t="s">
-        <v>910</v>
+        <v>957</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
-        <v>911</v>
+        <v>958</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>912</v>
+        <v>959</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>852</v>
+        <v>899</v>
       </c>
       <c r="D57" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G57" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H57" s="27" t="s">
-        <v>892</v>
+        <v>939</v>
       </c>
       <c r="I57" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J57" s="27" t="s">
-        <v>913</v>
+        <v>960</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="59" t="s">
-        <v>914</v>
+        <v>961</v>
       </c>
       <c r="B58" s="59" t="s">
-        <v>915</v>
+        <v>962</v>
       </c>
       <c r="C58" s="59" t="s">
-        <v>638</v>
+        <v>685</v>
       </c>
       <c r="D58" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E58" s="59" t="s">
-        <v>819</v>
+        <v>866</v>
       </c>
       <c r="F58" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G58" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H58" s="59" t="s">
-        <v>795</v>
+        <v>842</v>
       </c>
       <c r="I58" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J58" s="59" t="s">
-        <v>916</v>
+        <v>963</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="27" t="s">
-        <v>917</v>
+        <v>964</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>918</v>
+        <v>965</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>778</v>
+        <v>825</v>
       </c>
       <c r="D59" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E59" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G59" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H59" s="27" t="s">
-        <v>809</v>
+        <v>856</v>
       </c>
       <c r="I59" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J59" s="27" t="s">
-        <v>919</v>
+        <v>966</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="59" t="s">
-        <v>920</v>
+        <v>967</v>
       </c>
       <c r="B60" s="59" t="s">
-        <v>921</v>
+        <v>968</v>
       </c>
       <c r="C60" s="59" t="s">
-        <v>922</v>
+        <v>969</v>
       </c>
       <c r="D60" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E60" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F60" s="59" t="s">
-        <v>922</v>
+        <v>969</v>
       </c>
       <c r="G60" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H60" s="59" t="s">
-        <v>911</v>
+        <v>958</v>
       </c>
       <c r="I60" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J60" s="59" t="s">
-        <v>923</v>
+        <v>970</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="27" t="s">
-        <v>924</v>
+        <v>971</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>925</v>
+        <v>972</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>852</v>
+        <v>899</v>
       </c>
       <c r="D61" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G61" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H61" s="27" t="s">
-        <v>911</v>
+        <v>958</v>
       </c>
       <c r="I61" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J61" s="27" t="s">
-        <v>926</v>
+        <v>973</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="59" t="s">
-        <v>927</v>
+        <v>974</v>
       </c>
       <c r="B62" s="59" t="s">
-        <v>928</v>
+        <v>975</v>
       </c>
       <c r="C62" s="59" t="s">
-        <v>638</v>
+        <v>685</v>
       </c>
       <c r="D62" s="59" t="s">
         <v>104</v>
       </c>
       <c r="E62" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F62" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G62" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H62" s="59" t="s">
-        <v>795</v>
+        <v>842</v>
       </c>
       <c r="I62" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J62" s="59" t="s">
-        <v>929</v>
+        <v>976</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="27" t="s">
-        <v>930</v>
+        <v>977</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>931</v>
+        <v>978</v>
       </c>
       <c r="C63" s="27" t="s">
-        <v>932</v>
+        <v>979</v>
       </c>
       <c r="D63" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E63" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G63" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H63" s="27" t="s">
-        <v>911</v>
+        <v>958</v>
       </c>
       <c r="I63" s="70" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="J63" s="27" t="s">
-        <v>933</v>
+        <v>980</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="59" t="s">
-        <v>934</v>
+        <v>981</v>
       </c>
       <c r="B64" s="59" t="s">
-        <v>935</v>
+        <v>982</v>
       </c>
       <c r="C64" s="59" t="s">
-        <v>886</v>
+        <v>933</v>
       </c>
       <c r="D64" s="59" t="s">
         <v>104</v>
       </c>
       <c r="E64" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F64" s="59" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="G64" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H64" s="59" t="s">
-        <v>924</v>
+        <v>971</v>
       </c>
       <c r="I64" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J64" s="59" t="s">
-        <v>936</v>
+        <v>983</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="27" t="s">
-        <v>937</v>
+        <v>984</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>938</v>
+        <v>985</v>
       </c>
       <c r="C65" s="27" t="s">
-        <v>766</v>
+        <v>813</v>
       </c>
       <c r="D65" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E65" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G65" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H65" s="27" t="s">
-        <v>911</v>
+        <v>958</v>
       </c>
       <c r="I65" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J65" s="27" t="s">
-        <v>939</v>
+        <v>986</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="59" t="s">
-        <v>940</v>
+        <v>987</v>
       </c>
       <c r="B66" s="59" t="s">
-        <v>941</v>
+        <v>988</v>
       </c>
       <c r="C66" s="59" t="s">
-        <v>818</v>
+        <v>865</v>
       </c>
       <c r="D66" s="59" t="s">
         <v>104</v>
       </c>
       <c r="E66" s="59" t="s">
-        <v>819</v>
+        <v>866</v>
       </c>
       <c r="F66" s="59" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G66" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H66" s="59" t="s">
-        <v>869</v>
+        <v>916</v>
       </c>
       <c r="I66" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J66" s="59" t="s">
-        <v>942</v>
+        <v>989</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="27" t="s">
-        <v>943</v>
+        <v>990</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>944</v>
+        <v>991</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>818</v>
+        <v>865</v>
       </c>
       <c r="D67" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F67" s="27" t="s">
         <v>100</v>
@@ -15910,30 +16373,30 @@
         <v>5</v>
       </c>
       <c r="H67" s="27" t="s">
-        <v>924</v>
+        <v>971</v>
       </c>
       <c r="I67" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J67" s="27" t="s">
-        <v>945</v>
+        <v>992</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="59" t="s">
-        <v>946</v>
+        <v>993</v>
       </c>
       <c r="B68" s="59" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="C68" s="59" t="s">
-        <v>818</v>
+        <v>865</v>
       </c>
       <c r="D68" s="59" t="s">
         <v>106</v>
       </c>
       <c r="E68" s="59" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F68" s="59" t="s">
         <v>100</v>
@@ -15942,45 +16405,45 @@
         <v>1</v>
       </c>
       <c r="H68" s="59" t="s">
-        <v>943</v>
+        <v>990</v>
       </c>
       <c r="I68" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J68" s="59" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="27" t="s">
-        <v>949</v>
+        <v>996</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>950</v>
+        <v>997</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>818</v>
+        <v>865</v>
       </c>
       <c r="D69" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E69" s="27" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="F69" s="27" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="G69" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H69" s="27" t="s">
-        <v>937</v>
+        <v>984</v>
       </c>
       <c r="I69" s="70" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="J69" s="27" t="s">
-        <v>951</v>
+        <v>998</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16117,7 +16580,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D82" s="73" t="s">
-        <v>952</v>
+        <v>999</v>
       </c>
       <c r="E82" s="73"/>
       <c r="F82" s="73"/>
@@ -16128,7 +16591,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D83" s="74" t="s">
-        <v>953</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="74"/>
       <c r="F83" s="74"/>
@@ -16139,7 +16602,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D84" s="74" t="s">
-        <v>954</v>
+        <v>1001</v>
       </c>
       <c r="E84" s="74"/>
       <c r="F84" s="74"/>
@@ -16150,29 +16613,29 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D85" s="74" t="s">
-        <v>955</v>
+        <v>1002</v>
       </c>
       <c r="E85" s="74"/>
       <c r="F85" s="74"/>
       <c r="G85" s="32" t="n">
         <f aca="false">SUMIF(I$5:I$80,"Done",G$5:G$80)</f>
-        <v>82</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D86" s="74" t="s">
-        <v>956</v>
+        <v>1003</v>
       </c>
       <c r="E86" s="74"/>
       <c r="F86" s="74"/>
       <c r="G86" s="75" t="n">
         <f aca="false">IF(G83=0,0,SUMIFS(G$5:G$80,E$5:E$80,"Must",I$5:I$80,"Done")/G83)</f>
-        <v>0.23202614379085</v>
+        <v>0.274509803921569</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>957</v>
+        <v>1004</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -16186,25 +16649,25 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>755</v>
+        <v>802</v>
       </c>
       <c r="B90" s="9"/>
       <c r="C90" s="9" t="s">
-        <v>958</v>
+        <v>1005</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>959</v>
+        <v>1006</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>960</v>
+        <v>1007</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>961</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="76" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
       <c r="B91" s="76"/>
       <c r="C91" s="32" t="n">
@@ -16226,7 +16689,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="76" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="B92" s="76"/>
       <c r="C92" s="32" t="n">
@@ -16248,7 +16711,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="76" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="B93" s="76"/>
       <c r="C93" s="32" t="n">
@@ -16270,7 +16733,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="76" t="s">
-        <v>867</v>
+        <v>914</v>
       </c>
       <c r="B94" s="76"/>
       <c r="C94" s="32" t="n">
@@ -16292,7 +16755,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="76" t="s">
-        <v>922</v>
+        <v>969</v>
       </c>
       <c r="B95" s="76"/>
       <c r="C95" s="32" t="n">
@@ -16336,7 +16799,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="73" t="s">
-        <v>962</v>
+        <v>1009</v>
       </c>
       <c r="B97" s="73"/>
       <c r="C97" s="21" t="n">
@@ -16362,16 +16825,16 @@
       </c>
       <c r="B99" s="29"/>
       <c r="C99" s="9" t="s">
-        <v>958</v>
+        <v>1005</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>963</v>
+        <v>1010</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>960</v>
+        <v>1007</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>961</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16514,7 +16977,7 @@
     </row>
     <row r="107" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="54" t="s">
-        <v>964</v>
+        <v>1011</v>
       </c>
       <c r="B107" s="54"/>
       <c r="C107" s="54"/>
@@ -16648,7 +17111,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>965</v>
+        <v>1012</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -16666,22 +17129,22 @@
         <v>6</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>966</v>
+        <v>1013</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>967</v>
+        <v>1014</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>968</v>
+        <v>1015</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>969</v>
+        <v>1016</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>970</v>
+        <v>1017</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>971</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16702,16 +17165,16 @@
         <v>46383</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>972</v>
+        <v>1019</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>973</v>
+        <v>1020</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>974</v>
+        <v>1021</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>975</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16732,16 +17195,16 @@
         <v>46453</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>976</v>
+        <v>1023</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>977</v>
+        <v>1024</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>978</v>
+        <v>1025</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>979</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16762,16 +17225,16 @@
         <v>46579</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>980</v>
+        <v>1027</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>981</v>
+        <v>1028</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>982</v>
+        <v>1029</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>983</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16792,16 +17255,16 @@
         <v>46621</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>984</v>
+        <v>1031</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>985</v>
+        <v>1032</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>986</v>
+        <v>1033</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>987</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16822,16 +17285,16 @@
         <v>46663</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>988</v>
+        <v>1035</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>989</v>
+        <v>1036</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>990</v>
+        <v>1037</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>991</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16852,21 +17315,21 @@
         <v>46691</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>992</v>
+        <v>1039</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>993</v>
+        <v>1040</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>994</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>995</v>
+        <v>1042</v>
       </c>
       <c r="B12" s="82" t="n">
         <f aca="false">D10</f>
@@ -16876,7 +17339,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>996</v>
+        <v>1043</v>
       </c>
       <c r="B13" s="83" t="n">
         <f aca="false">B12-Assumptions!B7</f>
@@ -16886,7 +17349,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>997</v>
+        <v>1044</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="24"/>
@@ -16898,7 +17361,7 @@
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
-        <v>998</v>
+        <v>1045</v>
       </c>
       <c r="B15" s="54"/>
       <c r="C15" s="54"/>
@@ -16910,7 +17373,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="54" t="s">
-        <v>999</v>
+        <v>1046</v>
       </c>
       <c r="B16" s="54"/>
       <c r="C16" s="54"/>
@@ -16990,7 +17453,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1000</v>
+        <v>1047</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -17024,13 +17487,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1001</v>
+        <v>1048</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>966</v>
+        <v>1013</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>967</v>
+        <v>1014</v>
       </c>
       <c r="D4" s="84" t="n">
         <v>1</v>
@@ -17215,7 +17678,7 @@
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>1002</v>
+        <v>1049</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -17462,7 +17925,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>1003</v>
+        <v>1050</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -19233,7 +19696,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>1004</v>
+        <v>1051</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -19480,7 +19943,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>1005</v>
+        <v>1052</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>

--- a/docs/Vinland_Game_Development_Plan.xlsx
+++ b/docs/Vinland_Game_Development_Plan.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="1360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="1387">
   <si>
     <t xml:space="preserve">VINLAND</t>
   </si>
@@ -1483,6 +1483,81 @@
     <t xml:space="preserve">Recruitment (F26): room left for stores and stock in 24 units</t>
   </si>
   <si>
+    <t xml:space="preserve">RELIEF VOYAGE AND SCORE (F30, F31)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relief price: food unit (marks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relief stores (F30): the household feeds the crossing; more costs silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relief price: drink unit (marks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relief stores (F30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relief price: fodder unit (marks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relief price: head of cattle (marks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relief stock (F30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relief price: sheep or goat (marks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relief price: trade unit (marks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relief trade goods (F30): cloth or iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score: per timber unit delivered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score (F31): the return is the win (P7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score: per person alive at the end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score (F31): at the camp and at home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score: per point of goodwill left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score (F31): peace left on the table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score: per cargo home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score (F31)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score: for a relief that reached the camp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score: for a living camp at the end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score (F31): the colony is the point (P5); an abandoned camp scores below it (P8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score: per death</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cargoes for the full win</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score (F31): two cargoes and one relief ship is the full win (P7)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pillars, fantasy, clocks, and the win</t>
   </si>
   <si>
@@ -2929,7 +3004,7 @@
     <t xml:space="preserve">Recruitment and second hull</t>
   </si>
   <si>
-    <t xml:space="preserve">A living crew and a true story recruit better than silver.  [Built: the story (people alive in both places, buildings, deaths, goodwill) brings volunteers; silver hires more and can buy a second hull (40 marks); each hull carries 30. The relief sails in F30.]</t>
+    <t xml:space="preserve">A living crew and a true story recruit better than silver.  [Built: the story (people alive in both places, buildings, deaths, goodwill) brings volunteers; silver hires more and can buy a second hull (40 marks); each hull carries 30. The relief carries them west in F30.]</t>
   </si>
   <si>
     <t xml:space="preserve">F27</t>
@@ -2968,7 +3043,7 @@
     <t xml:space="preserve">Full three-summer sim</t>
   </si>
   <si>
-    <t xml:space="preserve">A run goes outfit to score with no debug commands.</t>
+    <t xml:space="preserve">A run goes outfit to score with no debug commands.  [Built: outfit, outbound voyage, camp, cargo home, appraisal and recruitment, the relief loaded with silver (stores, stock, trade goods; one or two hulls), the camp run on its own while you are away (hay sized to the herd), the reunion, a second cargo home and the score. Rules-level runs for every outfit go outfit to score (8 of 8 full sagas each with a planning player); a ship that never goes home strands the camp at the third winter.]</t>
   </si>
   <si>
     <t xml:space="preserve">F54</t>
@@ -3007,7 +3082,7 @@
     <t xml:space="preserve">Score and saga ending</t>
   </si>
   <si>
-    <t xml:space="preserve">Qualified ending scored below a living camp, never scolded.</t>
+    <t xml:space="preserve">Qualified ending scored below a living camp, never scolded.  [First pass: score from timber delivered, cargoes, people alive in both places, the relief, a living camp, goodwill and deaths; endings titled The full saga, Home and rich, A camp at the Strait, A camp without a ship, A hard road. Saga text (F56) and tuning to come.]</t>
   </si>
   <si>
     <t xml:space="preserve">F32</t>
@@ -4166,6 +4241,12 @@
   </si>
   <si>
     <t xml:space="preserve">Alpha begins: the timber goes home and buys the relief.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F26 and F30 done, F31 first pass; RELIEF VOYAGE AND SCORE knobs added.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A run now goes from outfit to score: three summers, two cargoes, one relief.</t>
   </si>
 </sst>
 </file>
@@ -5374,11 +5455,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="71538381"/>
-        <c:axId val="28951518"/>
+        <c:axId val="62289495"/>
+        <c:axId val="84427033"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="71538381"/>
+        <c:axId val="62289495"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5410,7 +5491,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28951518"/>
+        <c:crossAx val="84427033"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5418,7 +5499,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28951518"/>
+        <c:axId val="84427033"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5494,7 +5575,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71538381"/>
+        <c:crossAx val="62289495"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5533,9 +5614,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>738720</xdr:colOff>
+      <xdr:colOff>738000</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>55080</xdr:rowOff>
+      <xdr:rowOff>54360</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5544,7 +5625,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="6562800"/>
-        <a:ext cx="5390640" cy="2150640"/>
+        <a:ext cx="5389920" cy="2149920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6459,7 +6540,7 @@
       </c>
       <c r="B55" s="5" t="str">
         <f aca="false">COUNTIF(Backlog!I5:I80,"Done")&amp;" of "&amp;COUNTA(Backlog!A5:A80)</f>
-        <v>15 of 65</v>
+        <v>17 of 65</v>
       </c>
       <c r="C55" s="31" t="s">
         <v>68</v>
@@ -6481,7 +6562,7 @@
       </c>
       <c r="B56" s="38" t="n">
         <f aca="false">Backlog!G86</f>
-        <v>0.274509803921569</v>
+        <v>0.320261437908497</v>
       </c>
       <c r="C56" s="34" t="s">
         <v>71</v>
@@ -6626,7 +6707,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1053</v>
+        <v>1078</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -6638,10 +6719,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>1054</v>
+        <v>1079</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1055</v>
+        <v>1080</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>96</v>
@@ -6662,7 +6743,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="58" t="s">
-        <v>1056</v>
+        <v>1081</v>
       </c>
       <c r="J4" s="58" t="s">
         <v>7</v>
@@ -6670,7 +6751,7 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="B5" s="90" t="n">
         <f aca="false">Assumptions!B26</f>
@@ -6705,7 +6786,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="B6" s="90" t="n">
         <f aca="false">Assumptions!B27</f>
@@ -6740,7 +6821,7 @@
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="B7" s="90" t="n">
         <f aca="false">Assumptions!B28</f>
@@ -6775,7 +6856,7 @@
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>914</v>
+        <v>939</v>
       </c>
       <c r="B8" s="90" t="n">
         <f aca="false">Assumptions!B29</f>
@@ -6810,7 +6891,7 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>969</v>
+        <v>994</v>
       </c>
       <c r="B9" s="90" t="n">
         <f aca="false">Assumptions!B30</f>
@@ -6880,10 +6961,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="72" t="s">
-        <v>1057</v>
+        <v>1082</v>
       </c>
       <c r="B11" s="72" t="s">
-        <v>1058</v>
+        <v>1083</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -6920,10 +7001,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="72" t="s">
-        <v>1059</v>
+        <v>1084</v>
       </c>
       <c r="B12" s="72" t="s">
-        <v>1060</v>
+        <v>1085</v>
       </c>
       <c r="C12" s="63" t="n">
         <f aca="false">IF(Assumptions!B16=0,0,C11/Assumptions!B16)</f>
@@ -6956,7 +7037,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1061</v>
+        <v>1086</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -6971,28 +7052,28 @@
         <v>5</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1062</v>
+        <v>1087</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>914</v>
+        <v>939</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>969</v>
+        <v>994</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>100</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>1056</v>
+        <v>1081</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>7</v>
@@ -7252,7 +7333,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>1063</v>
+        <v>1088</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -7269,7 +7350,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="50" t="s">
-        <v>1064</v>
+        <v>1089</v>
       </c>
       <c r="B22" s="50"/>
       <c r="C22" s="50"/>
@@ -7289,7 +7370,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="50" t="s">
-        <v>1065</v>
+        <v>1090</v>
       </c>
       <c r="B23" s="50"/>
       <c r="C23" s="50"/>
@@ -7306,7 +7387,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="50" t="s">
-        <v>1066</v>
+        <v>1091</v>
       </c>
       <c r="B24" s="50"/>
       <c r="C24" s="50"/>
@@ -7374,7 +7455,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="50" t="s">
-        <v>1067</v>
+        <v>1092</v>
       </c>
       <c r="B28" s="50"/>
       <c r="C28" s="50"/>
@@ -7391,7 +7472,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>1068</v>
+        <v>1093</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
@@ -7428,7 +7509,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="67" t="s">
-        <v>1069</v>
+        <v>1094</v>
       </c>
       <c r="B31" s="67"/>
       <c r="C31" s="67"/>
@@ -7446,12 +7527,12 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="72" t="s">
-        <v>1070</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="96" t="s">
-        <v>1071</v>
+        <v>1096</v>
       </c>
       <c r="B34" s="96"/>
       <c r="C34" s="96"/>
@@ -7465,7 +7546,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>1063</v>
+        <v>1088</v>
       </c>
       <c r="B35" s="91" t="n">
         <f aca="false">J21</f>
@@ -7474,7 +7555,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>1072</v>
+        <v>1097</v>
       </c>
       <c r="B36" s="91" t="n">
         <f aca="false">J31</f>
@@ -7483,7 +7564,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>1073</v>
+        <v>1098</v>
       </c>
       <c r="B37" s="91" t="n">
         <f aca="false">SUM(J22:J28)*(1+I30)</f>
@@ -7535,7 +7616,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1074</v>
+        <v>1099</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7544,7 +7625,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -7559,7 +7640,7 @@
         <v>42</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="D5" s="29"/>
       <c r="E5" s="29"/>
@@ -7573,28 +7654,28 @@
         <v>19.99</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>1076</v>
+        <v>1101</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1077</v>
+        <v>1102</v>
       </c>
       <c r="B7" s="98" t="n">
         <f aca="false">B6*Assumptions!B70</f>
         <v>15.992</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>1078</v>
+        <v>1103</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>1079</v>
+        <v>1104</v>
       </c>
       <c r="B8" s="98" t="n">
         <f aca="false">B7*(1-Assumptions!B71)</f>
@@ -7606,35 +7687,35 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>1080</v>
+        <v>1105</v>
       </c>
       <c r="B9" s="75" t="n">
         <f aca="false">Assumptions!B72*(1-Assumptions!B74)+Assumptions!B73*Assumptions!B74</f>
         <v>0.29</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>1081</v>
+        <v>1106</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>1082</v>
+        <v>1107</v>
       </c>
       <c r="B10" s="99" t="n">
         <f aca="false">B8*(1-B9)</f>
         <v>10.4459744</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>1083</v>
+        <v>1108</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1084</v>
+        <v>1109</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -7649,7 +7730,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="29"/>
@@ -7663,70 +7744,70 @@
         <v>460504.8</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>1085</v>
+        <v>1110</v>
       </c>
       <c r="D14" s="33"/>
       <c r="E14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>1086</v>
+        <v>1111</v>
       </c>
       <c r="B15" s="100" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B14/B10,0))</f>
         <v>44085</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>1087</v>
+        <v>1112</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>1088</v>
+        <v>1113</v>
       </c>
       <c r="B16" s="90" t="n">
         <f aca="false">TeamBudget!B37</f>
         <v>98632.8</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>1089</v>
+        <v>1114</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="67" t="s">
-        <v>1090</v>
+        <v>1115</v>
       </c>
       <c r="B17" s="100" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B16/B10,0))</f>
         <v>9443</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>1091</v>
+        <v>1116</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>1092</v>
+        <v>1117</v>
       </c>
       <c r="B18" s="91" t="n">
         <f aca="false">B15*B6</f>
         <v>881259.15</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>1093</v>
+        <v>1118</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>1094</v>
+        <v>1119</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -7735,19 +7816,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>1095</v>
+        <v>1120</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1096</v>
+        <v>1121</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1097</v>
+        <v>1122</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1098</v>
+        <v>1123</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>1008</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7862,7 +7943,7 @@
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="54" t="s">
-        <v>1099</v>
+        <v>1124</v>
       </c>
       <c r="B28" s="54"/>
       <c r="C28" s="54"/>
@@ -7944,7 +8025,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7956,195 +8037,195 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>1018</v>
+        <v>1043</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1101</v>
+        <v>1126</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1102</v>
+        <v>1127</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1103</v>
+        <v>1128</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>802</v>
+        <v>827</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1104</v>
+        <v>1129</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>1105</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1022</v>
+        <v>1047</v>
       </c>
       <c r="B5" s="87" t="n">
         <f aca="false">Schedule!D5</f>
         <v>46383</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1106</v>
+        <v>1131</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1107</v>
+        <v>1132</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="F5" s="70" t="s">
-        <v>1108</v>
+        <v>1133</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1109</v>
+        <v>1134</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>1110</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
       <c r="B6" s="87" t="n">
         <f aca="false">Schedule!D6</f>
         <v>46453</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1111</v>
+        <v>1136</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1112</v>
+        <v>1137</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="F6" s="70" t="s">
-        <v>1108</v>
+        <v>1133</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>1113</v>
+        <v>1138</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>1114</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="B7" s="87" t="n">
         <f aca="false">Schedule!D7</f>
         <v>46579</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1115</v>
+        <v>1140</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1116</v>
+        <v>1141</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="F7" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1117</v>
+        <v>1142</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>1118</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1034</v>
+        <v>1059</v>
       </c>
       <c r="B8" s="87" t="n">
         <f aca="false">Schedule!D8</f>
         <v>46621</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1119</v>
+        <v>1144</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1120</v>
+        <v>1145</v>
       </c>
       <c r="E8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="F8" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>1121</v>
+        <v>1146</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>1122</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1038</v>
+        <v>1063</v>
       </c>
       <c r="B9" s="87" t="n">
         <f aca="false">Schedule!D9</f>
         <v>46663</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1123</v>
+        <v>1148</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1124</v>
+        <v>1149</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>969</v>
+        <v>994</v>
       </c>
       <c r="F9" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>1126</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1041</v>
+        <v>1066</v>
       </c>
       <c r="B10" s="87" t="n">
         <f aca="false">Schedule!D10</f>
         <v>46691</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1127</v>
+        <v>1152</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>1128</v>
+        <v>1153</v>
       </c>
       <c r="E10" s="59" t="s">
         <v>100</v>
       </c>
       <c r="F10" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>1129</v>
+        <v>1154</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>1130</v>
+        <v>1155</v>
       </c>
       <c r="B12" s="54"/>
       <c r="C12" s="54"/>
@@ -8224,7 +8305,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1131</v>
+        <v>1156</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8238,31 +8319,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1132</v>
+        <v>1157</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1133</v>
+        <v>1158</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1134</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>616</v>
+        <v>641</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>1135</v>
+        <v>1160</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>802</v>
+        <v>827</v>
       </c>
       <c r="H4" s="58" t="s">
-        <v>1136</v>
+        <v>1161</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>1137</v>
+        <v>1162</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>44</v>
@@ -8270,10 +8351,10 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="59" t="s">
-        <v>1138</v>
+        <v>1163</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>1139</v>
+        <v>1164</v>
       </c>
       <c r="C5" s="43" t="n">
         <v>3</v>
@@ -8286,27 +8367,27 @@
         <v>15</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>1140</v>
+        <v>1165</v>
       </c>
       <c r="G5" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="H5" s="59" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
       <c r="I5" s="59" t="s">
-        <v>1141</v>
+        <v>1166</v>
       </c>
       <c r="J5" s="70" t="s">
-        <v>1142</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>1143</v>
+        <v>1168</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1144</v>
+        <v>1169</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>3</v>
@@ -8319,27 +8400,27 @@
         <v>12</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>1145</v>
+        <v>1170</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>1146</v>
+        <v>1171</v>
       </c>
       <c r="J6" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="59" t="s">
-        <v>1148</v>
+        <v>1173</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>1149</v>
+        <v>1174</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>2</v>
@@ -8352,27 +8433,27 @@
         <v>8</v>
       </c>
       <c r="F7" s="59" t="s">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G7" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="H7" s="59" t="s">
-        <v>1038</v>
+        <v>1063</v>
       </c>
       <c r="I7" s="59" t="s">
-        <v>1151</v>
+        <v>1176</v>
       </c>
       <c r="J7" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1152</v>
+        <v>1177</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1153</v>
+        <v>1178</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>4</v>
@@ -8385,27 +8466,27 @@
         <v>12</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>1154</v>
+        <v>1179</v>
       </c>
       <c r="G8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>1155</v>
+        <v>1180</v>
       </c>
       <c r="J8" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="59" t="s">
-        <v>1156</v>
+        <v>1181</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1157</v>
+        <v>1182</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>2</v>
@@ -8418,27 +8499,27 @@
         <v>6</v>
       </c>
       <c r="F9" s="59" t="s">
-        <v>1158</v>
+        <v>1183</v>
       </c>
       <c r="G9" s="59" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="H9" s="59" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="I9" s="59" t="s">
-        <v>1159</v>
+        <v>1184</v>
       </c>
       <c r="J9" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1160</v>
+        <v>1185</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1161</v>
+        <v>1186</v>
       </c>
       <c r="C10" s="43" t="n">
         <v>2</v>
@@ -8451,27 +8532,27 @@
         <v>10</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>1162</v>
+        <v>1187</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>1163</v>
+        <v>1188</v>
       </c>
       <c r="J10" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="59" t="s">
-        <v>1164</v>
+        <v>1189</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>1165</v>
+        <v>1190</v>
       </c>
       <c r="C11" s="43" t="n">
         <v>3</v>
@@ -8484,27 +8565,27 @@
         <v>12</v>
       </c>
       <c r="F11" s="59" t="s">
-        <v>1166</v>
+        <v>1191</v>
       </c>
       <c r="G11" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H11" s="59" t="s">
-        <v>1034</v>
+        <v>1059</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>1167</v>
+        <v>1192</v>
       </c>
       <c r="J11" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1168</v>
+        <v>1193</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1169</v>
+        <v>1194</v>
       </c>
       <c r="C12" s="43" t="n">
         <v>2</v>
@@ -8517,27 +8598,27 @@
         <v>8</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>1170</v>
+        <v>1195</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>1022</v>
+        <v>1047</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>1171</v>
+        <v>1196</v>
       </c>
       <c r="J12" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="59" t="s">
-        <v>1172</v>
+        <v>1197</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>1173</v>
+        <v>1198</v>
       </c>
       <c r="C13" s="43" t="n">
         <v>2</v>
@@ -8550,27 +8631,27 @@
         <v>4</v>
       </c>
       <c r="F13" s="59" t="s">
-        <v>1174</v>
+        <v>1199</v>
       </c>
       <c r="G13" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="H13" s="59" t="s">
-        <v>1022</v>
+        <v>1047</v>
       </c>
       <c r="I13" s="59" t="s">
-        <v>1175</v>
+        <v>1200</v>
       </c>
       <c r="J13" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1176</v>
+        <v>1201</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1177</v>
+        <v>1202</v>
       </c>
       <c r="C14" s="43" t="n">
         <v>3</v>
@@ -8583,27 +8664,27 @@
         <v>12</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>1178</v>
+        <v>1203</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="H14" s="59" t="s">
-        <v>1034</v>
+        <v>1059</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>1179</v>
+        <v>1204</v>
       </c>
       <c r="J14" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="59" t="s">
-        <v>1180</v>
+        <v>1205</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>1181</v>
+        <v>1206</v>
       </c>
       <c r="C15" s="43" t="n">
         <v>3</v>
@@ -8616,27 +8697,27 @@
         <v>15</v>
       </c>
       <c r="F15" s="59" t="s">
-        <v>1182</v>
+        <v>1207</v>
       </c>
       <c r="G15" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="H15" s="59" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="I15" s="59" t="s">
-        <v>1183</v>
+        <v>1208</v>
       </c>
       <c r="J15" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>1184</v>
+        <v>1209</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>1185</v>
+        <v>1210</v>
       </c>
       <c r="C16" s="43" t="n">
         <v>4</v>
@@ -8649,27 +8730,27 @@
         <v>16</v>
       </c>
       <c r="F16" s="59" t="s">
-        <v>1186</v>
+        <v>1211</v>
       </c>
       <c r="G16" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H16" s="59" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
       <c r="I16" s="59" t="s">
-        <v>1187</v>
+        <v>1212</v>
       </c>
       <c r="J16" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="59" t="s">
-        <v>1188</v>
+        <v>1213</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>1189</v>
+        <v>1214</v>
       </c>
       <c r="C17" s="43" t="n">
         <v>3</v>
@@ -8682,27 +8763,27 @@
         <v>12</v>
       </c>
       <c r="F17" s="59" t="s">
-        <v>1190</v>
+        <v>1215</v>
       </c>
       <c r="G17" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="59" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="I17" s="59" t="s">
-        <v>1191</v>
+        <v>1216</v>
       </c>
       <c r="J17" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>1192</v>
+        <v>1217</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1193</v>
+        <v>1218</v>
       </c>
       <c r="C18" s="43" t="n">
         <v>2</v>
@@ -8715,27 +8796,27 @@
         <v>6</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>1194</v>
+        <v>1219</v>
       </c>
       <c r="G18" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="H18" s="59" t="s">
-        <v>1038</v>
+        <v>1063</v>
       </c>
       <c r="I18" s="59" t="s">
-        <v>1195</v>
+        <v>1220</v>
       </c>
       <c r="J18" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="59" t="s">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>1197</v>
+        <v>1222</v>
       </c>
       <c r="C19" s="43" t="n">
         <v>2</v>
@@ -8748,27 +8829,27 @@
         <v>8</v>
       </c>
       <c r="F19" s="59" t="s">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="G19" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="H19" s="59" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="I19" s="59" t="s">
-        <v>1199</v>
+        <v>1224</v>
       </c>
       <c r="J19" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>1200</v>
+        <v>1225</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1201</v>
+        <v>1226</v>
       </c>
       <c r="C20" s="43" t="n">
         <v>3</v>
@@ -8781,19 +8862,19 @@
         <v>15</v>
       </c>
       <c r="F20" s="59" t="s">
-        <v>1202</v>
+        <v>1227</v>
       </c>
       <c r="G20" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
       <c r="I20" s="59" t="s">
-        <v>1203</v>
+        <v>1228</v>
       </c>
       <c r="J20" s="70" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
   </sheetData>
@@ -8871,7 +8952,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1204</v>
+        <v>1229</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8882,278 +8963,278 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>1205</v>
+        <v>1230</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1206</v>
+        <v>1231</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1207</v>
+        <v>1232</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1208</v>
+        <v>1233</v>
       </c>
       <c r="E4" s="58" t="s">
         <v>95</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>802</v>
+        <v>827</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1209</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1210</v>
+        <v>1235</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1211</v>
+        <v>1236</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1212</v>
+        <v>1237</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1213</v>
+        <v>1238</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>1214</v>
+        <v>1239</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1215</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>774</v>
+        <v>799</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1216</v>
+        <v>1241</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1217</v>
+        <v>1242</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1218</v>
+        <v>1243</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>1219</v>
+        <v>1244</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>1220</v>
+        <v>1245</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>1221</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1222</v>
+        <v>1247</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1223</v>
+        <v>1248</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1224</v>
+        <v>1249</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>1226</v>
+        <v>1251</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1221</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1227</v>
+        <v>1252</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1228</v>
+        <v>1253</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1229</v>
+        <v>1254</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1230</v>
+        <v>1255</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>1231</v>
+        <v>1256</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>1232</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>659</v>
+        <v>684</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1233</v>
+        <v>1258</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1234</v>
+        <v>1259</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1235</v>
+        <v>1260</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1236</v>
+        <v>1261</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1237</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1238</v>
+        <v>1263</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1239</v>
+        <v>1264</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>972</v>
+        <v>997</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>1240</v>
+        <v>1265</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>1241</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>914</v>
+        <v>939</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1242</v>
+        <v>1267</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1243</v>
+        <v>1268</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1244</v>
+        <v>1269</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>1245</v>
+        <v>1270</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>914</v>
+        <v>939</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>1246</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>933</v>
+        <v>958</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1247</v>
+        <v>1272</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1248</v>
+        <v>1273</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>1249</v>
+        <v>1274</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>1221</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1251</v>
+        <v>1276</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1252</v>
+        <v>1277</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1253</v>
+        <v>1278</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1254</v>
+        <v>1279</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>1255</v>
+        <v>1280</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>1221</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1256</v>
+        <v>1281</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1257</v>
+        <v>1282</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1258</v>
+        <v>1283</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>1259</v>
+        <v>1284</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>1260</v>
+        <v>1285</v>
       </c>
       <c r="F14" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>1261</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1262</v>
+        <v>1287</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1263</v>
+        <v>1288</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1264</v>
+        <v>1289</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1265</v>
+        <v>1290</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>1266</v>
+        <v>1291</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>1267</v>
+        <v>1292</v>
       </c>
     </row>
   </sheetData>
@@ -9195,7 +9276,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1268</v>
+        <v>1293</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9206,24 +9287,24 @@
         <v>110</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1269</v>
+        <v>1294</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1270</v>
+        <v>1295</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>802</v>
+        <v>827</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1271</v>
+        <v>1296</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1272</v>
+        <v>1297</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1022</v>
+        <v>1047</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>100</v>
@@ -9231,55 +9312,55 @@
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>1273</v>
+        <v>1298</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1274</v>
+        <v>1299</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1276</v>
+        <v>1301</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1277</v>
+        <v>1302</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1278</v>
+        <v>1303</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1279</v>
+        <v>1304</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1280</v>
+        <v>1305</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1281</v>
+        <v>1306</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1022</v>
+        <v>1047</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>100</v>
@@ -9287,27 +9368,27 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1282</v>
+        <v>1307</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1283</v>
+        <v>1308</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>1284</v>
+        <v>1309</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1285</v>
+        <v>1310</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1038</v>
+        <v>1063</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>100</v>
@@ -9315,13 +9396,13 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1286</v>
+        <v>1311</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1287</v>
+        <v>1312</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1041</v>
+        <v>1066</v>
       </c>
       <c r="D12" s="59" t="s">
         <v>100</v>
@@ -9329,41 +9410,41 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1288</v>
+        <v>1313</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1289</v>
+        <v>1314</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1041</v>
+        <v>1066</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>969</v>
+        <v>994</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1290</v>
+        <v>1315</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1291</v>
+        <v>1316</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1292</v>
+        <v>1317</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1293</v>
+        <v>1318</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1294</v>
+        <v>1319</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>100</v>
@@ -9371,14 +9452,14 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>1295</v>
+        <v>1320</v>
       </c>
       <c r="B16" s="59" t="str">
         <f aca="false">"Premium at $"&amp;TEXT(Assumptions!B69,"0.00")&amp;". Launch discount no deeper than the realized-price factor on Assumptions."</f>
         <v>Premium at $19.99. Launch discount no deeper than the realized-price factor on Assumptions.</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>1034</v>
+        <v>1059</v>
       </c>
       <c r="D16" s="59" t="s">
         <v>100</v>
@@ -9386,13 +9467,13 @@
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>1296</v>
+        <v>1321</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1297</v>
+        <v>1322</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>100</v>
@@ -9400,13 +9481,13 @@
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>1016</v>
+        <v>1041</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1298</v>
+        <v>1323</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>1034</v>
+        <v>1059</v>
       </c>
       <c r="D18" s="59" t="s">
         <v>100</v>
@@ -9414,27 +9495,27 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1299</v>
+        <v>1324</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1038</v>
+        <v>1063</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>1301</v>
+        <v>1326</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1302</v>
+        <v>1327</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>1038</v>
+        <v>1063</v>
       </c>
       <c r="D20" s="59" t="s">
         <v>100</v>
@@ -9442,27 +9523,27 @@
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>1303</v>
+        <v>1328</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1304</v>
+        <v>1329</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>1038</v>
+        <v>1063</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="59" t="s">
-        <v>1305</v>
+        <v>1330</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1306</v>
+        <v>1331</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>1041</v>
+        <v>1066</v>
       </c>
       <c r="D22" s="59" t="s">
         <v>100</v>
@@ -9489,7 +9570,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -9508,7 +9589,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1307</v>
+        <v>1332</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9516,16 +9597,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1308</v>
+        <v>1333</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1309</v>
+        <v>1334</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1310</v>
+        <v>1335</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1311</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9533,13 +9614,13 @@
         <v>46311</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1312</v>
+        <v>1337</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1313</v>
+        <v>1338</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1314</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9547,13 +9628,13 @@
         <v>46311</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1312</v>
+        <v>1337</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1315</v>
+        <v>1340</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1316</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9561,13 +9642,13 @@
         <v>46311</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1312</v>
+        <v>1337</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1317</v>
+        <v>1342</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1318</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9575,13 +9656,13 @@
         <v>46311</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1076</v>
+        <v>1101</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1319</v>
+        <v>1344</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1320</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9589,13 +9670,13 @@
         <v>46311</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1321</v>
+        <v>1346</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1322</v>
+        <v>1347</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1323</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9606,10 +9687,10 @@
         <v>53</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1324</v>
+        <v>1349</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>1325</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9617,13 +9698,13 @@
         <v>46311</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1326</v>
+        <v>1351</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1327</v>
+        <v>1352</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1328</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9631,13 +9712,13 @@
         <v>46311</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1329</v>
+        <v>1354</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>1330</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9645,13 +9726,13 @@
         <v>46311</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1331</v>
+        <v>1356</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1333</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9659,13 +9740,13 @@
         <v>46311</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1334</v>
+        <v>1359</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1335</v>
+        <v>1360</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>1336</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9676,10 +9757,10 @@
         <v>58</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1337</v>
+        <v>1362</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1338</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9687,13 +9768,13 @@
         <v>46311</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>1339</v>
+        <v>1364</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>1340</v>
+        <v>1365</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>1341</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9704,10 +9785,10 @@
         <v>62</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1342</v>
+        <v>1367</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1343</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9715,13 +9796,13 @@
         <v>46311</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>589</v>
+        <v>614</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>1344</v>
+        <v>1369</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>1345</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9729,13 +9810,13 @@
         <v>46311</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>865</v>
+        <v>890</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1346</v>
+        <v>1371</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>1347</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9743,13 +9824,13 @@
         <v>46311</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1348</v>
+        <v>1373</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>1349</v>
+        <v>1374</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>1350</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9757,13 +9838,13 @@
         <v>46313</v>
       </c>
       <c r="B21" s="59" t="s">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="C21" s="59" t="s">
-        <v>1351</v>
+        <v>1376</v>
       </c>
       <c r="D21" s="59" t="s">
-        <v>1352</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9771,13 +9852,13 @@
         <v>46313</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1353</v>
+        <v>1378</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>1354</v>
+        <v>1379</v>
       </c>
       <c r="D22" s="59" t="s">
-        <v>1355</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9785,27 +9866,41 @@
         <v>46313</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>1353</v>
+        <v>1378</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>1356</v>
+        <v>1381</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="103" t="n">
         <v>46313</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>1353</v>
+        <v>1378</v>
       </c>
       <c r="C24" s="59" t="s">
-        <v>1358</v>
+        <v>1383</v>
       </c>
       <c r="D24" s="59" t="s">
-        <v>1359</v>
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="103" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B25" s="59" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C25" s="59" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D25" s="59" t="s">
+        <v>1386</v>
       </c>
     </row>
   </sheetData>
@@ -9829,7 +9924,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F241"/>
+  <dimension ref="A1:F258"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
@@ -12240,6 +12335,176 @@
       </c>
       <c r="C241" s="41" t="s">
         <v>464</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A243" s="57" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A244" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B244" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C244" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A245" s="42" t="s">
+        <v>466</v>
+      </c>
+      <c r="B245" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" s="41" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A246" s="42" t="s">
+        <v>468</v>
+      </c>
+      <c r="B246" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C246" s="41" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A247" s="42" t="s">
+        <v>470</v>
+      </c>
+      <c r="B247" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C247" s="41" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A248" s="42" t="s">
+        <v>471</v>
+      </c>
+      <c r="B248" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C248" s="41" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A249" s="42" t="s">
+        <v>473</v>
+      </c>
+      <c r="B249" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C249" s="41" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A250" s="42" t="s">
+        <v>474</v>
+      </c>
+      <c r="B250" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C250" s="41" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A251" s="42" t="s">
+        <v>476</v>
+      </c>
+      <c r="B251" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C251" s="41" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A252" s="42" t="s">
+        <v>478</v>
+      </c>
+      <c r="B252" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C252" s="41" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A253" s="42" t="s">
+        <v>480</v>
+      </c>
+      <c r="B253" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C253" s="41" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A254" s="42" t="s">
+        <v>482</v>
+      </c>
+      <c r="B254" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C254" s="41" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A255" s="42" t="s">
+        <v>484</v>
+      </c>
+      <c r="B255" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C255" s="41" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A256" s="42" t="s">
+        <v>485</v>
+      </c>
+      <c r="B256" s="43" t="n">
+        <v>25</v>
+      </c>
+      <c r="C256" s="41" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A257" s="42" t="s">
+        <v>487</v>
+      </c>
+      <c r="B257" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C257" s="41" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A258" s="42" t="s">
+        <v>488</v>
+      </c>
+      <c r="B258" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C258" s="41" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -12306,7 +12571,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12315,160 +12580,160 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>469</v>
+        <v>494</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>471</v>
+        <v>496</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>472</v>
+        <v>497</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>474</v>
+        <v>499</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>476</v>
+        <v>501</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>477</v>
+        <v>502</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>478</v>
+        <v>503</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>483</v>
+        <v>508</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>485</v>
+        <v>510</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>486</v>
+        <v>511</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>487</v>
+        <v>512</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>488</v>
+        <v>513</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>489</v>
+        <v>514</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>491</v>
+        <v>516</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>494</v>
+        <v>519</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>495</v>
+        <v>520</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>496</v>
+        <v>521</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>497</v>
+        <v>522</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
+        <v>525</v>
+      </c>
+      <c r="B12" s="59" t="s">
+        <v>526</v>
+      </c>
+      <c r="C12" s="59" t="s">
+        <v>527</v>
+      </c>
+      <c r="D12" s="59" t="s">
+        <v>528</v>
+      </c>
+      <c r="E12" s="59" t="s">
         <v>500</v>
-      </c>
-      <c r="B12" s="59" t="s">
-        <v>501</v>
-      </c>
-      <c r="C12" s="59" t="s">
-        <v>502</v>
-      </c>
-      <c r="D12" s="59" t="s">
-        <v>503</v>
-      </c>
-      <c r="E12" s="59" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>504</v>
+        <v>529</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -12477,16 +12742,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>505</v>
+        <v>530</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>506</v>
+        <v>531</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>507</v>
+        <v>532</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>508</v>
+        <v>533</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>95</v>
@@ -12494,58 +12759,58 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="60" t="s">
-        <v>509</v>
+        <v>534</v>
       </c>
       <c r="B16" s="60" t="s">
-        <v>510</v>
+        <v>535</v>
       </c>
       <c r="C16" s="60" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="D16" s="60" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="E16" s="60" t="s">
-        <v>513</v>
+        <v>538</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="59" t="s">
-        <v>514</v>
+        <v>539</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>515</v>
+        <v>540</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="D17" s="59" t="s">
-        <v>517</v>
+        <v>542</v>
       </c>
       <c r="E17" s="59" t="s">
-        <v>518</v>
+        <v>543</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="60" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="B18" s="60" t="s">
-        <v>520</v>
+        <v>545</v>
       </c>
       <c r="C18" s="60" t="s">
-        <v>521</v>
+        <v>546</v>
       </c>
       <c r="D18" s="60" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="E18" s="60" t="s">
-        <v>523</v>
+        <v>548</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="24"/>
@@ -12554,87 +12819,87 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>526</v>
+        <v>551</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>527</v>
+        <v>552</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>528</v>
+        <v>553</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>529</v>
+        <v>554</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>530</v>
+        <v>555</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>531</v>
+        <v>556</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>532</v>
+        <v>557</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>533</v>
+        <v>558</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>534</v>
+        <v>559</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="59" t="s">
-        <v>535</v>
+        <v>560</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>538</v>
+        <v>563</v>
       </c>
       <c r="E23" s="59" t="s">
-        <v>539</v>
+        <v>564</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>540</v>
+        <v>565</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>544</v>
+        <v>569</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="59" t="s">
-        <v>545</v>
+        <v>570</v>
       </c>
       <c r="B25" s="59" t="s">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>546</v>
+        <v>571</v>
       </c>
       <c r="D25" s="59" t="s">
-        <v>547</v>
+        <v>572</v>
       </c>
       <c r="E25" s="59" t="s">
-        <v>548</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -12687,7 +12952,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>549</v>
+        <v>574</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12698,33 +12963,33 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>552</v>
+        <v>577</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>553</v>
+        <v>578</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="F4" s="58" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>555</v>
+        <v>580</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>556</v>
+        <v>581</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>557</v>
+        <v>582</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>134</v>
@@ -12734,37 +12999,37 @@
         <v>24</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>558</v>
+        <v>583</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>561</v>
+        <v>586</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>562</v>
+        <v>587</v>
       </c>
       <c r="D6" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>563</v>
+        <v>588</v>
       </c>
       <c r="F6" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12772,71 +13037,71 @@
         <v>228</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>565</v>
+        <v>590</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>566</v>
+        <v>591</v>
       </c>
       <c r="D7" s="61" t="n">
         <f aca="false">Assumptions!B44</f>
         <v>120</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>568</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>569</v>
+        <v>594</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>570</v>
+        <v>595</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="D8" s="61" t="n">
         <f aca="false">Assumptions!B46</f>
         <v>400</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="F8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>573</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>574</v>
+        <v>599</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>576</v>
+        <v>601</v>
       </c>
       <c r="D9" s="61" t="n">
         <f aca="false">Assumptions!B45</f>
         <v>120</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12844,151 +13109,151 @@
         <v>219</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="F10" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>582</v>
+        <v>607</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>585</v>
+        <v>610</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>586</v>
+        <v>611</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>587</v>
+        <v>612</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>588</v>
+        <v>613</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>589</v>
+        <v>614</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>590</v>
+        <v>615</v>
       </c>
       <c r="F12" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>592</v>
+        <v>617</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>593</v>
+        <v>618</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>594</v>
+        <v>619</v>
       </c>
       <c r="D13" s="61" t="n">
         <f aca="false">Assumptions!B43</f>
         <v>168</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>595</v>
+        <v>620</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>596</v>
+        <v>621</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>597</v>
+        <v>622</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>598</v>
+        <v>623</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>599</v>
+        <v>624</v>
       </c>
       <c r="D14" s="61" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="F14" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>601</v>
+        <v>626</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>602</v>
+        <v>627</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>604</v>
+        <v>629</v>
       </c>
       <c r="D15" s="61" t="n">
         <f aca="false">Assumptions!B50</f>
         <v>5</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>605</v>
+        <v>630</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>606</v>
+        <v>631</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>607</v>
+        <v>632</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>608</v>
+        <v>633</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>609</v>
+        <v>634</v>
       </c>
       <c r="D16" s="61" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -13001,78 +13266,78 @@
         <v>102</v>
       </c>
       <c r="G16" s="59" t="s">
-        <v>610</v>
+        <v>635</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>612</v>
+        <v>637</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>613</v>
+        <v>638</v>
       </c>
       <c r="D17" s="61" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>614</v>
+        <v>639</v>
       </c>
       <c r="F17" s="27" t="s">
         <v>102</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>615</v>
+        <v>640</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>616</v>
+        <v>641</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>617</v>
+        <v>642</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>618</v>
+        <v>643</v>
       </c>
       <c r="F18" s="59" t="s">
         <v>104</v>
       </c>
       <c r="G18" s="59" t="s">
-        <v>619</v>
+        <v>644</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>620</v>
+        <v>645</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>621</v>
+        <v>646</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>622</v>
+        <v>647</v>
       </c>
       <c r="D19" s="61" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="F19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>624</v>
+        <v>649</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13080,46 +13345,46 @@
         <v>224</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="E20" s="59" t="s">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="F20" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G20" s="59" t="s">
-        <v>627</v>
+        <v>652</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>628</v>
+        <v>653</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>629</v>
+        <v>654</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>562</v>
+        <v>587</v>
       </c>
       <c r="D21" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>630</v>
+        <v>655</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>631</v>
+        <v>656</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13127,55 +13392,55 @@
         <v>236</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>632</v>
+        <v>657</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>633</v>
+        <v>658</v>
       </c>
       <c r="D22" s="61" t="n">
         <f aca="false">Assumptions!B57</f>
         <v>2</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>634</v>
+        <v>659</v>
       </c>
       <c r="F22" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G22" s="59" t="s">
-        <v>635</v>
+        <v>660</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>637</v>
+        <v>662</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>599</v>
+        <v>624</v>
       </c>
       <c r="D23" s="61" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>638</v>
+        <v>663</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>639</v>
+        <v>664</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="59" t="s">
-        <v>640</v>
+        <v>665</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="C24" s="59" t="s">
         <v>134</v>
@@ -13185,13 +13450,13 @@
         <v>24</v>
       </c>
       <c r="E24" s="59" t="s">
-        <v>642</v>
+        <v>667</v>
       </c>
       <c r="F24" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G24" s="59" t="s">
-        <v>643</v>
+        <v>668</v>
       </c>
     </row>
   </sheetData>
@@ -13237,7 +13502,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>644</v>
+        <v>669</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -13246,7 +13511,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -13261,21 +13526,21 @@
         <v>42</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>647</v>
+        <v>672</v>
       </c>
       <c r="B6" s="62" t="n">
         <f aca="false">Assumptions!B62</f>
         <v>1200</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>648</v>
+        <v>673</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
@@ -13289,21 +13554,21 @@
         <v>120</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>649</v>
+        <v>674</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="B8" s="63" t="n">
         <f aca="false">IF(B7=0,0,B6/B7)</f>
         <v>10</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>651</v>
+        <v>676</v>
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="33"/>
@@ -13317,7 +13582,7 @@
         <v>1.3</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>652</v>
+        <v>677</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
@@ -13331,14 +13596,14 @@
         <v>13</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>653</v>
+        <v>678</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>654</v>
+        <v>679</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -13347,24 +13612,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>551</v>
+        <v>576</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>659</v>
+        <v>684</v>
       </c>
       <c r="B14" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
@@ -13379,12 +13644,12 @@
         <v>9.6</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>660</v>
+        <v>685</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="B15" s="61" t="n">
         <f aca="false">Assumptions!B57</f>
@@ -13399,12 +13664,12 @@
         <v>3</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>662</v>
+        <v>687</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>663</v>
+        <v>688</v>
       </c>
       <c r="B16" s="61" t="n">
         <f aca="false">Assumptions!B58</f>
@@ -13422,7 +13687,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>595</v>
+        <v>620</v>
       </c>
       <c r="B17" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B43,0)</f>
@@ -13436,12 +13701,12 @@
         <v>2</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>664</v>
+        <v>689</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>665</v>
+        <v>690</v>
       </c>
       <c r="B18" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B44,0)</f>
@@ -13455,12 +13720,12 @@
         <v>3</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>666</v>
+        <v>691</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>667</v>
+        <v>692</v>
       </c>
       <c r="B19" s="32" t="n">
         <f aca="false">ROUNDUP((B15+B16*Assumptions!B60)*$B$10/Assumptions!B59,0)</f>
@@ -13474,12 +13739,12 @@
         <v>2</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>668</v>
+        <v>693</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>669</v>
+        <v>694</v>
       </c>
       <c r="B20" s="61" t="n">
         <f aca="false">Assumptions!B61</f>
@@ -13498,7 +13763,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>670</v>
+        <v>695</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -13510,7 +13775,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>671</v>
+        <v>696</v>
       </c>
       <c r="D22" s="65" t="n">
         <f aca="false">Assumptions!B41</f>
@@ -13519,7 +13784,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="67" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="B23" s="67"/>
       <c r="C23" s="67"/>
@@ -13534,7 +13799,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -13543,24 +13808,24 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>551</v>
+        <v>576</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="B27" s="61" t="n">
         <f aca="false">Assumptions!B64</f>
@@ -13580,7 +13845,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="59" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="B28" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B43,0)</f>
@@ -13594,12 +13859,12 @@
         <v>1</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>676</v>
+        <v>701</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>677</v>
+        <v>702</v>
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B44,0)</f>
@@ -13616,7 +13881,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>678</v>
+        <v>703</v>
       </c>
       <c r="D30" s="63" t="n">
         <f aca="false">SUM(D27:D29)</f>
@@ -13625,7 +13890,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>679</v>
+        <v>704</v>
       </c>
       <c r="D31" s="63" t="n">
         <f aca="false">Assumptions!B41-D30</f>
@@ -13634,7 +13899,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>680</v>
+        <v>705</v>
       </c>
       <c r="D32" s="32" t="n">
         <f aca="false">INT(D31/Assumptions!B65)</f>
@@ -13643,7 +13908,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>681</v>
+        <v>706</v>
       </c>
       <c r="D33" s="61" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -13652,7 +13917,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="67" t="s">
-        <v>607</v>
+        <v>632</v>
       </c>
       <c r="B34" s="67"/>
       <c r="C34" s="67"/>
@@ -13667,7 +13932,7 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="54" t="s">
-        <v>682</v>
+        <v>707</v>
       </c>
       <c r="B36" s="54"/>
       <c r="C36" s="54"/>
@@ -13748,7 +14013,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>683</v>
+        <v>708</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -13763,392 +14028,392 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="B4" s="58" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>684</v>
+        <v>709</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>685</v>
+        <v>710</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>686</v>
+        <v>711</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>687</v>
+        <v>712</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>688</v>
+        <v>713</v>
       </c>
       <c r="H4" s="58" t="s">
-        <v>689</v>
+        <v>714</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>690</v>
+        <v>715</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>691</v>
+        <v>716</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>692</v>
+        <v>717</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>693</v>
+        <v>718</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>694</v>
+        <v>719</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>695</v>
+        <v>720</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>696</v>
+        <v>721</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>697</v>
+        <v>722</v>
       </c>
       <c r="H5" s="70" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>698</v>
+        <v>723</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>699</v>
+        <v>724</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>700</v>
+        <v>725</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>701</v>
+        <v>726</v>
       </c>
       <c r="B6" s="59" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>702</v>
+        <v>727</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>704</v>
+        <v>729</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>705</v>
+        <v>730</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>706</v>
+        <v>731</v>
       </c>
       <c r="H6" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>707</v>
+        <v>732</v>
       </c>
       <c r="J6" s="59" t="s">
-        <v>708</v>
+        <v>733</v>
       </c>
       <c r="K6" s="59" t="s">
-        <v>709</v>
+        <v>734</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>710</v>
+        <v>735</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>711</v>
+        <v>736</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>712</v>
+        <v>737</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>713</v>
+        <v>738</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>714</v>
+        <v>739</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>715</v>
+        <v>740</v>
       </c>
       <c r="H7" s="70" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>716</v>
+        <v>741</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>717</v>
+        <v>742</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>718</v>
+        <v>743</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>719</v>
+        <v>744</v>
       </c>
       <c r="B8" s="59" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>720</v>
+        <v>745</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>721</v>
+        <v>746</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>722</v>
+        <v>747</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>723</v>
+        <v>748</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>724</v>
+        <v>749</v>
       </c>
       <c r="H8" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="J8" s="59" t="s">
-        <v>726</v>
+        <v>751</v>
       </c>
       <c r="K8" s="59" t="s">
-        <v>727</v>
+        <v>752</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>728</v>
+        <v>753</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>729</v>
+        <v>754</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>730</v>
+        <v>755</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>731</v>
+        <v>756</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>732</v>
+        <v>757</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>733</v>
+        <v>758</v>
       </c>
       <c r="H9" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>734</v>
+        <v>759</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>735</v>
+        <v>760</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>736</v>
+        <v>761</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>737</v>
+        <v>762</v>
       </c>
       <c r="B10" s="59" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>738</v>
+        <v>763</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>739</v>
+        <v>764</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>741</v>
+        <v>766</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>742</v>
+        <v>767</v>
       </c>
       <c r="H10" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>743</v>
+        <v>768</v>
       </c>
       <c r="J10" s="59" t="s">
-        <v>744</v>
+        <v>769</v>
       </c>
       <c r="K10" s="59" t="s">
-        <v>745</v>
+        <v>770</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>746</v>
+        <v>771</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>747</v>
+        <v>772</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>748</v>
+        <v>773</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>749</v>
+        <v>774</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>751</v>
+        <v>776</v>
       </c>
       <c r="H11" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>752</v>
+        <v>777</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>753</v>
+        <v>778</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>754</v>
+        <v>779</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>755</v>
+        <v>780</v>
       </c>
       <c r="B12" s="59" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>756</v>
+        <v>781</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>757</v>
+        <v>782</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>758</v>
+        <v>783</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>759</v>
+        <v>784</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>760</v>
+        <v>785</v>
       </c>
       <c r="H12" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>761</v>
+        <v>786</v>
       </c>
       <c r="J12" s="59" t="s">
-        <v>762</v>
+        <v>787</v>
       </c>
       <c r="K12" s="59" t="s">
-        <v>763</v>
+        <v>788</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>764</v>
+        <v>789</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>765</v>
+        <v>790</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>767</v>
+        <v>792</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>768</v>
+        <v>793</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>769</v>
+        <v>794</v>
       </c>
       <c r="H13" s="70" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>770</v>
+        <v>795</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>771</v>
+        <v>796</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>772</v>
+        <v>797</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>773</v>
+        <v>798</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>774</v>
+        <v>799</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>775</v>
+        <v>800</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>776</v>
+        <v>801</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>777</v>
+        <v>802</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>778</v>
+        <v>803</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>779</v>
+        <v>804</v>
       </c>
       <c r="H14" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>780</v>
+        <v>805</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>781</v>
+        <v>806</v>
       </c>
       <c r="K14" s="59" t="s">
-        <v>782</v>
+        <v>807</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>783</v>
+        <v>808</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
@@ -14160,10 +14425,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>784</v>
+        <v>809</v>
       </c>
       <c r="B17" s="71" t="s">
-        <v>785</v>
+        <v>810</v>
       </c>
       <c r="C17" s="71"/>
       <c r="D17" s="71"/>
@@ -14174,10 +14439,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>786</v>
+        <v>811</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>787</v>
+        <v>812</v>
       </c>
       <c r="C18" s="71"/>
       <c r="D18" s="71"/>
@@ -14188,10 +14453,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>788</v>
+        <v>813</v>
       </c>
       <c r="B19" s="71" t="s">
-        <v>789</v>
+        <v>814</v>
       </c>
       <c r="C19" s="71"/>
       <c r="D19" s="71"/>
@@ -14202,10 +14467,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>790</v>
+        <v>815</v>
       </c>
       <c r="B20" s="71" t="s">
-        <v>791</v>
+        <v>816</v>
       </c>
       <c r="C20" s="71"/>
       <c r="D20" s="71"/>
@@ -14216,10 +14481,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>792</v>
+        <v>817</v>
       </c>
       <c r="B21" s="71" t="s">
-        <v>793</v>
+        <v>818</v>
       </c>
       <c r="C21" s="71"/>
       <c r="D21" s="71"/>
@@ -14230,10 +14495,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>794</v>
+        <v>819</v>
       </c>
       <c r="B22" s="71" t="s">
-        <v>795</v>
+        <v>820</v>
       </c>
       <c r="C22" s="71"/>
       <c r="D22" s="71"/>
@@ -14244,10 +14509,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>796</v>
+        <v>821</v>
       </c>
       <c r="B23" s="71" t="s">
-        <v>797</v>
+        <v>822</v>
       </c>
       <c r="C23" s="71"/>
       <c r="D23" s="71"/>
@@ -14258,7 +14523,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="72" t="s">
-        <v>798</v>
+        <v>823</v>
       </c>
     </row>
   </sheetData>
@@ -14322,7 +14587,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>799</v>
+        <v>824</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -14336,42 +14601,42 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>800</v>
+        <v>825</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>801</v>
+        <v>826</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>802</v>
+        <v>827</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>805</v>
+        <v>830</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>806</v>
+        <v>831</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>807</v>
+        <v>832</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
@@ -14380,190 +14645,190 @@
         <v>96</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G5" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="I5" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>810</v>
+        <v>835</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>811</v>
+        <v>836</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>812</v>
+        <v>837</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>813</v>
+        <v>838</v>
       </c>
       <c r="D6" s="59" t="s">
         <v>96</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G6" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>806</v>
+        <v>831</v>
       </c>
       <c r="I6" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J6" s="59" t="s">
-        <v>815</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>816</v>
+        <v>841</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>817</v>
+        <v>842</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>813</v>
+        <v>838</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G7" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>811</v>
+        <v>836</v>
       </c>
       <c r="I7" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>818</v>
+        <v>843</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>819</v>
+        <v>844</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>820</v>
+        <v>845</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="D8" s="59" t="s">
         <v>96</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="G8" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="I8" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J8" s="59" t="s">
-        <v>823</v>
+        <v>848</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>824</v>
+        <v>849</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>825</v>
+        <v>850</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G9" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="I9" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>827</v>
+        <v>852</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>828</v>
+        <v>853</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>829</v>
+        <v>854</v>
       </c>
       <c r="D10" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G10" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="I10" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J10" s="59" t="s">
-        <v>830</v>
+        <v>855</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>698</v>
+        <v>723</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>831</v>
+        <v>856</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>23</v>
@@ -14572,30 +14837,30 @@
         <v>98</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G11" s="43" t="n">
         <v>12</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="I11" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>832</v>
+        <v>857</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>707</v>
+        <v>732</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>833</v>
+        <v>858</v>
       </c>
       <c r="C12" s="59" t="s">
         <v>23</v>
@@ -14604,30 +14869,30 @@
         <v>98</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G12" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>698</v>
+        <v>723</v>
       </c>
       <c r="I12" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J12" s="59" t="s">
-        <v>834</v>
+        <v>859</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>716</v>
+        <v>741</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>835</v>
+        <v>860</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>26</v>
@@ -14636,62 +14901,62 @@
         <v>98</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G13" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="I13" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>836</v>
+        <v>861</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>837</v>
+        <v>862</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>838</v>
+        <v>863</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="D14" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G14" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H14" s="59" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="I14" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>839</v>
+        <v>864</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>752</v>
+        <v>777</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>35</v>
@@ -14700,263 +14965,263 @@
         <v>98</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G15" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>837</v>
+        <v>862</v>
       </c>
       <c r="I15" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J15" s="27" t="s">
-        <v>841</v>
+        <v>866</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>842</v>
+        <v>867</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>843</v>
+        <v>868</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>685</v>
+        <v>710</v>
       </c>
       <c r="D16" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E16" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F16" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G16" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H16" s="59" t="s">
-        <v>698</v>
+        <v>723</v>
       </c>
       <c r="I16" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J16" s="59" t="s">
-        <v>844</v>
+        <v>869</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>624</v>
+        <v>649</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>845</v>
+        <v>870</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>846</v>
+        <v>871</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G17" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="I17" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>847</v>
+        <v>872</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>848</v>
+        <v>873</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>849</v>
+        <v>874</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="D18" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="G18" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H18" s="59" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="I18" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J18" s="59" t="s">
-        <v>851</v>
+        <v>876</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>852</v>
+        <v>877</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>825</v>
+        <v>850</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G19" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="I19" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>853</v>
+        <v>878</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>582</v>
+        <v>607</v>
       </c>
       <c r="B20" s="59" t="s">
+        <v>879</v>
+      </c>
+      <c r="C20" s="59" t="s">
         <v>854</v>
-      </c>
-      <c r="C20" s="59" t="s">
-        <v>829</v>
       </c>
       <c r="D20" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E20" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F20" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G20" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>698</v>
+        <v>723</v>
       </c>
       <c r="I20" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J20" s="59" t="s">
-        <v>855</v>
+        <v>880</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>856</v>
+        <v>881</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>857</v>
+        <v>882</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>858</v>
+        <v>883</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G21" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="I21" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J21" s="27" t="s">
-        <v>859</v>
+        <v>884</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="59" t="s">
-        <v>860</v>
+        <v>885</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>861</v>
+        <v>886</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>685</v>
+        <v>710</v>
       </c>
       <c r="D22" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F22" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G22" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="59" t="s">
-        <v>842</v>
+        <v>867</v>
       </c>
       <c r="I22" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J22" s="59" t="s">
-        <v>862</v>
+        <v>887</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>863</v>
+        <v>888</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>864</v>
+        <v>889</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>865</v>
+        <v>890</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>866</v>
+        <v>891</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
@@ -14965,117 +15230,117 @@
         <v>3</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>819</v>
+        <v>844</v>
       </c>
       <c r="I23" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>867</v>
+        <v>892</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="59" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>587</v>
+        <v>612</v>
       </c>
       <c r="C24" s="59" t="s">
-        <v>829</v>
+        <v>854</v>
       </c>
       <c r="D24" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E24" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F24" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G24" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H24" s="59" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="I24" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J24" s="59" t="s">
-        <v>868</v>
+        <v>893</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>780</v>
+        <v>805</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>775</v>
+        <v>800</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>829</v>
+        <v>854</v>
       </c>
       <c r="D25" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G25" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="I25" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J25" s="27" t="s">
-        <v>869</v>
+        <v>894</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="59" t="s">
-        <v>870</v>
+        <v>895</v>
       </c>
       <c r="B26" s="59" t="s">
-        <v>871</v>
+        <v>896</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>829</v>
+        <v>854</v>
       </c>
       <c r="D26" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E26" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F26" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G26" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="I26" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J26" s="59" t="s">
-        <v>872</v>
+        <v>897</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>734</v>
+        <v>759</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>729</v>
+        <v>754</v>
       </c>
       <c r="C27" s="27" t="s">
         <v>29</v>
@@ -15084,30 +15349,30 @@
         <v>100</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G27" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>837</v>
+        <v>862</v>
       </c>
       <c r="I27" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J27" s="27" t="s">
-        <v>873</v>
+        <v>898</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="59" t="s">
-        <v>743</v>
+        <v>768</v>
       </c>
       <c r="B28" s="59" t="s">
-        <v>874</v>
+        <v>899</v>
       </c>
       <c r="C28" s="59" t="s">
         <v>32</v>
@@ -15116,30 +15381,30 @@
         <v>100</v>
       </c>
       <c r="E28" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F28" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G28" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H28" s="59" t="s">
-        <v>837</v>
+        <v>862</v>
       </c>
       <c r="I28" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J28" s="59" t="s">
-        <v>875</v>
+        <v>900</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>876</v>
+        <v>901</v>
       </c>
       <c r="C29" s="27" t="s">
         <v>26</v>
@@ -15148,94 +15413,94 @@
         <v>100</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>866</v>
+        <v>891</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G29" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>716</v>
+        <v>741</v>
       </c>
       <c r="I29" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>877</v>
+        <v>902</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="59" t="s">
-        <v>770</v>
+        <v>795</v>
       </c>
       <c r="B30" s="59" t="s">
-        <v>878</v>
+        <v>903</v>
       </c>
       <c r="C30" s="59" t="s">
-        <v>825</v>
+        <v>850</v>
       </c>
       <c r="D30" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F30" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G30" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="59" t="s">
-        <v>716</v>
+        <v>741</v>
       </c>
       <c r="I30" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J30" s="59" t="s">
-        <v>879</v>
+        <v>904</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="s">
-        <v>635</v>
+        <v>660</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>880</v>
+        <v>905</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="D31" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G31" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="I31" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J31" s="27" t="s">
-        <v>881</v>
+        <v>906</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="59" t="s">
-        <v>882</v>
+        <v>907</v>
       </c>
       <c r="B32" s="59" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="C32" s="59" t="s">
         <v>35</v>
@@ -15244,30 +15509,30 @@
         <v>100</v>
       </c>
       <c r="E32" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F32" s="59" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="G32" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H32" s="59" t="s">
-        <v>752</v>
+        <v>777</v>
       </c>
       <c r="I32" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J32" s="59" t="s">
-        <v>884</v>
+        <v>909</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>761</v>
+        <v>786</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>885</v>
+        <v>910</v>
       </c>
       <c r="C33" s="27" t="s">
         <v>35</v>
@@ -15276,487 +15541,487 @@
         <v>100</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G33" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>752</v>
+        <v>777</v>
       </c>
       <c r="I33" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J33" s="27" t="s">
-        <v>886</v>
+        <v>911</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="59" t="s">
-        <v>887</v>
+        <v>912</v>
       </c>
       <c r="B34" s="59" t="s">
-        <v>888</v>
+        <v>913</v>
       </c>
       <c r="C34" s="59" t="s">
-        <v>889</v>
+        <v>914</v>
       </c>
       <c r="D34" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F34" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G34" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H34" s="59" t="s">
-        <v>635</v>
+        <v>660</v>
       </c>
       <c r="I34" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J34" s="59" t="s">
-        <v>890</v>
+        <v>915</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>891</v>
+        <v>916</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>892</v>
+        <v>917</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>889</v>
+        <v>914</v>
       </c>
       <c r="D35" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G35" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>887</v>
+        <v>912</v>
       </c>
       <c r="I35" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J35" s="27" t="s">
-        <v>893</v>
+        <v>918</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="59" t="s">
-        <v>894</v>
+        <v>919</v>
       </c>
       <c r="B36" s="59" t="s">
-        <v>895</v>
+        <v>920</v>
       </c>
       <c r="C36" s="59" t="s">
-        <v>889</v>
+        <v>914</v>
       </c>
       <c r="D36" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F36" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G36" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H36" s="59" t="s">
-        <v>891</v>
+        <v>916</v>
       </c>
       <c r="I36" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J36" s="59" t="s">
-        <v>896</v>
+        <v>921</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="27" t="s">
-        <v>897</v>
+        <v>922</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>898</v>
+        <v>923</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>899</v>
+        <v>924</v>
       </c>
       <c r="D37" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>866</v>
+        <v>891</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G37" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H37" s="27" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="I37" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J37" s="27" t="s">
-        <v>900</v>
+        <v>925</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="59" t="s">
-        <v>901</v>
+        <v>926</v>
       </c>
       <c r="B38" s="59" t="s">
-        <v>902</v>
+        <v>927</v>
       </c>
       <c r="C38" s="59" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="D38" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="59" t="s">
-        <v>866</v>
+        <v>891</v>
       </c>
       <c r="F38" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G38" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="59" t="s">
-        <v>897</v>
+        <v>922</v>
       </c>
       <c r="I38" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J38" s="59" t="s">
-        <v>903</v>
+        <v>928</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="27" t="s">
-        <v>627</v>
+        <v>652</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>904</v>
+        <v>929</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>846</v>
+        <v>871</v>
       </c>
       <c r="D39" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G39" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="I39" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J39" s="27" t="s">
-        <v>905</v>
+        <v>930</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="59" t="s">
-        <v>631</v>
+        <v>656</v>
       </c>
       <c r="B40" s="59" t="s">
-        <v>628</v>
+        <v>653</v>
       </c>
       <c r="C40" s="59" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="D40" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F40" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G40" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H40" s="59" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="I40" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J40" s="59" t="s">
-        <v>906</v>
+        <v>931</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>639</v>
+        <v>664</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>907</v>
+        <v>932</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="D41" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G41" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>635</v>
+        <v>660</v>
       </c>
       <c r="I41" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J41" s="27" t="s">
-        <v>908</v>
+        <v>933</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="59" t="s">
-        <v>909</v>
+        <v>934</v>
       </c>
       <c r="B42" s="59" t="s">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="C42" s="59" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="D42" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="59" t="s">
-        <v>866</v>
+        <v>891</v>
       </c>
       <c r="F42" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G42" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="59" t="s">
-        <v>901</v>
+        <v>926</v>
       </c>
       <c r="I42" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J42" s="59" t="s">
-        <v>911</v>
+        <v>936</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
-        <v>912</v>
+        <v>937</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>913</v>
+        <v>938</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>914</v>
+        <v>939</v>
       </c>
       <c r="D43" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>914</v>
+        <v>939</v>
       </c>
       <c r="G43" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H43" s="27" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="I43" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J43" s="27" t="s">
-        <v>915</v>
+        <v>940</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="59" t="s">
-        <v>916</v>
+        <v>941</v>
       </c>
       <c r="B44" s="59" t="s">
-        <v>917</v>
+        <v>942</v>
       </c>
       <c r="C44" s="59" t="s">
-        <v>813</v>
+        <v>838</v>
       </c>
       <c r="D44" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E44" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F44" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G44" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H44" s="59" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="I44" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J44" s="59" t="s">
-        <v>918</v>
+        <v>943</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="27" t="s">
-        <v>919</v>
+        <v>944</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>920</v>
+        <v>945</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="D45" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G45" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H45" s="27" t="s">
-        <v>848</v>
+        <v>873</v>
       </c>
       <c r="I45" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J45" s="27" t="s">
-        <v>921</v>
+        <v>946</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="59" t="s">
-        <v>922</v>
+        <v>947</v>
       </c>
       <c r="B46" s="59" t="s">
-        <v>923</v>
+        <v>948</v>
       </c>
       <c r="C46" s="59" t="s">
-        <v>685</v>
+        <v>710</v>
       </c>
       <c r="D46" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E46" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F46" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G46" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H46" s="59" t="s">
-        <v>842</v>
+        <v>867</v>
       </c>
       <c r="I46" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J46" s="59" t="s">
-        <v>924</v>
+        <v>949</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
-        <v>925</v>
+        <v>950</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>926</v>
+        <v>951</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>899</v>
+        <v>924</v>
       </c>
       <c r="D47" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G47" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H47" s="27" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="I47" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J47" s="27" t="s">
-        <v>927</v>
+        <v>952</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="59" t="s">
-        <v>928</v>
+        <v>953</v>
       </c>
       <c r="B48" s="59" t="s">
-        <v>929</v>
+        <v>954</v>
       </c>
       <c r="C48" s="59" t="s">
-        <v>589</v>
+        <v>614</v>
       </c>
       <c r="D48" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E48" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F48" s="59" t="s">
         <v>100</v>
@@ -15765,62 +16030,62 @@
         <v>3</v>
       </c>
       <c r="H48" s="59" t="s">
-        <v>891</v>
+        <v>916</v>
       </c>
       <c r="I48" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J48" s="59" t="s">
-        <v>930</v>
+        <v>955</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="27" t="s">
-        <v>931</v>
+        <v>956</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>932</v>
+        <v>957</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>933</v>
+        <v>958</v>
       </c>
       <c r="D49" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>866</v>
+        <v>891</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G49" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H49" s="27" t="s">
-        <v>919</v>
+        <v>944</v>
       </c>
       <c r="I49" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J49" s="27" t="s">
-        <v>934</v>
+        <v>959</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="59" t="s">
-        <v>935</v>
+        <v>960</v>
       </c>
       <c r="B50" s="59" t="s">
-        <v>936</v>
+        <v>961</v>
       </c>
       <c r="C50" s="59" t="s">
-        <v>937</v>
+        <v>962</v>
       </c>
       <c r="D50" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E50" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F50" s="59" t="s">
         <v>100</v>
@@ -15829,181 +16094,181 @@
         <v>4</v>
       </c>
       <c r="H50" s="59" t="s">
-        <v>856</v>
+        <v>881</v>
       </c>
       <c r="I50" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J50" s="59" t="s">
-        <v>938</v>
+        <v>963</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
-        <v>939</v>
+        <v>964</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>940</v>
+        <v>965</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>941</v>
+        <v>966</v>
       </c>
       <c r="D51" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G51" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H51" s="27" t="s">
-        <v>870</v>
+        <v>895</v>
       </c>
       <c r="I51" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J51" s="27" t="s">
-        <v>942</v>
+        <v>967</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="59" t="s">
-        <v>943</v>
+        <v>968</v>
       </c>
       <c r="B52" s="59" t="s">
-        <v>944</v>
+        <v>969</v>
       </c>
       <c r="C52" s="59" t="s">
-        <v>941</v>
+        <v>966</v>
       </c>
       <c r="D52" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E52" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F52" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G52" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H52" s="59" t="s">
-        <v>761</v>
+        <v>786</v>
       </c>
       <c r="I52" s="70" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J52" s="59" t="s">
-        <v>945</v>
+        <v>970</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="27" t="s">
-        <v>615</v>
+        <v>640</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>946</v>
+        <v>971</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>941</v>
+        <v>966</v>
       </c>
       <c r="D53" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F53" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G53" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H53" s="27" t="s">
-        <v>943</v>
+        <v>968</v>
       </c>
       <c r="I53" s="70" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="J53" s="27" t="s">
-        <v>947</v>
+        <v>972</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="59" t="s">
-        <v>948</v>
+        <v>973</v>
       </c>
       <c r="B54" s="59" t="s">
-        <v>949</v>
+        <v>974</v>
       </c>
       <c r="C54" s="59" t="s">
-        <v>829</v>
+        <v>854</v>
       </c>
       <c r="D54" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E54" s="59" t="s">
-        <v>866</v>
+        <v>891</v>
       </c>
       <c r="F54" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G54" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H54" s="59" t="s">
-        <v>870</v>
+        <v>895</v>
       </c>
       <c r="I54" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J54" s="59" t="s">
-        <v>950</v>
+        <v>975</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
-        <v>951</v>
+        <v>976</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>952</v>
+        <v>977</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="D55" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>953</v>
+        <v>978</v>
       </c>
       <c r="F55" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G55" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>894</v>
+        <v>919</v>
       </c>
       <c r="I55" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J55" s="27" t="s">
-        <v>954</v>
+        <v>979</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="59" t="s">
-        <v>955</v>
+        <v>980</v>
       </c>
       <c r="B56" s="59" t="s">
-        <v>956</v>
+        <v>981</v>
       </c>
       <c r="C56" s="59" t="s">
         <v>26</v>
@@ -16012,359 +16277,359 @@
         <v>102</v>
       </c>
       <c r="E56" s="59" t="s">
-        <v>953</v>
+        <v>978</v>
       </c>
       <c r="F56" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G56" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H56" s="59" t="s">
-        <v>716</v>
+        <v>741</v>
       </c>
       <c r="I56" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J56" s="59" t="s">
-        <v>957</v>
+        <v>982</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
-        <v>958</v>
+        <v>983</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>959</v>
+        <v>984</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>899</v>
+        <v>924</v>
       </c>
       <c r="D57" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G57" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H57" s="27" t="s">
-        <v>939</v>
+        <v>964</v>
       </c>
       <c r="I57" s="70" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="J57" s="27" t="s">
-        <v>960</v>
+        <v>985</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="59" t="s">
-        <v>961</v>
+        <v>986</v>
       </c>
       <c r="B58" s="59" t="s">
-        <v>962</v>
+        <v>987</v>
       </c>
       <c r="C58" s="59" t="s">
-        <v>685</v>
+        <v>710</v>
       </c>
       <c r="D58" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E58" s="59" t="s">
-        <v>866</v>
+        <v>891</v>
       </c>
       <c r="F58" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G58" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H58" s="59" t="s">
-        <v>842</v>
+        <v>867</v>
       </c>
       <c r="I58" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J58" s="59" t="s">
-        <v>963</v>
+        <v>988</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="27" t="s">
-        <v>964</v>
+        <v>989</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>965</v>
+        <v>990</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>825</v>
+        <v>850</v>
       </c>
       <c r="D59" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E59" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G59" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H59" s="27" t="s">
-        <v>856</v>
+        <v>881</v>
       </c>
       <c r="I59" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J59" s="27" t="s">
-        <v>966</v>
+        <v>991</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="59" t="s">
-        <v>967</v>
+        <v>992</v>
       </c>
       <c r="B60" s="59" t="s">
-        <v>968</v>
+        <v>993</v>
       </c>
       <c r="C60" s="59" t="s">
-        <v>969</v>
+        <v>994</v>
       </c>
       <c r="D60" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E60" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F60" s="59" t="s">
-        <v>969</v>
+        <v>994</v>
       </c>
       <c r="G60" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H60" s="59" t="s">
-        <v>958</v>
+        <v>983</v>
       </c>
       <c r="I60" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J60" s="59" t="s">
-        <v>970</v>
+        <v>995</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="27" t="s">
-        <v>971</v>
+        <v>996</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>972</v>
+        <v>997</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>899</v>
+        <v>924</v>
       </c>
       <c r="D61" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G61" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H61" s="27" t="s">
-        <v>958</v>
+        <v>983</v>
       </c>
       <c r="I61" s="70" t="s">
-        <v>822</v>
+        <v>851</v>
       </c>
       <c r="J61" s="27" t="s">
-        <v>973</v>
+        <v>998</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="59" t="s">
-        <v>974</v>
+        <v>999</v>
       </c>
       <c r="B62" s="59" t="s">
-        <v>975</v>
+        <v>1000</v>
       </c>
       <c r="C62" s="59" t="s">
-        <v>685</v>
+        <v>710</v>
       </c>
       <c r="D62" s="59" t="s">
         <v>104</v>
       </c>
       <c r="E62" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F62" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G62" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H62" s="59" t="s">
-        <v>842</v>
+        <v>867</v>
       </c>
       <c r="I62" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J62" s="59" t="s">
-        <v>976</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="27" t="s">
-        <v>977</v>
+        <v>1002</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>978</v>
+        <v>1003</v>
       </c>
       <c r="C63" s="27" t="s">
-        <v>979</v>
+        <v>1004</v>
       </c>
       <c r="D63" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E63" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G63" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H63" s="27" t="s">
-        <v>958</v>
+        <v>983</v>
       </c>
       <c r="I63" s="70" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="J63" s="27" t="s">
-        <v>980</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="59" t="s">
-        <v>981</v>
+        <v>1006</v>
       </c>
       <c r="B64" s="59" t="s">
-        <v>982</v>
+        <v>1007</v>
       </c>
       <c r="C64" s="59" t="s">
-        <v>933</v>
+        <v>958</v>
       </c>
       <c r="D64" s="59" t="s">
         <v>104</v>
       </c>
       <c r="E64" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F64" s="59" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G64" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H64" s="59" t="s">
-        <v>971</v>
+        <v>996</v>
       </c>
       <c r="I64" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J64" s="59" t="s">
-        <v>983</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="27" t="s">
-        <v>984</v>
+        <v>1009</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>985</v>
+        <v>1010</v>
       </c>
       <c r="C65" s="27" t="s">
-        <v>813</v>
+        <v>838</v>
       </c>
       <c r="D65" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E65" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G65" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H65" s="27" t="s">
-        <v>958</v>
+        <v>983</v>
       </c>
       <c r="I65" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J65" s="27" t="s">
-        <v>986</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="59" t="s">
-        <v>987</v>
+        <v>1012</v>
       </c>
       <c r="B66" s="59" t="s">
-        <v>988</v>
+        <v>1013</v>
       </c>
       <c r="C66" s="59" t="s">
-        <v>865</v>
+        <v>890</v>
       </c>
       <c r="D66" s="59" t="s">
         <v>104</v>
       </c>
       <c r="E66" s="59" t="s">
-        <v>866</v>
+        <v>891</v>
       </c>
       <c r="F66" s="59" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G66" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H66" s="59" t="s">
-        <v>916</v>
+        <v>941</v>
       </c>
       <c r="I66" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J66" s="59" t="s">
-        <v>989</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="27" t="s">
-        <v>990</v>
+        <v>1015</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>991</v>
+        <v>1016</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>865</v>
+        <v>890</v>
       </c>
       <c r="D67" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F67" s="27" t="s">
         <v>100</v>
@@ -16373,30 +16638,30 @@
         <v>5</v>
       </c>
       <c r="H67" s="27" t="s">
-        <v>971</v>
+        <v>996</v>
       </c>
       <c r="I67" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J67" s="27" t="s">
-        <v>992</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="59" t="s">
-        <v>993</v>
+        <v>1018</v>
       </c>
       <c r="B68" s="59" t="s">
-        <v>994</v>
+        <v>1019</v>
       </c>
       <c r="C68" s="59" t="s">
-        <v>865</v>
+        <v>890</v>
       </c>
       <c r="D68" s="59" t="s">
         <v>106</v>
       </c>
       <c r="E68" s="59" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F68" s="59" t="s">
         <v>100</v>
@@ -16405,45 +16670,45 @@
         <v>1</v>
       </c>
       <c r="H68" s="59" t="s">
-        <v>990</v>
+        <v>1015</v>
       </c>
       <c r="I68" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J68" s="59" t="s">
-        <v>995</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="27" t="s">
-        <v>996</v>
+        <v>1021</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>997</v>
+        <v>1022</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>865</v>
+        <v>890</v>
       </c>
       <c r="D69" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E69" s="27" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F69" s="27" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="G69" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H69" s="27" t="s">
-        <v>984</v>
+        <v>1009</v>
       </c>
       <c r="I69" s="70" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="J69" s="27" t="s">
-        <v>998</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16580,7 +16845,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D82" s="73" t="s">
-        <v>999</v>
+        <v>1024</v>
       </c>
       <c r="E82" s="73"/>
       <c r="F82" s="73"/>
@@ -16591,7 +16856,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D83" s="74" t="s">
-        <v>1000</v>
+        <v>1025</v>
       </c>
       <c r="E83" s="74"/>
       <c r="F83" s="74"/>
@@ -16602,7 +16867,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D84" s="74" t="s">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="E84" s="74"/>
       <c r="F84" s="74"/>
@@ -16613,29 +16878,29 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D85" s="74" t="s">
-        <v>1002</v>
+        <v>1027</v>
       </c>
       <c r="E85" s="74"/>
       <c r="F85" s="74"/>
       <c r="G85" s="32" t="n">
         <f aca="false">SUMIF(I$5:I$80,"Done",G$5:G$80)</f>
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D86" s="74" t="s">
-        <v>1003</v>
+        <v>1028</v>
       </c>
       <c r="E86" s="74"/>
       <c r="F86" s="74"/>
       <c r="G86" s="75" t="n">
         <f aca="false">IF(G83=0,0,SUMIFS(G$5:G$80,E$5:E$80,"Must",I$5:I$80,"Done")/G83)</f>
-        <v>0.274509803921569</v>
+        <v>0.320261437908497</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>1004</v>
+        <v>1029</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -16649,25 +16914,25 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>802</v>
+        <v>827</v>
       </c>
       <c r="B90" s="9"/>
       <c r="C90" s="9" t="s">
-        <v>1005</v>
+        <v>1030</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>1006</v>
+        <v>1031</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>1007</v>
+        <v>1032</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>1008</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="76" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="B91" s="76"/>
       <c r="C91" s="32" t="n">
@@ -16689,7 +16954,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="76" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="B92" s="76"/>
       <c r="C92" s="32" t="n">
@@ -16711,7 +16976,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="76" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="B93" s="76"/>
       <c r="C93" s="32" t="n">
@@ -16733,7 +16998,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="76" t="s">
-        <v>914</v>
+        <v>939</v>
       </c>
       <c r="B94" s="76"/>
       <c r="C94" s="32" t="n">
@@ -16755,7 +17020,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="76" t="s">
-        <v>969</v>
+        <v>994</v>
       </c>
       <c r="B95" s="76"/>
       <c r="C95" s="32" t="n">
@@ -16799,7 +17064,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="73" t="s">
-        <v>1009</v>
+        <v>1034</v>
       </c>
       <c r="B97" s="73"/>
       <c r="C97" s="21" t="n">
@@ -16825,16 +17090,16 @@
       </c>
       <c r="B99" s="29"/>
       <c r="C99" s="9" t="s">
-        <v>1005</v>
+        <v>1030</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>1010</v>
+        <v>1035</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>1007</v>
+        <v>1032</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>1008</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16977,7 +17242,7 @@
     </row>
     <row r="107" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="54" t="s">
-        <v>1011</v>
+        <v>1036</v>
       </c>
       <c r="B107" s="54"/>
       <c r="C107" s="54"/>
@@ -17111,7 +17376,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1012</v>
+        <v>1037</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -17129,22 +17394,22 @@
         <v>6</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1013</v>
+        <v>1038</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1014</v>
+        <v>1039</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>1015</v>
+        <v>1040</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>1016</v>
+        <v>1041</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>1017</v>
+        <v>1042</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>1018</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17165,16 +17430,16 @@
         <v>46383</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>1019</v>
+        <v>1044</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>1020</v>
+        <v>1045</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1021</v>
+        <v>1046</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>1022</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17195,16 +17460,16 @@
         <v>46453</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>1023</v>
+        <v>1048</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>1024</v>
+        <v>1049</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17225,16 +17490,16 @@
         <v>46579</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>1027</v>
+        <v>1052</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>1028</v>
+        <v>1053</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1029</v>
+        <v>1054</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17255,16 +17520,16 @@
         <v>46621</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>1032</v>
+        <v>1057</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>1033</v>
+        <v>1058</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>1034</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17285,16 +17550,16 @@
         <v>46663</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1035</v>
+        <v>1060</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>1036</v>
+        <v>1061</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1037</v>
+        <v>1062</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>1038</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17315,21 +17580,21 @@
         <v>46691</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>1039</v>
+        <v>1064</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>514</v>
+        <v>539</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>1040</v>
+        <v>1065</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>1041</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>1042</v>
+        <v>1067</v>
       </c>
       <c r="B12" s="82" t="n">
         <f aca="false">D10</f>
@@ -17339,7 +17604,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>1043</v>
+        <v>1068</v>
       </c>
       <c r="B13" s="83" t="n">
         <f aca="false">B12-Assumptions!B7</f>
@@ -17349,7 +17614,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>1044</v>
+        <v>1069</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="24"/>
@@ -17361,7 +17626,7 @@
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
-        <v>1045</v>
+        <v>1070</v>
       </c>
       <c r="B15" s="54"/>
       <c r="C15" s="54"/>
@@ -17373,7 +17638,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="54" t="s">
-        <v>1046</v>
+        <v>1071</v>
       </c>
       <c r="B16" s="54"/>
       <c r="C16" s="54"/>
@@ -17453,7 +17718,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1047</v>
+        <v>1072</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -17487,13 +17752,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1048</v>
+        <v>1073</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1013</v>
+        <v>1038</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1014</v>
+        <v>1039</v>
       </c>
       <c r="D4" s="84" t="n">
         <v>1</v>
@@ -17678,7 +17943,7 @@
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>1049</v>
+        <v>1074</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -17925,7 +18190,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -19696,7 +19961,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>1051</v>
+        <v>1076</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -19943,7 +20208,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>1052</v>
+        <v>1077</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>

--- a/docs/Vinland_Game_Development_Plan.xlsx
+++ b/docs/Vinland_Game_Development_Plan.xlsx
@@ -23,7 +23,9 @@
     <sheet name="Risks" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="Content" sheetId="14" state="visible" r:id="rId16"/>
     <sheet name="Release" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="Revisions" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="Regression" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="Balance" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="Revisions" sheetId="18" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Assumptions!$1:$2</definedName>
@@ -41,7 +43,7 @@
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">Pillars!$1:$3</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Pillars!$A$4:$E$12</definedName>
     <definedName function="false" hidden="false" localSheetId="14" name="_xlnm.Print_Titles" vbProcedure="false">Release!$1:$4</definedName>
-    <definedName function="false" hidden="false" localSheetId="15" name="_xlnm.Print_Titles" vbProcedure="false">Revisions!$1:$4</definedName>
+    <definedName function="false" hidden="false" localSheetId="17" name="_xlnm.Print_Titles" vbProcedure="false">Revisions!$1:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="12" name="_xlnm.Print_Titles" vbProcedure="false">Risks!$1:$4</definedName>
     <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">Risks!$A$4:$J$20</definedName>
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Titles" vbProcedure="false">Schedule!$1:$4</definedName>
@@ -86,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="1387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2429" uniqueCount="1529">
   <si>
     <t xml:space="preserve">VINLAND</t>
   </si>
@@ -1558,6 +1560,12 @@
     <t xml:space="preserve">Score (F31): two cargoes and one relief ship is the full win (P7)</t>
   </si>
   <si>
+    <t xml:space="preserve">Most deaths for the full saga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score (F31, F55): more dead and the saga is dear-bought; set from the balance sweep</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pillars, fantasy, clocks, and the win</t>
   </si>
   <si>
@@ -3061,7 +3069,7 @@
     <t xml:space="preserve">Economy tuning pass from run logs</t>
   </si>
   <si>
-    <t xml:space="preserve">Knob changes made on Assumptions, backed by logged runs.</t>
+    <t xml:space="preserve">Knob changes made on Assumptions, backed by logged runs.  [First pass: balance sweep of whole runs by three player models (sheet Balance, docs/balance/fullrun_sweep.csv); full saga now also needs few deaths; regression test holds the spread. Retune from real play logs after playtest 2.]</t>
   </si>
   <si>
     <t xml:space="preserve">F64</t>
@@ -3073,7 +3081,7 @@
     <t xml:space="preserve">QA</t>
   </si>
   <si>
-    <t xml:space="preserve">Each gate has a written pass list run on the tagged build.</t>
+    <t xml:space="preserve">Each gate has a written pass list run on the tagged build.  [Built: Regression sheet with 27 pass items across G1 to G5 (automated and manual); tools/regression.sh runs every automated pass and writes docs/regression/&lt;date&gt;_&lt;commit&gt;.txt. Git tags cannot be pushed from the build machine, so reports name the commit.]</t>
   </si>
   <si>
     <t xml:space="preserve">F31</t>
@@ -3523,7 +3531,7 @@
     <t xml:space="preserve">Three-summer run completable. Qualified ending and full ending both reachable.</t>
   </si>
   <si>
-    <t xml:space="preserve">Alpha save set</t>
+    <t xml:space="preserve">Alpha save set; Regression sheet; Balance sheet</t>
   </si>
   <si>
     <t xml:space="preserve">F24, F25, F26, F27, F28, F29, F30, F54, F55, F64</t>
@@ -4084,6 +4092,408 @@
     <t xml:space="preserve">Store page lists remaps, no-haptic mode, hold-to-repeat, and text size.</t>
   </si>
   <si>
+    <t xml:space="preserve">Regression pass list per gate  ·  F64: each gate has a written pass list run on the tagged build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated items run with tools/regression.sh (full suite, novice sweep, saves, balance sweep, boot smoke) and write docs/regression/&lt;date&gt;_&lt;commit&gt;.txt. Manual items are played on the same build and ticked here with the report name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How it is checked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result on this build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leave a fjord and sail every leg to the Strait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slice: plays from Eriksfjord through the first winter to the second spring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-18_7975193.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A missed fix walks the ship downwind; partial halves, clean refunds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drift: clean refunds, partial halves, none walks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star ring winnable in every sky; mislevelling punished</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot night: clear / twilight / fog / storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fish on the hand line; a joint seats; the hold changes because of them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slice: every G1 gate item is met by a played run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F05, F07, F01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A first-time player passes each slice mini-game on Forgiving (85%+) and Standard (60%+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">novice sweep: ring, line, joint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play the slice on a gamepad: leave Eriksfjord, take a ring fix, fish once, seat one joint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 minutes on the Windows build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passed 17 Oct 2026 (playtest: "much better")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web build boots in a browser and the ring plays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">itch.io web zip in Chrome; console free of errors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass (automated browser check this build)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every verb is in and practicable from the title (Y, 1 to 8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_minigames, test_work_games, novice sweep (9 games)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F09-F15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The market can break: fear cap stops trade, raids follow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market: at the fear cap no one comes to trade; ... raided now and then</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F19-F21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hay can kill the herd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">camp year: forgetting hay costs the herd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The slipway can spill a log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F18 lift and slipway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not built yet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saves: watch-level at sea, day-level ashore, three slots, exact replay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">save runner; return: a saved voyage home keeps its course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pause and options: difficulty, vibration, prompts, save and quit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">options: ... (10 checks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfits and named roles change the hold, the kit and the verbs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outfits / crew / roles (47 checks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F22, F23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitors stay neutral placeholders until the consultant review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the market screen: no clothing, boats or dialogue art beyond grey shapes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass (placeholder only); review pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each mini-game played once from the title on keyboard and on a pad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice keys Y, 1 to 8; note any that feel unfair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due at playtest 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A three-summer run is completable from outfit to score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">full run: every outfit goes outfit to score (8 of 8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualified ending and full ending both reachable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">score: full saga / home and rich / dear-bought / camp without a ship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance: planner 75%+ full saga, average 15-80%, careless 10% or less</t>
+  </si>
+  <si>
+    <t xml:space="preserve">balance sweep (240 runs), balance runner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The return gate, the appraisal, recruitment, the relief and the reunion work in the scenes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">camp scene / voyage scene / homecoming scene / relief scene checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F24-F26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play one whole run on Forgiving with a gamepad and note the score and ending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About 3 to 4 hours; Continue from the title between sittings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every verb completable without a gamepad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyboard-only run of each mini-game</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partly: keyboard prompts in place; F54 pass due</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remaps work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No-haptic fallback taught: every tell has a visual twin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vibration off in options; play each mini-game</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visual twins in place; teaching pass due</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F32, F40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No must-ship bug open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bug list empty of Must rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ship build exports for Windows and the web</t>
+  </si>
+  <si>
+    <t xml:space="preserve">export presets build in CI-like step (tools in README)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trailer, store copy, day-one notes in the release folder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance sweep  ·  F55: knob changes backed by logged runs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole three-summer runs played by three player models (tests/balance.gd), 20 seeds per outfit. Every run is in docs/balance/fullrun_sweep.csv. Re-run: godot --headless --path . res://tests/balance_runner.tscn -- --n=20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Player model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full saga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dear-bought</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other endings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average deaths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average timber home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All outfits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A camp at the Strait 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stranded 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A camp at the Strait 1, stranded 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Careless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lost homeward 2, stranded 3, A camp at the Strait 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lost homeward 1, A camp at the Strait 3, stranded 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A camp at the Strait 2, lost homeward 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lost homeward 3, stranded 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lost homeward 7, stranded 11, A camp at the Strait 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planner: plans by season, hay sized to the herd, careful captain, sails the day the gate opens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average: uneven hands, three haymakers, little drying, average captain, sails weeks late, buys nothing extra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Careless: summer-only camp, no hay, no rack, reckless captain, sails late</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changes made from this sweep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First sweep (8 seeds): planner 100%, average 97%, careless 78% reached the full saga: the arc was too easy to close.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full saga now also needs no more than "Most deaths for the full saga" (Assumptions, 3). The whole arc with more dead is "A dear-bought saga", scored and named, never scolded (P8).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camp running itself while you are away: hay sized to the herd (the first pass lost whole herds over the second winter).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Targets held by the regression test: planner 75%+ full saga, average 15-80%, careless 10% or less; scores and deaths ordered planner &gt; average &gt; careless.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Revision log  ·  what changed in this pass and why</t>
   </si>
   <si>
@@ -4247,6 +4657,24 @@
   </si>
   <si>
     <t xml:space="preserve">A run now goes from outfit to score: three summers, two cargoes, one relief.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance, Assumptions, Backlog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Balance sheet from a 240-run sweep; "Most deaths for the full saga" knob; F55 in progress.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The first sweep showed even careless play reaching the full saga.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression, Milestones, Backlog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Regression sheet (F64 done); G3 in progress.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every gate now has a written pass list and a script that runs the automated half.</t>
   </si>
 </sst>
 </file>
@@ -4273,7 +4701,7 @@
     <numFmt numFmtId="180" formatCode=";;;"/>
     <numFmt numFmtId="181" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -4448,6 +4876,13 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -4579,7 +5014,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="113">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4986,6 +5421,42 @@
     </xf>
     <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -5455,11 +5926,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="62289495"/>
-        <c:axId val="84427033"/>
+        <c:axId val="45485430"/>
+        <c:axId val="74301498"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="62289495"/>
+        <c:axId val="45485430"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5491,7 +5962,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84427033"/>
+        <c:crossAx val="74301498"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5499,7 +5970,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84427033"/>
+        <c:axId val="74301498"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5575,7 +6046,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62289495"/>
+        <c:crossAx val="45485430"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5614,9 +6085,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>738000</xdr:colOff>
+      <xdr:colOff>736920</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>54360</xdr:rowOff>
+      <xdr:rowOff>53280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5625,7 +6096,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="6562800"/>
-        <a:ext cx="5389920" cy="2149920"/>
+        <a:ext cx="5388840" cy="2148840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6540,7 +7011,7 @@
       </c>
       <c r="B55" s="5" t="str">
         <f aca="false">COUNTIF(Backlog!I5:I80,"Done")&amp;" of "&amp;COUNTA(Backlog!A5:A80)</f>
-        <v>17 of 65</v>
+        <v>18 of 65</v>
       </c>
       <c r="C55" s="31" t="s">
         <v>68</v>
@@ -6562,7 +7033,7 @@
       </c>
       <c r="B56" s="38" t="n">
         <f aca="false">Backlog!G86</f>
-        <v>0.320261437908497</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="C56" s="34" t="s">
         <v>71</v>
@@ -6707,7 +7178,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -6719,10 +7190,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>96</v>
@@ -6743,7 +7214,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="58" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="J4" s="58" t="s">
         <v>7</v>
@@ -6751,7 +7222,7 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B5" s="90" t="n">
         <f aca="false">Assumptions!B26</f>
@@ -6786,7 +7257,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B6" s="90" t="n">
         <f aca="false">Assumptions!B27</f>
@@ -6821,7 +7292,7 @@
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B7" s="90" t="n">
         <f aca="false">Assumptions!B28</f>
@@ -6856,7 +7327,7 @@
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B8" s="90" t="n">
         <f aca="false">Assumptions!B29</f>
@@ -6891,7 +7362,7 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="B9" s="90" t="n">
         <f aca="false">Assumptions!B30</f>
@@ -6961,10 +7432,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="72" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="B11" s="72" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -7001,10 +7472,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="72" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B12" s="72" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C12" s="63" t="n">
         <f aca="false">IF(Assumptions!B16=0,0,C11/Assumptions!B16)</f>
@@ -7037,7 +7508,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -7052,28 +7523,28 @@
         <v>5</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>100</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>7</v>
@@ -7333,7 +7804,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -7350,7 +7821,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="50" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B22" s="50"/>
       <c r="C22" s="50"/>
@@ -7370,7 +7841,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="50" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B23" s="50"/>
       <c r="C23" s="50"/>
@@ -7387,7 +7858,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="50" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B24" s="50"/>
       <c r="C24" s="50"/>
@@ -7455,7 +7926,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="50" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="B28" s="50"/>
       <c r="C28" s="50"/>
@@ -7472,7 +7943,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
@@ -7509,7 +7980,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="67" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="B31" s="67"/>
       <c r="C31" s="67"/>
@@ -7527,12 +7998,12 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="72" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="96" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B34" s="96"/>
       <c r="C34" s="96"/>
@@ -7546,7 +8017,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B35" s="91" t="n">
         <f aca="false">J21</f>
@@ -7555,7 +8026,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="B36" s="91" t="n">
         <f aca="false">J31</f>
@@ -7564,7 +8035,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B37" s="91" t="n">
         <f aca="false">SUM(J22:J28)*(1+I30)</f>
@@ -7616,7 +8087,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7625,7 +8096,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -7640,7 +8111,7 @@
         <v>42</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D5" s="29"/>
       <c r="E5" s="29"/>
@@ -7654,28 +8125,28 @@
         <v>19.99</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B7" s="98" t="n">
         <f aca="false">B6*Assumptions!B70</f>
         <v>15.992</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B8" s="98" t="n">
         <f aca="false">B7*(1-Assumptions!B71)</f>
@@ -7687,35 +8158,35 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="B9" s="75" t="n">
         <f aca="false">Assumptions!B72*(1-Assumptions!B74)+Assumptions!B73*Assumptions!B74</f>
         <v>0.29</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B10" s="99" t="n">
         <f aca="false">B8*(1-B9)</f>
         <v>10.4459744</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -7730,7 +8201,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="29"/>
@@ -7744,70 +8215,70 @@
         <v>460504.8</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="D14" s="33"/>
       <c r="E14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B15" s="100" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B14/B10,0))</f>
         <v>44085</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B16" s="90" t="n">
         <f aca="false">TeamBudget!B37</f>
         <v>98632.8</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="67" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="B17" s="100" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B16/B10,0))</f>
         <v>9443</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B18" s="91" t="n">
         <f aca="false">B15*B6</f>
         <v>881259.15</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -7816,19 +8287,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7943,7 +8414,7 @@
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="54" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B28" s="54"/>
       <c r="C28" s="54"/>
@@ -8025,7 +8496,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8037,195 +8508,195 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B5" s="87" t="n">
         <f aca="false">Schedule!D5</f>
         <v>46383</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F5" s="70" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B6" s="87" t="n">
         <f aca="false">Schedule!D6</f>
         <v>46453</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="F6" s="70" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B7" s="87" t="n">
         <f aca="false">Schedule!D7</f>
         <v>46579</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F7" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B8" s="87" t="n">
         <f aca="false">Schedule!D8</f>
         <v>46621</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="E8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="F8" s="70" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B9" s="87" t="n">
         <f aca="false">Schedule!D9</f>
         <v>46663</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="F9" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B10" s="87" t="n">
         <f aca="false">Schedule!D10</f>
         <v>46691</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="E10" s="59" t="s">
         <v>100</v>
       </c>
       <c r="F10" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="B12" s="54"/>
       <c r="C12" s="54"/>
@@ -8305,7 +8776,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8319,31 +8790,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H4" s="58" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>44</v>
@@ -8351,10 +8822,10 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="59" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="C5" s="43" t="n">
         <v>3</v>
@@ -8367,27 +8838,27 @@
         <v>15</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="G5" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H5" s="59" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="I5" s="59" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="J5" s="70" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>3</v>
@@ -8400,27 +8871,27 @@
         <v>12</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="J6" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="59" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>2</v>
@@ -8433,27 +8904,27 @@
         <v>8</v>
       </c>
       <c r="F7" s="59" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="G7" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="H7" s="59" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="I7" s="59" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="J7" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>4</v>
@@ -8466,27 +8937,27 @@
         <v>12</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="G8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="J8" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="59" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>2</v>
@@ -8499,27 +8970,27 @@
         <v>6</v>
       </c>
       <c r="F9" s="59" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="G9" s="59" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="H9" s="59" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="I9" s="59" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="J9" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="C10" s="43" t="n">
         <v>2</v>
@@ -8532,27 +9003,27 @@
         <v>10</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="J10" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="59" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="C11" s="43" t="n">
         <v>3</v>
@@ -8565,27 +9036,27 @@
         <v>12</v>
       </c>
       <c r="F11" s="59" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="G11" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H11" s="59" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="J11" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="C12" s="43" t="n">
         <v>2</v>
@@ -8598,27 +9069,27 @@
         <v>8</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="J12" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="59" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="C13" s="43" t="n">
         <v>2</v>
@@ -8631,27 +9102,27 @@
         <v>4</v>
       </c>
       <c r="F13" s="59" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="G13" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H13" s="59" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="I13" s="59" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="J13" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="C14" s="43" t="n">
         <v>3</v>
@@ -8664,27 +9135,27 @@
         <v>12</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H14" s="59" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="J14" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="59" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="C15" s="43" t="n">
         <v>3</v>
@@ -8697,27 +9168,27 @@
         <v>15</v>
       </c>
       <c r="F15" s="59" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="G15" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H15" s="59" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="I15" s="59" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="J15" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="C16" s="43" t="n">
         <v>4</v>
@@ -8730,27 +9201,27 @@
         <v>16</v>
       </c>
       <c r="F16" s="59" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="G16" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H16" s="59" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="I16" s="59" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="J16" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="59" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="C17" s="43" t="n">
         <v>3</v>
@@ -8763,27 +9234,27 @@
         <v>12</v>
       </c>
       <c r="F17" s="59" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="G17" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="59" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="I17" s="59" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="J17" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="C18" s="43" t="n">
         <v>2</v>
@@ -8796,27 +9267,27 @@
         <v>6</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="G18" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H18" s="59" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="I18" s="59" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="J18" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="59" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="C19" s="43" t="n">
         <v>2</v>
@@ -8829,27 +9300,27 @@
         <v>8</v>
       </c>
       <c r="F19" s="59" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="G19" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="H19" s="59" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="I19" s="59" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="J19" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="C20" s="43" t="n">
         <v>3</v>
@@ -8862,19 +9333,19 @@
         <v>15</v>
       </c>
       <c r="F20" s="59" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="G20" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="I20" s="59" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="J20" s="70" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
   </sheetData>
@@ -8952,7 +9423,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8963,278 +9434,278 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="E4" s="58" t="s">
         <v>95</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="B7" s="27" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>848</v>
+      </c>
+      <c r="G7" s="27" t="s">
         <v>1248</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>1250</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>1251</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>846</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="F14" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
     </row>
   </sheetData>
@@ -9276,7 +9747,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9287,24 +9758,24 @@
         <v>110</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>100</v>
@@ -9312,55 +9783,55 @@
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>100</v>
@@ -9368,27 +9839,27 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>100</v>
@@ -9396,13 +9867,13 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D12" s="59" t="s">
         <v>100</v>
@@ -9410,41 +9881,41 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>100</v>
@@ -9452,14 +9923,14 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="B16" s="59" t="str">
         <f aca="false">"Premium at $"&amp;TEXT(Assumptions!B69,"0.00")&amp;". Launch discount no deeper than the realized-price factor on Assumptions."</f>
         <v>Premium at $19.99. Launch discount no deeper than the realized-price factor on Assumptions.</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D16" s="59" t="s">
         <v>100</v>
@@ -9467,13 +9938,13 @@
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>100</v>
@@ -9481,13 +9952,13 @@
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D18" s="59" t="s">
         <v>100</v>
@@ -9495,27 +9966,27 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D20" s="59" t="s">
         <v>100</v>
@@ -9523,27 +9994,27 @@
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="59" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D22" s="59" t="s">
         <v>100</v>
@@ -9567,10 +10038,1398 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="102" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="103" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="104" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B3" s="104"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="104"/>
+    </row>
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="58" t="s">
+        <v>493</v>
+      </c>
+      <c r="B5" s="58" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C5" s="58" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E5" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="58" t="s">
+        <v>1338</v>
+      </c>
+      <c r="G5" s="58" t="s">
+        <v>1339</v>
+      </c>
+      <c r="H5" s="58" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="105" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B6" s="105" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C6" s="105" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D6" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E6" s="105" t="s">
+        <v>1343</v>
+      </c>
+      <c r="F6" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G6" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H6" s="105" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="105" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B7" s="105" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C7" s="105" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D7" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E7" s="105" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F7" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G7" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H7" s="105" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="105" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B8" s="105" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C8" s="105" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D8" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E8" s="105" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F8" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G8" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H8" s="105" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="105" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B9" s="105" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C9" s="105" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D9" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E9" s="105" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F9" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G9" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H9" s="105" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="105" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B10" s="105" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C10" s="105" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D10" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E10" s="105" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F10" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G10" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H10" s="105" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="105" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B11" s="105" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C11" s="105" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D11" s="105" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E11" s="105" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F11" s="105" t="s">
+        <v>1363</v>
+      </c>
+      <c r="G11" s="105"/>
+      <c r="H11" s="105" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="105" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B12" s="105" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C12" s="105" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D12" s="105" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E12" s="105" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F12" s="105" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="105" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B13" s="105" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C13" s="105" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D13" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E13" s="105" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F13" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G13" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H13" s="105" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="105" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B14" s="105" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C14" s="105" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D14" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E14" s="105" t="s">
+        <v>1374</v>
+      </c>
+      <c r="F14" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G14" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H14" s="105" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="105" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B15" s="105" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C15" s="105" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D15" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E15" s="105" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F15" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G15" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H15" s="105" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="105" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B16" s="105" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C16" s="105" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D16" s="105" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E16" s="105" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F16" s="105" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G16" s="105"/>
+      <c r="H16" s="105" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="105" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B17" s="105" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C17" s="105" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D17" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E17" s="105" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F17" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G17" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H17" s="105" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="105" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B18" s="105" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C18" s="105" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D18" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E18" s="105" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F18" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G18" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H18" s="105" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="105" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B19" s="105" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C19" s="105" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D19" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E19" s="105" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F19" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G19" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H19" s="105" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="105" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B20" s="105" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C20" s="105" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D20" s="105" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E20" s="105" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F20" s="105" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G20" s="105"/>
+      <c r="H20" s="105" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="105" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B21" s="105" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C21" s="105" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D21" s="105" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E21" s="105" t="s">
+        <v>1399</v>
+      </c>
+      <c r="F21" s="105" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G21" s="105"/>
+      <c r="H21" s="105" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="105" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B22" s="105" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C22" s="105" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D22" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E22" s="105" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F22" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G22" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H22" s="105" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="105" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B23" s="105" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C23" s="105" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D23" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E23" s="105" t="s">
+        <v>1406</v>
+      </c>
+      <c r="F23" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G23" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H23" s="105" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="105" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B24" s="105" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C24" s="105" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D24" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E24" s="105" t="s">
+        <v>1409</v>
+      </c>
+      <c r="F24" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G24" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H24" s="105" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="105" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B25" s="105" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C25" s="105" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D25" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E25" s="105" t="s">
+        <v>1412</v>
+      </c>
+      <c r="F25" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G25" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H25" s="105" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="105" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B26" s="105" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C26" s="105" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D26" s="105" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E26" s="105" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F26" s="105" t="s">
+        <v>1417</v>
+      </c>
+      <c r="G26" s="105"/>
+      <c r="H26" s="105" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="105" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B27" s="105" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C27" s="105" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D27" s="105" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E27" s="105" t="s">
+        <v>1420</v>
+      </c>
+      <c r="F27" s="105" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G27" s="105"/>
+      <c r="H27" s="105" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="105" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B28" s="105" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C28" s="105" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D28" s="105" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E28" s="105" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F28" s="105" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G28" s="105"/>
+      <c r="H28" s="105" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="105" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B29" s="105" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C29" s="105" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D29" s="105" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E29" s="105" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F29" s="105" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G29" s="105"/>
+      <c r="H29" s="105" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="105" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B30" s="105" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C30" s="105" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D30" s="105" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E30" s="105" t="s">
+        <v>1431</v>
+      </c>
+      <c r="F30" s="105" t="s">
+        <v>1417</v>
+      </c>
+      <c r="G30" s="105"/>
+      <c r="H30" s="105" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="105" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B31" s="105" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C31" s="105" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D31" s="105" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E31" s="105" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F31" s="105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G31" s="105" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H31" s="105" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="105" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B32" s="105" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C32" s="105" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D32" s="105" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E32" s="105" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F32" s="105" t="s">
+        <v>849</v>
+      </c>
+      <c r="G32" s="105"/>
+      <c r="H32" s="105" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="102" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="103" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="104" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B3" s="104"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="104"/>
+      <c r="I3" s="104"/>
+    </row>
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="58" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B5" s="58" t="s">
+        <v>552</v>
+      </c>
+      <c r="C5" s="58" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E5" s="58" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F5" s="58" t="s">
+        <v>1443</v>
+      </c>
+      <c r="G5" s="58" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H5" s="58" t="s">
+        <v>1445</v>
+      </c>
+      <c r="I5" s="58" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="59" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>562</v>
+      </c>
+      <c r="C6" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="59" t="s">
+        <v>607</v>
+      </c>
+      <c r="G6" s="59" t="n">
+        <v>346</v>
+      </c>
+      <c r="H6" s="59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="59" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="59" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>557</v>
+      </c>
+      <c r="C7" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="59" t="s">
+        <v>607</v>
+      </c>
+      <c r="G7" s="59" t="n">
+        <v>344</v>
+      </c>
+      <c r="H7" s="59" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I7" s="59" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="59" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>567</v>
+      </c>
+      <c r="C8" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" s="106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="59" t="s">
+        <v>607</v>
+      </c>
+      <c r="G8" s="59" t="n">
+        <v>352</v>
+      </c>
+      <c r="H8" s="59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="59" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="59" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B9" s="59" t="s">
+        <v>572</v>
+      </c>
+      <c r="C9" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" s="106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="59" t="s">
+        <v>607</v>
+      </c>
+      <c r="G9" s="59" t="n">
+        <v>352</v>
+      </c>
+      <c r="H9" s="59" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I9" s="59" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="107" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B10" s="107" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C10" s="107" t="n">
+        <v>80</v>
+      </c>
+      <c r="D10" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="107" t="s">
+        <v>607</v>
+      </c>
+      <c r="G10" s="107" t="n">
+        <v>349</v>
+      </c>
+      <c r="H10" s="107" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I10" s="107" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="59" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B11" s="59" t="s">
+        <v>562</v>
+      </c>
+      <c r="C11" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" s="106" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E11" s="106" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F11" s="59" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G11" s="59" t="n">
+        <v>259</v>
+      </c>
+      <c r="H11" s="59" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I11" s="59" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="59" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B12" s="59" t="s">
+        <v>557</v>
+      </c>
+      <c r="C12" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="106" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E12" s="106" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F12" s="59" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G12" s="59" t="n">
+        <v>237</v>
+      </c>
+      <c r="H12" s="59" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I12" s="59" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="59" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B13" s="59" t="s">
+        <v>567</v>
+      </c>
+      <c r="C13" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" s="106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="59" t="s">
+        <v>607</v>
+      </c>
+      <c r="G13" s="59" t="n">
+        <v>299</v>
+      </c>
+      <c r="H13" s="59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="59" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="59" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B14" s="59" t="s">
+        <v>572</v>
+      </c>
+      <c r="C14" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" s="106" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E14" s="106" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F14" s="59" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G14" s="59" t="n">
+        <v>263</v>
+      </c>
+      <c r="H14" s="59" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I14" s="59" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="107" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B15" s="107" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C15" s="107" t="n">
+        <v>80</v>
+      </c>
+      <c r="D15" s="108" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="E15" s="108" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="F15" s="107" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G15" s="107" t="n">
+        <v>265</v>
+      </c>
+      <c r="H15" s="107" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I15" s="107" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="59" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B16" s="59" t="s">
+        <v>562</v>
+      </c>
+      <c r="C16" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="106" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F16" s="59" t="s">
+        <v>1454</v>
+      </c>
+      <c r="G16" s="59" t="n">
+        <v>127</v>
+      </c>
+      <c r="H16" s="59" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="I16" s="59" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="59" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B17" s="59" t="s">
+        <v>557</v>
+      </c>
+      <c r="C17" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="106" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F17" s="59" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G17" s="59" t="n">
+        <v>119</v>
+      </c>
+      <c r="H17" s="59" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I17" s="59" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="59" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B18" s="59" t="s">
+        <v>567</v>
+      </c>
+      <c r="C18" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="106" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F18" s="59" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G18" s="59" t="n">
+        <v>161</v>
+      </c>
+      <c r="H18" s="59" t="n">
+        <v>9.7</v>
+      </c>
+      <c r="I18" s="59" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="59" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B19" s="59" t="s">
+        <v>572</v>
+      </c>
+      <c r="C19" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="106" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F19" s="59" t="s">
+        <v>1457</v>
+      </c>
+      <c r="G19" s="59" t="n">
+        <v>108</v>
+      </c>
+      <c r="H19" s="59" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I19" s="59" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="107" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B20" s="107" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C20" s="107" t="n">
+        <v>80</v>
+      </c>
+      <c r="D20" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="108" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F20" s="107" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G20" s="107" t="n">
+        <v>129</v>
+      </c>
+      <c r="H20" s="107" t="n">
+        <v>9.8</v>
+      </c>
+      <c r="I20" s="107" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="109" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="110" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="110"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="110" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B24" s="110"/>
+      <c r="C24" s="110"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="110"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="110"/>
+      <c r="I24" s="110"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="110" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B25" s="110"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="110"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="109" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="104" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B28" s="104"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="104"/>
+      <c r="I28" s="104"/>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="104" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B29" s="104"/>
+      <c r="C29" s="104"/>
+      <c r="D29" s="104"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="104"/>
+      <c r="I29" s="104"/>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="104" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B30" s="104"/>
+      <c r="C30" s="104"/>
+      <c r="D30" s="104"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="104"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="104"/>
+      <c r="I30" s="104"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="104" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B31" s="104"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="104"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A31:I31"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -9589,7 +11448,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1332</v>
+        <v>1468</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9597,310 +11456,338 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1333</v>
+        <v>1469</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1334</v>
+        <v>1470</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1335</v>
+        <v>1471</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1336</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="102" t="n">
+      <c r="A5" s="111" t="n">
         <v>46311</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1337</v>
+        <v>1473</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1338</v>
+        <v>1474</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1339</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="103" t="n">
+      <c r="A6" s="112" t="n">
         <v>46311</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1337</v>
+        <v>1473</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1340</v>
+        <v>1476</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1341</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="102" t="n">
+      <c r="A7" s="111" t="n">
         <v>46311</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1337</v>
+        <v>1473</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1342</v>
+        <v>1478</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1343</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="103" t="n">
+      <c r="A8" s="112" t="n">
         <v>46311</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1344</v>
+        <v>1480</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1345</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="102" t="n">
+      <c r="A9" s="111" t="n">
         <v>46311</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1346</v>
+        <v>1482</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1347</v>
+        <v>1483</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1348</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="103" t="n">
+      <c r="A10" s="112" t="n">
         <v>46311</v>
       </c>
       <c r="B10" s="59" t="s">
         <v>53</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1349</v>
+        <v>1485</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>1350</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="102" t="n">
+      <c r="A11" s="111" t="n">
         <v>46311</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1351</v>
+        <v>1487</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1352</v>
+        <v>1488</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1353</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="103" t="n">
+      <c r="A12" s="112" t="n">
         <v>46311</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1354</v>
+        <v>1490</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>1355</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="102" t="n">
+      <c r="A13" s="111" t="n">
         <v>46311</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1356</v>
+        <v>1492</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1357</v>
+        <v>1493</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1358</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="103" t="n">
+      <c r="A14" s="112" t="n">
         <v>46311</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1359</v>
+        <v>1495</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1360</v>
+        <v>1496</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>1361</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="102" t="n">
+      <c r="A15" s="111" t="n">
         <v>46311</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1362</v>
+        <v>1498</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1363</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="103" t="n">
+      <c r="A16" s="112" t="n">
         <v>46311</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>1364</v>
+        <v>1500</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>1365</v>
+        <v>1501</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>1366</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="102" t="n">
+      <c r="A17" s="111" t="n">
         <v>46311</v>
       </c>
       <c r="B17" s="27" t="s">
         <v>62</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1367</v>
+        <v>1503</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1368</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="103" t="n">
+      <c r="A18" s="112" t="n">
         <v>46311</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>1369</v>
+        <v>1505</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>1370</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="102" t="n">
+      <c r="A19" s="111" t="n">
         <v>46311</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1371</v>
+        <v>1507</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>1372</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="103" t="n">
+      <c r="A20" s="112" t="n">
         <v>46311</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1373</v>
+        <v>1509</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>1374</v>
+        <v>1510</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>1375</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="103" t="n">
+      <c r="A21" s="112" t="n">
         <v>46313</v>
       </c>
       <c r="B21" s="59" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C21" s="59" t="s">
-        <v>1376</v>
+        <v>1512</v>
       </c>
       <c r="D21" s="59" t="s">
-        <v>1377</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="103" t="n">
+      <c r="A22" s="112" t="n">
         <v>46313</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1378</v>
+        <v>1514</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>1379</v>
+        <v>1515</v>
       </c>
       <c r="D22" s="59" t="s">
-        <v>1380</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="103" t="n">
+      <c r="A23" s="112" t="n">
         <v>46313</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>1378</v>
+        <v>1514</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>1381</v>
+        <v>1517</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>1382</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="103" t="n">
+      <c r="A24" s="112" t="n">
         <v>46313</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>1378</v>
+        <v>1514</v>
       </c>
       <c r="C24" s="59" t="s">
-        <v>1383</v>
+        <v>1519</v>
       </c>
       <c r="D24" s="59" t="s">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="103" t="n">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="112" t="n">
         <v>46313</v>
       </c>
       <c r="B25" s="59" t="s">
-        <v>1378</v>
+        <v>1514</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>1385</v>
+        <v>1521</v>
       </c>
       <c r="D25" s="59" t="s">
-        <v>1386</v>
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="112" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B26" s="59" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C26" s="59" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D26" s="59" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="112" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B27" s="59" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C27" s="59" t="s">
+        <v>1527</v>
+      </c>
+      <c r="D27" s="59" t="s">
+        <v>1528</v>
       </c>
     </row>
   </sheetData>
@@ -9924,7 +11811,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F258"/>
+  <dimension ref="A1:F259"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
@@ -12505,6 +14392,17 @@
       </c>
       <c r="C258" s="41" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A259" s="42" t="s">
+        <v>490</v>
+      </c>
+      <c r="B259" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C259" s="41" t="s">
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -12571,7 +14469,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12580,160 +14478,160 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B6" s="59" t="s">
+        <v>504</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>505</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>506</v>
+      </c>
+      <c r="E6" s="59" t="s">
         <v>502</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>503</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>504</v>
-      </c>
-      <c r="E6" s="59" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -12742,16 +14640,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>95</v>
@@ -12759,58 +14657,58 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="60" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B16" s="60" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C16" s="60" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D16" s="60" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E16" s="60" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="59" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D17" s="59" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E17" s="59" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="60" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B18" s="60" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C18" s="60" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D18" s="60" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E18" s="60" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="24"/>
@@ -12819,87 +14717,87 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="59" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E23" s="59" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="59" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B25" s="59" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D25" s="59" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E25" s="59" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>
@@ -12952,7 +14850,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12963,33 +14861,33 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F4" s="58" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>134</v>
@@ -12999,37 +14897,37 @@
         <v>24</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D6" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F6" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13037,71 +14935,71 @@
         <v>228</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D7" s="61" t="n">
         <f aca="false">Assumptions!B44</f>
         <v>120</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D8" s="61" t="n">
         <f aca="false">Assumptions!B46</f>
         <v>400</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="F8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D9" s="61" t="n">
         <f aca="false">Assumptions!B45</f>
         <v>120</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13109,151 +15007,151 @@
         <v>219</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="F10" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="F12" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D13" s="61" t="n">
         <f aca="false">Assumptions!B43</f>
         <v>168</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D14" s="61" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="F14" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D15" s="61" t="n">
         <f aca="false">Assumptions!B50</f>
         <v>5</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D16" s="61" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -13266,78 +15164,78 @@
         <v>102</v>
       </c>
       <c r="G16" s="59" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D17" s="61" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="F17" s="27" t="s">
         <v>102</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="F18" s="59" t="s">
         <v>104</v>
       </c>
       <c r="G18" s="59" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D19" s="61" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="F19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13345,46 +15243,46 @@
         <v>224</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E20" s="59" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="F20" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G20" s="59" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D21" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13392,55 +15290,55 @@
         <v>236</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D22" s="61" t="n">
         <f aca="false">Assumptions!B57</f>
         <v>2</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="F22" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G22" s="59" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D23" s="61" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="59" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C24" s="59" t="s">
         <v>134</v>
@@ -13450,13 +15348,13 @@
         <v>24</v>
       </c>
       <c r="E24" s="59" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="F24" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G24" s="59" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>
@@ -13502,7 +15400,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -13511,7 +15409,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -13526,21 +15424,21 @@
         <v>42</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B6" s="62" t="n">
         <f aca="false">Assumptions!B62</f>
         <v>1200</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
@@ -13554,21 +15452,21 @@
         <v>120</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B8" s="63" t="n">
         <f aca="false">IF(B7=0,0,B6/B7)</f>
         <v>10</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="33"/>
@@ -13582,7 +15480,7 @@
         <v>1.3</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
@@ -13596,14 +15494,14 @@
         <v>13</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -13612,24 +15510,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B14" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
@@ -13644,12 +15542,12 @@
         <v>9.6</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B15" s="61" t="n">
         <f aca="false">Assumptions!B57</f>
@@ -13664,12 +15562,12 @@
         <v>3</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B16" s="61" t="n">
         <f aca="false">Assumptions!B58</f>
@@ -13687,7 +15585,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B17" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B43,0)</f>
@@ -13701,12 +15599,12 @@
         <v>2</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B18" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B44,0)</f>
@@ -13720,12 +15618,12 @@
         <v>3</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B19" s="32" t="n">
         <f aca="false">ROUNDUP((B15+B16*Assumptions!B60)*$B$10/Assumptions!B59,0)</f>
@@ -13739,12 +15637,12 @@
         <v>2</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B20" s="61" t="n">
         <f aca="false">Assumptions!B61</f>
@@ -13763,7 +15661,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -13775,7 +15673,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="D22" s="65" t="n">
         <f aca="false">Assumptions!B41</f>
@@ -13784,7 +15682,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="67" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B23" s="67"/>
       <c r="C23" s="67"/>
@@ -13799,7 +15697,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -13808,24 +15706,24 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B27" s="61" t="n">
         <f aca="false">Assumptions!B64</f>
@@ -13845,7 +15743,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="59" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B28" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B43,0)</f>
@@ -13859,12 +15757,12 @@
         <v>1</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B44,0)</f>
@@ -13881,7 +15779,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D30" s="63" t="n">
         <f aca="false">SUM(D27:D29)</f>
@@ -13890,7 +15788,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D31" s="63" t="n">
         <f aca="false">Assumptions!B41-D30</f>
@@ -13899,7 +15797,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D32" s="32" t="n">
         <f aca="false">INT(D31/Assumptions!B65)</f>
@@ -13908,7 +15806,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D33" s="61" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -13917,7 +15815,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="67" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B34" s="67"/>
       <c r="C34" s="67"/>
@@ -13932,7 +15830,7 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="54" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B36" s="54"/>
       <c r="C36" s="54"/>
@@ -14013,7 +15911,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -14028,392 +15926,392 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B4" s="58" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="H4" s="58" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="H5" s="70" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B6" s="59" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="H6" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="J6" s="59" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="K6" s="59" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="H7" s="70" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B8" s="59" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="H8" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="J8" s="59" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="K8" s="59" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="H9" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B10" s="59" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H10" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="J10" s="59" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="K10" s="59" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="H11" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B12" s="59" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="H12" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="J12" s="59" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="K12" s="59" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="H13" s="70" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H14" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="K14" s="59" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
@@ -14425,10 +16323,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B17" s="71" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C17" s="71"/>
       <c r="D17" s="71"/>
@@ -14439,10 +16337,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C18" s="71"/>
       <c r="D18" s="71"/>
@@ -14453,10 +16351,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B19" s="71" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C19" s="71"/>
       <c r="D19" s="71"/>
@@ -14467,10 +16365,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B20" s="71" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C20" s="71"/>
       <c r="D20" s="71"/>
@@ -14481,10 +16379,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B21" s="71" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C21" s="71"/>
       <c r="D21" s="71"/>
@@ -14495,10 +16393,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B22" s="71" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C22" s="71"/>
       <c r="D22" s="71"/>
@@ -14509,10 +16407,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="B23" s="71" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C23" s="71"/>
       <c r="D23" s="71"/>
@@ -14523,7 +16421,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="72" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
     </row>
   </sheetData>
@@ -14587,7 +16485,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -14601,42 +16499,42 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
@@ -14645,190 +16543,190 @@
         <v>96</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G5" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="I5" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D6" s="59" t="s">
         <v>96</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G6" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="I6" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J6" s="59" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G7" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="27" t="s">
+        <v>838</v>
+      </c>
+      <c r="I7" s="70" t="s">
         <v>836</v>
       </c>
-      <c r="I7" s="70" t="s">
-        <v>834</v>
-      </c>
       <c r="J7" s="27" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D8" s="59" t="s">
         <v>96</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="G8" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="I8" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J8" s="59" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G9" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="I9" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D10" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G10" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="I10" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J10" s="59" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>23</v>
@@ -14837,30 +16735,30 @@
         <v>98</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G11" s="43" t="n">
         <v>12</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="I11" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C12" s="59" t="s">
         <v>23</v>
@@ -14869,30 +16767,30 @@
         <v>98</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G12" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="I12" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J12" s="59" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>26</v>
@@ -14901,62 +16799,62 @@
         <v>98</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G13" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="I13" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D14" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G14" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H14" s="59" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="I14" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>35</v>
@@ -14965,263 +16863,263 @@
         <v>98</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G15" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="I15" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J15" s="27" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D16" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E16" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F16" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G16" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H16" s="59" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="I16" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J16" s="59" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G17" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="I17" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D18" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="G18" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H18" s="59" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="I18" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J18" s="59" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G19" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="I19" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D20" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E20" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F20" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G20" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="I20" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J20" s="59" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G21" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="I21" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J21" s="27" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="59" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D22" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F22" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G22" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="59" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="I22" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J22" s="59" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
@@ -15230,117 +17128,117 @@
         <v>3</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="I23" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="59" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C24" s="59" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D24" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E24" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F24" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G24" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H24" s="59" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="I24" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J24" s="59" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D25" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G25" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="I25" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J25" s="27" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="59" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B26" s="59" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D26" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E26" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F26" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G26" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="I26" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J26" s="59" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C27" s="27" t="s">
         <v>29</v>
@@ -15349,30 +17247,30 @@
         <v>100</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G27" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="I27" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J27" s="27" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="59" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B28" s="59" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C28" s="59" t="s">
         <v>32</v>
@@ -15381,30 +17279,30 @@
         <v>100</v>
       </c>
       <c r="E28" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F28" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G28" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H28" s="59" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="I28" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J28" s="59" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C29" s="27" t="s">
         <v>26</v>
@@ -15413,94 +17311,94 @@
         <v>100</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G29" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="I29" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="59" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B30" s="59" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C30" s="59" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D30" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F30" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G30" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="59" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="I30" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J30" s="59" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D31" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G31" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="I31" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J31" s="27" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="59" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B32" s="59" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C32" s="59" t="s">
         <v>35</v>
@@ -15509,30 +17407,30 @@
         <v>100</v>
       </c>
       <c r="E32" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F32" s="59" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="G32" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H32" s="59" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="I32" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J32" s="59" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C33" s="27" t="s">
         <v>35</v>
@@ -15541,487 +17439,487 @@
         <v>100</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G33" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="I33" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J33" s="27" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="59" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B34" s="59" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C34" s="59" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D34" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F34" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G34" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H34" s="59" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="I34" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J34" s="59" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
+        <v>918</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>919</v>
+      </c>
+      <c r="C35" s="27" t="s">
         <v>916</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>917</v>
-      </c>
-      <c r="C35" s="27" t="s">
-        <v>914</v>
       </c>
       <c r="D35" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G35" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="I35" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J35" s="27" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="59" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B36" s="59" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C36" s="59" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D36" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F36" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G36" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H36" s="59" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="I36" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J36" s="59" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="27" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D37" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G37" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H37" s="27" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="I37" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J37" s="27" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="59" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B38" s="59" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C38" s="59" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D38" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="59" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F38" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G38" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="59" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="I38" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J38" s="59" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="27" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="D39" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G39" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="I39" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J39" s="27" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="59" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B40" s="59" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C40" s="59" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D40" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F40" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G40" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H40" s="59" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="I40" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J40" s="59" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D41" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G41" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="I41" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J41" s="27" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="59" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B42" s="59" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C42" s="59" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D42" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="59" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F42" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G42" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="59" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="I42" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J42" s="59" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D43" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="G43" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H43" s="27" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="I43" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J43" s="27" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="59" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B44" s="59" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C44" s="59" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D44" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E44" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F44" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G44" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H44" s="59" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="I44" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J44" s="59" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="27" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D45" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G45" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H45" s="27" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="I45" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J45" s="27" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="59" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B46" s="59" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="C46" s="59" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D46" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E46" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F46" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G46" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H46" s="59" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="I46" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J46" s="59" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D47" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G47" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H47" s="27" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="I47" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J47" s="27" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="59" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B48" s="59" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C48" s="59" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D48" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E48" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F48" s="59" t="s">
         <v>100</v>
@@ -16030,62 +17928,62 @@
         <v>3</v>
       </c>
       <c r="H48" s="59" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="I48" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J48" s="59" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="27" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="D49" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G49" s="43" t="n">
         <v>2</v>
       </c>
       <c r="H49" s="27" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="I49" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J49" s="27" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="59" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B50" s="59" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C50" s="59" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="D50" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E50" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F50" s="59" t="s">
         <v>100</v>
@@ -16094,181 +17992,181 @@
         <v>4</v>
       </c>
       <c r="H50" s="59" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="I50" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J50" s="59" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="D51" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G51" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H51" s="27" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="I51" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J51" s="27" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="59" t="s">
+        <v>970</v>
+      </c>
+      <c r="B52" s="59" t="s">
+        <v>971</v>
+      </c>
+      <c r="C52" s="59" t="s">
         <v>968</v>
-      </c>
-      <c r="B52" s="59" t="s">
-        <v>969</v>
-      </c>
-      <c r="C52" s="59" t="s">
-        <v>966</v>
       </c>
       <c r="D52" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E52" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F52" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G52" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H52" s="59" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="I52" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J52" s="59" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="27" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="D53" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F53" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G53" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H53" s="27" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="I53" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J53" s="27" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="59" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B54" s="59" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="C54" s="59" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D54" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E54" s="59" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F54" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G54" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H54" s="59" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="I54" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J54" s="59" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D55" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="F55" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G55" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="I55" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J55" s="27" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="59" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="B56" s="59" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C56" s="59" t="s">
         <v>26</v>
@@ -16277,359 +18175,359 @@
         <v>102</v>
       </c>
       <c r="E56" s="59" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="F56" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G56" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H56" s="59" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="I56" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J56" s="59" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D57" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G57" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H57" s="27" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="I57" s="70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J57" s="27" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="59" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B58" s="59" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C58" s="59" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D58" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E58" s="59" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F58" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G58" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H58" s="59" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="I58" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J58" s="59" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="27" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D59" s="27" t="s">
         <v>102</v>
       </c>
       <c r="E59" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G59" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H59" s="27" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="I59" s="70" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="J59" s="27" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="59" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="B60" s="59" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C60" s="59" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="D60" s="59" t="s">
         <v>102</v>
       </c>
       <c r="E60" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F60" s="59" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="G60" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H60" s="59" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="I60" s="70" t="s">
-        <v>847</v>
+        <v>836</v>
       </c>
       <c r="J60" s="59" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="27" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D61" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G61" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H61" s="27" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="I61" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J61" s="27" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="59" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B62" s="59" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C62" s="59" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D62" s="59" t="s">
         <v>104</v>
       </c>
       <c r="E62" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F62" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G62" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H62" s="59" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="I62" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J62" s="59" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="27" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C63" s="27" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D63" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E63" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G63" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H63" s="27" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="I63" s="70" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J63" s="27" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="59" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B64" s="59" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C64" s="59" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="D64" s="59" t="s">
         <v>104</v>
       </c>
       <c r="E64" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F64" s="59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G64" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H64" s="59" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="I64" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J64" s="59" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="27" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C65" s="27" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D65" s="27" t="s">
         <v>104</v>
       </c>
       <c r="E65" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G65" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H65" s="27" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="I65" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J65" s="27" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="59" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B66" s="59" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C66" s="59" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D66" s="59" t="s">
         <v>104</v>
       </c>
       <c r="E66" s="59" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F66" s="59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G66" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H66" s="59" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="I66" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J66" s="59" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="27" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D67" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F67" s="27" t="s">
         <v>100</v>
@@ -16638,30 +18536,30 @@
         <v>5</v>
       </c>
       <c r="H67" s="27" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="I67" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J67" s="27" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="59" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B68" s="59" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C68" s="59" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D68" s="59" t="s">
         <v>106</v>
       </c>
       <c r="E68" s="59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F68" s="59" t="s">
         <v>100</v>
@@ -16670,45 +18568,45 @@
         <v>1</v>
       </c>
       <c r="H68" s="59" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="I68" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J68" s="59" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="27" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D69" s="27" t="s">
         <v>106</v>
       </c>
       <c r="E69" s="27" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F69" s="27" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G69" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H69" s="27" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="I69" s="70" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="J69" s="27" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16845,7 +18743,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D82" s="73" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="E82" s="73"/>
       <c r="F82" s="73"/>
@@ -16856,7 +18754,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D83" s="74" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E83" s="74"/>
       <c r="F83" s="74"/>
@@ -16867,7 +18765,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D84" s="74" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="E84" s="74"/>
       <c r="F84" s="74"/>
@@ -16878,29 +18776,29 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D85" s="74" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="E85" s="74"/>
       <c r="F85" s="74"/>
       <c r="G85" s="32" t="n">
         <f aca="false">SUMIF(I$5:I$80,"Done",G$5:G$80)</f>
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D86" s="74" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="E86" s="74"/>
       <c r="F86" s="74"/>
       <c r="G86" s="75" t="n">
         <f aca="false">IF(G83=0,0,SUMIFS(G$5:G$80,E$5:E$80,"Must",I$5:I$80,"Done")/G83)</f>
-        <v>0.320261437908497</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -16914,25 +18812,25 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B90" s="9"/>
       <c r="C90" s="9" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="76" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B91" s="76"/>
       <c r="C91" s="32" t="n">
@@ -16954,7 +18852,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="76" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B92" s="76"/>
       <c r="C92" s="32" t="n">
@@ -16976,7 +18874,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="76" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B93" s="76"/>
       <c r="C93" s="32" t="n">
@@ -16998,7 +18896,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="76" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B94" s="76"/>
       <c r="C94" s="32" t="n">
@@ -17020,7 +18918,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="76" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="B95" s="76"/>
       <c r="C95" s="32" t="n">
@@ -17064,7 +18962,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="73" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B97" s="73"/>
       <c r="C97" s="21" t="n">
@@ -17090,16 +18988,16 @@
       </c>
       <c r="B99" s="29"/>
       <c r="C99" s="9" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D99" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F99" s="9" t="s">
         <v>1035</v>
-      </c>
-      <c r="E99" s="9" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17242,7 +19140,7 @@
     </row>
     <row r="107" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="54" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B107" s="54"/>
       <c r="C107" s="54"/>
@@ -17376,7 +19274,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -17394,22 +19292,22 @@
         <v>6</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17430,16 +19328,16 @@
         <v>46383</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17460,16 +19358,16 @@
         <v>46453</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17490,16 +19388,16 @@
         <v>46579</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17520,16 +19418,16 @@
         <v>46621</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17550,16 +19448,16 @@
         <v>46663</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17580,21 +19478,21 @@
         <v>46691</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B12" s="82" t="n">
         <f aca="false">D10</f>
@@ -17604,7 +19502,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B13" s="83" t="n">
         <f aca="false">B12-Assumptions!B7</f>
@@ -17614,7 +19512,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="24"/>
@@ -17626,7 +19524,7 @@
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B15" s="54"/>
       <c r="C15" s="54"/>
@@ -17638,7 +19536,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="54" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="B16" s="54"/>
       <c r="C16" s="54"/>
@@ -17718,7 +19616,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -17752,13 +19650,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="D4" s="84" t="n">
         <v>1</v>
@@ -17943,7 +19841,7 @@
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -18190,7 +20088,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -19961,7 +21859,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -20208,7 +22106,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>

--- a/docs/Vinland_Game_Development_Plan.xlsx
+++ b/docs/Vinland_Game_Development_Plan.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2429" uniqueCount="1529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2471" uniqueCount="1561">
   <si>
     <t xml:space="preserve">VINLAND</t>
   </si>
@@ -1518,10 +1518,10 @@
     <t xml:space="preserve">Relief trade goods (F30): cloth or iron</t>
   </si>
   <si>
-    <t xml:space="preserve">Score: per timber unit delivered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score (F31): the return is the win (P7)</t>
+    <t xml:space="preserve">Score: per mark of cargo sold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score (F31): the return is the win (P7); timber, vines and pelts by what they fetch, so grade counts</t>
   </si>
   <si>
     <t xml:space="preserve">Score: per person alive at the end</t>
@@ -1566,6 +1566,78 @@
     <t xml:space="preserve">Score (F31, F55): more dead and the saga is dear-bought; set from the balance sweep</t>
   </si>
   <si>
+    <t xml:space="preserve">HÓP PUSH (F27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp: days away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp (F27): ten days south, ten there, ten back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp: earliest start (day of year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp (F27): second summer, 1 June</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp: latest start (day of year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp (F27): 24 July, so the knarr is back for the voyage home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp: smallest party</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp (F27): enough to work her</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp: vines and grapes per person (cargo units)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp (F27): the cargo the land was named for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp: self-sown wheat per person (food units)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp (F27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp: salmon per person (person-days, dried)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp (F27): the rivers were full of salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp: chance fear rises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp (F27): many people live at Hóp; less with goodwill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp: fear chance taken off per point of goodwill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp: fear added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp: chance the hull is strained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver per unit of vines (marks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appraisal (F25, F27): worth more than timber, takes the same room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Story: points for the voyage to Hóp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recruitment (F26, F27): a tale of a better land</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pillars, fantasy, clocks, and the win</t>
   </si>
   <si>
@@ -3021,7 +3093,7 @@
     <t xml:space="preserve">Hóp push</t>
   </si>
   <si>
-    <t xml:space="preserve">Second-summer site. First cut if Production slips.</t>
+    <t xml:space="preserve">Second-summer site. First cut if Production slips.  [Built: B on the knarr row in the second summer (1 June to 24 July) sends 10+ south for about 30 days. They bring back vines and grapes (0.5 units a person, 6 marks a unit at home), self-sown wheat and dried salmon; fear may rise (less with goodwill) and the hull may be strained; the knarr is away meanwhile. The vines go first in the hold home and the story counts the voyage. Worth about +5 score to a planner, with risk. The meeting at Hóp stays an abstract fear outcome pending F59.]</t>
   </si>
   <si>
     <t xml:space="preserve">F28</t>
@@ -3069,7 +3141,7 @@
     <t xml:space="preserve">Economy tuning pass from run logs</t>
   </si>
   <si>
-    <t xml:space="preserve">Knob changes made on Assumptions, backed by logged runs.  [First pass: balance sweep of whole runs by three player models (sheet Balance, docs/balance/fullrun_sweep.csv); full saga now also needs few deaths; regression test holds the spread. Retune from real play logs after playtest 2.]</t>
+    <t xml:space="preserve">Knob changes made on Assumptions, backed by logged runs.  [Balance sweep of whole runs by three player models (sheet Balance, tools/balance_to_plan.py, docs/balance/fullrun_sweep.csv): planner 100% full saga, average 44%, careless 0%; scores 374 / 288 / 132. Changes: full saga needs 3 or fewer deaths; score by marks of cargo sold; Hóp vines 0.5. Retune from real play logs after playtest 2.]</t>
   </si>
   <si>
     <t xml:space="preserve">F64</t>
@@ -4401,10 +4473,19 @@
     <t xml:space="preserve">Trailer, store copy, day-one notes in the release folder</t>
   </si>
   <si>
+    <t xml:space="preserve">RG28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hóp push pays, with risk, and an expedition survives a save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hóp: (11 checks), hóp worth</t>
+  </si>
+  <si>
     <t xml:space="preserve">Balance sweep  ·  F55: knob changes backed by logged runs</t>
   </si>
   <si>
-    <t xml:space="preserve">Whole three-summer runs played by three player models (tests/balance.gd), 20 seeds per outfit. Every run is in docs/balance/fullrun_sweep.csv. Re-run: godot --headless --path . res://tests/balance_runner.tscn -- --n=20</t>
+    <t xml:space="preserve">Whole three-summer runs played by three player models (tests/balance.gd), 20 seeds per outfit. Every run is in docs/balance/fullrun_sweep.csv. Re-run: godot --headless --path . res://tests/balance_runner.tscn -- --n=20, then python3 tools/balance_to_plan.py.</t>
   </si>
   <si>
     <t xml:space="preserve">Player model</t>
@@ -4479,16 +4560,22 @@
     <t xml:space="preserve">Careless: summer-only camp, no hay, no rack, reckless captain, sails late</t>
   </si>
   <si>
-    <t xml:space="preserve">Changes made from this sweep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First sweep (8 seeds): planner 100%, average 97%, careless 78% reached the full saga: the arc was too easy to close.</t>
+    <t xml:space="preserve">Changes made from these sweeps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweep 1 (8 seeds): planner 100%, average 97%, careless 78% reached the full saga: the arc was too easy to close.</t>
   </si>
   <si>
     <t xml:space="preserve">Full saga now also needs no more than "Most deaths for the full saga" (Assumptions, 3). The whole arc with more dead is "A dear-bought saga", scored and named, never scolded (P8).</t>
   </si>
   <si>
-    <t xml:space="preserve">Camp running itself while you are away: hay sized to the herd (the first pass lost whole herds over the second winter).</t>
+    <t xml:space="preserve">The camp running itself while you are away sizes hay to the herd (the first pass lost whole herds over the second winter).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The score counts cargo by what it fetched ("Score: per mark of cargo sold", 0.65) instead of timber units, so grade, pelts and Hóp vines count.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hóp (F27): vines per person raised from 0.25 to 0.5 so the push south pays (planner +5 score on average, with fear and hull risk).</t>
   </si>
   <si>
     <t xml:space="preserve">Targets held by the regression test: planner 75%+ full saga, average 15-80%, careless 10% or less; scores and deaths ordered planner &gt; average &gt; careless.</t>
@@ -4675,6 +4762,15 @@
   </si>
   <si>
     <t xml:space="preserve">Every gate now has a written pass list and a script that runs the automated half.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backlog, Assumptions, Balance, Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F27 Hóp push done; HÓP PUSH knobs; score by cargo value; Balance sheet regenerated from a fresh sweep.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The second summer gets its optional push south, and the score now values what the cargo fetches.</t>
   </si>
 </sst>
 </file>
@@ -5451,7 +5547,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5926,11 +6022,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="45485430"/>
-        <c:axId val="74301498"/>
+        <c:axId val="6586677"/>
+        <c:axId val="22223727"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="45485430"/>
+        <c:axId val="6586677"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5962,7 +6058,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74301498"/>
+        <c:crossAx val="22223727"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5970,7 +6066,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="74301498"/>
+        <c:axId val="22223727"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6046,7 +6142,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45485430"/>
+        <c:crossAx val="6586677"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6085,9 +6181,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>736920</xdr:colOff>
+      <xdr:colOff>735480</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>53280</xdr:rowOff>
+      <xdr:rowOff>51840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6096,7 +6192,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="6562800"/>
-        <a:ext cx="5388840" cy="2148840"/>
+        <a:ext cx="5387400" cy="2147400"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7011,7 +7107,7 @@
       </c>
       <c r="B55" s="5" t="str">
         <f aca="false">COUNTIF(Backlog!I5:I80,"Done")&amp;" of "&amp;COUNTA(Backlog!A5:A80)</f>
-        <v>18 of 65</v>
+        <v>19 of 65</v>
       </c>
       <c r="C55" s="31" t="s">
         <v>68</v>
@@ -7178,7 +7274,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1080</v>
+        <v>1104</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7190,10 +7286,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>1081</v>
+        <v>1105</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1082</v>
+        <v>1106</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>96</v>
@@ -7214,7 +7310,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="58" t="s">
-        <v>1083</v>
+        <v>1107</v>
       </c>
       <c r="J4" s="58" t="s">
         <v>7</v>
@@ -7222,7 +7318,7 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="B5" s="90" t="n">
         <f aca="false">Assumptions!B26</f>
@@ -7257,7 +7353,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="B6" s="90" t="n">
         <f aca="false">Assumptions!B27</f>
@@ -7292,7 +7388,7 @@
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="B7" s="90" t="n">
         <f aca="false">Assumptions!B28</f>
@@ -7327,7 +7423,7 @@
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>941</v>
+        <v>965</v>
       </c>
       <c r="B8" s="90" t="n">
         <f aca="false">Assumptions!B29</f>
@@ -7362,7 +7458,7 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>996</v>
+        <v>1020</v>
       </c>
       <c r="B9" s="90" t="n">
         <f aca="false">Assumptions!B30</f>
@@ -7432,10 +7528,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="72" t="s">
-        <v>1084</v>
+        <v>1108</v>
       </c>
       <c r="B11" s="72" t="s">
-        <v>1085</v>
+        <v>1109</v>
       </c>
       <c r="C11" s="32" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -7472,10 +7568,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="72" t="s">
-        <v>1086</v>
+        <v>1110</v>
       </c>
       <c r="B12" s="72" t="s">
-        <v>1087</v>
+        <v>1111</v>
       </c>
       <c r="C12" s="63" t="n">
         <f aca="false">IF(Assumptions!B16=0,0,C11/Assumptions!B16)</f>
@@ -7508,7 +7604,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1088</v>
+        <v>1112</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -7523,28 +7619,28 @@
         <v>5</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1089</v>
+        <v>1113</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>941</v>
+        <v>965</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>996</v>
+        <v>1020</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>100</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>1083</v>
+        <v>1107</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>7</v>
@@ -7804,7 +7900,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>1090</v>
+        <v>1114</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -7821,7 +7917,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="50" t="s">
-        <v>1091</v>
+        <v>1115</v>
       </c>
       <c r="B22" s="50"/>
       <c r="C22" s="50"/>
@@ -7841,7 +7937,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="50" t="s">
-        <v>1092</v>
+        <v>1116</v>
       </c>
       <c r="B23" s="50"/>
       <c r="C23" s="50"/>
@@ -7858,7 +7954,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="50" t="s">
-        <v>1093</v>
+        <v>1117</v>
       </c>
       <c r="B24" s="50"/>
       <c r="C24" s="50"/>
@@ -7926,7 +8022,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="50" t="s">
-        <v>1094</v>
+        <v>1118</v>
       </c>
       <c r="B28" s="50"/>
       <c r="C28" s="50"/>
@@ -7943,7 +8039,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>1095</v>
+        <v>1119</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
@@ -7980,7 +8076,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="67" t="s">
-        <v>1096</v>
+        <v>1120</v>
       </c>
       <c r="B31" s="67"/>
       <c r="C31" s="67"/>
@@ -7998,12 +8094,12 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="72" t="s">
-        <v>1097</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="96" t="s">
-        <v>1098</v>
+        <v>1122</v>
       </c>
       <c r="B34" s="96"/>
       <c r="C34" s="96"/>
@@ -8017,7 +8113,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>1090</v>
+        <v>1114</v>
       </c>
       <c r="B35" s="91" t="n">
         <f aca="false">J21</f>
@@ -8026,7 +8122,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>1099</v>
+        <v>1123</v>
       </c>
       <c r="B36" s="91" t="n">
         <f aca="false">J31</f>
@@ -8035,7 +8131,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>1100</v>
+        <v>1124</v>
       </c>
       <c r="B37" s="91" t="n">
         <f aca="false">SUM(J22:J28)*(1+I30)</f>
@@ -8087,7 +8183,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1101</v>
+        <v>1125</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8096,7 +8192,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1102</v>
+        <v>1126</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -8111,7 +8207,7 @@
         <v>42</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>673</v>
+        <v>697</v>
       </c>
       <c r="D5" s="29"/>
       <c r="E5" s="29"/>
@@ -8125,28 +8221,28 @@
         <v>19.99</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>1103</v>
+        <v>1127</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1104</v>
+        <v>1128</v>
       </c>
       <c r="B7" s="98" t="n">
         <f aca="false">B6*Assumptions!B70</f>
         <v>15.992</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>1105</v>
+        <v>1129</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>1106</v>
+        <v>1130</v>
       </c>
       <c r="B8" s="98" t="n">
         <f aca="false">B7*(1-Assumptions!B71)</f>
@@ -8158,35 +8254,35 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>1107</v>
+        <v>1131</v>
       </c>
       <c r="B9" s="75" t="n">
         <f aca="false">Assumptions!B72*(1-Assumptions!B74)+Assumptions!B73*Assumptions!B74</f>
         <v>0.29</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>1108</v>
+        <v>1132</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>1109</v>
+        <v>1133</v>
       </c>
       <c r="B10" s="99" t="n">
         <f aca="false">B8*(1-B9)</f>
         <v>10.4459744</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>1110</v>
+        <v>1134</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1111</v>
+        <v>1135</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -8201,7 +8297,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>673</v>
+        <v>697</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="29"/>
@@ -8215,70 +8311,70 @@
         <v>460504.8</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>1112</v>
+        <v>1136</v>
       </c>
       <c r="D14" s="33"/>
       <c r="E14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>1113</v>
+        <v>1137</v>
       </c>
       <c r="B15" s="100" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B14/B10,0))</f>
         <v>44085</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>1114</v>
+        <v>1138</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>1115</v>
+        <v>1139</v>
       </c>
       <c r="B16" s="90" t="n">
         <f aca="false">TeamBudget!B37</f>
         <v>98632.8</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>1116</v>
+        <v>1140</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="67" t="s">
-        <v>1117</v>
+        <v>1141</v>
       </c>
       <c r="B17" s="100" t="n">
         <f aca="false">IF(B10=0,0,ROUNDUP(B16/B10,0))</f>
         <v>9443</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>1118</v>
+        <v>1142</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>1119</v>
+        <v>1143</v>
       </c>
       <c r="B18" s="91" t="n">
         <f aca="false">B15*B6</f>
         <v>881259.15</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>1120</v>
+        <v>1144</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>1121</v>
+        <v>1145</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -8287,19 +8383,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>1122</v>
+        <v>1146</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1123</v>
+        <v>1147</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1124</v>
+        <v>1148</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1125</v>
+        <v>1149</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>1035</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8414,7 +8510,7 @@
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="54" t="s">
-        <v>1126</v>
+        <v>1150</v>
       </c>
       <c r="B28" s="54"/>
       <c r="C28" s="54"/>
@@ -8496,7 +8592,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1127</v>
+        <v>1151</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8508,195 +8604,195 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>1045</v>
+        <v>1069</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1128</v>
+        <v>1152</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1129</v>
+        <v>1153</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1130</v>
+        <v>1154</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>829</v>
+        <v>853</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1131</v>
+        <v>1155</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>1132</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1049</v>
+        <v>1073</v>
       </c>
       <c r="B5" s="87" t="n">
         <f aca="false">Schedule!D5</f>
         <v>46383</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1133</v>
+        <v>1157</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1134</v>
+        <v>1158</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="F5" s="70" t="s">
-        <v>1135</v>
+        <v>1159</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1136</v>
+        <v>1160</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>1137</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="B6" s="87" t="n">
         <f aca="false">Schedule!D6</f>
         <v>46453</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1138</v>
+        <v>1162</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1139</v>
+        <v>1163</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F6" s="70" t="s">
-        <v>1135</v>
+        <v>1159</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>1140</v>
+        <v>1164</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>1141</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="B7" s="87" t="n">
         <f aca="false">Schedule!D7</f>
         <v>46579</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1142</v>
+        <v>1166</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1143</v>
+        <v>1167</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="F7" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1144</v>
+        <v>1168</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>1145</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
       <c r="B8" s="87" t="n">
         <f aca="false">Schedule!D8</f>
         <v>46621</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1146</v>
+        <v>1170</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1147</v>
+        <v>1171</v>
       </c>
       <c r="E8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="F8" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>1148</v>
+        <v>1172</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>1149</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1065</v>
+        <v>1089</v>
       </c>
       <c r="B9" s="87" t="n">
         <f aca="false">Schedule!D9</f>
         <v>46663</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1150</v>
+        <v>1174</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1151</v>
+        <v>1175</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>996</v>
+        <v>1020</v>
       </c>
       <c r="F9" s="70" t="s">
-        <v>849</v>
+        <v>873</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1152</v>
+        <v>1176</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>1153</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1068</v>
+        <v>1092</v>
       </c>
       <c r="B10" s="87" t="n">
         <f aca="false">Schedule!D10</f>
         <v>46691</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1154</v>
+        <v>1178</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>1155</v>
+        <v>1179</v>
       </c>
       <c r="E10" s="59" t="s">
         <v>100</v>
       </c>
       <c r="F10" s="70" t="s">
-        <v>849</v>
+        <v>873</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>1156</v>
+        <v>1180</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>1157</v>
+        <v>1181</v>
       </c>
       <c r="B12" s="54"/>
       <c r="C12" s="54"/>
@@ -8776,7 +8872,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1158</v>
+        <v>1182</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8790,31 +8886,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1159</v>
+        <v>1183</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1160</v>
+        <v>1184</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1161</v>
+        <v>1185</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>643</v>
+        <v>667</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>1162</v>
+        <v>1186</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>829</v>
+        <v>853</v>
       </c>
       <c r="H4" s="58" t="s">
-        <v>1163</v>
+        <v>1187</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>1164</v>
+        <v>1188</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>44</v>
@@ -8822,10 +8918,10 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="59" t="s">
-        <v>1165</v>
+        <v>1189</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>1166</v>
+        <v>1190</v>
       </c>
       <c r="C5" s="43" t="n">
         <v>3</v>
@@ -8838,27 +8934,27 @@
         <v>15</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>1167</v>
+        <v>1191</v>
       </c>
       <c r="G5" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="H5" s="59" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="I5" s="59" t="s">
-        <v>1168</v>
+        <v>1192</v>
       </c>
       <c r="J5" s="70" t="s">
-        <v>1169</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>1170</v>
+        <v>1194</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1171</v>
+        <v>1195</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>3</v>
@@ -8871,27 +8967,27 @@
         <v>12</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>1172</v>
+        <v>1196</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>1173</v>
+        <v>1197</v>
       </c>
       <c r="J6" s="70" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="59" t="s">
-        <v>1175</v>
+        <v>1199</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>1176</v>
+        <v>1200</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>2</v>
@@ -8904,27 +9000,27 @@
         <v>8</v>
       </c>
       <c r="F7" s="59" t="s">
-        <v>1177</v>
+        <v>1201</v>
       </c>
       <c r="G7" s="59" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="H7" s="59" t="s">
-        <v>1065</v>
+        <v>1089</v>
       </c>
       <c r="I7" s="59" t="s">
-        <v>1178</v>
+        <v>1202</v>
       </c>
       <c r="J7" s="70" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1180</v>
+        <v>1204</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>4</v>
@@ -8937,27 +9033,27 @@
         <v>12</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>1181</v>
+        <v>1205</v>
       </c>
       <c r="G8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>1182</v>
+        <v>1206</v>
       </c>
       <c r="J8" s="70" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="59" t="s">
-        <v>1183</v>
+        <v>1207</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1184</v>
+        <v>1208</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>2</v>
@@ -8970,27 +9066,27 @@
         <v>6</v>
       </c>
       <c r="F9" s="59" t="s">
-        <v>1185</v>
+        <v>1209</v>
       </c>
       <c r="G9" s="59" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="H9" s="59" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="I9" s="59" t="s">
-        <v>1186</v>
+        <v>1210</v>
       </c>
       <c r="J9" s="70" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1187</v>
+        <v>1211</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1188</v>
+        <v>1212</v>
       </c>
       <c r="C10" s="43" t="n">
         <v>2</v>
@@ -9003,27 +9099,27 @@
         <v>10</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>1189</v>
+        <v>1213</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>1190</v>
+        <v>1214</v>
       </c>
       <c r="J10" s="70" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="59" t="s">
-        <v>1191</v>
+        <v>1215</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>1192</v>
+        <v>1216</v>
       </c>
       <c r="C11" s="43" t="n">
         <v>3</v>
@@ -9036,27 +9132,27 @@
         <v>12</v>
       </c>
       <c r="F11" s="59" t="s">
-        <v>1193</v>
+        <v>1217</v>
       </c>
       <c r="G11" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H11" s="59" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>1194</v>
+        <v>1218</v>
       </c>
       <c r="J11" s="70" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1195</v>
+        <v>1219</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1196</v>
+        <v>1220</v>
       </c>
       <c r="C12" s="43" t="n">
         <v>2</v>
@@ -9069,27 +9165,27 @@
         <v>8</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>1197</v>
+        <v>1221</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>1049</v>
+        <v>1073</v>
       </c>
       <c r="I12" s="59" t="s">
+        <v>1222</v>
+      </c>
+      <c r="J12" s="70" t="s">
         <v>1198</v>
-      </c>
-      <c r="J12" s="70" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="59" t="s">
-        <v>1199</v>
+        <v>1223</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>1200</v>
+        <v>1224</v>
       </c>
       <c r="C13" s="43" t="n">
         <v>2</v>
@@ -9102,27 +9198,27 @@
         <v>4</v>
       </c>
       <c r="F13" s="59" t="s">
-        <v>1201</v>
+        <v>1225</v>
       </c>
       <c r="G13" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="H13" s="59" t="s">
-        <v>1049</v>
+        <v>1073</v>
       </c>
       <c r="I13" s="59" t="s">
-        <v>1202</v>
+        <v>1226</v>
       </c>
       <c r="J13" s="70" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1203</v>
+        <v>1227</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1204</v>
+        <v>1228</v>
       </c>
       <c r="C14" s="43" t="n">
         <v>3</v>
@@ -9135,27 +9231,27 @@
         <v>12</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>1205</v>
+        <v>1229</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="H14" s="59" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>1206</v>
+        <v>1230</v>
       </c>
       <c r="J14" s="70" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="59" t="s">
-        <v>1207</v>
+        <v>1231</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>1208</v>
+        <v>1232</v>
       </c>
       <c r="C15" s="43" t="n">
         <v>3</v>
@@ -9168,27 +9264,27 @@
         <v>15</v>
       </c>
       <c r="F15" s="59" t="s">
-        <v>1209</v>
+        <v>1233</v>
       </c>
       <c r="G15" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="H15" s="59" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="I15" s="59" t="s">
-        <v>1210</v>
+        <v>1234</v>
       </c>
       <c r="J15" s="70" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>1211</v>
+        <v>1235</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>1212</v>
+        <v>1236</v>
       </c>
       <c r="C16" s="43" t="n">
         <v>4</v>
@@ -9201,27 +9297,27 @@
         <v>16</v>
       </c>
       <c r="F16" s="59" t="s">
-        <v>1213</v>
+        <v>1237</v>
       </c>
       <c r="G16" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H16" s="59" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="I16" s="59" t="s">
-        <v>1214</v>
+        <v>1238</v>
       </c>
       <c r="J16" s="70" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="59" t="s">
-        <v>1215</v>
+        <v>1239</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>1216</v>
+        <v>1240</v>
       </c>
       <c r="C17" s="43" t="n">
         <v>3</v>
@@ -9234,27 +9330,27 @@
         <v>12</v>
       </c>
       <c r="F17" s="59" t="s">
-        <v>1217</v>
+        <v>1241</v>
       </c>
       <c r="G17" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="59" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="I17" s="59" t="s">
-        <v>1218</v>
+        <v>1242</v>
       </c>
       <c r="J17" s="70" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>1219</v>
+        <v>1243</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1220</v>
+        <v>1244</v>
       </c>
       <c r="C18" s="43" t="n">
         <v>2</v>
@@ -9267,27 +9363,27 @@
         <v>6</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>1221</v>
+        <v>1245</v>
       </c>
       <c r="G18" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="H18" s="59" t="s">
-        <v>1065</v>
+        <v>1089</v>
       </c>
       <c r="I18" s="59" t="s">
-        <v>1222</v>
+        <v>1246</v>
       </c>
       <c r="J18" s="70" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="59" t="s">
-        <v>1223</v>
+        <v>1247</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>1224</v>
+        <v>1248</v>
       </c>
       <c r="C19" s="43" t="n">
         <v>2</v>
@@ -9300,27 +9396,27 @@
         <v>8</v>
       </c>
       <c r="F19" s="59" t="s">
-        <v>1225</v>
+        <v>1249</v>
       </c>
       <c r="G19" s="59" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="H19" s="59" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="I19" s="59" t="s">
-        <v>1226</v>
+        <v>1250</v>
       </c>
       <c r="J19" s="70" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>1227</v>
+        <v>1251</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1228</v>
+        <v>1252</v>
       </c>
       <c r="C20" s="43" t="n">
         <v>3</v>
@@ -9333,19 +9429,19 @@
         <v>15</v>
       </c>
       <c r="F20" s="59" t="s">
-        <v>1229</v>
+        <v>1253</v>
       </c>
       <c r="G20" s="59" t="s">
         <v>100</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="I20" s="59" t="s">
-        <v>1230</v>
+        <v>1254</v>
       </c>
       <c r="J20" s="70" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
   </sheetData>
@@ -9423,7 +9519,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1231</v>
+        <v>1255</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9434,278 +9530,278 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>1232</v>
+        <v>1256</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1233</v>
+        <v>1257</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1234</v>
+        <v>1258</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>1235</v>
+        <v>1259</v>
       </c>
       <c r="E4" s="58" t="s">
         <v>95</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>829</v>
+        <v>853</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1236</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1237</v>
+        <v>1261</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1238</v>
+        <v>1262</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1239</v>
+        <v>1263</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1240</v>
+        <v>1264</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>1241</v>
+        <v>1265</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>1242</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>801</v>
+        <v>825</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1243</v>
+        <v>1267</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1244</v>
+        <v>1268</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1245</v>
+        <v>1269</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>1246</v>
+        <v>1270</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>1247</v>
+        <v>1271</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>1248</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1249</v>
+        <v>1273</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1250</v>
+        <v>1274</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1251</v>
+        <v>1275</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1252</v>
+        <v>1276</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>1253</v>
+        <v>1277</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1248</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1254</v>
+        <v>1278</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1255</v>
+        <v>1279</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1256</v>
+        <v>1280</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1257</v>
+        <v>1281</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>1258</v>
+        <v>1282</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>1259</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>686</v>
+        <v>710</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1260</v>
+        <v>1284</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1261</v>
+        <v>1285</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1262</v>
+        <v>1286</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1263</v>
+        <v>1287</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>1264</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>877</v>
+        <v>901</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1265</v>
+        <v>1289</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1266</v>
+        <v>1290</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>999</v>
+        <v>1023</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>1267</v>
+        <v>1291</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>1268</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>941</v>
+        <v>965</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1269</v>
+        <v>1293</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1271</v>
+        <v>1295</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>941</v>
+        <v>965</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>1273</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>960</v>
+        <v>984</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1274</v>
+        <v>1298</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1275</v>
+        <v>1299</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>1276</v>
+        <v>1300</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>1277</v>
+        <v>1301</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>1248</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1278</v>
+        <v>1302</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1279</v>
+        <v>1303</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1280</v>
+        <v>1304</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1281</v>
+        <v>1305</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>1282</v>
+        <v>1306</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>1248</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1283</v>
+        <v>1307</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1284</v>
+        <v>1308</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1285</v>
+        <v>1309</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>1286</v>
+        <v>1310</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>1287</v>
+        <v>1311</v>
       </c>
       <c r="F14" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>1288</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1289</v>
+        <v>1313</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1290</v>
+        <v>1314</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1291</v>
+        <v>1315</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1292</v>
+        <v>1316</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>1293</v>
+        <v>1317</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>1294</v>
+        <v>1318</v>
       </c>
     </row>
   </sheetData>
@@ -9747,7 +9843,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1295</v>
+        <v>1319</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9758,24 +9854,24 @@
         <v>110</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1296</v>
+        <v>1320</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1297</v>
+        <v>1321</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>829</v>
+        <v>853</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1298</v>
+        <v>1322</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1299</v>
+        <v>1323</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1049</v>
+        <v>1073</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>100</v>
@@ -9783,55 +9879,55 @@
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>1300</v>
+        <v>1324</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1301</v>
+        <v>1325</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1302</v>
+        <v>1326</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>1303</v>
+        <v>1327</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1304</v>
+        <v>1328</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1305</v>
+        <v>1329</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1306</v>
+        <v>1330</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1307</v>
+        <v>1331</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1308</v>
+        <v>1332</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1049</v>
+        <v>1073</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>100</v>
@@ -9839,27 +9935,27 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1309</v>
+        <v>1333</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1310</v>
+        <v>1334</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>1311</v>
+        <v>1335</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1312</v>
+        <v>1336</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1065</v>
+        <v>1089</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>100</v>
@@ -9867,13 +9963,13 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1313</v>
+        <v>1337</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1314</v>
+        <v>1338</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1068</v>
+        <v>1092</v>
       </c>
       <c r="D12" s="59" t="s">
         <v>100</v>
@@ -9881,41 +9977,41 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1315</v>
+        <v>1339</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1316</v>
+        <v>1340</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1068</v>
+        <v>1092</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>996</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1317</v>
+        <v>1341</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1318</v>
+        <v>1342</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1319</v>
+        <v>1343</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1320</v>
+        <v>1344</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1321</v>
+        <v>1345</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>100</v>
@@ -9923,14 +10019,14 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>1322</v>
+        <v>1346</v>
       </c>
       <c r="B16" s="59" t="str">
         <f aca="false">"Premium at $"&amp;TEXT(Assumptions!B69,"0.00")&amp;". Launch discount no deeper than the realized-price factor on Assumptions."</f>
         <v>Premium at $19.99. Launch discount no deeper than the realized-price factor on Assumptions.</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
       <c r="D16" s="59" t="s">
         <v>100</v>
@@ -9938,13 +10034,13 @@
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>1323</v>
+        <v>1347</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1324</v>
+        <v>1348</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>100</v>
@@ -9952,13 +10048,13 @@
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1325</v>
+        <v>1349</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
       <c r="D18" s="59" t="s">
         <v>100</v>
@@ -9966,27 +10062,27 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1326</v>
+        <v>1350</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1327</v>
+        <v>1351</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1065</v>
+        <v>1089</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>1328</v>
+        <v>1352</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1329</v>
+        <v>1353</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>1065</v>
+        <v>1089</v>
       </c>
       <c r="D20" s="59" t="s">
         <v>100</v>
@@ -9994,27 +10090,27 @@
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>1330</v>
+        <v>1354</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1331</v>
+        <v>1355</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>1065</v>
+        <v>1089</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="59" t="s">
-        <v>1332</v>
+        <v>1356</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1333</v>
+        <v>1357</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>1068</v>
+        <v>1092</v>
       </c>
       <c r="D22" s="59" t="s">
         <v>100</v>
@@ -10040,32 +10136,32 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="102" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="103" t="s">
-        <v>1334</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="104" t="s">
-        <v>1335</v>
+        <v>1359</v>
       </c>
       <c r="B3" s="104"/>
       <c r="C3" s="104"/>
@@ -10075,710 +10171,734 @@
       <c r="G3" s="104"/>
       <c r="H3" s="104"/>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="58" t="s">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>1045</v>
+        <v>1069</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>1336</v>
+        <v>1360</v>
       </c>
       <c r="D5" s="58" t="s">
-        <v>1337</v>
+        <v>1361</v>
       </c>
       <c r="E5" s="58" t="s">
         <v>41</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>1338</v>
+        <v>1362</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>1339</v>
+        <v>1363</v>
       </c>
       <c r="H5" s="58" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="105" t="s">
-        <v>1340</v>
+        <v>1364</v>
       </c>
       <c r="B6" s="105" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="C6" s="105" t="s">
-        <v>1341</v>
+        <v>1365</v>
       </c>
       <c r="D6" s="105" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="E6" s="105" t="s">
-        <v>1343</v>
+        <v>1367</v>
       </c>
       <c r="F6" s="105" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="G6" s="105" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="H6" s="105" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="105" t="s">
-        <v>1346</v>
+        <v>1370</v>
       </c>
       <c r="B7" s="105" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="C7" s="105" t="s">
-        <v>1347</v>
+        <v>1371</v>
       </c>
       <c r="D7" s="105" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="E7" s="105" t="s">
-        <v>1348</v>
+        <v>1372</v>
       </c>
       <c r="F7" s="105" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="G7" s="105" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="H7" s="105" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="105" t="s">
-        <v>1349</v>
+        <v>1373</v>
       </c>
       <c r="B8" s="105" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="C8" s="105" t="s">
-        <v>1350</v>
+        <v>1374</v>
       </c>
       <c r="D8" s="105" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="E8" s="105" t="s">
-        <v>1351</v>
+        <v>1375</v>
       </c>
       <c r="F8" s="105" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="G8" s="105" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="H8" s="105" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="105" t="s">
-        <v>1352</v>
+        <v>1376</v>
       </c>
       <c r="B9" s="105" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="C9" s="105" t="s">
-        <v>1353</v>
+        <v>1377</v>
       </c>
       <c r="D9" s="105" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="E9" s="105" t="s">
-        <v>1354</v>
+        <v>1378</v>
       </c>
       <c r="F9" s="105" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="G9" s="105" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="H9" s="105" t="s">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="105" t="s">
-        <v>1356</v>
+        <v>1380</v>
       </c>
       <c r="B10" s="105" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="C10" s="105" t="s">
-        <v>1357</v>
+        <v>1381</v>
       </c>
       <c r="D10" s="105" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="E10" s="105" t="s">
-        <v>1358</v>
+        <v>1382</v>
       </c>
       <c r="F10" s="105" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="G10" s="105" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="H10" s="105" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="105" t="s">
-        <v>1359</v>
+        <v>1383</v>
       </c>
       <c r="B11" s="105" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="C11" s="105" t="s">
-        <v>1360</v>
+        <v>1384</v>
       </c>
       <c r="D11" s="105" t="s">
-        <v>1361</v>
+        <v>1385</v>
       </c>
       <c r="E11" s="105" t="s">
-        <v>1362</v>
+        <v>1386</v>
       </c>
       <c r="F11" s="105" t="s">
-        <v>1363</v>
+        <v>1387</v>
       </c>
       <c r="G11" s="105"/>
       <c r="H11" s="105" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="105" t="s">
-        <v>1364</v>
+        <v>1388</v>
       </c>
       <c r="B12" s="105" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="C12" s="105" t="s">
-        <v>1365</v>
+        <v>1389</v>
       </c>
       <c r="D12" s="105" t="s">
-        <v>1361</v>
+        <v>1385</v>
       </c>
       <c r="E12" s="105" t="s">
-        <v>1366</v>
+        <v>1390</v>
       </c>
       <c r="F12" s="105" t="s">
-        <v>1367</v>
+        <v>1391</v>
       </c>
       <c r="G12" s="105"/>
       <c r="H12" s="105" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="105" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B13" s="105" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C13" s="105" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D13" s="105" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E13" s="105" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F13" s="105" t="s">
         <v>1368</v>
       </c>
-      <c r="B13" s="105" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C13" s="105" t="s">
+      <c r="G13" s="105" t="s">
         <v>1369</v>
       </c>
-      <c r="D13" s="105" t="s">
-        <v>1342</v>
-      </c>
-      <c r="E13" s="105" t="s">
-        <v>1370</v>
-      </c>
-      <c r="F13" s="105" t="s">
-        <v>1344</v>
-      </c>
-      <c r="G13" s="105" t="s">
-        <v>1345</v>
-      </c>
       <c r="H13" s="105" t="s">
-        <v>1371</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="105" t="s">
-        <v>1372</v>
+        <v>1396</v>
       </c>
       <c r="B14" s="105" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="C14" s="105" t="s">
-        <v>1373</v>
+        <v>1397</v>
       </c>
       <c r="D14" s="105" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="E14" s="105" t="s">
-        <v>1374</v>
+        <v>1398</v>
       </c>
       <c r="F14" s="105" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="G14" s="105" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="H14" s="105" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="105" t="s">
-        <v>1376</v>
+        <v>1400</v>
       </c>
       <c r="B15" s="105" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="C15" s="105" t="s">
-        <v>1377</v>
+        <v>1401</v>
       </c>
       <c r="D15" s="105" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="E15" s="105" t="s">
-        <v>1378</v>
+        <v>1402</v>
       </c>
       <c r="F15" s="105" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="G15" s="105" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="H15" s="105" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="105" t="s">
-        <v>1379</v>
+        <v>1403</v>
       </c>
       <c r="B16" s="105" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="C16" s="105" t="s">
-        <v>1380</v>
+        <v>1404</v>
       </c>
       <c r="D16" s="105" t="s">
-        <v>1361</v>
+        <v>1385</v>
       </c>
       <c r="E16" s="105" t="s">
-        <v>1381</v>
+        <v>1405</v>
       </c>
       <c r="F16" s="105" t="s">
-        <v>1382</v>
+        <v>1406</v>
       </c>
       <c r="G16" s="105"/>
       <c r="H16" s="105" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="105" t="s">
-        <v>1383</v>
+        <v>1407</v>
       </c>
       <c r="B17" s="105" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="C17" s="105" t="s">
-        <v>1384</v>
+        <v>1408</v>
       </c>
       <c r="D17" s="105" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="E17" s="105" t="s">
+        <v>1409</v>
+      </c>
+      <c r="F17" s="105" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G17" s="105" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H17" s="105" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="105" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B18" s="105" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C18" s="105" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D18" s="105" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E18" s="105" t="s">
+        <v>1412</v>
+      </c>
+      <c r="F18" s="105" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G18" s="105" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H18" s="105" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="105" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B19" s="105" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C19" s="105" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D19" s="105" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E19" s="105" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F19" s="105" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G19" s="105" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H19" s="105" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="105" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B20" s="105" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C20" s="105" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D20" s="105" t="s">
         <v>1385</v>
       </c>
-      <c r="F17" s="105" t="s">
-        <v>1344</v>
-      </c>
-      <c r="G17" s="105" t="s">
-        <v>1345</v>
-      </c>
-      <c r="H17" s="105" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="105" t="s">
-        <v>1386</v>
-      </c>
-      <c r="B18" s="105" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C18" s="105" t="s">
-        <v>1387</v>
-      </c>
-      <c r="D18" s="105" t="s">
-        <v>1342</v>
-      </c>
-      <c r="E18" s="105" t="s">
-        <v>1388</v>
-      </c>
-      <c r="F18" s="105" t="s">
-        <v>1344</v>
-      </c>
-      <c r="G18" s="105" t="s">
-        <v>1345</v>
-      </c>
-      <c r="H18" s="105" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="105" t="s">
-        <v>1389</v>
-      </c>
-      <c r="B19" s="105" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C19" s="105" t="s">
-        <v>1390</v>
-      </c>
-      <c r="D19" s="105" t="s">
-        <v>1342</v>
-      </c>
-      <c r="E19" s="105" t="s">
-        <v>1391</v>
-      </c>
-      <c r="F19" s="105" t="s">
-        <v>1344</v>
-      </c>
-      <c r="G19" s="105" t="s">
-        <v>1345</v>
-      </c>
-      <c r="H19" s="105" t="s">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="105" t="s">
-        <v>1393</v>
-      </c>
-      <c r="B20" s="105" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C20" s="105" t="s">
-        <v>1394</v>
-      </c>
-      <c r="D20" s="105" t="s">
-        <v>1361</v>
-      </c>
       <c r="E20" s="105" t="s">
-        <v>1395</v>
+        <v>1419</v>
       </c>
       <c r="F20" s="105" t="s">
-        <v>1396</v>
+        <v>1420</v>
       </c>
       <c r="G20" s="105"/>
       <c r="H20" s="105" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="105" t="s">
-        <v>1397</v>
+        <v>1421</v>
       </c>
       <c r="B21" s="105" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="C21" s="105" t="s">
-        <v>1398</v>
+        <v>1422</v>
       </c>
       <c r="D21" s="105" t="s">
-        <v>1361</v>
+        <v>1385</v>
       </c>
       <c r="E21" s="105" t="s">
-        <v>1399</v>
+        <v>1423</v>
       </c>
       <c r="F21" s="105" t="s">
-        <v>1400</v>
+        <v>1424</v>
       </c>
       <c r="G21" s="105"/>
       <c r="H21" s="105" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="105" t="s">
-        <v>1401</v>
+        <v>1425</v>
       </c>
       <c r="B22" s="105" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
       <c r="C22" s="105" t="s">
-        <v>1402</v>
+        <v>1426</v>
       </c>
       <c r="D22" s="105" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="E22" s="105" t="s">
-        <v>1403</v>
+        <v>1427</v>
       </c>
       <c r="F22" s="105" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="G22" s="105" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="H22" s="105" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="105" t="s">
-        <v>1404</v>
+        <v>1428</v>
       </c>
       <c r="B23" s="105" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
       <c r="C23" s="105" t="s">
-        <v>1405</v>
+        <v>1429</v>
       </c>
       <c r="D23" s="105" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="E23" s="105" t="s">
-        <v>1406</v>
+        <v>1430</v>
       </c>
       <c r="F23" s="105" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="G23" s="105" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="H23" s="105" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="105" t="s">
-        <v>1407</v>
+        <v>1431</v>
       </c>
       <c r="B24" s="105" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
       <c r="C24" s="105" t="s">
-        <v>1408</v>
+        <v>1432</v>
       </c>
       <c r="D24" s="105" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="E24" s="105" t="s">
-        <v>1409</v>
+        <v>1433</v>
       </c>
       <c r="F24" s="105" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="G24" s="105" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="H24" s="105" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="105" t="s">
-        <v>1410</v>
+        <v>1434</v>
       </c>
       <c r="B25" s="105" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
       <c r="C25" s="105" t="s">
-        <v>1411</v>
+        <v>1435</v>
       </c>
       <c r="D25" s="105" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="E25" s="105" t="s">
-        <v>1412</v>
+        <v>1436</v>
       </c>
       <c r="F25" s="105" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="G25" s="105" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="H25" s="105" t="s">
-        <v>1413</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="105" t="s">
-        <v>1414</v>
+        <v>1438</v>
       </c>
       <c r="B26" s="105" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
       <c r="C26" s="105" t="s">
-        <v>1415</v>
+        <v>1439</v>
       </c>
       <c r="D26" s="105" t="s">
-        <v>1361</v>
+        <v>1385</v>
       </c>
       <c r="E26" s="105" t="s">
-        <v>1416</v>
+        <v>1440</v>
       </c>
       <c r="F26" s="105" t="s">
-        <v>1417</v>
+        <v>1441</v>
       </c>
       <c r="G26" s="105"/>
       <c r="H26" s="105" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="105" t="s">
-        <v>1418</v>
+        <v>1442</v>
       </c>
       <c r="B27" s="105" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
       <c r="C27" s="105" t="s">
-        <v>1419</v>
+        <v>1443</v>
       </c>
       <c r="D27" s="105" t="s">
-        <v>1361</v>
+        <v>1385</v>
       </c>
       <c r="E27" s="105" t="s">
-        <v>1420</v>
+        <v>1444</v>
       </c>
       <c r="F27" s="105" t="s">
-        <v>1421</v>
+        <v>1445</v>
       </c>
       <c r="G27" s="105"/>
       <c r="H27" s="105" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="105" t="s">
-        <v>1422</v>
+        <v>1446</v>
       </c>
       <c r="B28" s="105" t="s">
-        <v>1065</v>
+        <v>1089</v>
       </c>
       <c r="C28" s="105" t="s">
-        <v>1423</v>
+        <v>1447</v>
       </c>
       <c r="D28" s="105" t="s">
-        <v>1361</v>
+        <v>1385</v>
       </c>
       <c r="E28" s="105" t="s">
-        <v>1001</v>
+        <v>1025</v>
       </c>
       <c r="F28" s="105" t="s">
-        <v>1382</v>
+        <v>1406</v>
       </c>
       <c r="G28" s="105"/>
       <c r="H28" s="105" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="105" t="s">
-        <v>1424</v>
+        <v>1448</v>
       </c>
       <c r="B29" s="105" t="s">
-        <v>1065</v>
+        <v>1089</v>
       </c>
       <c r="C29" s="105" t="s">
-        <v>1425</v>
+        <v>1449</v>
       </c>
       <c r="D29" s="105" t="s">
-        <v>1361</v>
+        <v>1385</v>
       </c>
       <c r="E29" s="105" t="s">
-        <v>1426</v>
+        <v>1450</v>
       </c>
       <c r="F29" s="105" t="s">
-        <v>1427</v>
+        <v>1451</v>
       </c>
       <c r="G29" s="105"/>
       <c r="H29" s="105" t="s">
-        <v>1428</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="105" t="s">
-        <v>1429</v>
+        <v>1453</v>
       </c>
       <c r="B30" s="105" t="s">
-        <v>1065</v>
+        <v>1089</v>
       </c>
       <c r="C30" s="105" t="s">
-        <v>1430</v>
+        <v>1454</v>
       </c>
       <c r="D30" s="105" t="s">
-        <v>1361</v>
+        <v>1385</v>
       </c>
       <c r="E30" s="105" t="s">
-        <v>1431</v>
+        <v>1455</v>
       </c>
       <c r="F30" s="105" t="s">
-        <v>1417</v>
+        <v>1441</v>
       </c>
       <c r="G30" s="105"/>
       <c r="H30" s="105" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="105" t="s">
-        <v>1432</v>
+        <v>1456</v>
       </c>
       <c r="B31" s="105" t="s">
-        <v>1068</v>
+        <v>1092</v>
       </c>
       <c r="C31" s="105" t="s">
-        <v>1433</v>
+        <v>1457</v>
       </c>
       <c r="D31" s="105" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="E31" s="105" t="s">
-        <v>1434</v>
+        <v>1458</v>
       </c>
       <c r="F31" s="105" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="G31" s="105" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="H31" s="105" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="105" t="s">
-        <v>1435</v>
+        <v>1459</v>
       </c>
       <c r="B32" s="105" t="s">
-        <v>1068</v>
+        <v>1092</v>
       </c>
       <c r="C32" s="105" t="s">
-        <v>1436</v>
+        <v>1460</v>
       </c>
       <c r="D32" s="105" t="s">
-        <v>1361</v>
+        <v>1385</v>
       </c>
       <c r="E32" s="105" t="s">
-        <v>1155</v>
+        <v>1179</v>
       </c>
       <c r="F32" s="105" t="s">
-        <v>849</v>
+        <v>873</v>
       </c>
       <c r="G32" s="105"/>
       <c r="H32" s="105" t="s">
-        <v>1017</v>
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="105" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B33" s="105" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C33" s="105" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D33" s="105" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E33" s="105" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F33" s="105" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G33" s="105"/>
+      <c r="H33" s="105" t="s">
+        <v>999</v>
       </c>
     </row>
   </sheetData>
@@ -10800,33 +10920,33 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="102" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="103" t="s">
-        <v>1437</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="104" t="s">
-        <v>1438</v>
+        <v>1465</v>
       </c>
       <c r="B3" s="104"/>
       <c r="C3" s="104"/>
@@ -10837,41 +10957,41 @@
       <c r="H3" s="104"/>
       <c r="I3" s="104"/>
     </row>
-    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="58" t="s">
-        <v>1439</v>
+        <v>1466</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>552</v>
+        <v>576</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>1440</v>
+        <v>1467</v>
       </c>
       <c r="D5" s="58" t="s">
-        <v>1441</v>
+        <v>1468</v>
       </c>
       <c r="E5" s="58" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>1444</v>
+        <v>1471</v>
       </c>
       <c r="H5" s="58" t="s">
-        <v>1445</v>
+        <v>1472</v>
       </c>
       <c r="I5" s="58" t="s">
-        <v>1446</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>1447</v>
+        <v>1474</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>562</v>
+        <v>586</v>
       </c>
       <c r="C6" s="59" t="n">
         <v>20</v>
@@ -10883,10 +11003,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="G6" s="59" t="n">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="H6" s="59" t="n">
         <v>0.5</v>
@@ -10895,12 +11015,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="59" t="s">
-        <v>1447</v>
+        <v>1474</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>557</v>
+        <v>581</v>
       </c>
       <c r="C7" s="59" t="n">
         <v>20</v>
@@ -10912,10 +11032,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="59" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="G7" s="59" t="n">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="H7" s="59" t="n">
         <v>0.3</v>
@@ -10924,12 +11044,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1447</v>
+        <v>1474</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="C8" s="59" t="n">
         <v>20</v>
@@ -10941,10 +11061,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="G8" s="59" t="n">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="H8" s="59" t="n">
         <v>0.5</v>
@@ -10953,12 +11073,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="59" t="s">
-        <v>1447</v>
+        <v>1474</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>572</v>
+        <v>596</v>
       </c>
       <c r="C9" s="59" t="n">
         <v>20</v>
@@ -10970,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="59" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="G9" s="59" t="n">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="H9" s="59" t="n">
         <v>0.4</v>
@@ -10982,12 +11102,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="107" t="s">
-        <v>1447</v>
+        <v>1474</v>
       </c>
       <c r="B10" s="107" t="s">
-        <v>1448</v>
+        <v>1475</v>
       </c>
       <c r="C10" s="107" t="n">
         <v>80</v>
@@ -10999,10 +11119,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="107" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="G10" s="107" t="n">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="H10" s="107" t="n">
         <v>0.4</v>
@@ -11011,12 +11131,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="59" t="s">
-        <v>1449</v>
+        <v>1476</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>562</v>
+        <v>586</v>
       </c>
       <c r="C11" s="59" t="n">
         <v>20</v>
@@ -11028,10 +11148,10 @@
         <v>0.8</v>
       </c>
       <c r="F11" s="59" t="s">
-        <v>1450</v>
+        <v>1477</v>
       </c>
       <c r="G11" s="59" t="n">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="H11" s="59" t="n">
         <v>5.1</v>
@@ -11040,12 +11160,12 @@
         <v>33.9</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1449</v>
+        <v>1476</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>557</v>
+        <v>581</v>
       </c>
       <c r="C12" s="59" t="n">
         <v>20</v>
@@ -11057,10 +11177,10 @@
         <v>0.7</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>1451</v>
+        <v>1478</v>
       </c>
       <c r="G12" s="59" t="n">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="H12" s="59" t="n">
         <v>5.3</v>
@@ -11069,12 +11189,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="59" t="s">
-        <v>1449</v>
+        <v>1476</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="C13" s="59" t="n">
         <v>20</v>
@@ -11086,10 +11206,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="59" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="G13" s="59" t="n">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="H13" s="59" t="n">
         <v>0.1</v>
@@ -11098,12 +11218,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1449</v>
+        <v>1476</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>572</v>
+        <v>596</v>
       </c>
       <c r="C14" s="59" t="n">
         <v>20</v>
@@ -11115,10 +11235,10 @@
         <v>0.6</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>1451</v>
+        <v>1478</v>
       </c>
       <c r="G14" s="59" t="n">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="H14" s="59" t="n">
         <v>4.8</v>
@@ -11127,12 +11247,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="107" t="s">
-        <v>1449</v>
+        <v>1476</v>
       </c>
       <c r="B15" s="107" t="s">
-        <v>1448</v>
+        <v>1475</v>
       </c>
       <c r="C15" s="107" t="n">
         <v>80</v>
@@ -11144,10 +11264,10 @@
         <v>0.525</v>
       </c>
       <c r="F15" s="107" t="s">
-        <v>1452</v>
+        <v>1479</v>
       </c>
       <c r="G15" s="107" t="n">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="H15" s="107" t="n">
         <v>3.8</v>
@@ -11156,12 +11276,12 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>1453</v>
+        <v>1480</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>562</v>
+        <v>586</v>
       </c>
       <c r="C16" s="59" t="n">
         <v>20</v>
@@ -11173,7 +11293,7 @@
         <v>0.7</v>
       </c>
       <c r="F16" s="59" t="s">
-        <v>1454</v>
+        <v>1481</v>
       </c>
       <c r="G16" s="59" t="n">
         <v>127</v>
@@ -11185,12 +11305,12 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="59" t="s">
-        <v>1453</v>
+        <v>1480</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>557</v>
+        <v>581</v>
       </c>
       <c r="C17" s="59" t="n">
         <v>20</v>
@@ -11202,10 +11322,10 @@
         <v>0.65</v>
       </c>
       <c r="F17" s="59" t="s">
-        <v>1455</v>
+        <v>1482</v>
       </c>
       <c r="G17" s="59" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H17" s="59" t="n">
         <v>10.6</v>
@@ -11214,12 +11334,12 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>1453</v>
+        <v>1480</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="C18" s="59" t="n">
         <v>20</v>
@@ -11231,10 +11351,10 @@
         <v>0.85</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>1456</v>
+        <v>1483</v>
       </c>
       <c r="G18" s="59" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H18" s="59" t="n">
         <v>9.7</v>
@@ -11243,12 +11363,12 @@
         <v>32.2</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="59" t="s">
-        <v>1453</v>
+        <v>1480</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>572</v>
+        <v>596</v>
       </c>
       <c r="C19" s="59" t="n">
         <v>20</v>
@@ -11260,10 +11380,10 @@
         <v>0.6</v>
       </c>
       <c r="F19" s="59" t="s">
-        <v>1457</v>
+        <v>1484</v>
       </c>
       <c r="G19" s="59" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H19" s="59" t="n">
         <v>10.2</v>
@@ -11272,12 +11392,12 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="107" t="s">
-        <v>1453</v>
+        <v>1480</v>
       </c>
       <c r="B20" s="107" t="s">
-        <v>1448</v>
+        <v>1475</v>
       </c>
       <c r="C20" s="107" t="n">
         <v>80</v>
@@ -11289,10 +11409,10 @@
         <v>0.7</v>
       </c>
       <c r="F20" s="107" t="s">
-        <v>1458</v>
+        <v>1485</v>
       </c>
       <c r="G20" s="107" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H20" s="107" t="n">
         <v>9.8</v>
@@ -11301,14 +11421,14 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="109" t="s">
-        <v>1459</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="110" t="s">
-        <v>1460</v>
+        <v>1487</v>
       </c>
       <c r="B23" s="110"/>
       <c r="C23" s="110"/>
@@ -11319,9 +11439,9 @@
       <c r="H23" s="110"/>
       <c r="I23" s="110"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="110" t="s">
-        <v>1461</v>
+        <v>1488</v>
       </c>
       <c r="B24" s="110"/>
       <c r="C24" s="110"/>
@@ -11332,9 +11452,9 @@
       <c r="H24" s="110"/>
       <c r="I24" s="110"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="110" t="s">
-        <v>1462</v>
+        <v>1489</v>
       </c>
       <c r="B25" s="110"/>
       <c r="C25" s="110"/>
@@ -11345,14 +11465,14 @@
       <c r="H25" s="110"/>
       <c r="I25" s="110"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="109" t="s">
-        <v>1463</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="104" t="s">
-        <v>1464</v>
+        <v>1491</v>
       </c>
       <c r="B28" s="104"/>
       <c r="C28" s="104"/>
@@ -11365,7 +11485,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="104" t="s">
-        <v>1465</v>
+        <v>1492</v>
       </c>
       <c r="B29" s="104"/>
       <c r="C29" s="104"/>
@@ -11378,7 +11498,7 @@
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="104" t="s">
-        <v>1466</v>
+        <v>1493</v>
       </c>
       <c r="B30" s="104"/>
       <c r="C30" s="104"/>
@@ -11391,7 +11511,7 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="104" t="s">
-        <v>1467</v>
+        <v>1494</v>
       </c>
       <c r="B31" s="104"/>
       <c r="C31" s="104"/>
@@ -11402,8 +11522,34 @@
       <c r="H31" s="104"/>
       <c r="I31" s="104"/>
     </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="104" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B32" s="104"/>
+      <c r="C32" s="104"/>
+      <c r="D32" s="104"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="104"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="104"/>
+      <c r="I32" s="104"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="104" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B33" s="104"/>
+      <c r="C33" s="104"/>
+      <c r="D33" s="104"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="104"/>
+      <c r="I33" s="104"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A24:I24"/>
@@ -11412,6 +11558,8 @@
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A33:I33"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11429,7 +11577,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -11448,7 +11596,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1468</v>
+        <v>1497</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11456,16 +11604,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1469</v>
+        <v>1498</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1470</v>
+        <v>1499</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1471</v>
+        <v>1500</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1472</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11473,13 +11621,13 @@
         <v>46311</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1473</v>
+        <v>1502</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1474</v>
+        <v>1503</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1475</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11487,13 +11635,13 @@
         <v>46311</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1473</v>
+        <v>1502</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1476</v>
+        <v>1505</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>1477</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11501,13 +11649,13 @@
         <v>46311</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1473</v>
+        <v>1502</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1478</v>
+        <v>1507</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1479</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11515,13 +11663,13 @@
         <v>46311</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1103</v>
+        <v>1127</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1480</v>
+        <v>1509</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1481</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11529,13 +11677,13 @@
         <v>46311</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1482</v>
+        <v>1511</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1483</v>
+        <v>1512</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1484</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11546,10 +11694,10 @@
         <v>53</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1485</v>
+        <v>1514</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>1486</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11557,13 +11705,13 @@
         <v>46311</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1487</v>
+        <v>1516</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1488</v>
+        <v>1517</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1489</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11571,13 +11719,13 @@
         <v>46311</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1490</v>
+        <v>1519</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>1491</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11585,13 +11733,13 @@
         <v>46311</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1492</v>
+        <v>1521</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1493</v>
+        <v>1522</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1494</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11599,13 +11747,13 @@
         <v>46311</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1495</v>
+        <v>1524</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1496</v>
+        <v>1525</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>1497</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11616,10 +11764,10 @@
         <v>58</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1498</v>
+        <v>1527</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1499</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11627,13 +11775,13 @@
         <v>46311</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>1500</v>
+        <v>1529</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>1501</v>
+        <v>1530</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>1502</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11644,10 +11792,10 @@
         <v>62</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1503</v>
+        <v>1532</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1504</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11655,13 +11803,13 @@
         <v>46311</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>616</v>
+        <v>640</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>1505</v>
+        <v>1534</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>1506</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11669,13 +11817,13 @@
         <v>46311</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>892</v>
+        <v>916</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1507</v>
+        <v>1536</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>1508</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11683,13 +11831,13 @@
         <v>46311</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1509</v>
+        <v>1538</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>1510</v>
+        <v>1539</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>1511</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11697,13 +11845,13 @@
         <v>46313</v>
       </c>
       <c r="B21" s="59" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="C21" s="59" t="s">
-        <v>1512</v>
+        <v>1541</v>
       </c>
       <c r="D21" s="59" t="s">
-        <v>1513</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11711,13 +11859,13 @@
         <v>46313</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1514</v>
+        <v>1543</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>1515</v>
+        <v>1544</v>
       </c>
       <c r="D22" s="59" t="s">
-        <v>1516</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11725,13 +11873,13 @@
         <v>46313</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>1514</v>
+        <v>1543</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>1517</v>
+        <v>1546</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>1518</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11739,13 +11887,13 @@
         <v>46313</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>1514</v>
+        <v>1543</v>
       </c>
       <c r="C24" s="59" t="s">
-        <v>1519</v>
+        <v>1548</v>
       </c>
       <c r="D24" s="59" t="s">
-        <v>1520</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11753,13 +11901,13 @@
         <v>46313</v>
       </c>
       <c r="B25" s="59" t="s">
-        <v>1514</v>
+        <v>1543</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>1521</v>
+        <v>1550</v>
       </c>
       <c r="D25" s="59" t="s">
-        <v>1522</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11767,27 +11915,41 @@
         <v>46313</v>
       </c>
       <c r="B26" s="59" t="s">
-        <v>1523</v>
+        <v>1552</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>1524</v>
+        <v>1553</v>
       </c>
       <c r="D26" s="59" t="s">
-        <v>1525</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="112" t="n">
         <v>46313</v>
       </c>
       <c r="B27" s="59" t="s">
-        <v>1526</v>
+        <v>1555</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>1527</v>
+        <v>1556</v>
       </c>
       <c r="D27" s="59" t="s">
-        <v>1528</v>
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="112" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B28" s="59" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C28" s="59" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D28" s="59" t="s">
+        <v>1560</v>
       </c>
     </row>
   </sheetData>
@@ -11811,7 +11973,7 @@
     <tabColor rgb="FFC4A46A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F259"/>
+  <dimension ref="A1:F275"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
@@ -14311,7 +14473,7 @@
         <v>476</v>
       </c>
       <c r="B251" s="43" t="n">
-        <v>2</v>
+        <v>0.65</v>
       </c>
       <c r="C251" s="41" t="s">
         <v>477</v>
@@ -14403,6 +14565,165 @@
       </c>
       <c r="C259" s="41" t="s">
         <v>491</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A261" s="57" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A262" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B262" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C262" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A263" s="42" t="s">
+        <v>493</v>
+      </c>
+      <c r="B263" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="C263" s="41" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A264" s="42" t="s">
+        <v>495</v>
+      </c>
+      <c r="B264" s="43" t="n">
+        <v>152</v>
+      </c>
+      <c r="C264" s="41" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A265" s="42" t="s">
+        <v>497</v>
+      </c>
+      <c r="B265" s="43" t="n">
+        <v>205</v>
+      </c>
+      <c r="C265" s="41" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A266" s="42" t="s">
+        <v>499</v>
+      </c>
+      <c r="B266" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C266" s="41" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A267" s="42" t="s">
+        <v>501</v>
+      </c>
+      <c r="B267" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C267" s="41" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A268" s="42" t="s">
+        <v>503</v>
+      </c>
+      <c r="B268" s="43" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C268" s="41" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A269" s="42" t="s">
+        <v>505</v>
+      </c>
+      <c r="B269" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C269" s="41" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A270" s="42" t="s">
+        <v>507</v>
+      </c>
+      <c r="B270" s="43" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C270" s="41" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A271" s="42" t="s">
+        <v>509</v>
+      </c>
+      <c r="B271" s="43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C271" s="41" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A272" s="42" t="s">
+        <v>510</v>
+      </c>
+      <c r="B272" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C272" s="41" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A273" s="42" t="s">
+        <v>511</v>
+      </c>
+      <c r="B273" s="43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C273" s="41" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A274" s="42" t="s">
+        <v>512</v>
+      </c>
+      <c r="B274" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C274" s="41" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A275" s="42" t="s">
+        <v>514</v>
+      </c>
+      <c r="B275" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C275" s="41" t="s">
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -14469,7 +14790,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>492</v>
+        <v>516</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -14478,160 +14799,160 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>494</v>
+        <v>518</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>495</v>
+        <v>519</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>496</v>
+        <v>520</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>497</v>
+        <v>521</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>499</v>
+        <v>523</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>500</v>
+        <v>524</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>501</v>
+        <v>525</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>503</v>
+        <v>527</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>504</v>
+        <v>528</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>505</v>
+        <v>529</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>506</v>
+        <v>530</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>507</v>
+        <v>531</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>508</v>
+        <v>532</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>511</v>
+        <v>535</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>513</v>
+        <v>537</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>514</v>
+        <v>538</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>515</v>
+        <v>539</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>516</v>
+        <v>540</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>517</v>
+        <v>541</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>519</v>
+        <v>543</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>521</v>
+        <v>545</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>522</v>
+        <v>546</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>523</v>
+        <v>547</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>524</v>
+        <v>548</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>525</v>
+        <v>549</v>
       </c>
       <c r="D11" s="27" t="s">
+        <v>550</v>
+      </c>
+      <c r="E11" s="27" t="s">
         <v>526</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>527</v>
+        <v>551</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>529</v>
+        <v>553</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>530</v>
+        <v>554</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -14640,16 +14961,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>534</v>
+        <v>558</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>535</v>
+        <v>559</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>95</v>
@@ -14657,58 +14978,58 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="60" t="s">
-        <v>536</v>
+        <v>560</v>
       </c>
       <c r="B16" s="60" t="s">
-        <v>537</v>
+        <v>561</v>
       </c>
       <c r="C16" s="60" t="s">
-        <v>538</v>
+        <v>562</v>
       </c>
       <c r="D16" s="60" t="s">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="E16" s="60" t="s">
-        <v>540</v>
+        <v>564</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="59" t="s">
-        <v>541</v>
+        <v>565</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>542</v>
+        <v>566</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>543</v>
+        <v>567</v>
       </c>
       <c r="D17" s="59" t="s">
-        <v>544</v>
+        <v>568</v>
       </c>
       <c r="E17" s="59" t="s">
-        <v>545</v>
+        <v>569</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="60" t="s">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="B18" s="60" t="s">
-        <v>547</v>
+        <v>571</v>
       </c>
       <c r="C18" s="60" t="s">
-        <v>548</v>
+        <v>572</v>
       </c>
       <c r="D18" s="60" t="s">
-        <v>549</v>
+        <v>573</v>
       </c>
       <c r="E18" s="60" t="s">
-        <v>550</v>
+        <v>574</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>551</v>
+        <v>575</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="24"/>
@@ -14717,87 +15038,87 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>552</v>
+        <v>576</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>553</v>
+        <v>577</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>555</v>
+        <v>579</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>556</v>
+        <v>580</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>557</v>
+        <v>581</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>558</v>
+        <v>582</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>559</v>
+        <v>583</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>560</v>
+        <v>584</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>561</v>
+        <v>585</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="59" t="s">
-        <v>562</v>
+        <v>586</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>563</v>
+        <v>587</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>564</v>
+        <v>588</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>565</v>
+        <v>589</v>
       </c>
       <c r="E23" s="59" t="s">
-        <v>566</v>
+        <v>590</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>568</v>
+        <v>592</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>570</v>
+        <v>594</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>571</v>
+        <v>595</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="59" t="s">
-        <v>572</v>
+        <v>596</v>
       </c>
       <c r="B25" s="59" t="s">
-        <v>568</v>
+        <v>592</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>573</v>
+        <v>597</v>
       </c>
       <c r="D25" s="59" t="s">
-        <v>574</v>
+        <v>598</v>
       </c>
       <c r="E25" s="59" t="s">
-        <v>575</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -14850,7 +15171,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -14861,33 +15182,33 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="F4" s="58" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>134</v>
@@ -14897,37 +15218,37 @@
         <v>24</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>587</v>
+        <v>611</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>588</v>
+        <v>612</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="D6" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="F6" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>591</v>
+        <v>615</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14935,71 +15256,71 @@
         <v>228</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="D7" s="61" t="n">
         <f aca="false">Assumptions!B44</f>
         <v>120</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>595</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>596</v>
+        <v>620</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>597</v>
+        <v>621</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="D8" s="61" t="n">
         <f aca="false">Assumptions!B46</f>
         <v>400</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>599</v>
+        <v>623</v>
       </c>
       <c r="F8" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>600</v>
+        <v>624</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>603</v>
+        <v>627</v>
       </c>
       <c r="D9" s="61" t="n">
         <f aca="false">Assumptions!B45</f>
         <v>120</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>604</v>
+        <v>628</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15007,151 +15328,151 @@
         <v>219</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>606</v>
+        <v>630</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>608</v>
+        <v>632</v>
       </c>
       <c r="F10" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>610</v>
+        <v>634</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>611</v>
+        <v>635</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>612</v>
+        <v>636</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>613</v>
+        <v>637</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>614</v>
+        <v>638</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>616</v>
+        <v>640</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>617</v>
+        <v>641</v>
       </c>
       <c r="F12" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>618</v>
+        <v>642</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>619</v>
+        <v>643</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>620</v>
+        <v>644</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="D13" s="61" t="n">
         <f aca="false">Assumptions!B43</f>
         <v>168</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>622</v>
+        <v>646</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>623</v>
+        <v>647</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>624</v>
+        <v>648</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>625</v>
+        <v>649</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="D14" s="61" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>627</v>
+        <v>651</v>
       </c>
       <c r="F14" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>628</v>
+        <v>652</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>629</v>
+        <v>653</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>630</v>
+        <v>654</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>631</v>
+        <v>655</v>
       </c>
       <c r="D15" s="61" t="n">
         <f aca="false">Assumptions!B50</f>
         <v>5</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>632</v>
+        <v>656</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>633</v>
+        <v>657</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>634</v>
+        <v>658</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>635</v>
+        <v>659</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>636</v>
+        <v>660</v>
       </c>
       <c r="D16" s="61" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -15164,78 +15485,78 @@
         <v>102</v>
       </c>
       <c r="G16" s="59" t="s">
-        <v>637</v>
+        <v>661</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>638</v>
+        <v>662</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>639</v>
+        <v>663</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>640</v>
+        <v>664</v>
       </c>
       <c r="D17" s="61" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>641</v>
+        <v>665</v>
       </c>
       <c r="F17" s="27" t="s">
         <v>102</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>642</v>
+        <v>666</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>643</v>
+        <v>667</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>644</v>
+        <v>668</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>645</v>
+        <v>669</v>
       </c>
       <c r="F18" s="59" t="s">
         <v>104</v>
       </c>
       <c r="G18" s="59" t="s">
-        <v>646</v>
+        <v>670</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>647</v>
+        <v>671</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>648</v>
+        <v>672</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>649</v>
+        <v>673</v>
       </c>
       <c r="D19" s="61" t="n">
         <f aca="false">Assumptions!B47</f>
         <v>3</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>650</v>
+        <v>674</v>
       </c>
       <c r="F19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>651</v>
+        <v>675</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15243,46 +15564,46 @@
         <v>224</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>652</v>
+        <v>676</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="E20" s="59" t="s">
-        <v>653</v>
+        <v>677</v>
       </c>
       <c r="F20" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G20" s="59" t="s">
-        <v>654</v>
+        <v>678</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>655</v>
+        <v>679</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>656</v>
+        <v>680</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="D21" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
         <v>24</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>657</v>
+        <v>681</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>658</v>
+        <v>682</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15290,55 +15611,55 @@
         <v>236</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>659</v>
+        <v>683</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>660</v>
+        <v>684</v>
       </c>
       <c r="D22" s="61" t="n">
         <f aca="false">Assumptions!B57</f>
         <v>2</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>661</v>
+        <v>685</v>
       </c>
       <c r="F22" s="59" t="s">
         <v>100</v>
       </c>
       <c r="G22" s="59" t="s">
-        <v>662</v>
+        <v>686</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>663</v>
+        <v>687</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>664</v>
+        <v>688</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="D23" s="61" t="n">
         <f aca="false">Assumptions!B48</f>
         <v>2</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>665</v>
+        <v>689</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>666</v>
+        <v>690</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="59" t="s">
-        <v>667</v>
+        <v>691</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="C24" s="59" t="s">
         <v>134</v>
@@ -15348,13 +15669,13 @@
         <v>24</v>
       </c>
       <c r="E24" s="59" t="s">
-        <v>669</v>
+        <v>693</v>
       </c>
       <c r="F24" s="59" t="s">
         <v>98</v>
       </c>
       <c r="G24" s="59" t="s">
-        <v>670</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -15400,7 +15721,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>671</v>
+        <v>695</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -15409,7 +15730,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>672</v>
+        <v>696</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -15424,21 +15745,21 @@
         <v>42</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>673</v>
+        <v>697</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>674</v>
+        <v>698</v>
       </c>
       <c r="B6" s="62" t="n">
         <f aca="false">Assumptions!B62</f>
         <v>1200</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>675</v>
+        <v>699</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
@@ -15452,21 +15773,21 @@
         <v>120</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>676</v>
+        <v>700</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>677</v>
+        <v>701</v>
       </c>
       <c r="B8" s="63" t="n">
         <f aca="false">IF(B7=0,0,B6/B7)</f>
         <v>10</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>678</v>
+        <v>702</v>
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="33"/>
@@ -15480,7 +15801,7 @@
         <v>1.3</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>679</v>
+        <v>703</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
@@ -15494,14 +15815,14 @@
         <v>13</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>680</v>
+        <v>704</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>681</v>
+        <v>705</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -15510,24 +15831,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>682</v>
+        <v>706</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>683</v>
+        <v>707</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>684</v>
+        <v>708</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>685</v>
+        <v>709</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>686</v>
+        <v>710</v>
       </c>
       <c r="B14" s="61" t="n">
         <f aca="false">Assumptions!B42</f>
@@ -15542,12 +15863,12 @@
         <v>9.6</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>687</v>
+        <v>711</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>688</v>
+        <v>712</v>
       </c>
       <c r="B15" s="61" t="n">
         <f aca="false">Assumptions!B57</f>
@@ -15562,12 +15883,12 @@
         <v>3</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>689</v>
+        <v>713</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>690</v>
+        <v>714</v>
       </c>
       <c r="B16" s="61" t="n">
         <f aca="false">Assumptions!B58</f>
@@ -15585,7 +15906,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>622</v>
+        <v>646</v>
       </c>
       <c r="B17" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B43,0)</f>
@@ -15599,12 +15920,12 @@
         <v>2</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>691</v>
+        <v>715</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>692</v>
+        <v>716</v>
       </c>
       <c r="B18" s="32" t="n">
         <f aca="false">ROUNDUP(B14*$B$10/Assumptions!B44,0)</f>
@@ -15618,12 +15939,12 @@
         <v>3</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>693</v>
+        <v>717</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="B19" s="32" t="n">
         <f aca="false">ROUNDUP((B15+B16*Assumptions!B60)*$B$10/Assumptions!B59,0)</f>
@@ -15637,12 +15958,12 @@
         <v>2</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>695</v>
+        <v>719</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>696</v>
+        <v>720</v>
       </c>
       <c r="B20" s="61" t="n">
         <f aca="false">Assumptions!B61</f>
@@ -15661,7 +15982,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>697</v>
+        <v>721</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -15673,7 +15994,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>698</v>
+        <v>722</v>
       </c>
       <c r="D22" s="65" t="n">
         <f aca="false">Assumptions!B41</f>
@@ -15682,7 +16003,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="67" t="s">
-        <v>699</v>
+        <v>723</v>
       </c>
       <c r="B23" s="67"/>
       <c r="C23" s="67"/>
@@ -15697,7 +16018,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>700</v>
+        <v>724</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -15706,24 +16027,24 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>682</v>
+        <v>706</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>683</v>
+        <v>707</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>684</v>
+        <v>708</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>685</v>
+        <v>709</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>701</v>
+        <v>725</v>
       </c>
       <c r="B27" s="61" t="n">
         <f aca="false">Assumptions!B64</f>
@@ -15743,7 +16064,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="59" t="s">
-        <v>702</v>
+        <v>726</v>
       </c>
       <c r="B28" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B43,0)</f>
@@ -15757,12 +16078,12 @@
         <v>1</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>703</v>
+        <v>727</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>704</v>
+        <v>728</v>
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">ROUNDUP(B27*$B$10/Assumptions!B44,0)</f>
@@ -15779,7 +16100,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>705</v>
+        <v>729</v>
       </c>
       <c r="D30" s="63" t="n">
         <f aca="false">SUM(D27:D29)</f>
@@ -15788,7 +16109,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>706</v>
+        <v>730</v>
       </c>
       <c r="D31" s="63" t="n">
         <f aca="false">Assumptions!B41-D30</f>
@@ -15797,7 +16118,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="D32" s="32" t="n">
         <f aca="false">INT(D31/Assumptions!B65)</f>
@@ -15806,7 +16127,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>708</v>
+        <v>732</v>
       </c>
       <c r="D33" s="61" t="n">
         <f aca="false">Assumptions!B49</f>
@@ -15815,7 +16136,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="67" t="s">
-        <v>634</v>
+        <v>658</v>
       </c>
       <c r="B34" s="67"/>
       <c r="C34" s="67"/>
@@ -15830,7 +16151,7 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="54" t="s">
-        <v>709</v>
+        <v>733</v>
       </c>
       <c r="B36" s="54"/>
       <c r="C36" s="54"/>
@@ -15911,7 +16232,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>710</v>
+        <v>734</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -15926,392 +16247,392 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="B4" s="58" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>711</v>
+        <v>735</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>712</v>
+        <v>736</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>713</v>
+        <v>737</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>714</v>
+        <v>738</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>715</v>
+        <v>739</v>
       </c>
       <c r="H4" s="58" t="s">
-        <v>716</v>
+        <v>740</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>717</v>
+        <v>741</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>718</v>
+        <v>742</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>719</v>
+        <v>743</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>720</v>
+        <v>744</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>721</v>
+        <v>745</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>722</v>
+        <v>746</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>723</v>
+        <v>747</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>724</v>
+        <v>748</v>
       </c>
       <c r="H5" s="70" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>725</v>
+        <v>749</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>726</v>
+        <v>750</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>727</v>
+        <v>751</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>728</v>
+        <v>752</v>
       </c>
       <c r="B6" s="59" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>729</v>
+        <v>753</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>730</v>
+        <v>754</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>731</v>
+        <v>755</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>732</v>
+        <v>756</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>733</v>
+        <v>757</v>
       </c>
       <c r="H6" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>734</v>
+        <v>758</v>
       </c>
       <c r="J6" s="59" t="s">
-        <v>735</v>
+        <v>759</v>
       </c>
       <c r="K6" s="59" t="s">
-        <v>736</v>
+        <v>760</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>737</v>
+        <v>761</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>738</v>
+        <v>762</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>739</v>
+        <v>763</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>740</v>
+        <v>764</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>741</v>
+        <v>765</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>742</v>
+        <v>766</v>
       </c>
       <c r="H7" s="70" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>743</v>
+        <v>767</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>744</v>
+        <v>768</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>745</v>
+        <v>769</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>746</v>
+        <v>770</v>
       </c>
       <c r="B8" s="59" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>747</v>
+        <v>771</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>748</v>
+        <v>772</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>749</v>
+        <v>773</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>750</v>
+        <v>774</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>751</v>
+        <v>775</v>
       </c>
       <c r="H8" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>752</v>
+        <v>776</v>
       </c>
       <c r="J8" s="59" t="s">
-        <v>753</v>
+        <v>777</v>
       </c>
       <c r="K8" s="59" t="s">
-        <v>754</v>
+        <v>778</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>755</v>
+        <v>779</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>756</v>
+        <v>780</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>757</v>
+        <v>781</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>758</v>
+        <v>782</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>759</v>
+        <v>783</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>760</v>
+        <v>784</v>
       </c>
       <c r="H9" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>761</v>
+        <v>785</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>762</v>
+        <v>786</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>763</v>
+        <v>787</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>764</v>
+        <v>788</v>
       </c>
       <c r="B10" s="59" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>765</v>
+        <v>789</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>766</v>
+        <v>790</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>767</v>
+        <v>791</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>768</v>
+        <v>792</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>769</v>
+        <v>793</v>
       </c>
       <c r="H10" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>770</v>
+        <v>794</v>
       </c>
       <c r="J10" s="59" t="s">
-        <v>771</v>
+        <v>795</v>
       </c>
       <c r="K10" s="59" t="s">
-        <v>772</v>
+        <v>796</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>773</v>
+        <v>797</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>774</v>
+        <v>798</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>775</v>
+        <v>799</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>776</v>
+        <v>800</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>777</v>
+        <v>801</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>778</v>
+        <v>802</v>
       </c>
       <c r="H11" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>779</v>
+        <v>803</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>780</v>
+        <v>804</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>781</v>
+        <v>805</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>782</v>
+        <v>806</v>
       </c>
       <c r="B12" s="59" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>783</v>
+        <v>807</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>784</v>
+        <v>808</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>785</v>
+        <v>809</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>786</v>
+        <v>810</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>787</v>
+        <v>811</v>
       </c>
       <c r="H12" s="70" t="n">
         <v>3</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>788</v>
+        <v>812</v>
       </c>
       <c r="J12" s="59" t="s">
-        <v>789</v>
+        <v>813</v>
       </c>
       <c r="K12" s="59" t="s">
-        <v>790</v>
+        <v>814</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>791</v>
+        <v>815</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>792</v>
+        <v>816</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>793</v>
+        <v>817</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>794</v>
+        <v>818</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>795</v>
+        <v>819</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>796</v>
+        <v>820</v>
       </c>
       <c r="H13" s="70" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>797</v>
+        <v>821</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>798</v>
+        <v>822</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>799</v>
+        <v>823</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>800</v>
+        <v>824</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>801</v>
+        <v>825</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>802</v>
+        <v>826</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>803</v>
+        <v>827</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>804</v>
+        <v>828</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>805</v>
+        <v>829</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>806</v>
+        <v>830</v>
       </c>
       <c r="H14" s="70" t="n">
         <v>2</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>807</v>
+        <v>831</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>808</v>
+        <v>832</v>
       </c>
       <c r="K14" s="59" t="s">
-        <v>809</v>
+        <v>833</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>810</v>
+        <v>834</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
@@ -16323,10 +16644,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>811</v>
+        <v>835</v>
       </c>
       <c r="B17" s="71" t="s">
-        <v>812</v>
+        <v>836</v>
       </c>
       <c r="C17" s="71"/>
       <c r="D17" s="71"/>
@@ -16337,10 +16658,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>813</v>
+        <v>837</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>814</v>
+        <v>838</v>
       </c>
       <c r="C18" s="71"/>
       <c r="D18" s="71"/>
@@ -16351,10 +16672,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>815</v>
+        <v>839</v>
       </c>
       <c r="B19" s="71" t="s">
-        <v>816</v>
+        <v>840</v>
       </c>
       <c r="C19" s="71"/>
       <c r="D19" s="71"/>
@@ -16365,10 +16686,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>817</v>
+        <v>841</v>
       </c>
       <c r="B20" s="71" t="s">
-        <v>818</v>
+        <v>842</v>
       </c>
       <c r="C20" s="71"/>
       <c r="D20" s="71"/>
@@ -16379,10 +16700,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>819</v>
+        <v>843</v>
       </c>
       <c r="B21" s="71" t="s">
-        <v>820</v>
+        <v>844</v>
       </c>
       <c r="C21" s="71"/>
       <c r="D21" s="71"/>
@@ -16393,10 +16714,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>821</v>
+        <v>845</v>
       </c>
       <c r="B22" s="71" t="s">
-        <v>822</v>
+        <v>846</v>
       </c>
       <c r="C22" s="71"/>
       <c r="D22" s="71"/>
@@ -16407,10 +16728,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>823</v>
+        <v>847</v>
       </c>
       <c r="B23" s="71" t="s">
-        <v>824</v>
+        <v>848</v>
       </c>
       <c r="C23" s="71"/>
       <c r="D23" s="71"/>
@@ -16421,7 +16742,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="72" t="s">
-        <v>825</v>
+        <v>849</v>
       </c>
     </row>
   </sheetData>
@@ -16485,7 +16806,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>826</v>
+        <v>850</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -16499,42 +16820,42 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>827</v>
+        <v>851</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>828</v>
+        <v>852</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>829</v>
+        <v>853</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>830</v>
+        <v>854</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>831</v>
+        <v>855</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>832</v>
+        <v>856</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>833</v>
+        <v>857</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>834</v>
+        <v>858</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
@@ -16543,190 +16864,190 @@
         <v>96</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="G5" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="I5" s="70" t="s">
-        <v>836</v>
+        <v>860</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>837</v>
+        <v>861</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>838</v>
+        <v>862</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>839</v>
+        <v>863</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>840</v>
+        <v>864</v>
       </c>
       <c r="D6" s="59" t="s">
         <v>96</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="G6" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>833</v>
+        <v>857</v>
       </c>
       <c r="I6" s="70" t="s">
-        <v>836</v>
+        <v>860</v>
       </c>
       <c r="J6" s="59" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>843</v>
+        <v>867</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>844</v>
+        <v>868</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>840</v>
+        <v>864</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="G7" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>838</v>
+        <v>862</v>
       </c>
       <c r="I7" s="70" t="s">
-        <v>836</v>
+        <v>860</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>845</v>
+        <v>869</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>846</v>
+        <v>870</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>847</v>
+        <v>871</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="D8" s="59" t="s">
         <v>96</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F8" s="59" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="G8" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="I8" s="70" t="s">
-        <v>849</v>
+        <v>873</v>
       </c>
       <c r="J8" s="59" t="s">
-        <v>850</v>
+        <v>874</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>851</v>
+        <v>875</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="G9" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="I9" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>854</v>
+        <v>878</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>856</v>
+        <v>880</v>
       </c>
       <c r="D10" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="G10" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="I10" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J10" s="59" t="s">
-        <v>857</v>
+        <v>881</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>725</v>
+        <v>749</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>858</v>
+        <v>882</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>23</v>
@@ -16735,30 +17056,30 @@
         <v>98</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="G11" s="43" t="n">
         <v>12</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="I11" s="70" t="s">
-        <v>836</v>
+        <v>860</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>859</v>
+        <v>883</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>734</v>
+        <v>758</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>860</v>
+        <v>884</v>
       </c>
       <c r="C12" s="59" t="s">
         <v>23</v>
@@ -16767,30 +17088,30 @@
         <v>98</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="G12" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>725</v>
+        <v>749</v>
       </c>
       <c r="I12" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J12" s="59" t="s">
-        <v>861</v>
+        <v>885</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>743</v>
+        <v>767</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>862</v>
+        <v>886</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>26</v>
@@ -16799,62 +17120,62 @@
         <v>98</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="G13" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="I13" s="70" t="s">
-        <v>836</v>
+        <v>860</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>863</v>
+        <v>887</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>864</v>
+        <v>888</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>865</v>
+        <v>889</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="D14" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="G14" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H14" s="59" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="I14" s="70" t="s">
-        <v>836</v>
+        <v>860</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>866</v>
+        <v>890</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>779</v>
+        <v>803</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>867</v>
+        <v>891</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>35</v>
@@ -16863,263 +17184,263 @@
         <v>98</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="G15" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>864</v>
+        <v>888</v>
       </c>
       <c r="I15" s="70" t="s">
-        <v>836</v>
+        <v>860</v>
       </c>
       <c r="J15" s="27" t="s">
-        <v>868</v>
+        <v>892</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>869</v>
+        <v>893</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>870</v>
+        <v>894</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>712</v>
+        <v>736</v>
       </c>
       <c r="D16" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E16" s="59" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F16" s="59" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="G16" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H16" s="59" t="s">
-        <v>725</v>
+        <v>749</v>
       </c>
       <c r="I16" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J16" s="59" t="s">
-        <v>871</v>
+        <v>895</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>651</v>
+        <v>675</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>872</v>
+        <v>896</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>873</v>
+        <v>897</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="G17" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="I17" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>874</v>
+        <v>898</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>875</v>
+        <v>899</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>876</v>
+        <v>900</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>877</v>
+        <v>901</v>
       </c>
       <c r="D18" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="G18" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H18" s="59" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="I18" s="70" t="s">
-        <v>849</v>
+        <v>873</v>
       </c>
       <c r="J18" s="59" t="s">
-        <v>878</v>
+        <v>902</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>595</v>
+        <v>619</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>879</v>
+        <v>903</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="G19" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="I19" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>880</v>
+        <v>904</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>881</v>
+        <v>905</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>856</v>
+        <v>880</v>
       </c>
       <c r="D20" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E20" s="59" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F20" s="59" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="G20" s="43" t="n">
         <v>4</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>725</v>
+        <v>749</v>
       </c>
       <c r="I20" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J20" s="59" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>883</v>
+        <v>907</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>884</v>
+        <v>908</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>885</v>
+        <v>909</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="G21" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="I21" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J21" s="27" t="s">
-        <v>886</v>
+        <v>910</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="59" t="s">
-        <v>887</v>
+        <v>911</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>888</v>
+        <v>912</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>712</v>
+        <v>736</v>
       </c>
       <c r="D22" s="59" t="s">
         <v>98</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F22" s="59" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="G22" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="59" t="s">
-        <v>869</v>
+        <v>893</v>
       </c>
       <c r="I22" s="70" t="s">
-        <v>849</v>
+        <v>873</v>
       </c>
       <c r="J22" s="59" t="s">
-        <v>889</v>
+        <v>913</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>890</v>
+        <v>914</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>891</v>
+        <v>915</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>892</v>
+        <v>916</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>893</v>
+        <v>917</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>100</v>
@@ -17128,117 +17449,117 @@
         <v>3</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>846</v>
+        <v>870</v>
       </c>
       <c r="I23" s="70" t="s">
-        <v>849</v>
+        <v>873</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>894</v>
+        <v>918</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="59" t="s">
-        <v>618</v>
+        <v>642</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>614</v>
+        <v>638</v>
       </c>
       <c r="C24" s="59" t="s">
-        <v>856</v>
+        <v>880</v>
       </c>
       <c r="D24" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E24" s="59" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F24" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="G24" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H24" s="59" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="I24" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J24" s="59" t="s">
-        <v>895</v>
+        <v>919</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>807</v>
+        <v>831</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>802</v>
+        <v>826</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>856</v>
+        <v>880</v>
       </c>
       <c r="D25" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="G25" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>618</v>
+        <v>642</v>
       </c>
       <c r="I25" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J25" s="27" t="s">
-        <v>896</v>
+        <v>920</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="59" t="s">
-        <v>897</v>
+        <v>921</v>
       </c>
       <c r="B26" s="59" t="s">
-        <v>898</v>
+        <v>922</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>856</v>
+        <v>880</v>
       </c>
       <c r="D26" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E26" s="59" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F26" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="G26" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>618</v>
+        <v>642</v>
       </c>
       <c r="I26" s="70" t="s">
-        <v>849</v>
+        <v>873</v>
       </c>
       <c r="J26" s="59" t="s">
-        <v>899</v>
+        <v>923</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>761</v>
+        <v>785</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>756</v>
+        <v>780</v>
       </c>
       <c r="C27" s="27" t="s">
         <v>29</v>
@@ -17247,30 +17568,30 @@
         <v>100</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="G27" s="43" t="n">
         <v>10</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>864</v>
+        <v>888</v>
       </c>
       <c r="I27" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J27" s="27" t="s">
-        <v>900</v>
+        <v>924</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="59" t="s">
-        <v>770</v>
+        <v>794</v>
       </c>
       <c r="B28" s="59" t="s">
-        <v>901</v>
+        <v>925</v>
       </c>
       <c r="C28" s="59" t="s">
         <v>32</v>
@@ -17279,30 +17600,30 @@
         <v>100</v>
       </c>
       <c r="E28" s="59" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F28" s="59" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="G28" s="43" t="n">
         <v>6</v>
       </c>
       <c r="H28" s="59" t="s">
-        <v>864</v>
+        <v>888</v>
       </c>
       <c r="I28" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J28" s="59" t="s">
-        <v>902</v>
+        <v>926</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>752</v>
+        <v>776</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>903</v>
+        <v>927</v>
       </c>
       <c r="C29" s="27" t="s">
         <v>26</v>
@@ -17311,94 +17632,94 @@
         <v>100</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>893</v>
+        <v>917</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="G29" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>743</v>
+        <v>767</v>
       </c>
       <c r="I29" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>904</v>
+        <v>928</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="59" t="s">
-        <v>797</v>
+        <v>821</v>
       </c>
       <c r="B30" s="59" t="s">
-        <v>905</v>
+        <v>929</v>
       </c>
       <c r="C30" s="59" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="D30" s="59" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="59" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F30" s="59" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="G30" s="43" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="59" t="s">
-        <v>743</v>
+        <v>767</v>
       </c>
       <c r="I30" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J30" s="59" t="s">
-        <v>906</v>
+        <v>930</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="s">
-        <v>662</v>
+        <v>686</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>907</v>
+        <v>931</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="D31" s="27" t="s">
         <v>100</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="G31" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="I31" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="J31" s="27" t="s">
-        <v>908</v>
+        <v>932</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="59" t="s">
-        <v>909</v>
+        <v>933</v>
       </c>
       <c r="B32" s="59" t="s">
-        <v>910</v>
+        <v>934</v>
       </c>
       <c r="C32" s="59" t="s">
         <v>35</v>
@@ -17407,30 +17728,30 @@
         <v>100</v>
       </c>
       <c r="E32" s="59" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F32" s="59" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="G32" s="43" t="n">
         <v>8</v>
       </c>
       <c r="H32" s="59" t="s">
-        <v>779</v>
+        <v>803</v>
       </c>
       <c r="I32" s="70" t="s">
-        <v>853</v>
+        <v>877</v>
 